--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cleme\Documents\heig-vd\s5\ResoHT\mini_projet_trey\courbe de charge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B97DCCAA-BC6B-4B8F-9AEB-D6276BCE0DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AAB999-8504-40EE-A44D-6DA5518C15F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
@@ -634,76 +634,76 @@
         <v>0</v>
       </c>
       <c r="B3">
-        <v>8522.6381321998797</v>
+        <v>8.5226381321998801</v>
       </c>
       <c r="C3">
-        <v>2801.25568824537</v>
+        <v>2.8012556882453699</v>
       </c>
       <c r="D3">
-        <v>11912.360614826899</v>
+        <v>11.9123606148269</v>
       </c>
       <c r="E3">
-        <v>3915.4035892523102</v>
+        <v>3.91540358925231</v>
       </c>
       <c r="F3">
-        <v>1614.9349002036299</v>
+        <v>1.61493490020363</v>
       </c>
       <c r="G3">
-        <v>530.80343259554695</v>
+        <v>0.53080343259554696</v>
       </c>
       <c r="H3">
-        <v>5818.9374749499002</v>
+        <v>5.8189374749498999</v>
       </c>
       <c r="I3">
-        <v>1912.5922570456601</v>
+        <v>1.9125922570456599</v>
       </c>
       <c r="J3">
-        <v>2589.2767134268502</v>
+        <v>2.58927671342685</v>
       </c>
       <c r="K3">
-        <v>851.05409961317298</v>
+        <v>0.85105409961317302</v>
       </c>
       <c r="L3">
-        <v>9314.0961222444894</v>
+        <v>9.3140961222444894</v>
       </c>
       <c r="M3">
-        <v>3061.3953494898401</v>
+        <v>3.0613953494898398</v>
       </c>
       <c r="N3">
-        <v>13109.3989058116</v>
+        <v>13.1093989058116</v>
       </c>
       <c r="O3">
-        <v>4308.85104878946</v>
+        <v>4.3088510487894602</v>
       </c>
       <c r="P3">
-        <v>7708.6019372077399</v>
+        <v>7.7086019372077397</v>
       </c>
       <c r="Q3">
-        <v>2533.6949299111702</v>
+        <v>2.5336949299111802</v>
       </c>
       <c r="R3">
-        <v>658.78509677419299</v>
+        <v>0.65878509677419295</v>
       </c>
       <c r="S3">
-        <v>216.53219003839601</v>
+        <v>0.21653219003839599</v>
       </c>
       <c r="T3">
-        <v>5315.3501683366703</v>
+        <v>5.3153501683366704</v>
       </c>
       <c r="U3">
-        <v>1747.07111379205</v>
+        <v>1.74707111379205</v>
       </c>
       <c r="V3">
-        <v>1608.7132258064501</v>
+        <v>1.60871322580645</v>
       </c>
       <c r="W3">
-        <v>528.758467113596</v>
+        <v>0.52875846711359598</v>
       </c>
       <c r="X3">
-        <v>1834.74366935483</v>
+        <v>1.83474366935483</v>
       </c>
       <c r="Y3">
-        <v>603.05108119447902</v>
+        <v>0.60305108119447903</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
@@ -758,76 +758,76 @@
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="B4">
-        <v>7626.9076065679701</v>
+        <v>7.6269076065679702</v>
       </c>
       <c r="C4">
-        <v>2506.8433019466502</v>
+        <v>2.5068433019466601</v>
       </c>
       <c r="D4">
-        <v>10764.48751307</v>
+        <v>10.76448751307</v>
       </c>
       <c r="E4">
-        <v>3538.1159459424598</v>
+        <v>3.5381159459424598</v>
       </c>
       <c r="F4">
-        <v>1523.9610060443399</v>
+        <v>1.52396100604434</v>
       </c>
       <c r="G4">
-        <v>500.90175959916598</v>
+        <v>0.50090175959916605</v>
       </c>
       <c r="H4">
-        <v>5185.1250501001996</v>
+        <v>5.1851250501001998</v>
       </c>
       <c r="I4">
-        <v>1704.2681873326901</v>
+        <v>1.7042681873326899</v>
       </c>
       <c r="J4">
-        <v>2307.2465731462898</v>
+        <v>2.3072465731462901</v>
       </c>
       <c r="K4">
-        <v>758.35527532158699</v>
+        <v>0.75835527532158697</v>
       </c>
       <c r="L4">
-        <v>8299.5827555110209</v>
+        <v>8.29958275551102</v>
       </c>
       <c r="M4">
-        <v>2727.94093135306</v>
+        <v>2.7279409313530598</v>
       </c>
       <c r="N4">
-        <v>11681.4921883767</v>
+        <v>11.6814921883767</v>
       </c>
       <c r="O4">
-        <v>3839.5208070904901</v>
+        <v>3.8395208070904898</v>
       </c>
       <c r="P4">
-        <v>6868.96279225116</v>
+        <v>6.8689627922511596</v>
       </c>
       <c r="Q4">
-        <v>2257.7188888779801</v>
+        <v>2.2577188888779798</v>
       </c>
       <c r="R4">
-        <v>641.65896774193504</v>
+        <v>0.64165896774193498</v>
       </c>
       <c r="S4">
-        <v>210.90310364225101</v>
+        <v>0.21090310364225101</v>
       </c>
       <c r="T4">
-        <v>4736.3896633266504</v>
+        <v>4.7363896633266496</v>
       </c>
       <c r="U4">
-        <v>1556.7759982689299</v>
+        <v>1.55677599826893</v>
       </c>
       <c r="V4">
-        <v>1566.8922580645101</v>
+        <v>1.5668922580645099</v>
       </c>
       <c r="W4">
-        <v>515.01257975362296</v>
+        <v>0.51501257975362302</v>
       </c>
       <c r="X4">
-        <v>1787.0466935483801</v>
+        <v>1.78704669354838</v>
       </c>
       <c r="Y4">
-        <v>587.37384338179697</v>
+        <v>0.58737384338179699</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
@@ -882,76 +882,76 @@
         <v>2.0833333333333301E-2</v>
       </c>
       <c r="B5">
-        <v>6855.0040084685497</v>
+        <v>6.8550040084685397</v>
       </c>
       <c r="C5">
-        <v>2253.1308585209999</v>
+        <v>2.2531308585210001</v>
       </c>
       <c r="D5">
-        <v>9766.5013747645407</v>
+        <v>9.7665013747645393</v>
       </c>
       <c r="E5">
-        <v>3210.0937650926198</v>
+        <v>3.21009376509262</v>
       </c>
       <c r="F5">
-        <v>1445.43643003749</v>
+        <v>1.44543643003749</v>
       </c>
       <c r="G5">
-        <v>475.09197959980401</v>
+        <v>0.47509197959980398</v>
       </c>
       <c r="H5">
-        <v>4638.96753507014</v>
+        <v>4.6389675350701403</v>
       </c>
       <c r="I5">
-        <v>1524.7548932183199</v>
+        <v>1.5247548932183199</v>
       </c>
       <c r="J5">
-        <v>2064.2206012023998</v>
+        <v>2.0642206012024</v>
       </c>
       <c r="K5">
-        <v>678.47650119798698</v>
+        <v>0.67847650119798697</v>
       </c>
       <c r="L5">
-        <v>7425.37442885771</v>
+        <v>7.4253744288577099</v>
       </c>
       <c r="M5">
-        <v>2440.6025497671098</v>
+        <v>2.4406025497671</v>
       </c>
       <c r="N5">
-        <v>10451.0619318637</v>
+        <v>10.4510619318637</v>
       </c>
       <c r="O5">
-        <v>3435.0979392435102</v>
+        <v>3.4350979392435099</v>
       </c>
       <c r="P5">
-        <v>6145.4439545758096</v>
+        <v>6.1454439545758097</v>
       </c>
       <c r="Q5">
-        <v>2019.9097471365999</v>
+        <v>2.0199097471365999</v>
       </c>
       <c r="R5">
-        <v>626.81632258064496</v>
+        <v>0.62681632258064501</v>
       </c>
       <c r="S5">
-        <v>206.024562098925</v>
+        <v>0.206024562098925</v>
       </c>
       <c r="T5">
-        <v>4237.4981643286501</v>
+        <v>4.2374981643286498</v>
       </c>
       <c r="U5">
-        <v>1392.79829233944</v>
+        <v>1.39279829233944</v>
       </c>
       <c r="V5">
-        <v>1530.6474193548299</v>
+        <v>1.5306474193548301</v>
       </c>
       <c r="W5">
-        <v>503.09947737498101</v>
+        <v>0.50309947737498095</v>
       </c>
       <c r="X5">
-        <v>1745.70931451612</v>
+        <v>1.74570931451612</v>
       </c>
       <c r="Y5">
-        <v>573.78690394414002</v>
+        <v>0.57378690394414</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
@@ -1006,76 +1006,76 @@
         <v>3.125E-2</v>
       </c>
       <c r="B6">
-        <v>6243.9281667205296</v>
+        <v>6.2439281667205302</v>
       </c>
       <c r="C6">
-        <v>2052.2799422796302</v>
+        <v>2.0522799422796401</v>
       </c>
       <c r="D6">
-        <v>8967.0063806560502</v>
+        <v>8.9670063806560503</v>
       </c>
       <c r="E6">
-        <v>2947.31246835909</v>
+        <v>2.9473124683590899</v>
       </c>
       <c r="F6">
-        <v>1380.32448905876</v>
+        <v>1.38032448905876</v>
       </c>
       <c r="G6">
-        <v>453.69071954275</v>
+        <v>0.45369071954274998</v>
       </c>
       <c r="H6">
-        <v>4207.4356713426796</v>
+        <v>4.2074356713426804</v>
       </c>
       <c r="I6">
-        <v>1382.91722873289</v>
+        <v>1.3829172287328899</v>
       </c>
       <c r="J6">
-        <v>1872.2000801603201</v>
+        <v>1.87220008016032</v>
       </c>
       <c r="K6">
-        <v>615.36240806328999</v>
+        <v>0.61536240806329001</v>
       </c>
       <c r="L6">
-        <v>6734.6419238476901</v>
+        <v>6.7346419238476898</v>
       </c>
       <c r="M6">
-        <v>2213.56975443993</v>
+        <v>2.2135697544399302</v>
       </c>
       <c r="N6">
-        <v>9478.8701242484894</v>
+        <v>9.4788701242484894</v>
       </c>
       <c r="O6">
-        <v>3115.55394489527</v>
+        <v>3.1155539448952698</v>
       </c>
       <c r="P6">
-        <v>5573.7747494989899</v>
+        <v>5.5737747494989902</v>
       </c>
       <c r="Q6">
-        <v>1832.01116600762</v>
+        <v>1.8320111660076199</v>
       </c>
       <c r="R6">
-        <v>613.11541935483797</v>
+        <v>0.61311541935483804</v>
       </c>
       <c r="S6">
-        <v>201.52129298200799</v>
+        <v>0.20152129298200799</v>
       </c>
       <c r="T6">
-        <v>3843.31228857715</v>
+        <v>3.8433122885771498</v>
       </c>
       <c r="U6">
-        <v>1263.23566049391</v>
+        <v>1.2632356604939099</v>
       </c>
       <c r="V6">
-        <v>1497.1906451612899</v>
+        <v>1.49719064516129</v>
       </c>
       <c r="W6">
-        <v>492.10276748700301</v>
+        <v>0.49210276748700299</v>
       </c>
       <c r="X6">
-        <v>1707.5517338709601</v>
+        <v>1.70755173387096</v>
       </c>
       <c r="Y6">
-        <v>561.24511369399499</v>
+        <v>0.56124511369399499</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
@@ -1130,76 +1130,76 @@
         <v>4.1666666666666699E-2</v>
       </c>
       <c r="B7">
-        <v>5821.9413077768404</v>
+        <v>5.8219413077768403</v>
       </c>
       <c r="C7">
-        <v>1913.57956915049</v>
+        <v>1.91357956915049</v>
       </c>
       <c r="D7">
-        <v>8403.8967281452697</v>
+        <v>8.4038967281452699</v>
       </c>
       <c r="E7">
-        <v>2762.2272761059999</v>
+        <v>2.7622272761060001</v>
       </c>
       <c r="F7">
-        <v>1330.6788905229801</v>
+        <v>1.3306788905229801</v>
       </c>
       <c r="G7">
-        <v>437.373000411948</v>
+        <v>0.43737300041194799</v>
       </c>
       <c r="H7">
-        <v>3910.7575150300599</v>
+        <v>3.9107575150300602</v>
       </c>
       <c r="I7">
-        <v>1285.4038343991699</v>
+        <v>1.2854038343991701</v>
       </c>
       <c r="J7">
-        <v>1740.1859719438801</v>
+        <v>1.7401859719438799</v>
       </c>
       <c r="K7">
-        <v>571.97146903318696</v>
+        <v>0.57197146903318696</v>
       </c>
       <c r="L7">
-        <v>6259.7633266533003</v>
+        <v>6.2597633266533004</v>
       </c>
       <c r="M7">
-        <v>2057.4847076525002</v>
+        <v>2.0574847076524998</v>
       </c>
       <c r="N7">
-        <v>8810.4882565130192</v>
+        <v>8.81048825651302</v>
       </c>
       <c r="O7">
-        <v>2895.8674487808598</v>
+        <v>2.89586744878086</v>
       </c>
       <c r="P7">
-        <v>5180.7521710086803</v>
+        <v>5.1807521710086801</v>
       </c>
       <c r="Q7">
-        <v>1702.8308914814399</v>
+        <v>1.7028308914814401</v>
       </c>
       <c r="R7">
-        <v>600.55625806451599</v>
+        <v>0.60055625806451596</v>
       </c>
       <c r="S7">
-        <v>197.393296291501</v>
+        <v>0.19739329629150101</v>
       </c>
       <c r="T7">
-        <v>3572.30949899799</v>
+        <v>3.5723094989979902</v>
       </c>
       <c r="U7">
-        <v>1174.1613511001001</v>
+        <v>1.1741613511000999</v>
       </c>
       <c r="V7">
-        <v>1466.52193548387</v>
+        <v>1.4665219354838701</v>
       </c>
       <c r="W7">
-        <v>482.02245008968998</v>
+        <v>0.48202245008969002</v>
       </c>
       <c r="X7">
-        <v>1672.5739516128999</v>
+        <v>1.6725739516128999</v>
       </c>
       <c r="Y7">
-        <v>549.74847263136201</v>
+        <v>0.54974847263136195</v>
       </c>
       <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
@@ -1254,76 +1254,76 @@
         <v>5.2083333333333301E-2</v>
       </c>
       <c r="B8">
-        <v>5560.7822051845596</v>
+        <v>5.5607822051845597</v>
       </c>
       <c r="C8">
-        <v>1827.74072320563</v>
+        <v>1.82774072320563</v>
       </c>
       <c r="D8">
-        <v>8043.4114896636002</v>
+        <v>8.0434114896635993</v>
       </c>
       <c r="E8">
-        <v>2643.74150806546</v>
+        <v>2.6437415080654598</v>
       </c>
       <c r="F8">
-        <v>1294.44592701532</v>
+        <v>1.2944459270153199</v>
       </c>
       <c r="G8">
-        <v>425.46380122345403</v>
+        <v>0.42546380122345401</v>
       </c>
       <c r="H8">
-        <v>3728.7050100200399</v>
+        <v>3.7287050100200401</v>
       </c>
       <c r="I8">
-        <v>1225.5660696943801</v>
+        <v>1.22556606969438</v>
       </c>
       <c r="J8">
-        <v>1659.1773146292501</v>
+        <v>1.6591773146292501</v>
       </c>
       <c r="K8">
-        <v>545.34521099198696</v>
+        <v>0.54534521099198696</v>
       </c>
       <c r="L8">
-        <v>5968.3605511021997</v>
+        <v>5.9683605511022</v>
       </c>
       <c r="M8">
-        <v>1961.7052471238501</v>
+        <v>1.9617052471238501</v>
       </c>
       <c r="N8">
-        <v>8400.3448376753495</v>
+        <v>8.40034483767535</v>
       </c>
       <c r="O8">
-        <v>2761.0598261651999</v>
+        <v>2.7610598261652002</v>
       </c>
       <c r="P8">
-        <v>4939.5792251168996</v>
+        <v>4.9395792251169004</v>
       </c>
       <c r="Q8">
-        <v>1623.56117756765</v>
+        <v>1.6235611775676499</v>
       </c>
       <c r="R8">
-        <v>589.13883870967697</v>
+        <v>0.58913883870967698</v>
       </c>
       <c r="S8">
-        <v>193.640572027404</v>
+        <v>0.19364057202740401</v>
       </c>
       <c r="T8">
-        <v>3406.0123326653302</v>
+        <v>3.40601233266533</v>
       </c>
       <c r="U8">
-        <v>1119.50211579027</v>
+        <v>1.11950211579027</v>
       </c>
       <c r="V8">
-        <v>1438.6412903225801</v>
+        <v>1.43864129032258</v>
       </c>
       <c r="W8">
-        <v>472.85852518304199</v>
+        <v>0.472858525183042</v>
       </c>
       <c r="X8">
-        <v>1640.7759677419299</v>
+        <v>1.64077596774193</v>
       </c>
       <c r="Y8">
-        <v>539.29698075624106</v>
+        <v>0.539296980756241</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
@@ -1378,76 +1378,76 @@
         <v>6.25E-2</v>
       </c>
       <c r="B9">
-        <v>5395.1888036718601</v>
+        <v>5.3951888036718598</v>
       </c>
       <c r="C9">
-        <v>1773.3128042059</v>
+        <v>1.7733128042059001</v>
       </c>
       <c r="D9">
-        <v>7803.1855568968303</v>
+        <v>7.80318555689683</v>
       </c>
       <c r="E9">
-        <v>2564.78306231326</v>
+        <v>2.5647830623132601</v>
       </c>
       <c r="F9">
-        <v>1268.6085742452599</v>
+        <v>1.26860857424526</v>
       </c>
       <c r="G9">
-        <v>416.97147404803798</v>
+        <v>0.41697147404803803</v>
       </c>
       <c r="H9">
-        <v>3614.0793587174298</v>
+        <v>3.6140793587174298</v>
       </c>
       <c r="I9">
-        <v>1187.8904400654301</v>
+        <v>1.18789044006543</v>
       </c>
       <c r="J9">
-        <v>1608.17186372745</v>
+        <v>1.60817186372745</v>
       </c>
       <c r="K9">
-        <v>528.58053000308303</v>
+        <v>0.52858053000308303</v>
       </c>
       <c r="L9">
-        <v>5784.8847294589104</v>
+        <v>5.7848847294589101</v>
       </c>
       <c r="M9">
-        <v>1901.39966086507</v>
+        <v>1.9013996608650701</v>
       </c>
       <c r="N9">
-        <v>8142.1063887775499</v>
+        <v>8.1421063887775507</v>
       </c>
       <c r="O9">
-        <v>2676.1809526664501</v>
+        <v>2.6761809526664502</v>
       </c>
       <c r="P9">
-        <v>4787.7295925183698</v>
+        <v>4.78772959251837</v>
       </c>
       <c r="Q9">
-        <v>1573.6506169552599</v>
+        <v>1.57365061695526</v>
       </c>
       <c r="R9">
-        <v>580.00490322580595</v>
+        <v>0.580004903225806</v>
       </c>
       <c r="S9">
-        <v>190.63839261612699</v>
+        <v>0.190638392616127</v>
       </c>
       <c r="T9">
-        <v>3301.30670941883</v>
+        <v>3.3013067094188302</v>
       </c>
       <c r="U9">
-        <v>1085.0870417062999</v>
+        <v>1.0850870417063001</v>
       </c>
       <c r="V9">
-        <v>1416.3367741935399</v>
+        <v>1.41633677419354</v>
       </c>
       <c r="W9">
-        <v>465.52738525772401</v>
+        <v>0.46552738525772402</v>
       </c>
       <c r="X9">
-        <v>1615.33758064516</v>
+        <v>1.61533758064516</v>
       </c>
       <c r="Y9">
-        <v>530.93578725614395</v>
+        <v>0.53093578725614399</v>
       </c>
       <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
@@ -1502,76 +1502,76 @@
         <v>7.2916666666666699E-2</v>
       </c>
       <c r="B10">
-        <v>5278.0590591505497</v>
+        <v>5.2780590591505501</v>
       </c>
       <c r="C10">
-        <v>1734.8141189380899</v>
+        <v>1.7348141189380899</v>
       </c>
       <c r="D10">
-        <v>7630.8307661393901</v>
+        <v>7.6308307661393897</v>
       </c>
       <c r="E10">
-        <v>2508.13278213986</v>
+        <v>2.5081327821398598</v>
       </c>
       <c r="F10">
-        <v>1249.7439865214301</v>
+        <v>1.2497439865214299</v>
       </c>
       <c r="G10">
-        <v>410.77098391246102</v>
+        <v>0.41077098391246097</v>
       </c>
       <c r="H10">
-        <v>3533.1671342685299</v>
+        <v>3.5331671342685298</v>
       </c>
       <c r="I10">
-        <v>1161.2958779744199</v>
+        <v>1.16129587797442</v>
       </c>
       <c r="J10">
-        <v>1572.16801603206</v>
+        <v>1.5721680160320599</v>
       </c>
       <c r="K10">
-        <v>516.74663754032701</v>
+        <v>0.51674663754032701</v>
       </c>
       <c r="L10">
-        <v>5655.3723847695301</v>
+        <v>5.6553723847695396</v>
       </c>
       <c r="M10">
-        <v>1858.83101174122</v>
+        <v>1.8588310117412199</v>
       </c>
       <c r="N10">
-        <v>7959.8204248496904</v>
+        <v>7.9598204248497</v>
       </c>
       <c r="O10">
-        <v>2616.2664537261599</v>
+        <v>2.6162664537261602</v>
       </c>
       <c r="P10">
-        <v>4680.5416165664601</v>
+        <v>4.68054161656646</v>
       </c>
       <c r="Q10">
-        <v>1538.4196329935701</v>
+        <v>1.53841963299357</v>
       </c>
       <c r="R10">
-        <v>573.15445161290302</v>
+        <v>0.57315445161290302</v>
       </c>
       <c r="S10">
-        <v>188.386758057669</v>
+        <v>0.188386758057669</v>
       </c>
       <c r="T10">
-        <v>3227.3968577154301</v>
+        <v>3.2273968577154299</v>
       </c>
       <c r="U10">
-        <v>1060.7940482352701</v>
+        <v>1.06079404823527</v>
       </c>
       <c r="V10">
-        <v>1399.60838709677</v>
+        <v>1.3996083870967699</v>
       </c>
       <c r="W10">
-        <v>460.02903031373501</v>
+        <v>0.46002903031373499</v>
       </c>
       <c r="X10">
-        <v>1596.2587903225799</v>
+        <v>1.59625879032258</v>
       </c>
       <c r="Y10">
-        <v>524.66489213107195</v>
+        <v>0.52466489213107104</v>
       </c>
       <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
@@ -1626,76 +1626,76 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="B11">
-        <v>5173.75375570495</v>
+        <v>5.1737537557049498</v>
       </c>
       <c r="C11">
-        <v>1700.5306236096601</v>
+        <v>1.70053062360966</v>
       </c>
       <c r="D11">
-        <v>7479.8095715617501</v>
+        <v>7.4798095715617503</v>
       </c>
       <c r="E11">
-        <v>2458.49451593707</v>
+        <v>2.4584945159370699</v>
       </c>
       <c r="F11">
-        <v>1240.43876632296</v>
+        <v>1.2404387663229599</v>
       </c>
       <c r="G11">
-        <v>407.712505938037</v>
+        <v>0.40771250593803698</v>
       </c>
       <c r="H11">
-        <v>3458.9975951903798</v>
+        <v>3.4589975951903802</v>
       </c>
       <c r="I11">
-        <v>1136.91752939098</v>
+        <v>1.1369175293909799</v>
       </c>
       <c r="J11">
-        <v>1539.16448897795</v>
+        <v>1.5391644889779501</v>
       </c>
       <c r="K11">
-        <v>505.89890278280097</v>
+        <v>0.50589890278280103</v>
       </c>
       <c r="L11">
-        <v>5536.6527354709397</v>
+        <v>5.5366527354709403</v>
       </c>
       <c r="M11">
-        <v>1819.80975004437</v>
+        <v>1.81980975004437</v>
       </c>
       <c r="N11">
-        <v>7792.7249579158297</v>
+        <v>7.79272495791583</v>
       </c>
       <c r="O11">
-        <v>2561.3448296975498</v>
+        <v>2.5613448296975498</v>
       </c>
       <c r="P11">
-        <v>4582.2859719438802</v>
+        <v>4.5822859719438798</v>
       </c>
       <c r="Q11">
-        <v>1506.12456436203</v>
+        <v>1.50612456436203</v>
       </c>
       <c r="R11">
-        <v>572.01270967741902</v>
+        <v>0.57201270967741902</v>
       </c>
       <c r="S11">
-        <v>188.01148563125901</v>
+        <v>0.188011485631259</v>
       </c>
       <c r="T11">
-        <v>3159.6461603206399</v>
+        <v>3.1596461603206398</v>
       </c>
       <c r="U11">
-        <v>1038.5254708868199</v>
+        <v>1.0385254708868199</v>
       </c>
       <c r="V11">
-        <v>1396.8203225806401</v>
+        <v>1.3968203225806399</v>
       </c>
       <c r="W11">
-        <v>459.11263782306997</v>
+        <v>0.45911263782306999</v>
       </c>
       <c r="X11">
-        <v>1593.07899193548</v>
+        <v>1.59307899193548</v>
       </c>
       <c r="Y11">
-        <v>523.619742943559</v>
+        <v>0.52361974294355895</v>
       </c>
       <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
@@ -1750,76 +1750,76 @@
         <v>9.375E-2</v>
       </c>
       <c r="B12">
-        <v>5080.2304739802103</v>
+        <v>5.08023047398021</v>
       </c>
       <c r="C12">
-        <v>1669.7910074425799</v>
+        <v>1.6697910074425799</v>
       </c>
       <c r="D12">
-        <v>7350.4124114185897</v>
+        <v>7.3504124114185903</v>
       </c>
       <c r="E12">
-        <v>2415.9637261427301</v>
+        <v>2.41596372614273</v>
       </c>
       <c r="F12">
-        <v>1235.36803461762</v>
+        <v>1.2353680346176199</v>
       </c>
       <c r="G12">
-        <v>406.045837024864</v>
+        <v>0.40604583702486402</v>
       </c>
       <c r="H12">
-        <v>3391.5707414829599</v>
+        <v>3.3915707414829601</v>
       </c>
       <c r="I12">
-        <v>1114.7553943151399</v>
+        <v>1.11475539431514</v>
       </c>
       <c r="J12">
-        <v>1509.16128256513</v>
+        <v>1.5091612825651299</v>
       </c>
       <c r="K12">
-        <v>496.03732573050502</v>
+        <v>0.49603732573050502</v>
       </c>
       <c r="L12">
-        <v>5428.7257815631201</v>
+        <v>5.42872578156312</v>
       </c>
       <c r="M12">
-        <v>1784.3358757745</v>
+        <v>1.7843358757745</v>
       </c>
       <c r="N12">
-        <v>7640.8199879759504</v>
+        <v>7.6408199879759504</v>
       </c>
       <c r="O12">
-        <v>2511.41608058064</v>
+        <v>2.51141608058064</v>
       </c>
       <c r="P12">
-        <v>4492.9626586506301</v>
+        <v>4.4929626586506304</v>
       </c>
       <c r="Q12">
-        <v>1476.76541106062</v>
+        <v>1.4767654110606201</v>
       </c>
       <c r="R12">
-        <v>573.15445161290302</v>
+        <v>0.57315445161290302</v>
       </c>
       <c r="S12">
-        <v>188.386758057669</v>
+        <v>0.188386758057669</v>
       </c>
       <c r="T12">
-        <v>3098.0546172344598</v>
+        <v>3.0980546172344599</v>
       </c>
       <c r="U12">
-        <v>1018.28130966095</v>
+        <v>1.01828130966095</v>
       </c>
       <c r="V12">
-        <v>1399.60838709677</v>
+        <v>1.3996083870967699</v>
       </c>
       <c r="W12">
-        <v>460.02903031373501</v>
+        <v>0.46002903031373499</v>
       </c>
       <c r="X12">
-        <v>1596.2587903225799</v>
+        <v>1.59625879032258</v>
       </c>
       <c r="Y12">
-        <v>524.66489213107195</v>
+        <v>0.52466489213107104</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
@@ -1874,76 +1874,76 @@
         <v>0.104166666666667</v>
       </c>
       <c r="B13">
-        <v>4977.2867834378403</v>
+        <v>4.9772867834378403</v>
       </c>
       <c r="C13">
-        <v>1635.9550526328401</v>
+        <v>1.6359550526328399</v>
       </c>
       <c r="D13">
-        <v>7215.0194142720402</v>
+        <v>7.2150194142720396</v>
       </c>
       <c r="E13">
-        <v>2371.4622000281302</v>
+        <v>2.3714622000281298</v>
       </c>
       <c r="F13">
-        <v>1229.6127337739899</v>
+        <v>1.2296127337739899</v>
       </c>
       <c r="G13">
-        <v>404.15416111704201</v>
+        <v>0.404154161117042</v>
       </c>
       <c r="H13">
-        <v>3317.4012024048002</v>
+        <v>3.3174012024047999</v>
       </c>
       <c r="I13">
-        <v>1090.3770457317</v>
+        <v>1.0903770457316999</v>
       </c>
       <c r="J13">
-        <v>1476.15775551102</v>
+        <v>1.4761577555110199</v>
       </c>
       <c r="K13">
-        <v>485.18959097297898</v>
+        <v>0.48518959097297898</v>
       </c>
       <c r="L13">
-        <v>5310.0061322645197</v>
+        <v>5.3100061322645198</v>
       </c>
       <c r="M13">
-        <v>1745.31461407764</v>
+        <v>1.7453146140776401</v>
       </c>
       <c r="N13">
-        <v>7473.7245210420797</v>
+        <v>7.4737245210420804</v>
       </c>
       <c r="O13">
-        <v>2456.49445655204</v>
+        <v>2.4564944565520399</v>
       </c>
       <c r="P13">
-        <v>4394.7070140280503</v>
+        <v>4.3947070140280502</v>
       </c>
       <c r="Q13">
-        <v>1444.4703424290799</v>
+        <v>1.4444703424290799</v>
       </c>
       <c r="R13">
-        <v>574.29619354838701</v>
+        <v>0.57429619354838701</v>
       </c>
       <c r="S13">
-        <v>188.762030484078</v>
+        <v>0.188762030484078</v>
       </c>
       <c r="T13">
-        <v>3030.30391983967</v>
+        <v>3.0303039198396702</v>
       </c>
       <c r="U13">
-        <v>996.01273231250605</v>
+        <v>0.99601273231250598</v>
       </c>
       <c r="V13">
-        <v>1402.3964516128999</v>
+        <v>1.4023964516128999</v>
       </c>
       <c r="W13">
-        <v>460.94542280439902</v>
+        <v>0.46094542280439899</v>
       </c>
       <c r="X13">
-        <v>1599.4385887096701</v>
+        <v>1.59943858870967</v>
       </c>
       <c r="Y13">
-        <v>525.71004131858399</v>
+        <v>0.52571004131858401</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
@@ -1998,76 +1998,76 @@
         <v>0.114583333333333</v>
       </c>
       <c r="B14">
-        <v>4891.8222976275101</v>
+        <v>4.8918222976275096</v>
       </c>
       <c r="C14">
-        <v>1607.8642345896999</v>
+        <v>1.6078642345897001</v>
       </c>
       <c r="D14">
-        <v>7109.6033617341</v>
+        <v>7.1096033617341003</v>
       </c>
       <c r="E14">
-        <v>2336.8136191282101</v>
+        <v>2.3368136191282098</v>
       </c>
       <c r="F14">
-        <v>1221.6766518520899</v>
+        <v>1.2216766518520901</v>
       </c>
       <c r="G14">
-        <v>401.54569713191398</v>
+        <v>0.40154569713191401</v>
       </c>
       <c r="H14">
-        <v>3256.71703406813</v>
+        <v>3.2567170340681302</v>
       </c>
       <c r="I14">
-        <v>1070.43112416344</v>
+        <v>1.0704311241634401</v>
       </c>
       <c r="J14">
-        <v>1449.1548697394701</v>
+        <v>1.4491548697394701</v>
       </c>
       <c r="K14">
-        <v>476.31417162591202</v>
+        <v>0.476314171625912</v>
       </c>
       <c r="L14">
-        <v>5212.8718737474901</v>
+        <v>5.2128718737474902</v>
       </c>
       <c r="M14">
-        <v>1713.3881272347501</v>
+        <v>1.71338812723475</v>
       </c>
       <c r="N14">
-        <v>7337.0100480961901</v>
+        <v>7.3370100480961904</v>
       </c>
       <c r="O14">
-        <v>2411.55858234682</v>
+        <v>2.41155858234682</v>
       </c>
       <c r="P14">
-        <v>4314.31603206412</v>
+        <v>4.3143160320641201</v>
       </c>
       <c r="Q14">
-        <v>1418.0471044578201</v>
+        <v>1.41804710445782</v>
       </c>
       <c r="R14">
-        <v>573.15445161290302</v>
+        <v>0.57315445161290302</v>
       </c>
       <c r="S14">
-        <v>188.386758057669</v>
+        <v>0.188386758057669</v>
       </c>
       <c r="T14">
-        <v>2974.8715310621201</v>
+        <v>2.9748715310621199</v>
       </c>
       <c r="U14">
-        <v>977.79298720922804</v>
+        <v>0.97779298720922803</v>
       </c>
       <c r="V14">
-        <v>1399.60838709677</v>
+        <v>1.3996083870967699</v>
       </c>
       <c r="W14">
-        <v>460.02903031373501</v>
+        <v>0.46002903031373499</v>
       </c>
       <c r="X14">
-        <v>1596.2587903225799</v>
+        <v>1.59625879032258</v>
       </c>
       <c r="Y14">
-        <v>524.66489213107195</v>
+        <v>0.52466489213107104</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
@@ -2122,76 +2122,76 @@
         <v>0.125</v>
       </c>
       <c r="B15">
-        <v>4814.4166077315904</v>
+        <v>4.81441660773159</v>
       </c>
       <c r="C15">
-        <v>1582.4222146705099</v>
+        <v>1.58242221467051</v>
       </c>
       <c r="D15">
-        <v>7019.4662197551397</v>
+        <v>7.0194662197551398</v>
       </c>
       <c r="E15">
-        <v>2307.1869732734699</v>
+        <v>2.30718697327347</v>
       </c>
       <c r="F15">
-        <v>1210.87521971362</v>
+        <v>1.2108752197136201</v>
       </c>
       <c r="G15">
-        <v>397.99543807483002</v>
+        <v>0.39799543807483001</v>
       </c>
       <c r="H15">
-        <v>3202.7755511022001</v>
+        <v>3.2027755511021998</v>
       </c>
       <c r="I15">
-        <v>1052.70141610276</v>
+        <v>1.0527014161027599</v>
       </c>
       <c r="J15">
-        <v>1425.15230460921</v>
+        <v>1.4251523046092101</v>
       </c>
       <c r="K15">
-        <v>468.42490998407499</v>
+        <v>0.46842490998407499</v>
       </c>
       <c r="L15">
-        <v>5126.5303106212396</v>
+        <v>5.1265303106212397</v>
       </c>
       <c r="M15">
-        <v>1685.00902781886</v>
+        <v>1.6850090278188601</v>
       </c>
       <c r="N15">
-        <v>7215.4860721442801</v>
+        <v>7.2154860721442802</v>
       </c>
       <c r="O15">
-        <v>2371.6155830532898</v>
+        <v>2.3716155830532899</v>
       </c>
       <c r="P15">
-        <v>4242.8573814295196</v>
+        <v>4.2428573814295198</v>
       </c>
       <c r="Q15">
-        <v>1394.55978181669</v>
+        <v>1.3945597818166899</v>
       </c>
       <c r="R15">
-        <v>569.72922580645104</v>
+        <v>0.56972922580645102</v>
       </c>
       <c r="S15">
-        <v>187.26094077843999</v>
+        <v>0.18726094077843999</v>
       </c>
       <c r="T15">
-        <v>2925.5982965931798</v>
+        <v>2.9255982965931802</v>
       </c>
       <c r="U15">
-        <v>961.59765822853706</v>
+        <v>0.96159765822853704</v>
       </c>
       <c r="V15">
-        <v>1391.2441935483801</v>
+        <v>1.3912441935483799</v>
       </c>
       <c r="W15">
-        <v>457.27985284174002</v>
+        <v>0.45727985284174</v>
       </c>
       <c r="X15">
-        <v>1586.7193951612901</v>
+        <v>1.5867193951612899</v>
       </c>
       <c r="Y15">
-        <v>521.52944456853504</v>
+        <v>0.52152944456853501</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
@@ -2246,76 +2246,76 @@
         <v>0.13541666666666699</v>
       </c>
       <c r="B16">
-        <v>4753.1285096644897</v>
+        <v>4.7531285096644798</v>
       </c>
       <c r="C16">
-        <v>1562.2777909992101</v>
+        <v>1.56227779099921</v>
       </c>
       <c r="D16">
-        <v>6961.51787642818</v>
+        <v>6.9615178764281804</v>
       </c>
       <c r="E16">
-        <v>2288.1402739004502</v>
+        <v>2.2881402739004502</v>
       </c>
       <c r="F16">
-        <v>1194.3430871420201</v>
+        <v>1.19434308714202</v>
       </c>
       <c r="G16">
-        <v>392.56158887383702</v>
+        <v>0.39256158887383702</v>
       </c>
       <c r="H16">
-        <v>3162.3194388777501</v>
+        <v>3.1623194388777498</v>
       </c>
       <c r="I16">
-        <v>1039.40413505726</v>
+        <v>1.03940413505725</v>
       </c>
       <c r="J16">
-        <v>1407.15038076152</v>
+        <v>1.40715038076152</v>
       </c>
       <c r="K16">
-        <v>462.50796375269698</v>
+        <v>0.46250796375269698</v>
       </c>
       <c r="L16">
-        <v>5061.7741382765498</v>
+        <v>5.06177413827655</v>
       </c>
       <c r="M16">
-        <v>1663.7247032569301</v>
+        <v>1.66372470325693</v>
       </c>
       <c r="N16">
-        <v>7124.3430901803604</v>
+        <v>7.1243430901803597</v>
       </c>
       <c r="O16">
-        <v>2341.6583335831401</v>
+        <v>2.34165833358314</v>
       </c>
       <c r="P16">
-        <v>4189.2633934535697</v>
+        <v>4.1892633934535697</v>
       </c>
       <c r="Q16">
-        <v>1376.94428983585</v>
+        <v>1.3769442898358499</v>
       </c>
       <c r="R16">
-        <v>561.737032258064</v>
+        <v>0.56173703225806404</v>
       </c>
       <c r="S16">
-        <v>184.634033793572</v>
+        <v>0.18463403379357199</v>
       </c>
       <c r="T16">
-        <v>2888.6433707414799</v>
+        <v>2.8886433707414798</v>
       </c>
       <c r="U16">
-        <v>949.45116149301896</v>
+        <v>0.949451161493019</v>
       </c>
       <c r="V16">
-        <v>1371.72774193548</v>
+        <v>1.3717277419354801</v>
       </c>
       <c r="W16">
-        <v>450.86510540708701</v>
+        <v>0.45086510540708702</v>
       </c>
       <c r="X16">
-        <v>1564.4608064516101</v>
+        <v>1.5644608064516099</v>
       </c>
       <c r="Y16">
-        <v>514.213400255951</v>
+        <v>0.51421340025595097</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
@@ -2370,76 +2370,76 @@
         <v>0.14583333333333301</v>
       </c>
       <c r="B17">
-        <v>4710.6812292326604</v>
+        <v>4.7106812292326596</v>
       </c>
       <c r="C17">
-        <v>1548.3260446132001</v>
+        <v>1.5483260446131999</v>
       </c>
       <c r="D17">
-        <v>6942.1034556287204</v>
+        <v>6.94210345562872</v>
       </c>
       <c r="E17">
-        <v>2281.75906237242</v>
+        <v>2.2817590623724202</v>
       </c>
       <c r="F17">
-        <v>1179.18009284698</v>
+        <v>1.17918009284698</v>
       </c>
       <c r="G17">
-        <v>387.577753662139</v>
+        <v>0.38757775366213898</v>
       </c>
       <c r="H17">
-        <v>3135.3486973947802</v>
+        <v>3.1353486973947899</v>
       </c>
       <c r="I17">
-        <v>1030.53928102692</v>
+        <v>1.0305392810269201</v>
       </c>
       <c r="J17">
-        <v>1395.14909819639</v>
+        <v>1.3951490981963901</v>
       </c>
       <c r="K17">
-        <v>458.56333293177897</v>
+        <v>0.45856333293177898</v>
       </c>
       <c r="L17">
-        <v>5018.60335671342</v>
+        <v>5.0186033567134203</v>
       </c>
       <c r="M17">
-        <v>1649.5351535489899</v>
+        <v>1.6495351535489899</v>
       </c>
       <c r="N17">
-        <v>7063.5811022043999</v>
+        <v>7.0635811022043997</v>
       </c>
       <c r="O17">
-        <v>2321.68683393638</v>
+        <v>2.3216868339363801</v>
       </c>
       <c r="P17">
-        <v>4153.5340681362704</v>
+        <v>4.1535340681362696</v>
       </c>
       <c r="Q17">
-        <v>1365.20062851529</v>
+        <v>1.36520062851529</v>
       </c>
       <c r="R17">
-        <v>553.74483870967697</v>
+        <v>0.55374483870967695</v>
       </c>
       <c r="S17">
-        <v>182.00712680870399</v>
+        <v>0.18200712680870401</v>
       </c>
       <c r="T17">
-        <v>2864.0067535070102</v>
+        <v>2.86400675350701</v>
       </c>
       <c r="U17">
-        <v>941.35349700267295</v>
+        <v>0.94135349700267301</v>
       </c>
       <c r="V17">
-        <v>1352.21129032258</v>
+        <v>1.35221129032258</v>
       </c>
       <c r="W17">
-        <v>444.45035797243298</v>
+        <v>0.44445035797243299</v>
       </c>
       <c r="X17">
-        <v>1542.2022177419301</v>
+        <v>1.5422022177419299</v>
       </c>
       <c r="Y17">
-        <v>506.89735594336599</v>
+        <v>0.50689735594336605</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
@@ -2494,76 +2494,76 @@
         <v>0.15625</v>
       </c>
       <c r="B18">
-        <v>4716.0167993406103</v>
+        <v>4.7160167993406104</v>
       </c>
       <c r="C18">
-        <v>1550.07976169975</v>
+        <v>1.5500797616997499</v>
       </c>
       <c r="D18">
-        <v>6994.4030084160204</v>
+        <v>6.99440300841602</v>
       </c>
       <c r="E18">
-        <v>2298.9490940815599</v>
+        <v>2.2989490940815598</v>
       </c>
       <c r="F18">
-        <v>1169.21490392074</v>
+        <v>1.16921490392074</v>
       </c>
       <c r="G18">
-        <v>384.30235445698003</v>
+        <v>0.38430235445698002</v>
       </c>
       <c r="H18">
-        <v>3142.0913827655299</v>
+        <v>3.1420913827655301</v>
       </c>
       <c r="I18">
-        <v>1032.7554945345</v>
+        <v>1.0327554945345001</v>
       </c>
       <c r="J18">
-        <v>1398.1494188376701</v>
+        <v>1.39814941883767</v>
       </c>
       <c r="K18">
-        <v>459.54949063700798</v>
+        <v>0.45954949063700801</v>
       </c>
       <c r="L18">
-        <v>5029.3960521042</v>
+        <v>5.0293960521042003</v>
       </c>
       <c r="M18">
-        <v>1653.08254097597</v>
+        <v>1.65308254097597</v>
       </c>
       <c r="N18">
-        <v>7078.7715991983896</v>
+        <v>7.0787715991983902</v>
       </c>
       <c r="O18">
-        <v>2326.6797088480698</v>
+        <v>2.32667970884807</v>
       </c>
       <c r="P18">
-        <v>4162.4663994655903</v>
+        <v>4.1624663994655897</v>
       </c>
       <c r="Q18">
-        <v>1368.13654384543</v>
+        <v>1.36813654384543</v>
       </c>
       <c r="R18">
-        <v>546.89438709677404</v>
+        <v>0.54689438709677396</v>
       </c>
       <c r="S18">
-        <v>179.75549225024599</v>
+        <v>0.17975549225024601</v>
       </c>
       <c r="T18">
-        <v>2870.1659078156299</v>
+        <v>2.8701659078156299</v>
       </c>
       <c r="U18">
-        <v>943.37791312525997</v>
+        <v>0.94337791312525998</v>
       </c>
       <c r="V18">
-        <v>1335.4829032258001</v>
+        <v>1.3354829032258</v>
       </c>
       <c r="W18">
-        <v>438.95200302844398</v>
+        <v>0.438952003028444</v>
       </c>
       <c r="X18">
-        <v>1523.12342741935</v>
+        <v>1.5231234274193499</v>
       </c>
       <c r="Y18">
-        <v>500.62646081829303</v>
+        <v>0.50062646081829298</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
@@ -2618,76 +2618,76 @@
         <v>0.16666666666666699</v>
       </c>
       <c r="B19">
-        <v>4759.7148111707202</v>
+        <v>4.7597148111707197</v>
       </c>
       <c r="C19">
-        <v>1564.4426036162299</v>
+        <v>1.56444260361623</v>
       </c>
       <c r="D19">
-        <v>7110.0636246159502</v>
+        <v>7.1100636246159503</v>
       </c>
       <c r="E19">
-        <v>2336.9649002216702</v>
+        <v>2.3369649002216701</v>
       </c>
       <c r="F19">
-        <v>1163.7629512250301</v>
+        <v>1.16376295122503</v>
       </c>
       <c r="G19">
-        <v>382.51038426371201</v>
+        <v>0.38251038426371198</v>
       </c>
       <c r="H19">
-        <v>3175.8048096192301</v>
+        <v>3.1758048096192302</v>
       </c>
       <c r="I19">
-        <v>1043.8365620724201</v>
+        <v>1.0438365620724199</v>
       </c>
       <c r="J19">
-        <v>1413.15102204408</v>
+        <v>1.4131510220440799</v>
       </c>
       <c r="K19">
-        <v>464.48027916315698</v>
+        <v>0.46448027916315698</v>
       </c>
       <c r="L19">
-        <v>5083.3595290581097</v>
+        <v>5.0833595290581099</v>
       </c>
       <c r="M19">
-        <v>1670.81947811091</v>
+        <v>1.67081947811091</v>
       </c>
       <c r="N19">
-        <v>7154.7240841683297</v>
+        <v>7.1547240841683299</v>
       </c>
       <c r="O19">
-        <v>2351.6440834065302</v>
+        <v>2.35164408340653</v>
       </c>
       <c r="P19">
-        <v>4207.1280561122203</v>
+        <v>4.2071280561122197</v>
       </c>
       <c r="Q19">
-        <v>1382.81612049613</v>
+        <v>1.38281612049613</v>
       </c>
       <c r="R19">
-        <v>541.18567741935396</v>
+        <v>0.54118567741935397</v>
       </c>
       <c r="S19">
-        <v>177.879130118197</v>
+        <v>0.177879130118197</v>
       </c>
       <c r="T19">
-        <v>2900.9616793587102</v>
+        <v>2.9009616793587099</v>
       </c>
       <c r="U19">
-        <v>953.49999373819196</v>
+        <v>0.95349999373819205</v>
       </c>
       <c r="V19">
-        <v>1321.5425806451599</v>
+        <v>1.3215425806451599</v>
       </c>
       <c r="W19">
-        <v>434.37004057512002</v>
+        <v>0.43437004057512002</v>
       </c>
       <c r="X19">
-        <v>1507.2244354838699</v>
+        <v>1.50722443548387</v>
       </c>
       <c r="Y19">
-        <v>495.40071488073301</v>
+        <v>0.49540071488073301</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
@@ -2742,76 +2742,76 @@
         <v>0.17708333333333301</v>
       </c>
       <c r="B20">
-        <v>4843.1368776262198</v>
+        <v>4.84313687762622</v>
       </c>
       <c r="C20">
-        <v>1591.8621108813199</v>
+        <v>1.59186211088132</v>
       </c>
       <c r="D20">
-        <v>7278.3164722662204</v>
+        <v>7.2783164722662201</v>
       </c>
       <c r="E20">
-        <v>2392.2669368953998</v>
+        <v>2.3922669368954002</v>
       </c>
       <c r="F20">
-        <v>1166.3741541146801</v>
+        <v>1.1663741541146799</v>
       </c>
       <c r="G20">
-        <v>383.36864514893699</v>
+        <v>0.38336864514893698</v>
       </c>
       <c r="H20">
-        <v>3236.4889779559098</v>
+        <v>3.2364889779559101</v>
       </c>
       <c r="I20">
-        <v>1063.7824836406901</v>
+        <v>1.0637824836406899</v>
       </c>
       <c r="J20">
-        <v>1440.15390781563</v>
+        <v>1.44015390781563</v>
       </c>
       <c r="K20">
-        <v>473.35569851022302</v>
+        <v>0.47335569851022302</v>
       </c>
       <c r="L20">
-        <v>5180.4937875751502</v>
+        <v>5.1804937875751502</v>
       </c>
       <c r="M20">
-        <v>1702.74596495379</v>
+        <v>1.7027459649537899</v>
       </c>
       <c r="N20">
-        <v>7291.4385571142202</v>
+        <v>7.2914385571142297</v>
       </c>
       <c r="O20">
-        <v>2396.5799576117502</v>
+        <v>2.3965799576117499</v>
       </c>
       <c r="P20">
-        <v>4287.5190380761496</v>
+        <v>4.2875190380761499</v>
       </c>
       <c r="Q20">
-        <v>1409.2393584674001</v>
+        <v>1.4092393584673999</v>
       </c>
       <c r="R20">
-        <v>538.902193548387</v>
+        <v>0.53890219354838698</v>
       </c>
       <c r="S20">
-        <v>177.12858526537801</v>
+        <v>0.177128585265378</v>
       </c>
       <c r="T20">
-        <v>2956.3940681362701</v>
+        <v>2.9563940681362699</v>
       </c>
       <c r="U20">
-        <v>971.71973884146905</v>
+        <v>0.97171973884146901</v>
       </c>
       <c r="V20">
-        <v>1315.9664516129001</v>
+        <v>1.3159664516128999</v>
       </c>
       <c r="W20">
-        <v>432.53725559379001</v>
+        <v>0.43253725559379003</v>
       </c>
       <c r="X20">
-        <v>1500.86483870967</v>
+        <v>1.5008648387096699</v>
       </c>
       <c r="Y20">
-        <v>493.31041650570899</v>
+        <v>0.493310416505709</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
@@ -2866,76 +2866,76 @@
         <v>0.1875</v>
       </c>
       <c r="B21">
-        <v>4966.9638051586999</v>
+        <v>4.9669638051587004</v>
       </c>
       <c r="C21">
-        <v>1632.56205375439</v>
+        <v>1.6325620537543899</v>
       </c>
       <c r="D21">
-        <v>7492.9616466186799</v>
+        <v>7.4929616466186797</v>
       </c>
       <c r="E21">
-        <v>2462.8173939583999</v>
+        <v>2.4628173939583999</v>
       </c>
       <c r="F21">
-        <v>1178.82347226711</v>
+        <v>1.17882347226711</v>
       </c>
       <c r="G21">
-        <v>387.460538145957</v>
+        <v>0.38746053814595699</v>
       </c>
       <c r="H21">
-        <v>3324.14388777555</v>
+        <v>3.3241438877755498</v>
       </c>
       <c r="I21">
-        <v>1092.5932592392901</v>
+        <v>1.09259325923929</v>
       </c>
       <c r="J21">
-        <v>1479.1580761523001</v>
+        <v>1.4791580761523</v>
       </c>
       <c r="K21">
-        <v>486.17574867820798</v>
+        <v>0.48617574867820801</v>
       </c>
       <c r="L21">
-        <v>5320.7988276553097</v>
+        <v>5.3207988276553104</v>
       </c>
       <c r="M21">
-        <v>1748.8620015046299</v>
+        <v>1.7488620015046299</v>
       </c>
       <c r="N21">
-        <v>7488.9150180360703</v>
+        <v>7.48891501803607</v>
       </c>
       <c r="O21">
-        <v>2461.4873314637298</v>
+        <v>2.4614873314637302</v>
       </c>
       <c r="P21">
-        <v>4403.6393453573801</v>
+        <v>4.4036393453573801</v>
       </c>
       <c r="Q21">
-        <v>1447.4062577592199</v>
+        <v>1.4474062577592199</v>
       </c>
       <c r="R21">
-        <v>541.18567741935396</v>
+        <v>0.54118567741935397</v>
       </c>
       <c r="S21">
-        <v>177.879130118197</v>
+        <v>0.177879130118197</v>
       </c>
       <c r="T21">
-        <v>3036.4630741482902</v>
+        <v>3.0364630741482901</v>
       </c>
       <c r="U21">
-        <v>998.03714843509204</v>
+        <v>0.99803714843509295</v>
       </c>
       <c r="V21">
-        <v>1321.5425806451599</v>
+        <v>1.3215425806451599</v>
       </c>
       <c r="W21">
-        <v>434.37004057512002</v>
+        <v>0.43437004057512002</v>
       </c>
       <c r="X21">
-        <v>1507.2244354838699</v>
+        <v>1.50722443548387</v>
       </c>
       <c r="Y21">
-        <v>495.40071488073301</v>
+        <v>0.49540071488073301</v>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
@@ -2990,76 +2990,76 @@
         <v>0.19791666666666699</v>
       </c>
       <c r="B22">
-        <v>5111.6739696812901</v>
+        <v>5.1116739696812896</v>
       </c>
       <c r="C22">
-        <v>1680.1259846907799</v>
+        <v>1.6801259846907799</v>
       </c>
       <c r="D22">
-        <v>7715.7556634004904</v>
+        <v>7.7157556634004996</v>
       </c>
       <c r="E22">
-        <v>2536.0462460035301</v>
+        <v>2.5360462460035298</v>
       </c>
       <c r="F22">
-        <v>1197.96680772835</v>
+        <v>1.1979668077283501</v>
       </c>
       <c r="G22">
-        <v>393.75264823217498</v>
+        <v>0.39375264823217498</v>
       </c>
       <c r="H22">
-        <v>3425.2841683366701</v>
+        <v>3.4252841683366699</v>
       </c>
       <c r="I22">
-        <v>1125.83646185306</v>
+        <v>1.1258364618530601</v>
       </c>
       <c r="J22">
-        <v>1524.16288577154</v>
+        <v>1.5241628857715399</v>
       </c>
       <c r="K22">
-        <v>500.968114256653</v>
+        <v>0.500968114256653</v>
       </c>
       <c r="L22">
-        <v>5482.6892585170299</v>
+        <v>5.4826892585170297</v>
       </c>
       <c r="M22">
-        <v>1802.07281290943</v>
+        <v>1.8020728129094301</v>
       </c>
       <c r="N22">
-        <v>7716.7724729458896</v>
+        <v>7.7167724729458902</v>
       </c>
       <c r="O22">
-        <v>2536.3804551390999</v>
+        <v>2.5363804551391</v>
       </c>
       <c r="P22">
-        <v>4537.6243152972602</v>
+        <v>4.5376243152972604</v>
       </c>
       <c r="Q22">
-        <v>1491.44498771133</v>
+        <v>1.4914449877113301</v>
       </c>
       <c r="R22">
-        <v>546.89438709677404</v>
+        <v>0.54689438709677396</v>
       </c>
       <c r="S22">
-        <v>179.75549225024599</v>
+        <v>0.17975549225024601</v>
       </c>
       <c r="T22">
-        <v>3128.8503887775501</v>
+        <v>3.1288503887775501</v>
       </c>
       <c r="U22">
-        <v>1028.4033902738799</v>
+        <v>1.0284033902738801</v>
       </c>
       <c r="V22">
-        <v>1335.4829032258001</v>
+        <v>1.3354829032258</v>
       </c>
       <c r="W22">
-        <v>438.95200302844398</v>
+        <v>0.438952003028444</v>
       </c>
       <c r="X22">
-        <v>1523.12342741935</v>
+        <v>1.5231234274193499</v>
       </c>
       <c r="Y22">
-        <v>500.62646081829303</v>
+        <v>0.50062646081829298</v>
       </c>
       <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
@@ -3114,76 +3114,76 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="B23">
-        <v>5297.4698017324899</v>
+        <v>5.2974698017324897</v>
       </c>
       <c r="C23">
-        <v>1741.19412149449</v>
+        <v>1.7411941214944899</v>
       </c>
       <c r="D23">
-        <v>7956.6235617024204</v>
+        <v>7.9566235617024201</v>
       </c>
       <c r="E23">
-        <v>2615.2156956232102</v>
+        <v>2.6152156956232102</v>
       </c>
       <c r="F23">
-        <v>1228.7232181298</v>
+        <v>1.2287232181298</v>
       </c>
       <c r="G23">
-        <v>403.86179146348798</v>
+        <v>0.403861791463488</v>
       </c>
       <c r="H23">
-        <v>3553.3951903807601</v>
+        <v>3.5533951903807601</v>
       </c>
       <c r="I23">
-        <v>1167.9445184971701</v>
+        <v>1.16794451849717</v>
       </c>
       <c r="J23">
-        <v>1581.1689779559099</v>
+        <v>1.5811689779559099</v>
       </c>
       <c r="K23">
-        <v>519.70511065601602</v>
+        <v>0.51970511065601599</v>
       </c>
       <c r="L23">
-        <v>5687.7504709418799</v>
+        <v>5.6877504709418796</v>
       </c>
       <c r="M23">
-        <v>1869.4731740221901</v>
+        <v>1.8694731740221899</v>
       </c>
       <c r="N23">
-        <v>8005.3919158316603</v>
+        <v>8.0053919158316607</v>
       </c>
       <c r="O23">
-        <v>2631.2450784612302</v>
+        <v>2.6312450784612298</v>
       </c>
       <c r="P23">
-        <v>4707.3386105544396</v>
+        <v>4.7073386105544399</v>
       </c>
       <c r="Q23">
-        <v>1547.2273789839901</v>
+        <v>1.5472273789839901</v>
       </c>
       <c r="R23">
-        <v>558.31180645161305</v>
+        <v>0.55831180645161305</v>
       </c>
       <c r="S23">
-        <v>183.50821651434299</v>
+        <v>0.18350821651434299</v>
       </c>
       <c r="T23">
-        <v>3245.8743206412801</v>
+        <v>3.2458743206412799</v>
       </c>
       <c r="U23">
-        <v>1066.8672966030299</v>
+        <v>1.0668672966030299</v>
       </c>
       <c r="V23">
-        <v>1363.3635483870901</v>
+        <v>1.3633635483870901</v>
       </c>
       <c r="W23">
-        <v>448.11592793509197</v>
+        <v>0.44811592793509197</v>
       </c>
       <c r="X23">
-        <v>1554.9214112903201</v>
+        <v>1.55492141129032</v>
       </c>
       <c r="Y23">
-        <v>511.07795269341398</v>
+        <v>0.51107795269341405</v>
       </c>
       <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
@@ -3238,76 +3238,76 @@
         <v>0.21875</v>
       </c>
       <c r="B24">
-        <v>5582.9161735729504</v>
+        <v>5.5829161735729498</v>
       </c>
       <c r="C24">
-        <v>1835.01580679942</v>
+        <v>1.83501580679942</v>
       </c>
       <c r="D24">
-        <v>8286.7848091117503</v>
+        <v>8.2867848091117509</v>
       </c>
       <c r="E24">
-        <v>2723.7344497926902</v>
+        <v>2.7237344497926901</v>
       </c>
       <c r="F24">
-        <v>1280.52499733337</v>
+        <v>1.2805249973333701</v>
       </c>
       <c r="G24">
-        <v>420.88821290768601</v>
+        <v>0.42088821290768602</v>
       </c>
       <c r="H24">
-        <v>3748.9330661322601</v>
+        <v>3.7489330661322602</v>
       </c>
       <c r="I24">
-        <v>1232.21471021713</v>
+        <v>1.2322147102171299</v>
       </c>
       <c r="J24">
-        <v>1668.1782765531</v>
+        <v>1.6681782765530999</v>
       </c>
       <c r="K24">
-        <v>548.30368410767505</v>
+        <v>0.54830368410767505</v>
       </c>
       <c r="L24">
-        <v>6000.7386372745495</v>
+        <v>6.0007386372745497</v>
       </c>
       <c r="M24">
-        <v>1972.3474094048099</v>
+        <v>1.9723474094048099</v>
       </c>
       <c r="N24">
-        <v>8445.9163286573094</v>
+        <v>8.4459163286573098</v>
       </c>
       <c r="O24">
-        <v>2776.0384509002702</v>
+        <v>2.7760384509002698</v>
       </c>
       <c r="P24">
-        <v>4966.37621910487</v>
+        <v>4.9663762191048697</v>
       </c>
       <c r="Q24">
-        <v>1632.36892355807</v>
+        <v>1.6323689235580701</v>
       </c>
       <c r="R24">
-        <v>578.86316129032195</v>
+        <v>0.578863161290322</v>
       </c>
       <c r="S24">
-        <v>190.263120189717</v>
+        <v>0.190263120189717</v>
       </c>
       <c r="T24">
-        <v>3424.4897955911802</v>
+        <v>3.4244897955911799</v>
       </c>
       <c r="U24">
-        <v>1125.57536415803</v>
+        <v>1.1255753641580299</v>
       </c>
       <c r="V24">
-        <v>1413.54870967741</v>
+        <v>1.41354870967741</v>
       </c>
       <c r="W24">
-        <v>464.61099276705897</v>
+        <v>0.46461099276705897</v>
       </c>
       <c r="X24">
-        <v>1612.15778225806</v>
+        <v>1.6121577822580599</v>
       </c>
       <c r="Y24">
-        <v>529.89063806863203</v>
+        <v>0.52989063806863201</v>
       </c>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -3362,76 +3362,76 @@
         <v>0.22916666666666699</v>
       </c>
       <c r="B25">
-        <v>6062.89797983062</v>
+        <v>6.0628979798306197</v>
       </c>
       <c r="C25">
-        <v>1992.7781972913599</v>
+        <v>1.9927781972913601</v>
       </c>
       <c r="D25">
-        <v>8812.0658340643295</v>
+        <v>8.8120658340643292</v>
       </c>
       <c r="E25">
-        <v>2896.38597344666</v>
+        <v>2.8963859734466602</v>
       </c>
       <c r="F25">
-        <v>1361.99279639925</v>
+        <v>1.36199279639925</v>
       </c>
       <c r="G25">
-        <v>447.66538354454502</v>
+        <v>0.44766538354454499</v>
       </c>
       <c r="H25">
-        <v>4079.32464929859</v>
+        <v>4.0793246492985897</v>
       </c>
       <c r="I25">
-        <v>1340.8091720887801</v>
+        <v>1.34080917208878</v>
       </c>
       <c r="J25">
-        <v>1815.19398797595</v>
+        <v>1.81519398797595</v>
       </c>
       <c r="K25">
-        <v>596.62541166392703</v>
+        <v>0.59662541166392702</v>
       </c>
       <c r="L25">
-        <v>6529.5807114228401</v>
+        <v>6.5295807114228399</v>
       </c>
       <c r="M25">
-        <v>2146.1693933271799</v>
+        <v>2.1461693933271802</v>
       </c>
       <c r="N25">
-        <v>9190.2506813627206</v>
+        <v>9.1902506813627198</v>
       </c>
       <c r="O25">
-        <v>3020.6893215731402</v>
+        <v>3.0206893215731401</v>
       </c>
       <c r="P25">
-        <v>5404.0604542418096</v>
+        <v>5.4040604542418098</v>
       </c>
       <c r="Q25">
-        <v>1776.2287747349501</v>
+        <v>1.7762287747349501</v>
       </c>
       <c r="R25">
-        <v>609.69019354838701</v>
+        <v>0.60969019354838705</v>
       </c>
       <c r="S25">
-        <v>200.39547570277901</v>
+        <v>0.20039547570277899</v>
       </c>
       <c r="T25">
-        <v>3726.2883567134199</v>
+        <v>3.72628835671342</v>
       </c>
       <c r="U25">
-        <v>1224.7717541647601</v>
+        <v>1.22477175416476</v>
       </c>
       <c r="V25">
-        <v>1488.8264516129</v>
+        <v>1.4888264516128999</v>
       </c>
       <c r="W25">
-        <v>489.35359001500899</v>
+        <v>0.489353590015009</v>
       </c>
       <c r="X25">
-        <v>1698.0123387096701</v>
+        <v>1.6980123387096699</v>
       </c>
       <c r="Y25">
-        <v>558.10966613145899</v>
+        <v>0.55810966613145896</v>
       </c>
       <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
@@ -3486,76 +3486,76 @@
         <v>0.23958333333333301</v>
       </c>
       <c r="B26">
-        <v>6814.1401039498296</v>
+        <v>6.8141401039498302</v>
       </c>
       <c r="C26">
-        <v>2239.6995426301501</v>
+        <v>2.23969954263015</v>
       </c>
       <c r="D26">
-        <v>9628.8036832872895</v>
+        <v>9.6288036832872894</v>
       </c>
       <c r="E26">
-        <v>3164.8347225842199</v>
+        <v>3.1648347225842199</v>
       </c>
       <c r="F26">
-        <v>1482.15308778848</v>
+        <v>1.4821530877884801</v>
       </c>
       <c r="G26">
-        <v>487.160161397845</v>
+        <v>0.48716016139784502</v>
       </c>
       <c r="H26">
-        <v>4598.5114228456896</v>
+        <v>4.5985114228456903</v>
       </c>
       <c r="I26">
-        <v>1511.4576121728101</v>
+        <v>1.51145761217281</v>
       </c>
       <c r="J26">
-        <v>2046.2186773547</v>
+        <v>2.0462186773547</v>
       </c>
       <c r="K26">
-        <v>672.55955496660897</v>
+        <v>0.67255955496660902</v>
       </c>
       <c r="L26">
-        <v>7360.6182565130202</v>
+        <v>7.3606182565130203</v>
       </c>
       <c r="M26">
-        <v>2419.3182252051802</v>
+        <v>2.4193182252051799</v>
       </c>
       <c r="N26">
-        <v>10359.9189498998</v>
+        <v>10.3599189498998</v>
       </c>
       <c r="O26">
-        <v>3405.14068977336</v>
+        <v>3.40514068977336</v>
       </c>
       <c r="P26">
-        <v>6091.8499665998597</v>
+        <v>6.0918499665998596</v>
       </c>
       <c r="Q26">
-        <v>2002.2942551557601</v>
+        <v>2.0022942551557601</v>
       </c>
       <c r="R26">
-        <v>653.07638709677406</v>
+        <v>0.65307638709677396</v>
       </c>
       <c r="S26">
-        <v>214.65582790634801</v>
+        <v>0.21465582790634799</v>
       </c>
       <c r="T26">
-        <v>4200.5432384769501</v>
+        <v>4.2005432384769499</v>
       </c>
       <c r="U26">
-        <v>1380.6517956039199</v>
+        <v>1.3806517956039199</v>
       </c>
       <c r="V26">
-        <v>1594.7729032258001</v>
+        <v>1.5947729032258</v>
       </c>
       <c r="W26">
-        <v>524.17650466027101</v>
+        <v>0.52417650466027099</v>
       </c>
       <c r="X26">
-        <v>1818.8446774193501</v>
+        <v>1.8188446774193501</v>
       </c>
       <c r="Y26">
-        <v>597.82533525691804</v>
+        <v>0.59782533525691794</v>
       </c>
       <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
@@ -3610,76 +3610,76 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>7888.5102351800297</v>
+        <v>7.8885102351800303</v>
       </c>
       <c r="C27">
-        <v>2592.8279278444502</v>
+        <v>2.5928279278444499</v>
       </c>
       <c r="D27">
-        <v>10795.441206107</v>
+        <v>10.795441206107</v>
       </c>
       <c r="E27">
-        <v>3548.28993284031</v>
+        <v>3.5482899328403099</v>
       </c>
       <c r="F27">
-        <v>1656.8534349343799</v>
+        <v>1.65685343493438</v>
       </c>
       <c r="G27">
-        <v>544.58138867393302</v>
+        <v>0.54458138867393402</v>
       </c>
       <c r="H27">
-        <v>5340.2068136272501</v>
+        <v>5.3402068136272502</v>
       </c>
       <c r="I27">
-        <v>1755.24109800714</v>
+        <v>1.75524109800714</v>
       </c>
       <c r="J27">
-        <v>2376.2539478957901</v>
+        <v>2.37625394789579</v>
       </c>
       <c r="K27">
-        <v>781.03690254186904</v>
+        <v>0.78103690254186897</v>
       </c>
       <c r="L27">
-        <v>8547.8147494989898</v>
+        <v>8.5478147494989898</v>
       </c>
       <c r="M27">
-        <v>2809.53084217376</v>
+        <v>2.8095308421737601</v>
       </c>
       <c r="N27">
-        <v>12030.8736192384</v>
+        <v>12.030873619238401</v>
       </c>
       <c r="O27">
-        <v>3954.3569300593799</v>
+        <v>3.9543569300593799</v>
       </c>
       <c r="P27">
-        <v>7074.4064128256496</v>
+        <v>7.0744064128256499</v>
       </c>
       <c r="Q27">
-        <v>2325.24494147121</v>
+        <v>2.32524494147121</v>
       </c>
       <c r="R27">
-        <v>717.01393548387102</v>
+        <v>0.71701393548387105</v>
       </c>
       <c r="S27">
-        <v>235.67108378529099</v>
+        <v>0.235671083785291</v>
       </c>
       <c r="T27">
-        <v>4878.0502124248496</v>
+        <v>4.8780502124248502</v>
       </c>
       <c r="U27">
-        <v>1603.33756908842</v>
+        <v>1.60333756908842</v>
       </c>
       <c r="V27">
-        <v>1750.9045161290301</v>
+        <v>1.75090451612903</v>
       </c>
       <c r="W27">
-        <v>575.49448413750099</v>
+        <v>0.57549448413750104</v>
       </c>
       <c r="X27">
-        <v>1996.9133870967701</v>
+        <v>1.9969133870967699</v>
       </c>
       <c r="Y27">
-        <v>656.35368975759502</v>
+        <v>0.656353689757595</v>
       </c>
       <c r="Z27" s="4"/>
       <c r="AA27" s="4"/>
@@ -3734,76 +3734,76 @@
         <v>0.26041666666666702</v>
       </c>
       <c r="B28">
-        <v>9151.5103057728302</v>
+        <v>9.1515103057728293</v>
       </c>
       <c r="C28">
-        <v>3007.95597588808</v>
+        <v>3.0079559758880801</v>
       </c>
       <c r="D28">
-        <v>12169.246788685799</v>
+        <v>12.1692467886858</v>
       </c>
       <c r="E28">
-        <v>3999.8379914399602</v>
+        <v>3.9998379914399602</v>
       </c>
       <c r="F28">
-        <v>1893.574897537</v>
+        <v>1.8935748975369999</v>
       </c>
       <c r="G28">
-        <v>622.38797078610901</v>
+        <v>0.62238797078610897</v>
       </c>
       <c r="H28">
-        <v>6203.27054108216</v>
+        <v>6.2032705410821602</v>
       </c>
       <c r="I28">
-        <v>2038.9164269779901</v>
+        <v>2.0389164269779898</v>
       </c>
       <c r="J28">
-        <v>2760.2949899799601</v>
+        <v>2.7602949899799598</v>
       </c>
       <c r="K28">
-        <v>907.26508881126199</v>
+        <v>0.907265088811262</v>
       </c>
       <c r="L28">
-        <v>9929.2797595190295</v>
+        <v>9.9292797595190301</v>
       </c>
       <c r="M28">
-        <v>3263.5964328281102</v>
+        <v>3.26359643282811</v>
       </c>
       <c r="N28">
-        <v>13975.2572344689</v>
+        <v>13.9752572344689</v>
       </c>
       <c r="O28">
-        <v>4593.4449187558503</v>
+        <v>4.5934449187558499</v>
       </c>
       <c r="P28">
-        <v>8217.7448229792899</v>
+        <v>8.2177448229792898</v>
       </c>
       <c r="Q28">
-        <v>2701.0421037291799</v>
+        <v>2.7010421037291801</v>
       </c>
       <c r="R28">
-        <v>812.92025806451602</v>
+        <v>0.81292025806451595</v>
       </c>
       <c r="S28">
-        <v>267.19396760370603</v>
+        <v>0.26719396760370601</v>
       </c>
       <c r="T28">
-        <v>5666.4219639278499</v>
+        <v>5.6664219639278501</v>
       </c>
       <c r="U28">
-        <v>1862.4628327794801</v>
+        <v>1.8624628327794801</v>
       </c>
       <c r="V28">
-        <v>1985.10193548387</v>
+        <v>1.9851019354838699</v>
       </c>
       <c r="W28">
-        <v>652.47145335334505</v>
+        <v>0.652471453353345</v>
       </c>
       <c r="X28">
-        <v>2264.0164516128998</v>
+        <v>2.2640164516129002</v>
       </c>
       <c r="Y28">
-        <v>744.14622150861203</v>
+        <v>0.74414622150861198</v>
       </c>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
@@ -3858,76 +3858,76 @@
         <v>0.27083333333333298</v>
       </c>
       <c r="B29">
-        <v>10435.0454514189</v>
+        <v>10.435045451418899</v>
       </c>
       <c r="C29">
-        <v>3429.8335767004</v>
+        <v>3.4298335767003998</v>
       </c>
       <c r="D29">
-        <v>13566.2462942074</v>
+        <v>13.566246294207399</v>
       </c>
       <c r="E29">
-        <v>4459.0095238476297</v>
+        <v>4.4590095238476302</v>
       </c>
       <c r="F29">
-        <v>2207.7100168078</v>
+        <v>2.2077100168078001</v>
       </c>
       <c r="G29">
-        <v>725.63919136888705</v>
+        <v>0.72563919136888699</v>
       </c>
       <c r="H29">
-        <v>7059.5915831663297</v>
+        <v>7.0595915831663296</v>
       </c>
       <c r="I29">
-        <v>2320.3755424412602</v>
+        <v>2.3203755424412602</v>
       </c>
       <c r="J29">
-        <v>3141.3357114228402</v>
+        <v>3.14133571142284</v>
       </c>
       <c r="K29">
-        <v>1032.50711737542</v>
+        <v>1.0325071173754199</v>
       </c>
       <c r="L29">
-        <v>11299.952074148199</v>
+        <v>11.2999520741482</v>
       </c>
       <c r="M29">
-        <v>3714.1146360554699</v>
+        <v>3.71411463605547</v>
       </c>
       <c r="N29">
-        <v>15904.4503527054</v>
+        <v>15.9044503527054</v>
       </c>
       <c r="O29">
-        <v>5227.5400325406299</v>
+        <v>5.22754003254063</v>
       </c>
       <c r="P29">
-        <v>9352.1509018035995</v>
+        <v>9.3521509018036095</v>
       </c>
       <c r="Q29">
-        <v>3073.9033506570099</v>
+        <v>3.0739033506570101</v>
       </c>
       <c r="R29">
-        <v>959.06322580645099</v>
+        <v>0.95906322580645098</v>
       </c>
       <c r="S29">
-        <v>315.22883818414698</v>
+        <v>0.31522883818414699</v>
       </c>
       <c r="T29">
-        <v>6448.6345611222396</v>
+        <v>6.4486345611222404</v>
       </c>
       <c r="U29">
-        <v>2119.5636803479501</v>
+        <v>2.1195636803479498</v>
       </c>
       <c r="V29">
-        <v>2341.9741935483798</v>
+        <v>2.34197419354838</v>
       </c>
       <c r="W29">
-        <v>769.76969215844099</v>
+        <v>0.76976969215844104</v>
       </c>
       <c r="X29">
-        <v>2671.0306451612901</v>
+        <v>2.6710306451612902</v>
       </c>
       <c r="Y29">
-        <v>877.92531751015997</v>
+        <v>0.87792531751016001</v>
       </c>
       <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
@@ -3982,76 +3982,76 @@
         <v>0.28125</v>
       </c>
       <c r="B30">
-        <v>11599.282034262</v>
+        <v>11.599282034262</v>
       </c>
       <c r="C30">
-        <v>3812.4996361486901</v>
+        <v>3.81249963614869</v>
       </c>
       <c r="D30">
-        <v>14840.214564128601</v>
+        <v>14.840214564128599</v>
       </c>
       <c r="E30">
-        <v>4877.7426446729696</v>
+        <v>4.8777426446729697</v>
       </c>
       <c r="F30">
-        <v>2616.7050413730599</v>
+        <v>2.6167050413730601</v>
       </c>
       <c r="G30">
-        <v>860.06935504072601</v>
+        <v>0.86006935504072701</v>
       </c>
       <c r="H30">
-        <v>7801.2869739478901</v>
+        <v>7.8012869739478896</v>
       </c>
       <c r="I30">
-        <v>2564.1590282755801</v>
+        <v>2.5641590282755802</v>
       </c>
       <c r="J30">
-        <v>3471.3709819639198</v>
+        <v>3.4713709819639198</v>
       </c>
       <c r="K30">
-        <v>1140.9844649506799</v>
+        <v>1.14098446495068</v>
       </c>
       <c r="L30">
-        <v>12487.1485671342</v>
+        <v>12.4871485671342</v>
       </c>
       <c r="M30">
-        <v>4104.3272530240502</v>
+        <v>4.1043272530240502</v>
       </c>
       <c r="N30">
-        <v>17575.405022044</v>
+        <v>17.575405022043999</v>
       </c>
       <c r="O30">
-        <v>5776.7562728266503</v>
+        <v>5.7767562728266499</v>
       </c>
       <c r="P30">
-        <v>10334.7073480293</v>
+        <v>10.334707348029299</v>
       </c>
       <c r="Q30">
-        <v>3396.8540369724601</v>
+        <v>3.39685403697246</v>
       </c>
       <c r="R30">
-        <v>1173.71070967741</v>
+        <v>1.17371070967741</v>
       </c>
       <c r="S30">
-        <v>385.780054349171</v>
+        <v>0.38578005434917101</v>
       </c>
       <c r="T30">
-        <v>7126.14153507014</v>
+        <v>7.1261415350701398</v>
       </c>
       <c r="U30">
-        <v>2342.2494538324499</v>
+        <v>2.3422494538324501</v>
       </c>
       <c r="V30">
-        <v>2866.13032258064</v>
+        <v>2.86613032258064</v>
       </c>
       <c r="W30">
-        <v>942.05148040342499</v>
+        <v>0.94205148040342501</v>
       </c>
       <c r="X30">
-        <v>3268.83274193548</v>
+        <v>3.2688327419354799</v>
       </c>
       <c r="Y30">
-        <v>1074.4133647624301</v>
+        <v>1.0744133647624301</v>
       </c>
       <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
@@ -4106,76 +4106,76 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="B31">
-        <v>12506.3179542956</v>
+        <v>12.5063179542956</v>
       </c>
       <c r="C31">
-        <v>4110.6279258900204</v>
+        <v>4.1106279258900198</v>
       </c>
       <c r="D31">
-        <v>15844.286714779901</v>
+        <v>15.8442867147799</v>
       </c>
       <c r="E31">
-        <v>5207.76520104478</v>
+        <v>5.2077652010447801</v>
       </c>
       <c r="F31">
-        <v>3119.1662325457301</v>
+        <v>3.1191662325457301</v>
       </c>
       <c r="G31">
-        <v>1025.2203620484199</v>
+        <v>1.0252203620484199</v>
       </c>
       <c r="H31">
-        <v>8327.2164328657309</v>
+        <v>8.3272164328657308</v>
       </c>
       <c r="I31">
-        <v>2737.0236818671901</v>
+        <v>2.73702368186719</v>
       </c>
       <c r="J31">
-        <v>3705.3959919839599</v>
+        <v>3.7053959919839601</v>
       </c>
       <c r="K31">
-        <v>1217.9047659585899</v>
+        <v>1.21790476595859</v>
       </c>
       <c r="L31">
-        <v>13328.9788076152</v>
+        <v>13.328978807615201</v>
       </c>
       <c r="M31">
-        <v>4381.0234723290396</v>
+        <v>4.3810234723290398</v>
       </c>
       <c r="N31">
-        <v>18760.263787575099</v>
+        <v>18.760263787575099</v>
       </c>
       <c r="O31">
-        <v>6166.2005159385599</v>
+        <v>6.1662005159385602</v>
       </c>
       <c r="P31">
-        <v>11031.429191716699</v>
+        <v>11.0314291917167</v>
       </c>
       <c r="Q31">
-        <v>3625.8554327234101</v>
+        <v>3.62585543272341</v>
       </c>
       <c r="R31">
-        <v>1462.5714193548299</v>
+        <v>1.46257141935483</v>
       </c>
       <c r="S31">
-        <v>480.72397823082503</v>
+        <v>0.48072397823082502</v>
       </c>
       <c r="T31">
-        <v>7606.5555711422803</v>
+        <v>7.6065555711422803</v>
       </c>
       <c r="U31">
-        <v>2500.1539113941899</v>
+        <v>2.50015391139419</v>
       </c>
       <c r="V31">
-        <v>3571.5106451612901</v>
+        <v>3.5715106451612901</v>
       </c>
       <c r="W31">
-        <v>1173.89878054162</v>
+        <v>1.1738987805416199</v>
       </c>
       <c r="X31">
-        <v>4073.3217338709601</v>
+        <v>4.0733217338709604</v>
       </c>
       <c r="Y31">
-        <v>1338.83610920299</v>
+        <v>1.3388361092029899</v>
       </c>
       <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
@@ -4230,76 +4230,76 @@
         <v>0.30208333333333298</v>
       </c>
       <c r="B32">
-        <v>13182.8310620596</v>
+        <v>13.1828310620596</v>
       </c>
       <c r="C32">
-        <v>4332.9870313571801</v>
+        <v>4.3329870313571801</v>
       </c>
       <c r="D32">
-        <v>16641.474522701599</v>
+        <v>16.6414745227016</v>
       </c>
       <c r="E32">
-        <v>5469.7881623510302</v>
+        <v>5.4697881623510298</v>
       </c>
       <c r="F32">
-        <v>3665.2676456946101</v>
+        <v>3.6652676456946098</v>
       </c>
       <c r="G32">
-        <v>1204.7152163661699</v>
+        <v>1.2047152163661701</v>
       </c>
       <c r="H32">
-        <v>8671.0933867735403</v>
+        <v>8.6710933867735402</v>
       </c>
       <c r="I32">
-        <v>2850.0505707540201</v>
+        <v>2.85005057075402</v>
       </c>
       <c r="J32">
-        <v>3858.41234468937</v>
+        <v>3.8584123446893699</v>
       </c>
       <c r="K32">
-        <v>1268.1988089253</v>
+        <v>1.2681988089253</v>
       </c>
       <c r="L32">
-        <v>13879.406272545</v>
+        <v>13.879406272544999</v>
       </c>
       <c r="M32">
-        <v>4561.94023110538</v>
+        <v>4.5619402311053801</v>
       </c>
       <c r="N32">
-        <v>19534.979134268498</v>
+        <v>19.5349791342685</v>
       </c>
       <c r="O32">
-        <v>6420.8371364348104</v>
+        <v>6.4208371364348098</v>
       </c>
       <c r="P32">
-        <v>11486.9780895123</v>
+        <v>11.4869780895123</v>
       </c>
       <c r="Q32">
-        <v>3775.5871145605702</v>
+        <v>3.7755871145605702</v>
       </c>
       <c r="R32">
-        <v>1791.3930967741901</v>
+        <v>1.79139309677419</v>
       </c>
       <c r="S32">
-        <v>588.80243703681799</v>
+        <v>0.588802437036818</v>
       </c>
       <c r="T32">
-        <v>7920.6724408817599</v>
+        <v>7.9206724408817601</v>
       </c>
       <c r="U32">
-        <v>2603.3991336460999</v>
+        <v>2.6033991336461</v>
       </c>
       <c r="V32">
-        <v>4374.4732258064496</v>
+        <v>4.37447322580645</v>
       </c>
       <c r="W32">
-        <v>1437.8198178530799</v>
+        <v>1.4378198178530801</v>
       </c>
       <c r="X32">
-        <v>4989.1036693548303</v>
+        <v>4.9891036693548303</v>
       </c>
       <c r="Y32">
-        <v>1639.8390752064699</v>
+        <v>1.63983907520647</v>
       </c>
       <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
@@ -4354,76 +4354,76 @@
         <v>0.3125</v>
       </c>
       <c r="B33">
-        <v>13695.7931876656</v>
+        <v>13.6957931876656</v>
       </c>
       <c r="C33">
-        <v>4501.5895286026498</v>
+        <v>4.5015895286026497</v>
       </c>
       <c r="D33">
-        <v>17344.820854969101</v>
+        <v>17.3448208549691</v>
       </c>
       <c r="E33">
-        <v>5700.9669222032298</v>
+        <v>5.7009669222032304</v>
       </c>
       <c r="F33">
-        <v>4190.8565851056901</v>
+        <v>4.1908565851056903</v>
       </c>
       <c r="G33">
-        <v>1377.4679466084101</v>
+        <v>1.3774679466084101</v>
       </c>
       <c r="H33">
-        <v>8900.3446893787495</v>
+        <v>8.9003446893787501</v>
       </c>
       <c r="I33">
-        <v>2925.4018300119001</v>
+        <v>2.9254018300119</v>
       </c>
       <c r="J33">
-        <v>3960.4232464929801</v>
+        <v>3.9604232464929798</v>
       </c>
       <c r="K33">
-        <v>1301.7281709031099</v>
+        <v>1.3017281709031101</v>
       </c>
       <c r="L33">
-        <v>14246.357915831601</v>
+        <v>14.2463579158316</v>
       </c>
       <c r="M33">
-        <v>4682.5514036229397</v>
+        <v>4.6825514036229396</v>
       </c>
       <c r="N33">
-        <v>20051.456032064099</v>
+        <v>20.051456032064099</v>
       </c>
       <c r="O33">
-        <v>6590.5948834323099</v>
+        <v>6.5905948834323098</v>
       </c>
       <c r="P33">
-        <v>11790.6773547094</v>
+        <v>11.7906773547094</v>
       </c>
       <c r="Q33">
-        <v>3875.4082357853499</v>
+        <v>3.8754082357853501</v>
       </c>
       <c r="R33">
-        <v>2114.5060645161202</v>
+        <v>2.11450606451612</v>
       </c>
       <c r="S33">
-        <v>695.00453371076298</v>
+        <v>0.69500453371076298</v>
       </c>
       <c r="T33">
-        <v>8130.0836873747403</v>
+        <v>8.13008368737475</v>
       </c>
       <c r="U33">
-        <v>2672.22928181404</v>
+        <v>2.6722292818140398</v>
       </c>
       <c r="V33">
-        <v>5163.49548387096</v>
+        <v>5.1634954838709604</v>
       </c>
       <c r="W33">
-        <v>1697.15889271122</v>
+        <v>1.69715889271123</v>
       </c>
       <c r="X33">
-        <v>5888.9866129032198</v>
+        <v>5.8889866129032198</v>
       </c>
       <c r="Y33">
-        <v>1935.6162952724001</v>
+        <v>1.9356162952724001</v>
       </c>
       <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
@@ -4478,76 +4478,76 @@
         <v>0.32291666666666702</v>
       </c>
       <c r="B34">
-        <v>14122.2773764949</v>
+        <v>14.1222773764949</v>
       </c>
       <c r="C34">
-        <v>4641.7681025809297</v>
+        <v>4.6417681025809303</v>
       </c>
       <c r="D34">
-        <v>18070.8621233632</v>
+        <v>18.070862123363199</v>
       </c>
       <c r="E34">
-        <v>5939.6051468282703</v>
+        <v>5.9396051468282698</v>
       </c>
       <c r="F34">
-        <v>4634.2398838806603</v>
+        <v>4.6342398838806602</v>
       </c>
       <c r="G34">
-        <v>1523.2009894175101</v>
+        <v>1.52320098941751</v>
       </c>
       <c r="H34">
-        <v>9089.1398797595193</v>
+        <v>9.0891398797595198</v>
       </c>
       <c r="I34">
-        <v>2987.4558082242702</v>
+        <v>2.9874558082242699</v>
       </c>
       <c r="J34">
-        <v>4044.4322244488899</v>
+        <v>4.0444322244488902</v>
       </c>
       <c r="K34">
-        <v>1329.34058664954</v>
+        <v>1.32934058664954</v>
       </c>
       <c r="L34">
-        <v>14548.553386773499</v>
+        <v>14.5485533867735</v>
       </c>
       <c r="M34">
-        <v>4781.8782515785797</v>
+        <v>4.78187825157858</v>
       </c>
       <c r="N34">
-        <v>20476.789947895701</v>
+        <v>20.4767899478957</v>
       </c>
       <c r="O34">
-        <v>6730.3953809596596</v>
+        <v>6.7303953809596599</v>
       </c>
       <c r="P34">
-        <v>12040.7826319305</v>
+        <v>12.040782631930499</v>
       </c>
       <c r="Q34">
-        <v>3957.6138650292801</v>
+        <v>3.95761386502928</v>
       </c>
       <c r="R34">
-        <v>2387.3823870967699</v>
+        <v>2.3873823870967699</v>
       </c>
       <c r="S34">
-        <v>784.69464362268104</v>
+        <v>0.78469464362268104</v>
       </c>
       <c r="T34">
-        <v>8302.5400080160307</v>
+        <v>8.3025400080160292</v>
       </c>
       <c r="U34">
-        <v>2728.9129332464599</v>
+        <v>2.7289129332464599</v>
       </c>
       <c r="V34">
-        <v>5829.8429032258</v>
+        <v>5.8298429032258001</v>
       </c>
       <c r="W34">
-        <v>1916.17669798011</v>
+        <v>1.91617669798011</v>
       </c>
       <c r="X34">
-        <v>6648.9584274193503</v>
+        <v>6.6489584274193501</v>
       </c>
       <c r="Y34">
-        <v>2185.4069510877898</v>
+        <v>2.1854069510877898</v>
       </c>
       <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
@@ -4602,76 +4602,76 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="B35">
-        <v>14515.180286185199</v>
+        <v>14.515180286185201</v>
       </c>
       <c r="C35">
-        <v>4770.9090438746798</v>
+        <v>4.7709090438746804</v>
       </c>
       <c r="D35">
-        <v>18905.166542648702</v>
+        <v>18.905166542648701</v>
       </c>
       <c r="E35">
-        <v>6213.8277483278898</v>
+        <v>6.2138277483278896</v>
       </c>
       <c r="F35">
-        <v>4942.3204257708903</v>
+        <v>4.9423204257708901</v>
       </c>
       <c r="G35">
-        <v>1624.4621666517201</v>
+        <v>1.6244621666517201</v>
       </c>
       <c r="H35">
-        <v>9291.4204408817604</v>
+        <v>9.29142044088176</v>
       </c>
       <c r="I35">
-        <v>3053.94221345182</v>
+        <v>3.0539422134518199</v>
       </c>
       <c r="J35">
-        <v>4134.4418436873702</v>
+        <v>4.1344418436873704</v>
       </c>
       <c r="K35">
-        <v>1358.92531780643</v>
+        <v>1.35892531780643</v>
       </c>
       <c r="L35">
-        <v>14872.3342484969</v>
+        <v>14.8723342484969</v>
       </c>
       <c r="M35">
-        <v>4888.2998743881899</v>
+        <v>4.8882998743881902</v>
       </c>
       <c r="N35">
-        <v>20932.504857715401</v>
+        <v>20.932504857715401</v>
       </c>
       <c r="O35">
-        <v>6880.1816283103999</v>
+        <v>6.8801816283103996</v>
       </c>
       <c r="P35">
-        <v>12308.752571810201</v>
+        <v>12.308752571810199</v>
       </c>
       <c r="Q35">
-        <v>4045.6913249334898</v>
+        <v>4.0456913249334896</v>
       </c>
       <c r="R35">
-        <v>2572.34458064516</v>
+        <v>2.5723445806451601</v>
       </c>
       <c r="S35">
-        <v>845.48877670105298</v>
+        <v>0.84548877670105305</v>
       </c>
       <c r="T35">
-        <v>8487.3146372745396</v>
+        <v>8.4873146372745492</v>
       </c>
       <c r="U35">
-        <v>2789.6454169240501</v>
+        <v>2.7896454169240501</v>
       </c>
       <c r="V35">
-        <v>6281.5093548387003</v>
+        <v>6.2815093548387004</v>
       </c>
       <c r="W35">
-        <v>2064.6322814678101</v>
+        <v>2.06463228146781</v>
       </c>
       <c r="X35">
-        <v>7164.0857661290302</v>
+        <v>7.1640857661290296</v>
       </c>
       <c r="Y35">
-        <v>2354.7211194647498</v>
+        <v>2.3547211194647502</v>
       </c>
       <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
@@ -4726,76 +4726,76 @@
         <v>0.34375</v>
       </c>
       <c r="B36">
-        <v>14838.0710128644</v>
+        <v>14.8380710128644</v>
       </c>
       <c r="C36">
-        <v>4877.0380934437699</v>
+        <v>4.8770380934437698</v>
       </c>
       <c r="D36">
-        <v>19757.950738535499</v>
+        <v>19.757950738535499</v>
       </c>
       <c r="E36">
-        <v>6494.1243586636001</v>
+        <v>6.4941243586636004</v>
       </c>
       <c r="F36">
-        <v>5091.7449872325196</v>
+        <v>5.09174498723252</v>
       </c>
       <c r="G36">
-        <v>1673.57564492748</v>
+        <v>1.6735756449274799</v>
       </c>
       <c r="H36">
-        <v>9486.9583166332595</v>
+        <v>9.4869583166332596</v>
       </c>
       <c r="I36">
-        <v>3118.2124051717701</v>
+        <v>3.1182124051717799</v>
       </c>
       <c r="J36">
-        <v>4221.4511422845599</v>
+        <v>4.2214511422845602</v>
       </c>
       <c r="K36">
-        <v>1387.5238912580901</v>
+        <v>1.3875238912580901</v>
       </c>
       <c r="L36">
-        <v>15185.322414829599</v>
+        <v>15.185322414829599</v>
       </c>
       <c r="M36">
-        <v>4991.17410977081</v>
+        <v>4.9911741097708102</v>
       </c>
       <c r="N36">
-        <v>21373.029270540999</v>
+        <v>21.373029270541</v>
       </c>
       <c r="O36">
-        <v>7024.9750007494404</v>
+        <v>7.02497500074944</v>
       </c>
       <c r="P36">
-        <v>12567.7901803607</v>
+        <v>12.567790180360699</v>
       </c>
       <c r="Q36">
-        <v>4130.8328695075597</v>
+        <v>4.13083286950756</v>
       </c>
       <c r="R36">
-        <v>2655.69174193548</v>
+        <v>2.6556917419354802</v>
       </c>
       <c r="S36">
-        <v>872.88366382896095</v>
+        <v>0.87288366382896099</v>
       </c>
       <c r="T36">
-        <v>8665.9301122244397</v>
+        <v>8.6659301122244496</v>
       </c>
       <c r="U36">
-        <v>2848.3534844790502</v>
+        <v>2.8483534844790501</v>
       </c>
       <c r="V36">
-        <v>6485.0380645161204</v>
+        <v>6.4850380645161199</v>
       </c>
       <c r="W36">
-        <v>2131.5289332863499</v>
+        <v>2.1315289332863498</v>
       </c>
       <c r="X36">
-        <v>7396.2110483870902</v>
+        <v>7.39621104838709</v>
       </c>
       <c r="Y36">
-        <v>2431.0170101531298</v>
+        <v>2.4310170101531301</v>
       </c>
       <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
@@ -4850,76 +4850,76 @@
         <v>0.35416666666666702</v>
       </c>
       <c r="B37">
-        <v>15062.007523627901</v>
+        <v>15.0620075236279</v>
       </c>
       <c r="C37">
-        <v>4950.6424651009402</v>
+        <v>4.9506424651009402</v>
       </c>
       <c r="D37">
-        <v>20528.662504771099</v>
+        <v>20.528662504771098</v>
       </c>
       <c r="E37">
-        <v>6747.4450658995702</v>
+        <v>6.7474450658995702</v>
       </c>
       <c r="F37">
-        <v>5078.6849011733102</v>
+        <v>5.0786849011733102</v>
       </c>
       <c r="G37">
-        <v>1669.28300222755</v>
+        <v>1.66928300222755</v>
       </c>
       <c r="H37">
-        <v>9655.5254509017996</v>
+        <v>9.6555254509018003</v>
       </c>
       <c r="I37">
-        <v>3173.6177428613901</v>
+        <v>3.1736177428613899</v>
       </c>
       <c r="J37">
-        <v>4296.4591583166302</v>
+        <v>4.2964591583166296</v>
       </c>
       <c r="K37">
-        <v>1412.17783388883</v>
+        <v>1.41217783388883</v>
       </c>
       <c r="L37">
-        <v>15455.139799599099</v>
+        <v>15.455139799599101</v>
       </c>
       <c r="M37">
-        <v>5079.8587954454897</v>
+        <v>5.0798587954454897</v>
       </c>
       <c r="N37">
-        <v>21752.791695390701</v>
+        <v>21.752791695390702</v>
       </c>
       <c r="O37">
-        <v>7149.7968735417198</v>
+        <v>7.1497968735417201</v>
       </c>
       <c r="P37">
-        <v>12791.0984635938</v>
+        <v>12.7910984635938</v>
       </c>
       <c r="Q37">
-        <v>4204.2307527610701</v>
+        <v>4.2042307527610703</v>
       </c>
       <c r="R37">
-        <v>2636.2821290322499</v>
+        <v>2.6362821290322498</v>
       </c>
       <c r="S37">
-        <v>866.50403257999596</v>
+        <v>0.86650403257999598</v>
       </c>
       <c r="T37">
-        <v>8819.9089699398792</v>
+        <v>8.8199089699398794</v>
       </c>
       <c r="U37">
-        <v>2898.9638875437099</v>
+        <v>2.8989638875437098</v>
       </c>
       <c r="V37">
-        <v>6437.6409677419297</v>
+        <v>6.4376409677419302</v>
       </c>
       <c r="W37">
-        <v>2115.9502609450401</v>
+        <v>2.11595026094504</v>
       </c>
       <c r="X37">
-        <v>7342.1544758064501</v>
+        <v>7.3421544758064501</v>
       </c>
       <c r="Y37">
-        <v>2413.2494739654198</v>
+        <v>2.4132494739654202</v>
       </c>
       <c r="Z37" s="4"/>
       <c r="AA37" s="4"/>
@@ -4974,76 +4974,76 @@
         <v>0.36458333333333298</v>
       </c>
       <c r="B38">
-        <v>15135.802935677801</v>
+        <v>15.1358029356778</v>
       </c>
       <c r="C38">
-        <v>4974.8978440768697</v>
+        <v>4.9748978440768701</v>
       </c>
       <c r="D38">
-        <v>21100.043814754899</v>
+        <v>21.100043814754901</v>
       </c>
       <c r="E38">
-        <v>6935.2490204875203</v>
+        <v>6.9352490204875199</v>
       </c>
       <c r="F38">
-        <v>4889.0675638373496</v>
+        <v>4.88906756383735</v>
       </c>
       <c r="G38">
-        <v>1606.95879737888</v>
+        <v>1.6069587973788799</v>
       </c>
       <c r="H38">
-        <v>9763.4084168336594</v>
+        <v>9.7634084168336592</v>
       </c>
       <c r="I38">
-        <v>3209.07715898275</v>
+        <v>3.2090771589827498</v>
       </c>
       <c r="J38">
-        <v>4344.46428857715</v>
+        <v>4.3444642885771501</v>
       </c>
       <c r="K38">
-        <v>1427.9563571725</v>
+        <v>1.4279563571725</v>
       </c>
       <c r="L38">
-        <v>15627.8229258517</v>
+        <v>15.627822925851699</v>
       </c>
       <c r="M38">
-        <v>5136.6169942772904</v>
+        <v>5.1366169942772899</v>
       </c>
       <c r="N38">
-        <v>21995.839647294499</v>
+        <v>21.995839647294499</v>
       </c>
       <c r="O38">
-        <v>7229.6828721287802</v>
+        <v>7.2296828721287802</v>
       </c>
       <c r="P38">
-        <v>12934.015764862999</v>
+        <v>12.934015764863</v>
       </c>
       <c r="Q38">
-        <v>4251.2053980433202</v>
+        <v>4.2512053980433198</v>
       </c>
       <c r="R38">
-        <v>2507.2652903225799</v>
+        <v>2.5072652903225801</v>
       </c>
       <c r="S38">
-        <v>824.09824839570001</v>
+        <v>0.82409824839570001</v>
       </c>
       <c r="T38">
-        <v>8918.4554388777506</v>
+        <v>8.9184554388777499</v>
       </c>
       <c r="U38">
-        <v>2931.3545455050998</v>
+        <v>2.9313545455051</v>
       </c>
       <c r="V38">
-        <v>6122.5896774193498</v>
+        <v>6.1225896774193496</v>
       </c>
       <c r="W38">
-        <v>2012.3979094999199</v>
+        <v>2.0123979094999198</v>
       </c>
       <c r="X38">
-        <v>6982.83725806451</v>
+        <v>6.9828372580645102</v>
       </c>
       <c r="Y38">
-        <v>2295.1476157765601</v>
+        <v>2.29514761577656</v>
       </c>
       <c r="Z38" s="4"/>
       <c r="AA38" s="4"/>
@@ -5098,76 +5098,76 @@
         <v>0.375</v>
       </c>
       <c r="B39">
-        <v>15045.3820765401</v>
+        <v>15.045382076540101</v>
       </c>
       <c r="C39">
-        <v>4945.1779449017104</v>
+        <v>4.9451779449017099</v>
       </c>
       <c r="D39">
-        <v>21404.370986013299</v>
+        <v>21.404370986013301</v>
       </c>
       <c r="E39">
-        <v>7035.2765244541997</v>
+        <v>7.0352765244541997</v>
       </c>
       <c r="F39">
-        <v>4533.9485546900196</v>
+        <v>4.5339485546900198</v>
       </c>
       <c r="G39">
-        <v>1490.2368236252901</v>
+        <v>1.4902368236252901</v>
       </c>
       <c r="H39">
-        <v>9797.1218436873696</v>
+        <v>9.7971218436873695</v>
       </c>
       <c r="I39">
-        <v>3220.1582265206698</v>
+        <v>3.2201582265206699</v>
       </c>
       <c r="J39">
-        <v>4359.4658917835604</v>
+        <v>4.35946589178356</v>
       </c>
       <c r="K39">
-        <v>1432.8871456986501</v>
+        <v>1.4328871456986501</v>
       </c>
       <c r="L39">
-        <v>15681.786402805599</v>
+        <v>15.681786402805599</v>
       </c>
       <c r="M39">
-        <v>5154.3539314122199</v>
+        <v>5.1543539314122198</v>
       </c>
       <c r="N39">
-        <v>22071.792132264502</v>
+        <v>22.071792132264498</v>
       </c>
       <c r="O39">
-        <v>7254.6472466872301</v>
+        <v>7.25464724668723</v>
       </c>
       <c r="P39">
-        <v>12978.677421509599</v>
+        <v>12.9786774215096</v>
       </c>
       <c r="Q39">
-        <v>4265.8849746940195</v>
+        <v>4.2658849746940204</v>
       </c>
       <c r="R39">
-        <v>2276.63341935483</v>
+        <v>2.2766334193548299</v>
       </c>
       <c r="S39">
-        <v>748.29321826093997</v>
+        <v>0.74829321826093997</v>
       </c>
       <c r="T39">
-        <v>8949.2512104208399</v>
+        <v>8.9492512104208402</v>
       </c>
       <c r="U39">
-        <v>2941.4766261180298</v>
+        <v>2.9414766261180301</v>
       </c>
       <c r="V39">
-        <v>5559.4006451612904</v>
+        <v>5.5594006451612898</v>
       </c>
       <c r="W39">
-        <v>1827.2866263856299</v>
+        <v>1.82728662638563</v>
       </c>
       <c r="X39">
-        <v>6340.5179838709601</v>
+        <v>6.34051798387096</v>
       </c>
       <c r="Y39">
-        <v>2084.0274798991099</v>
+        <v>2.0840274798991101</v>
       </c>
       <c r="Z39" s="4"/>
       <c r="AA39" s="4"/>
@@ -5222,76 +5222,76 @@
         <v>0.38541666666666702</v>
       </c>
       <c r="B40">
-        <v>14835.4564090115</v>
+        <v>14.835456409011501</v>
       </c>
       <c r="C40">
-        <v>4876.1787147159903</v>
+        <v>4.8761787147159996</v>
       </c>
       <c r="D40">
-        <v>21501.1011613556</v>
+        <v>21.501101161355599</v>
       </c>
       <c r="E40">
-        <v>7067.0701955803997</v>
+        <v>7.0670701955804001</v>
       </c>
       <c r="F40">
-        <v>4082.14547974982</v>
+        <v>4.08214547974982</v>
       </c>
       <c r="G40">
-        <v>1341.7363342215101</v>
+        <v>1.3417363342215101</v>
       </c>
       <c r="H40">
-        <v>9770.1511022044106</v>
+        <v>9.7701511022044105</v>
       </c>
       <c r="I40">
-        <v>3211.2933724903401</v>
+        <v>3.2112933724903399</v>
       </c>
       <c r="J40">
-        <v>4347.4646092184303</v>
+        <v>4.3474646092184299</v>
       </c>
       <c r="K40">
-        <v>1428.94251487773</v>
+        <v>1.4289425148777299</v>
       </c>
       <c r="L40">
-        <v>15638.615621242399</v>
+        <v>15.638615621242399</v>
       </c>
       <c r="M40">
-        <v>5140.1643817042705</v>
+        <v>5.1401643817042704</v>
       </c>
       <c r="N40">
-        <v>22011.030144288499</v>
+        <v>22.011030144288501</v>
       </c>
       <c r="O40">
-        <v>7234.67574704047</v>
+        <v>7.2346757470404697</v>
       </c>
       <c r="P40">
-        <v>12942.9480961923</v>
+        <v>12.9429480961923</v>
       </c>
       <c r="Q40">
-        <v>4254.1413133734604</v>
+        <v>4.2541413133734602</v>
       </c>
       <c r="R40">
-        <v>1987.7727096774199</v>
+        <v>1.98777270967742</v>
       </c>
       <c r="S40">
-        <v>653.34929437928599</v>
+        <v>0.65334929437928602</v>
       </c>
       <c r="T40">
-        <v>8924.6145931863703</v>
+        <v>8.9246145931863694</v>
       </c>
       <c r="U40">
-        <v>2933.3789616276799</v>
+        <v>2.93337896162768</v>
       </c>
       <c r="V40">
-        <v>4854.0203225806399</v>
+        <v>4.8540203225806398</v>
       </c>
       <c r="W40">
-        <v>1595.43932624743</v>
+        <v>1.59543932624743</v>
       </c>
       <c r="X40">
-        <v>5536.02899193548</v>
+        <v>5.5360289919354804</v>
       </c>
       <c r="Y40">
-        <v>1819.6047354585501</v>
+        <v>1.8196047354585501</v>
       </c>
       <c r="Z40" s="4"/>
       <c r="AA40" s="4"/>
@@ -5346,76 +5346,76 @@
         <v>0.39583333333333298</v>
       </c>
       <c r="B41">
-        <v>14557.545460404601</v>
+        <v>14.557545460404601</v>
       </c>
       <c r="C41">
-        <v>4784.8338032537304</v>
+        <v>4.7848338032537301</v>
       </c>
       <c r="D41">
-        <v>21469.743389109201</v>
+        <v>21.469743389109201</v>
       </c>
       <c r="E41">
-        <v>7056.7633942692</v>
+        <v>7.0567633942691996</v>
       </c>
       <c r="F41">
-        <v>3620.2255418094201</v>
+        <v>3.62022554180942</v>
       </c>
       <c r="G41">
-        <v>1189.9105927552901</v>
+        <v>1.18991059275529</v>
       </c>
       <c r="H41">
-        <v>9695.98156312625</v>
+        <v>9.6959815631262494</v>
       </c>
       <c r="I41">
-        <v>3186.9150239068999</v>
+        <v>3.1869150239069</v>
       </c>
       <c r="J41">
-        <v>4314.46108216432</v>
+        <v>4.3144610821643203</v>
       </c>
       <c r="K41">
-        <v>1418.0947801202101</v>
+        <v>1.41809478012021</v>
       </c>
       <c r="L41">
-        <v>15519.895971943801</v>
+        <v>15.5198959719438</v>
       </c>
       <c r="M41">
-        <v>5101.1431200074203</v>
+        <v>5.1011431200074204</v>
       </c>
       <c r="N41">
-        <v>21843.9346773547</v>
+        <v>21.843934677354699</v>
       </c>
       <c r="O41">
-        <v>7179.7541230118704</v>
+        <v>7.17975412301187</v>
       </c>
       <c r="P41">
-        <v>12844.692451569799</v>
+        <v>12.8446924515698</v>
       </c>
       <c r="Q41">
-        <v>4221.8462447419197</v>
+        <v>4.2218462447419203</v>
       </c>
       <c r="R41">
-        <v>1695.48677419354</v>
+        <v>1.69548677419354</v>
       </c>
       <c r="S41">
-        <v>557.27955321840295</v>
+        <v>0.55727955321840295</v>
       </c>
       <c r="T41">
-        <v>8856.8638957915791</v>
+        <v>8.8568638957915802</v>
       </c>
       <c r="U41">
-        <v>2911.1103842792299</v>
+        <v>2.9111103842792301</v>
       </c>
       <c r="V41">
-        <v>4140.2758064516102</v>
+        <v>4.1402758064516103</v>
       </c>
       <c r="W41">
-        <v>1360.84284863724</v>
+        <v>1.3608428486372399</v>
       </c>
       <c r="X41">
-        <v>4722.0006048387004</v>
+        <v>4.7220006048387004</v>
       </c>
       <c r="Y41">
-        <v>1552.0465434554601</v>
+        <v>1.55204654345546</v>
       </c>
       <c r="Z41" s="4"/>
       <c r="AA41" s="4"/>
@@ -5470,76 +5470,76 @@
         <v>0.40625</v>
       </c>
       <c r="B42">
-        <v>14271.9083603982</v>
+        <v>14.2719083603982</v>
       </c>
       <c r="C42">
-        <v>4690.9494286322197</v>
+        <v>4.6909494286322202</v>
       </c>
       <c r="D42">
-        <v>21400.3714818189</v>
+        <v>21.400371481818901</v>
       </c>
       <c r="E42">
-        <v>7033.9619509969298</v>
+        <v>7.0339619509969298</v>
       </c>
       <c r="F42">
-        <v>3233.6655531223701</v>
+        <v>3.2336655531223699</v>
       </c>
       <c r="G42">
-        <v>1062.8544687757401</v>
+        <v>1.06285446877574</v>
       </c>
       <c r="H42">
-        <v>9594.8412825651303</v>
+        <v>9.5948412825651292</v>
       </c>
       <c r="I42">
-        <v>3153.6718212931301</v>
+        <v>3.1536718212931301</v>
       </c>
       <c r="J42">
-        <v>4269.4562725450896</v>
+        <v>4.2694562725450904</v>
       </c>
       <c r="K42">
-        <v>1403.3024145417601</v>
+        <v>1.4033024145417601</v>
       </c>
       <c r="L42">
-        <v>15358.005541082101</v>
+        <v>15.3580055410821</v>
       </c>
       <c r="M42">
-        <v>5047.9323086026097</v>
+        <v>5.0479323086026104</v>
       </c>
       <c r="N42">
-        <v>21616.077222444801</v>
+        <v>21.616077222444801</v>
       </c>
       <c r="O42">
-        <v>7104.8609993364998</v>
+        <v>7.1048609993365002</v>
       </c>
       <c r="P42">
-        <v>12710.707481629899</v>
+        <v>12.7107074816299</v>
       </c>
       <c r="Q42">
-        <v>4177.8075147898098</v>
+        <v>4.1778075147898104</v>
       </c>
       <c r="R42">
-        <v>1453.43748387096</v>
+        <v>1.4534374838709601</v>
       </c>
       <c r="S42">
-        <v>477.72179881954702</v>
+        <v>0.47772179881954702</v>
       </c>
       <c r="T42">
-        <v>8764.4765811623201</v>
+        <v>8.7644765811623202</v>
       </c>
       <c r="U42">
-        <v>2880.7441424404401</v>
+        <v>2.8807441424404399</v>
       </c>
       <c r="V42">
-        <v>3549.2061290322499</v>
+        <v>3.5492061290322501</v>
       </c>
       <c r="W42">
-        <v>1166.5676406163</v>
+        <v>1.1665676406162999</v>
       </c>
       <c r="X42">
-        <v>4047.8833467741902</v>
+        <v>4.0478833467741904</v>
       </c>
       <c r="Y42">
-        <v>1330.47491570289</v>
+        <v>1.3304749157028899</v>
       </c>
       <c r="Z42" s="4"/>
       <c r="AA42" s="4"/>
@@ -5594,76 +5594,76 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="B43">
-        <v>14042.7781958756</v>
+        <v>14.0427781958756</v>
       </c>
       <c r="C43">
-        <v>4615.6379855366204</v>
+        <v>4.6156379855366199</v>
       </c>
       <c r="D43">
-        <v>21382.274307775398</v>
+        <v>21.382274307775401</v>
       </c>
       <c r="E43">
-        <v>7028.0136975401501</v>
+        <v>7.0280136975401497</v>
       </c>
       <c r="F43">
-        <v>2994.4272176611198</v>
+        <v>2.9944272176611202</v>
       </c>
       <c r="G43">
-        <v>984.22063056017998</v>
+        <v>0.98422063056018005</v>
       </c>
       <c r="H43">
-        <v>9493.7010020039997</v>
+        <v>9.4937010020040091</v>
       </c>
       <c r="I43">
-        <v>3120.4286186793602</v>
+        <v>3.1204286186793602</v>
       </c>
       <c r="J43">
-        <v>4224.4514629258501</v>
+        <v>4.2244514629258498</v>
       </c>
       <c r="K43">
-        <v>1388.5100489633201</v>
+        <v>1.38851004896332</v>
       </c>
       <c r="L43">
-        <v>15196.1151102204</v>
+        <v>15.196115110220401</v>
       </c>
       <c r="M43">
-        <v>4994.7214971978001</v>
+        <v>4.9947214971977996</v>
       </c>
       <c r="N43">
-        <v>21388.219767535</v>
+        <v>21.388219767534999</v>
       </c>
       <c r="O43">
-        <v>7029.9678756611302</v>
+        <v>7.0299678756611303</v>
       </c>
       <c r="P43">
-        <v>12576.722511690001</v>
+        <v>12.576722511690001</v>
       </c>
       <c r="Q43">
-        <v>4133.7687848377</v>
+        <v>4.1337687848376996</v>
       </c>
       <c r="R43">
-        <v>1306.1527741935399</v>
+        <v>1.3061527741935399</v>
       </c>
       <c r="S43">
-        <v>429.31165581269602</v>
+        <v>0.42931165581269598</v>
       </c>
       <c r="T43">
-        <v>8672.0892665330593</v>
+        <v>8.6720892665330602</v>
       </c>
       <c r="U43">
-        <v>2850.3779006016398</v>
+        <v>2.8503779006016399</v>
       </c>
       <c r="V43">
-        <v>3189.5458064516101</v>
+        <v>3.1895458064516098</v>
       </c>
       <c r="W43">
-        <v>1048.35300932054</v>
+        <v>1.04835300932054</v>
       </c>
       <c r="X43">
-        <v>3637.6893548387002</v>
+        <v>3.6376893548387099</v>
       </c>
       <c r="Y43">
-        <v>1195.6506705138299</v>
+        <v>1.1956506705138299</v>
       </c>
       <c r="Z43" s="4"/>
       <c r="AA43" s="4"/>
@@ -5718,76 +5718,76 @@
         <v>0.42708333333333298</v>
       </c>
       <c r="B44">
-        <v>13881.5069135044</v>
+        <v>13.881506913504399</v>
       </c>
       <c r="C44">
-        <v>4562.6306783993996</v>
+        <v>4.5626306783994002</v>
       </c>
       <c r="D44">
-        <v>21440.569446118301</v>
+        <v>21.4405694461183</v>
       </c>
       <c r="E44">
-        <v>7047.1743829226898</v>
+        <v>7.0471743829226901</v>
       </c>
       <c r="F44">
-        <v>2884.35511725063</v>
+        <v>2.8843551172506299</v>
       </c>
       <c r="G44">
-        <v>948.04168073159803</v>
+        <v>0.948041680731598</v>
       </c>
       <c r="H44">
-        <v>9406.0460921843696</v>
+        <v>9.4060460921843703</v>
       </c>
       <c r="I44">
-        <v>3091.6178430807599</v>
+        <v>3.0916178430807602</v>
       </c>
       <c r="J44">
-        <v>4185.4472945891703</v>
+        <v>4.1854472945891699</v>
       </c>
       <c r="K44">
-        <v>1375.68999879533</v>
+        <v>1.3756899987953299</v>
       </c>
       <c r="L44">
-        <v>15055.8100701402</v>
+        <v>15.0558100701402</v>
       </c>
       <c r="M44">
-        <v>4948.6054606469697</v>
+        <v>4.94860546064697</v>
       </c>
       <c r="N44">
-        <v>21190.7433066132</v>
+        <v>21.1907433066132</v>
       </c>
       <c r="O44">
-        <v>6965.0605018091501</v>
+        <v>6.96506050180915</v>
       </c>
       <c r="P44">
-        <v>12460.6022044088</v>
+        <v>12.460602204408801</v>
       </c>
       <c r="Q44">
-        <v>4095.6018855458801</v>
+        <v>4.0956018855458796</v>
       </c>
       <c r="R44">
-        <v>1241.07348387096</v>
+        <v>1.2410734838709601</v>
       </c>
       <c r="S44">
-        <v>407.92112750734299</v>
+        <v>0.407921127507343</v>
       </c>
       <c r="T44">
-        <v>8592.0202605210397</v>
+        <v>8.5920202605210392</v>
       </c>
       <c r="U44">
-        <v>2824.0604910080201</v>
+        <v>2.8240604910080198</v>
       </c>
       <c r="V44">
-        <v>3030.62612903225</v>
+        <v>3.03062612903225</v>
       </c>
       <c r="W44">
-        <v>996.11863735264899</v>
+        <v>0.99611863735264905</v>
       </c>
       <c r="X44">
-        <v>3456.44084677419</v>
+        <v>3.4564408467741901</v>
       </c>
       <c r="Y44">
-        <v>1136.07716682564</v>
+        <v>1.13607716682564</v>
       </c>
       <c r="Z44" s="4"/>
       <c r="AA44" s="4"/>
@@ -5842,76 +5842,76 @@
         <v>0.4375</v>
       </c>
       <c r="B45">
-        <v>13784.579599521599</v>
+        <v>13.784579599521599</v>
       </c>
       <c r="C45">
-        <v>4530.77221093557</v>
+        <v>4.5307722109355701</v>
       </c>
       <c r="D45">
-        <v>21569.612587124899</v>
+        <v>21.569612587124901</v>
       </c>
       <c r="E45">
-        <v>7089.58881225391</v>
+        <v>7.0895888122539104</v>
       </c>
       <c r="F45">
-        <v>2870.4095871581799</v>
+        <v>2.8704095871581798</v>
       </c>
       <c r="G45">
-        <v>943.45800665191803</v>
+        <v>0.94345800665191804</v>
       </c>
       <c r="H45">
-        <v>9338.6192384769492</v>
+        <v>9.3386192384769497</v>
       </c>
       <c r="I45">
-        <v>3069.4557080049099</v>
+        <v>3.0694557080049099</v>
       </c>
       <c r="J45">
-        <v>4155.4440881763503</v>
+        <v>4.1554440881763499</v>
       </c>
       <c r="K45">
-        <v>1365.8284217430401</v>
+        <v>1.3658284217430401</v>
       </c>
       <c r="L45">
-        <v>14947.8831162324</v>
+        <v>14.947883116232401</v>
       </c>
       <c r="M45">
-        <v>4913.1315863770997</v>
+        <v>4.9131315863770997</v>
       </c>
       <c r="N45">
-        <v>21038.8383366733</v>
+        <v>21.038838336673301</v>
       </c>
       <c r="O45">
-        <v>6915.1317526922403</v>
+        <v>6.9151317526922398</v>
       </c>
       <c r="P45">
-        <v>12371.2788911155</v>
+        <v>12.3712788911155</v>
       </c>
       <c r="Q45">
-        <v>4066.2427322444701</v>
+        <v>4.0662427322444703</v>
       </c>
       <c r="R45">
-        <v>1236.5065161290299</v>
+        <v>1.2365065161290301</v>
       </c>
       <c r="S45">
-        <v>406.42003780170398</v>
+        <v>0.40642003780170399</v>
       </c>
       <c r="T45">
-        <v>8530.4287174348701</v>
+        <v>8.5304287174348694</v>
       </c>
       <c r="U45">
-        <v>2803.8163297821502</v>
+        <v>2.8038163297821499</v>
       </c>
       <c r="V45">
-        <v>3019.4738709677399</v>
+        <v>3.0194738709677398</v>
       </c>
       <c r="W45">
-        <v>992.45306738999</v>
+        <v>0.99245306738998995</v>
       </c>
       <c r="X45">
-        <v>3443.7216532257999</v>
+        <v>3.4437216532258002</v>
       </c>
       <c r="Y45">
-        <v>1131.89657007559</v>
+        <v>1.1318965700755901</v>
       </c>
       <c r="Z45" s="4"/>
       <c r="AA45" s="4"/>
@@ -5966,76 +5966,76 @@
         <v>0.44791666666666702</v>
       </c>
       <c r="B46">
-        <v>13774.7001472622</v>
+        <v>13.7747001472622</v>
       </c>
       <c r="C46">
-        <v>4527.5249920100496</v>
+        <v>4.5275249920100498</v>
       </c>
       <c r="D46">
-        <v>21806.5129839418</v>
+        <v>21.806512983941801</v>
       </c>
       <c r="E46">
-        <v>7167.4542071981696</v>
+        <v>7.1674542071981699</v>
       </c>
       <c r="F46">
-        <v>2916.2797910336799</v>
+        <v>2.91627979103367</v>
       </c>
       <c r="G46">
-        <v>958.53481356710699</v>
+        <v>0.95853481356710701</v>
       </c>
       <c r="H46">
-        <v>9318.3911823647195</v>
+        <v>9.3183911823647296</v>
       </c>
       <c r="I46">
-        <v>3062.8070674821502</v>
+        <v>3.0628070674821499</v>
       </c>
       <c r="J46">
-        <v>4146.4431262525004</v>
+        <v>4.1464431262524997</v>
       </c>
       <c r="K46">
-        <v>1362.8699486273499</v>
+        <v>1.3628699486273499</v>
       </c>
       <c r="L46">
-        <v>14915.5050300601</v>
+        <v>14.9155050300601</v>
       </c>
       <c r="M46">
-        <v>4902.4894240961403</v>
+        <v>4.9024894240961396</v>
       </c>
       <c r="N46">
-        <v>20993.266845691302</v>
+        <v>20.993266845691299</v>
       </c>
       <c r="O46">
-        <v>6900.15312795716</v>
+        <v>6.90015312795716</v>
       </c>
       <c r="P46">
-        <v>12344.4818971275</v>
+        <v>12.344481897127499</v>
       </c>
       <c r="Q46">
-        <v>4057.4349862540498</v>
+        <v>4.0574349862540497</v>
       </c>
       <c r="R46">
-        <v>1267.3335483870901</v>
+        <v>1.26733354838709</v>
       </c>
       <c r="S46">
-        <v>416.55239331476599</v>
+        <v>0.41655239331476601</v>
       </c>
       <c r="T46">
-        <v>8511.9512545090092</v>
+        <v>8.5119512545090092</v>
       </c>
       <c r="U46">
-        <v>2797.74308141439</v>
+        <v>2.79774308141439</v>
       </c>
       <c r="V46">
-        <v>3094.7516129032201</v>
+        <v>3.0947516129032202</v>
       </c>
       <c r="W46">
-        <v>1017.19566463794</v>
+        <v>1.0171956646379401</v>
       </c>
       <c r="X46">
-        <v>3529.5762096774101</v>
+        <v>3.5295762096774101</v>
       </c>
       <c r="Y46">
-        <v>1160.11559813842</v>
+        <v>1.1601155981384199</v>
       </c>
       <c r="Z46" s="4"/>
       <c r="AA46" s="4"/>
@@ -6090,76 +6090,76 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="B47">
-        <v>13839.6140405973</v>
+        <v>13.839614040597301</v>
       </c>
       <c r="C47">
-        <v>4548.8611569545601</v>
+        <v>4.5488611569545601</v>
       </c>
       <c r="D47">
-        <v>22130.492635414201</v>
+        <v>22.1304926354142</v>
       </c>
       <c r="E47">
-        <v>7273.9411690385596</v>
+        <v>7.2739411690385598</v>
       </c>
       <c r="F47">
-        <v>2990.0164546835599</v>
+        <v>2.9900164546835599</v>
       </c>
       <c r="G47">
-        <v>982.770882877742</v>
+        <v>0.98277088287774195</v>
       </c>
       <c r="H47">
-        <v>9345.3619238476895</v>
+        <v>9.3453619238476904</v>
       </c>
       <c r="I47">
-        <v>3071.6719215124899</v>
+        <v>3.0716719215124901</v>
       </c>
       <c r="J47">
-        <v>4158.4444088176297</v>
+        <v>4.1584444088176298</v>
       </c>
       <c r="K47">
-        <v>1366.81457944827</v>
+        <v>1.36681457944827</v>
       </c>
       <c r="L47">
-        <v>14958.675811623199</v>
+        <v>14.9586758116232</v>
       </c>
       <c r="M47">
-        <v>4916.6789738040898</v>
+        <v>4.9166789738040899</v>
       </c>
       <c r="N47">
-        <v>21054.0288336673</v>
+        <v>21.054028833667299</v>
       </c>
       <c r="O47">
-        <v>6920.1246276039301</v>
+        <v>6.9201246276039301</v>
       </c>
       <c r="P47">
-        <v>12380.211222444799</v>
+        <v>12.3802112224448</v>
       </c>
       <c r="Q47">
-        <v>4069.1786475746098</v>
+        <v>4.0691786475746099</v>
       </c>
       <c r="R47">
-        <v>1313.00322580645</v>
+        <v>1.3130032258064499</v>
       </c>
       <c r="S47">
-        <v>431.56329037115398</v>
+        <v>0.43156329037115398</v>
       </c>
       <c r="T47">
-        <v>8536.5878717434807</v>
+        <v>8.53658787174348</v>
       </c>
       <c r="U47">
-        <v>2805.8407459047398</v>
+        <v>2.8058407459047401</v>
       </c>
       <c r="V47">
-        <v>3206.27419354838</v>
+        <v>3.2062741935483801</v>
       </c>
       <c r="W47">
-        <v>1053.85136426453</v>
+        <v>1.05385136426453</v>
       </c>
       <c r="X47">
-        <v>3656.7681451612898</v>
+        <v>3.6567681451612799</v>
       </c>
       <c r="Y47">
-        <v>1201.9215656388999</v>
+        <v>1.2019215656389</v>
       </c>
       <c r="Z47" s="4"/>
       <c r="AA47" s="4"/>
@@ -6214,76 +6214,76 @@
         <v>0.46875</v>
       </c>
       <c r="B48">
-        <v>14006.1100115715</v>
+        <v>14.006110011571501</v>
       </c>
       <c r="C48">
-        <v>4603.5857361900999</v>
+        <v>4.6035857361900998</v>
       </c>
       <c r="D48">
-        <v>22550.9567931495</v>
+        <v>22.550956793149499</v>
       </c>
       <c r="E48">
-        <v>7412.1410544835699</v>
+        <v>7.4121410544835697</v>
       </c>
       <c r="F48">
-        <v>3065.9584998222199</v>
+        <v>3.0659584998222198</v>
       </c>
       <c r="G48">
-        <v>1007.73182602959</v>
+        <v>1.00773182602959</v>
       </c>
       <c r="H48">
-        <v>9446.5022044088091</v>
+        <v>9.4465022044088105</v>
       </c>
       <c r="I48">
-        <v>3104.9151241262698</v>
+        <v>3.1049151241262698</v>
       </c>
       <c r="J48">
-        <v>4203.4492184368701</v>
+        <v>4.2034492184368704</v>
       </c>
       <c r="K48">
-        <v>1381.60694502671</v>
+        <v>1.3816069450267101</v>
       </c>
       <c r="L48">
-        <v>15120.5662424849</v>
+        <v>15.1205662424849</v>
       </c>
       <c r="M48">
-        <v>4969.8897852088903</v>
+        <v>4.9698897852088901</v>
       </c>
       <c r="N48">
-        <v>21281.886288577101</v>
+        <v>21.281886288577098</v>
       </c>
       <c r="O48">
-        <v>6995.0177512792898</v>
+        <v>6.9950177512792902</v>
       </c>
       <c r="P48">
-        <v>12514.196192384699</v>
+        <v>12.5141961923847</v>
       </c>
       <c r="Q48">
-        <v>4113.2173775267202</v>
+        <v>4.1132173775267198</v>
       </c>
       <c r="R48">
-        <v>1355.2476774193501</v>
+        <v>1.35524767741935</v>
       </c>
       <c r="S48">
-        <v>445.44837014831302</v>
+        <v>0.44544837014831301</v>
       </c>
       <c r="T48">
-        <v>8628.9751863727397</v>
+        <v>8.62897518637274</v>
       </c>
       <c r="U48">
-        <v>2836.2069877435301</v>
+        <v>2.8362069877435299</v>
       </c>
       <c r="V48">
-        <v>3309.4325806451602</v>
+        <v>3.3094325806451601</v>
       </c>
       <c r="W48">
-        <v>1087.75788641913</v>
+        <v>1.08775788641913</v>
       </c>
       <c r="X48">
-        <v>3774.4206854838699</v>
+        <v>3.7744206854838702</v>
       </c>
       <c r="Y48">
-        <v>1240.59208557685</v>
+        <v>1.24059208557685</v>
       </c>
       <c r="Z48" s="4"/>
       <c r="AA48" s="4"/>
@@ -6338,76 +6338,76 @@
         <v>0.47916666666666702</v>
       </c>
       <c r="B49">
-        <v>14257.2787803995</v>
+        <v>14.257278780399499</v>
       </c>
       <c r="C49">
-        <v>4686.1409182212001</v>
+        <v>4.6861409182212004</v>
       </c>
       <c r="D49">
-        <v>23025.2129833039</v>
+        <v>23.025212983303899</v>
       </c>
       <c r="E49">
-        <v>7568.0215259700099</v>
+        <v>7.5680215259700097</v>
       </c>
       <c r="F49">
-        <v>3123.8968008597799</v>
+        <v>3.1238968008597801</v>
       </c>
       <c r="G49">
-        <v>1026.7752246617099</v>
+        <v>1.0267752246617099</v>
       </c>
       <c r="H49">
-        <v>9615.0693386773492</v>
+        <v>9.6150693386773494</v>
       </c>
       <c r="I49">
-        <v>3160.3204618158902</v>
+        <v>3.16032046181589</v>
       </c>
       <c r="J49">
-        <v>4278.4572344689304</v>
+        <v>4.27845723446893</v>
       </c>
       <c r="K49">
-        <v>1406.26088765745</v>
+        <v>1.4062608876574501</v>
       </c>
       <c r="L49">
-        <v>15390.3836272545</v>
+        <v>15.390383627254501</v>
       </c>
       <c r="M49">
-        <v>5058.57447088357</v>
+        <v>5.0585744708835696</v>
       </c>
       <c r="N49">
-        <v>21661.648713426799</v>
+        <v>21.6616487134268</v>
       </c>
       <c r="O49">
-        <v>7119.8396240715701</v>
+        <v>7.1198396240715702</v>
       </c>
       <c r="P49">
-        <v>12737.5044756179</v>
+        <v>12.7375044756179</v>
       </c>
       <c r="Q49">
-        <v>4186.6152607802296</v>
+        <v>4.1866152607802301</v>
       </c>
       <c r="R49">
-        <v>1381.50774193548</v>
+        <v>1.38150774193548</v>
       </c>
       <c r="S49">
-        <v>454.07963595573602</v>
+        <v>0.45407963595573603</v>
       </c>
       <c r="T49">
-        <v>8782.9540440881701</v>
+        <v>8.7829540440881697</v>
       </c>
       <c r="U49">
-        <v>2886.8173908081899</v>
+        <v>2.88681739080819</v>
       </c>
       <c r="V49">
-        <v>3373.5580645161199</v>
+        <v>3.3735580645161201</v>
       </c>
       <c r="W49">
-        <v>1108.8349137044199</v>
+        <v>1.10883491370442</v>
       </c>
       <c r="X49">
-        <v>3847.55604838709</v>
+        <v>3.8475560483870899</v>
       </c>
       <c r="Y49">
-        <v>1264.6305168896299</v>
+        <v>1.2646305168896299</v>
       </c>
       <c r="Z49" s="4"/>
       <c r="AA49" s="4"/>
@@ -6462,76 +6462,76 @@
         <v>0.48958333333333298</v>
       </c>
       <c r="B50">
-        <v>14619.9090791259</v>
+        <v>14.6199090791259</v>
       </c>
       <c r="C50">
-        <v>4805.33173346886</v>
+        <v>4.8053317334688597</v>
       </c>
       <c r="D50">
-        <v>23548.814456714899</v>
+        <v>23.548814456714901</v>
       </c>
       <c r="E50">
-        <v>7740.1210077284204</v>
+        <v>7.7401210077284199</v>
       </c>
       <c r="F50">
-        <v>3138.1702795106298</v>
+        <v>3.1381702795106299</v>
       </c>
       <c r="G50">
-        <v>1031.4666902198501</v>
+        <v>1.0314666902198499</v>
       </c>
       <c r="H50">
-        <v>9878.0340681362704</v>
+        <v>9.8780340681362695</v>
       </c>
       <c r="I50">
-        <v>3246.75278861169</v>
+        <v>3.24675278861169</v>
       </c>
       <c r="J50">
-        <v>4395.46973947895</v>
+        <v>4.3954697394789504</v>
       </c>
       <c r="K50">
-        <v>1444.72103816141</v>
+        <v>1.44472103816141</v>
       </c>
       <c r="L50">
-        <v>15811.2987474949</v>
+        <v>15.8112987474949</v>
       </c>
       <c r="M50">
-        <v>5196.9225805360702</v>
+        <v>5.1969225805360697</v>
       </c>
       <c r="N50">
-        <v>22254.078096192301</v>
+        <v>22.254078096192298</v>
       </c>
       <c r="O50">
-        <v>7314.5617456275304</v>
+        <v>7.3145617456275298</v>
       </c>
       <c r="P50">
-        <v>13085.865397461501</v>
+        <v>13.0858653974615</v>
       </c>
       <c r="Q50">
-        <v>4301.1159586557096</v>
+        <v>4.3011159586557097</v>
       </c>
       <c r="R50">
-        <v>1373.5155483870899</v>
+        <v>1.37351554838709</v>
       </c>
       <c r="S50">
-        <v>451.45272897086801</v>
+        <v>0.45145272897086802</v>
       </c>
       <c r="T50">
-        <v>9023.1610621242398</v>
+        <v>9.02316106212424</v>
       </c>
       <c r="U50">
-        <v>2965.7696195890599</v>
+        <v>2.9657696195890599</v>
       </c>
       <c r="V50">
-        <v>3354.0416129032201</v>
+        <v>3.3540416129032198</v>
       </c>
       <c r="W50">
-        <v>1102.4201662697601</v>
+        <v>1.1024201662697599</v>
       </c>
       <c r="X50">
-        <v>3825.2974596774102</v>
+        <v>3.8252974596774099</v>
       </c>
       <c r="Y50">
-        <v>1257.3144725770501</v>
+        <v>1.25731447257705</v>
       </c>
       <c r="Z50" s="4"/>
       <c r="AA50" s="4"/>
@@ -6586,76 +6586,76 @@
         <v>0.5</v>
       </c>
       <c r="B51">
-        <v>15061.654842588399</v>
+        <v>15.0616548425884</v>
       </c>
       <c r="C51">
-        <v>4950.5265444490597</v>
+        <v>4.95052654444906</v>
       </c>
       <c r="D51">
-        <v>24067.5127229139</v>
+        <v>24.0675127229139</v>
       </c>
       <c r="E51">
-        <v>7910.6088832118703</v>
+        <v>7.9106088832118697</v>
       </c>
       <c r="F51">
-        <v>3096.07547029542</v>
+        <v>3.0960754702954199</v>
       </c>
       <c r="G51">
-        <v>1017.63079552028</v>
+        <v>1.0176307955202799</v>
       </c>
       <c r="H51">
-        <v>10215.1683366733</v>
+        <v>10.215168336673299</v>
       </c>
       <c r="I51">
-        <v>3357.5634639909299</v>
+        <v>3.35756346399093</v>
       </c>
       <c r="J51">
-        <v>4545.4857715430799</v>
+        <v>4.5454857715430803</v>
       </c>
       <c r="K51">
-        <v>1494.0289234228901</v>
+        <v>1.4940289234228901</v>
       </c>
       <c r="L51">
-        <v>16350.933517034</v>
+        <v>16.350933517034001</v>
       </c>
       <c r="M51">
-        <v>5374.2919518854196</v>
+        <v>5.3742919518854197</v>
       </c>
       <c r="N51">
-        <v>23013.6029458917</v>
+        <v>23.013602945891702</v>
       </c>
       <c r="O51">
-        <v>7564.2054912120902</v>
+        <v>7.56420549121209</v>
       </c>
       <c r="P51">
-        <v>13532.481963927799</v>
+        <v>13.5324819639278</v>
       </c>
       <c r="Q51">
-        <v>4447.9117251627304</v>
+        <v>4.4479117251627303</v>
       </c>
       <c r="R51">
-        <v>1324.4206451612899</v>
+        <v>1.3244206451612901</v>
       </c>
       <c r="S51">
-        <v>435.31601463525101</v>
+        <v>0.43531601463525099</v>
       </c>
       <c r="T51">
-        <v>9331.1187775551098</v>
+        <v>9.3311187775551101</v>
       </c>
       <c r="U51">
-        <v>3066.9904257183798</v>
+        <v>3.0669904257183802</v>
       </c>
       <c r="V51">
-        <v>3234.15483870967</v>
+        <v>3.2341548387096699</v>
       </c>
       <c r="W51">
-        <v>1063.01528917118</v>
+        <v>1.0630152891711799</v>
       </c>
       <c r="X51">
-        <v>3688.56612903225</v>
+        <v>3.68856612903225</v>
       </c>
       <c r="Y51">
-        <v>1212.3730575140301</v>
+        <v>1.2123730575140299</v>
       </c>
       <c r="Z51" s="4"/>
       <c r="AA51" s="4"/>
@@ -6710,76 +6710,76 @@
         <v>0.51041666666666696</v>
       </c>
       <c r="B52">
-        <v>15503.8596494925</v>
+        <v>15.503859649492499</v>
       </c>
       <c r="C52">
-        <v>5095.8722357121296</v>
+        <v>5.0958722357121298</v>
       </c>
       <c r="D52">
-        <v>24503.5957309025</v>
+        <v>24.5035957309025</v>
       </c>
       <c r="E52">
-        <v>8053.9424364762999</v>
+        <v>8.0539424364762997</v>
       </c>
       <c r="F52">
-        <v>3007.4258880664502</v>
+        <v>3.0074258880664502</v>
       </c>
       <c r="G52">
-        <v>988.49308691087003</v>
+        <v>0.98849308691087001</v>
       </c>
       <c r="H52">
-        <v>10565.7879759519</v>
+        <v>10.565787975951899</v>
       </c>
       <c r="I52">
-        <v>3472.8065663853399</v>
+        <v>3.4728065663853398</v>
       </c>
       <c r="J52">
-        <v>4701.5024448897702</v>
+        <v>4.70150244488977</v>
       </c>
       <c r="K52">
-        <v>1545.3091240948299</v>
+        <v>1.54530912409483</v>
       </c>
       <c r="L52">
-        <v>16912.153677354701</v>
+        <v>16.912153677354699</v>
       </c>
       <c r="M52">
-        <v>5558.7560980887502</v>
+        <v>5.5587560980887503</v>
       </c>
       <c r="N52">
-        <v>23803.5087895791</v>
+        <v>23.803508789579102</v>
       </c>
       <c r="O52">
-        <v>7823.8349866200297</v>
+        <v>7.8238349866200299</v>
       </c>
       <c r="P52">
-        <v>13996.963193052699</v>
+        <v>13.9969631930527</v>
       </c>
       <c r="Q52">
-        <v>4600.5793223300298</v>
+        <v>4.60057932233003</v>
       </c>
       <c r="R52">
-        <v>1244.49870967741</v>
+        <v>1.2444987096774101</v>
       </c>
       <c r="S52">
-        <v>409.046944786572</v>
+        <v>0.409046944786572</v>
       </c>
       <c r="T52">
-        <v>9651.3948016032009</v>
+        <v>9.6513948016031996</v>
       </c>
       <c r="U52">
-        <v>3172.2600640928799</v>
+        <v>3.17226006409288</v>
       </c>
       <c r="V52">
-        <v>3038.9903225806402</v>
+        <v>3.0389903225806401</v>
       </c>
       <c r="W52">
-        <v>998.86781482464403</v>
+        <v>0.99886781482464404</v>
       </c>
       <c r="X52">
-        <v>3465.9802419354801</v>
+        <v>3.4659802419354802</v>
       </c>
       <c r="Y52">
-        <v>1139.2126143881801</v>
+        <v>1.13921261438818</v>
       </c>
       <c r="Z52" s="4"/>
       <c r="AA52" s="4"/>
@@ -6834,76 +6834,76 @@
         <v>0.52083333333333304</v>
       </c>
       <c r="B53">
-        <v>15825.530679617201</v>
+        <v>15.8255306796172</v>
       </c>
       <c r="C53">
-        <v>5201.6003904106501</v>
+        <v>5.2016003904106496</v>
       </c>
       <c r="D53">
-        <v>24743.172339916899</v>
+        <v>24.743172339916899</v>
       </c>
       <c r="E53">
-        <v>8132.6874598320001</v>
+        <v>8.1326874598320007</v>
       </c>
       <c r="F53">
-        <v>2891.03691972654</v>
+        <v>2.89103691972654</v>
       </c>
       <c r="G53">
-        <v>950.23788299937701</v>
+        <v>0.95023788299937695</v>
       </c>
       <c r="H53">
-        <v>10835.4953907815</v>
+        <v>10.835495390781499</v>
       </c>
       <c r="I53">
-        <v>3561.4551066887302</v>
+        <v>3.5614551066887299</v>
       </c>
       <c r="J53">
-        <v>4821.5152705410801</v>
+        <v>4.82151527054108</v>
       </c>
       <c r="K53">
-        <v>1584.7554323040099</v>
+        <v>1.5847554323040101</v>
       </c>
       <c r="L53">
-        <v>17343.8614929859</v>
+        <v>17.343861492985901</v>
       </c>
       <c r="M53">
-        <v>5700.6515951682304</v>
+        <v>5.7006515951682299</v>
       </c>
       <c r="N53">
-        <v>24411.128669338599</v>
+        <v>24.411128669338598</v>
       </c>
       <c r="O53">
-        <v>8023.5499830876697</v>
+        <v>8.0235499830876709</v>
       </c>
       <c r="P53">
-        <v>14354.2564462257</v>
+        <v>14.354256446225699</v>
       </c>
       <c r="Q53">
-        <v>4718.01593553565</v>
+        <v>4.7180159355356404</v>
       </c>
       <c r="R53">
-        <v>1152.01761290322</v>
+        <v>1.15201761290322</v>
       </c>
       <c r="S53">
-        <v>378.64987824738603</v>
+        <v>0.378649878247386</v>
       </c>
       <c r="T53">
-        <v>9897.7609739478903</v>
+        <v>9.8977609739478893</v>
       </c>
       <c r="U53">
-        <v>3253.23670899633</v>
+        <v>3.2532367089963299</v>
       </c>
       <c r="V53">
-        <v>2813.15709677419</v>
+        <v>2.8131570967741899</v>
       </c>
       <c r="W53">
-        <v>924.64002308079398</v>
+        <v>0.92464002308079396</v>
       </c>
       <c r="X53">
-        <v>3208.4165725806401</v>
+        <v>3.2084165725806399</v>
       </c>
       <c r="Y53">
-        <v>1054.5555301996999</v>
+        <v>1.0545555301997001</v>
       </c>
       <c r="Z53" s="4"/>
       <c r="AA53" s="4"/>
@@ -6958,76 +6958,76 @@
         <v>0.53125</v>
       </c>
       <c r="B54">
-        <v>15925.877543280099</v>
+        <v>15.9258775432801</v>
       </c>
       <c r="C54">
-        <v>5234.5828095011702</v>
+        <v>5.2345828095011697</v>
       </c>
       <c r="D54">
-        <v>24691.269083585201</v>
+        <v>24.691269083585201</v>
       </c>
       <c r="E54">
-        <v>8115.62768446875</v>
+        <v>8.11562768446875</v>
       </c>
       <c r="F54">
-        <v>2770.6430098099399</v>
+        <v>2.7706430098099402</v>
       </c>
       <c r="G54">
-        <v>910.666318449453</v>
+        <v>0.91066631844945301</v>
       </c>
       <c r="H54">
-        <v>10943.3783567134</v>
+        <v>10.943378356713399</v>
       </c>
       <c r="I54">
-        <v>3596.9145228100901</v>
+        <v>3.5969145228100898</v>
       </c>
       <c r="J54">
-        <v>4869.5204008015999</v>
+        <v>4.8695204008016004</v>
       </c>
       <c r="K54">
-        <v>1600.5339555876899</v>
+        <v>1.6005339555876901</v>
       </c>
       <c r="L54">
-        <v>17516.544619238401</v>
+        <v>17.516544619238399</v>
       </c>
       <c r="M54">
-        <v>5757.4097940000202</v>
+        <v>5.7574097940000204</v>
       </c>
       <c r="N54">
-        <v>24654.176621242401</v>
+        <v>24.654176621242399</v>
       </c>
       <c r="O54">
-        <v>8103.4359816747301</v>
+        <v>8.1034359816747301</v>
       </c>
       <c r="P54">
-        <v>14497.1737474949</v>
+        <v>14.4971737474949</v>
       </c>
       <c r="Q54">
-        <v>4764.9905808178901</v>
+        <v>4.7649905808178898</v>
       </c>
       <c r="R54">
-        <v>1067.52870967741</v>
+        <v>1.06752870967741</v>
       </c>
       <c r="S54">
-        <v>350.87971869306898</v>
+        <v>0.350879718693069</v>
       </c>
       <c r="T54">
-        <v>9996.3074428857708</v>
+        <v>9.9963074428857706</v>
       </c>
       <c r="U54">
-        <v>3285.6273669577199</v>
+        <v>3.2856273669577098</v>
       </c>
       <c r="V54">
-        <v>2606.8403225806401</v>
+        <v>2.60684032258064</v>
       </c>
       <c r="W54">
-        <v>856.82697877159796</v>
+        <v>0.85682697877159797</v>
       </c>
       <c r="X54">
-        <v>2973.11149193548</v>
+        <v>2.9731114919354802</v>
       </c>
       <c r="Y54">
-        <v>977.21449032380895</v>
+        <v>0.97721449032380903</v>
       </c>
       <c r="Z54" s="4"/>
       <c r="AA54" s="4"/>
@@ -7082,76 +7082,76 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="B55">
-        <v>15718.185023272301</v>
+        <v>15.7181850232723</v>
       </c>
       <c r="C55">
-        <v>5166.3175794100798</v>
+        <v>5.1663175794100802</v>
       </c>
       <c r="D55">
-        <v>24268.747001119598</v>
+        <v>24.2687470011196</v>
       </c>
       <c r="E55">
-        <v>7976.7513918752302</v>
+        <v>7.9767513918752302</v>
       </c>
       <c r="F55">
-        <v>2658.9230233854801</v>
+        <v>2.6589230233854799</v>
       </c>
       <c r="G55">
-        <v>873.94573468093404</v>
+        <v>0.87394573468093395</v>
       </c>
       <c r="H55">
-        <v>10822.010020039999</v>
+        <v>10.82201002004</v>
       </c>
       <c r="I55">
-        <v>3557.0226796735601</v>
+        <v>3.55702267967356</v>
       </c>
       <c r="J55">
-        <v>4815.5146292585096</v>
+        <v>4.8155146292585096</v>
       </c>
       <c r="K55">
-        <v>1582.78311689356</v>
+        <v>1.58278311689356</v>
       </c>
       <c r="L55">
-        <v>17322.2761022044</v>
+        <v>17.322276102204398</v>
       </c>
       <c r="M55">
-        <v>5693.5568203142602</v>
+        <v>5.6935568203142601</v>
       </c>
       <c r="N55">
-        <v>24380.7476753507</v>
+        <v>24.380747675350701</v>
       </c>
       <c r="O55">
-        <v>8013.5642332642901</v>
+        <v>8.0135642332642902</v>
       </c>
       <c r="P55">
-        <v>14336.3917835671</v>
+        <v>14.3363917835671</v>
       </c>
       <c r="Q55">
-        <v>4712.1441048753704</v>
+        <v>4.7121441048753701</v>
       </c>
       <c r="R55">
-        <v>1003.59116129032</v>
+        <v>1.0035911612903201</v>
       </c>
       <c r="S55">
-        <v>329.86446281412498</v>
+        <v>0.32986446281412501</v>
       </c>
       <c r="T55">
-        <v>9885.44266533066</v>
+        <v>9.8854426653306593</v>
       </c>
       <c r="U55">
-        <v>3249.1878767511598</v>
+        <v>3.2491878767511602</v>
       </c>
       <c r="V55">
-        <v>2450.7087096774098</v>
+        <v>2.4507087096774098</v>
       </c>
       <c r="W55">
-        <v>805.50899929436798</v>
+        <v>0.80550899929436903</v>
       </c>
       <c r="X55">
-        <v>2795.04278225806</v>
+        <v>2.7950427822580601</v>
       </c>
       <c r="Y55">
-        <v>918.68613582313196</v>
+        <v>0.91868613582313197</v>
       </c>
       <c r="Z55" s="4"/>
       <c r="AA55" s="4"/>
@@ -7206,76 +7206,76 @@
         <v>0.55208333333333304</v>
       </c>
       <c r="B56">
-        <v>15278.497196586701</v>
+        <v>15.2784971965867</v>
       </c>
       <c r="C56">
-        <v>5021.7991795378703</v>
+        <v>5.0217991795378696</v>
       </c>
       <c r="D56">
-        <v>23569.876504331201</v>
+        <v>23.569876504331202</v>
       </c>
       <c r="E56">
-        <v>7747.0437680024097</v>
+        <v>7.7470437680024098</v>
       </c>
       <c r="F56">
-        <v>2563.1284732367899</v>
+        <v>2.5631284732367901</v>
       </c>
       <c r="G56">
-        <v>842.45958868430102</v>
+        <v>0.84245958868430104</v>
       </c>
       <c r="H56">
-        <v>10525.331863727401</v>
+        <v>10.5253318637274</v>
       </c>
       <c r="I56">
-        <v>3459.5092853398301</v>
+        <v>3.4595092853398302</v>
       </c>
       <c r="J56">
-        <v>4683.5005210420804</v>
+        <v>4.6835005210420801</v>
       </c>
       <c r="K56">
-        <v>1539.3921778634499</v>
+        <v>1.5393921778634501</v>
       </c>
       <c r="L56">
-        <v>16847.397505010002</v>
+        <v>16.847397505010001</v>
       </c>
       <c r="M56">
-        <v>5537.4717735268296</v>
+        <v>5.5374717735268204</v>
       </c>
       <c r="N56">
-        <v>23712.365807615199</v>
+        <v>23.7123658076152</v>
       </c>
       <c r="O56">
-        <v>7793.87773714988</v>
+        <v>7.79387773714988</v>
       </c>
       <c r="P56">
-        <v>13943.3692050768</v>
+        <v>13.943369205076801</v>
       </c>
       <c r="Q56">
-        <v>4582.9638303491902</v>
+        <v>4.5829638303491897</v>
       </c>
       <c r="R56">
-        <v>961.34670967741897</v>
+        <v>0.96134670967741898</v>
       </c>
       <c r="S56">
-        <v>315.97938303696702</v>
+        <v>0.31597938303696699</v>
       </c>
       <c r="T56">
-        <v>9614.4398757514991</v>
+        <v>9.6144398757515006</v>
       </c>
       <c r="U56">
-        <v>3160.1135673573599</v>
+        <v>3.1601135673573602</v>
       </c>
       <c r="V56">
-        <v>2347.5503225806401</v>
+        <v>2.34755032258064</v>
       </c>
       <c r="W56">
-        <v>771.60247713977003</v>
+        <v>0.77160247713977004</v>
       </c>
       <c r="X56">
-        <v>2677.3902419354799</v>
+        <v>2.67739024193548</v>
       </c>
       <c r="Y56">
-        <v>880.01561588518405</v>
+        <v>0.88001561588518395</v>
       </c>
       <c r="Z56" s="4"/>
       <c r="AA56" s="4"/>
@@ -7330,76 +7330,76 @@
         <v>0.5625</v>
       </c>
       <c r="B57">
-        <v>14709.076947313901</v>
+        <v>14.7090769473139</v>
       </c>
       <c r="C57">
-        <v>4834.6397944349401</v>
+        <v>4.8346397944349402</v>
       </c>
       <c r="D57">
-        <v>22712.970201661999</v>
+        <v>22.712970201661999</v>
       </c>
       <c r="E57">
-        <v>7465.39228668745</v>
+        <v>7.4653922866874503</v>
       </c>
       <c r="F57">
-        <v>2487.23970053009</v>
+        <v>2.4872397005300901</v>
       </c>
       <c r="G57">
-        <v>817.51615533407596</v>
+        <v>0.81751615533407596</v>
       </c>
       <c r="H57">
-        <v>10127.5134268537</v>
+        <v>10.127513426853699</v>
       </c>
       <c r="I57">
-        <v>3328.7526883923301</v>
+        <v>3.32875268839233</v>
       </c>
       <c r="J57">
-        <v>4506.48160320641</v>
+        <v>4.5064816032064101</v>
       </c>
       <c r="K57">
-        <v>1481.2088732549</v>
+        <v>1.4812088732549</v>
       </c>
       <c r="L57">
-        <v>16210.6284769539</v>
+        <v>16.2106284769539</v>
       </c>
       <c r="M57">
-        <v>5328.1759153345902</v>
+        <v>5.3281759153345902</v>
       </c>
       <c r="N57">
-        <v>22816.1264849699</v>
+        <v>22.816126484969899</v>
       </c>
       <c r="O57">
-        <v>7499.2981173601002</v>
+        <v>7.4992981173600999</v>
       </c>
       <c r="P57">
-        <v>13416.361656646601</v>
+        <v>13.4163616566466</v>
       </c>
       <c r="Q57">
-        <v>4409.7448258709001</v>
+        <v>4.4097448258709004</v>
       </c>
       <c r="R57">
-        <v>938.51187096774197</v>
+        <v>0.93851187096774202</v>
       </c>
       <c r="S57">
-        <v>308.47393450877303</v>
+        <v>0.30847393450877297</v>
       </c>
       <c r="T57">
-        <v>9251.0497715430793</v>
+        <v>9.2510497715430802</v>
       </c>
       <c r="U57">
-        <v>3040.6730161247601</v>
+        <v>3.0406730161247602</v>
       </c>
       <c r="V57">
-        <v>2291.7890322580602</v>
+        <v>2.2917890322580599</v>
       </c>
       <c r="W57">
-        <v>753.27462732647405</v>
+        <v>0.75327462732647399</v>
       </c>
       <c r="X57">
-        <v>2613.7942741935399</v>
+        <v>2.6137942741935398</v>
       </c>
       <c r="Y57">
-        <v>859.11263213494203</v>
+        <v>0.85911263213494204</v>
       </c>
       <c r="Z57" s="4"/>
       <c r="AA57" s="4"/>
@@ -7454,76 +7454,76 @@
         <v>0.57291666666666696</v>
       </c>
       <c r="B58">
-        <v>14122.288374814099</v>
+        <v>14.122288374814101</v>
       </c>
       <c r="C58">
-        <v>4641.77171755364</v>
+        <v>4.6417717175536399</v>
       </c>
       <c r="D58">
-        <v>21824.8388308555</v>
+        <v>21.824838830855501</v>
       </c>
       <c r="E58">
-        <v>7173.4776217926501</v>
+        <v>7.1734776217926504</v>
       </c>
       <c r="F58">
-        <v>2437.6965752472602</v>
+        <v>2.4376965752472599</v>
       </c>
       <c r="G58">
-        <v>801.23211753272699</v>
+        <v>0.80123211753272705</v>
       </c>
       <c r="H58">
-        <v>9709.4669338677304</v>
+        <v>9.7094669338677306</v>
       </c>
       <c r="I58">
-        <v>3191.34745092207</v>
+        <v>3.1913474509220698</v>
       </c>
       <c r="J58">
-        <v>4320.4617234468897</v>
+        <v>4.3204617234468898</v>
       </c>
       <c r="K58">
-        <v>1420.06709553067</v>
+        <v>1.42006709553067</v>
       </c>
       <c r="L58">
-        <v>15541.481362725401</v>
+        <v>15.541481362725399</v>
       </c>
       <c r="M58">
-        <v>5108.2378948613896</v>
+        <v>5.1082378948613902</v>
       </c>
       <c r="N58">
-        <v>21874.3156713426</v>
+        <v>21.8743156713426</v>
       </c>
       <c r="O58">
-        <v>7189.73987283525</v>
+        <v>7.1897398728352497</v>
       </c>
       <c r="P58">
-        <v>12862.557114228401</v>
+        <v>12.8625571142284</v>
       </c>
       <c r="Q58">
-        <v>4227.7180754022002</v>
+        <v>4.2277180754022003</v>
       </c>
       <c r="R58">
-        <v>933.944903225806</v>
+        <v>0.93394490322580603</v>
       </c>
       <c r="S58">
-        <v>306.97284480313402</v>
+        <v>0.30697284480313403</v>
       </c>
       <c r="T58">
-        <v>8869.1822044088094</v>
+        <v>8.8691822044088102</v>
       </c>
       <c r="U58">
-        <v>2915.1592165244001</v>
+        <v>2.9151592165243998</v>
       </c>
       <c r="V58">
-        <v>2280.6367741935401</v>
+        <v>2.2806367741935398</v>
       </c>
       <c r="W58">
-        <v>749.60905736381505</v>
+        <v>0.749609057363815</v>
       </c>
       <c r="X58">
-        <v>2601.0750806451601</v>
+        <v>2.6010750806451601</v>
       </c>
       <c r="Y58">
-        <v>854.93203538489399</v>
+        <v>0.85493203538489404</v>
       </c>
       <c r="Z58" s="4"/>
       <c r="AA58" s="4"/>
@@ -7578,76 +7578,76 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="B59">
-        <v>13599.511126187799</v>
+        <v>13.599511126187799</v>
       </c>
       <c r="C59">
-        <v>4469.9431453810503</v>
+        <v>4.4699431453810501</v>
       </c>
       <c r="D59">
-        <v>21012.384202856399</v>
+        <v>21.012384202856399</v>
       </c>
       <c r="E59">
-        <v>6906.4366993903604</v>
+        <v>6.9064366993903601</v>
       </c>
       <c r="F59">
-        <v>2411.78542124571</v>
+        <v>2.4117854212457099</v>
       </c>
       <c r="G59">
-        <v>792.71553306557598</v>
+        <v>0.79271553306557596</v>
       </c>
       <c r="H59">
-        <v>9331.8765531062108</v>
+        <v>9.3318765531062091</v>
       </c>
       <c r="I59">
-        <v>3067.2394944973198</v>
+        <v>3.0672394944973198</v>
       </c>
       <c r="J59">
-        <v>4152.44376753507</v>
+        <v>4.1524437675350701</v>
       </c>
       <c r="K59">
-        <v>1364.8422640378101</v>
+        <v>1.3648422640378099</v>
       </c>
       <c r="L59">
-        <v>14937.0904208416</v>
+        <v>14.937090420841599</v>
       </c>
       <c r="M59">
-        <v>4909.5841989501096</v>
+        <v>4.9095841989501103</v>
       </c>
       <c r="N59">
-        <v>21023.647839679299</v>
+        <v>21.023647839679299</v>
       </c>
       <c r="O59">
-        <v>6910.1388777805496</v>
+        <v>6.9101388777805504</v>
       </c>
       <c r="P59">
-        <v>12362.3465597862</v>
+        <v>12.3623465597862</v>
       </c>
       <c r="Q59">
-        <v>4063.3068169143298</v>
+        <v>4.0633068169143298</v>
       </c>
       <c r="R59">
-        <v>941.93709677419304</v>
+        <v>0.94193709677419302</v>
       </c>
       <c r="S59">
-        <v>309.59975178800198</v>
+        <v>0.30959975178800198</v>
       </c>
       <c r="T59">
-        <v>8524.2695631262504</v>
+        <v>8.5242695631262499</v>
       </c>
       <c r="U59">
-        <v>2801.7919136595701</v>
+        <v>2.8017919136595699</v>
       </c>
       <c r="V59">
-        <v>2300.1532258064499</v>
+        <v>2.3001532258064499</v>
       </c>
       <c r="W59">
-        <v>756.02380479846897</v>
+        <v>0.75602380479846898</v>
       </c>
       <c r="X59">
-        <v>2623.3336693548299</v>
+        <v>2.6233336693548299</v>
       </c>
       <c r="Y59">
-        <v>862.24807969747803</v>
+        <v>0.86224807969747796</v>
       </c>
       <c r="Z59" s="4"/>
       <c r="AA59" s="4"/>
@@ -7702,76 +7702,76 @@
         <v>0.59375</v>
       </c>
       <c r="B60">
-        <v>13156.862793263899</v>
+        <v>13.156862793263899</v>
       </c>
       <c r="C60">
-        <v>4324.4516741650305</v>
+        <v>4.3244516741650303</v>
       </c>
       <c r="D60">
-        <v>20313.525796549598</v>
+        <v>20.313525796549602</v>
       </c>
       <c r="E60">
-        <v>6676.7330494666703</v>
+        <v>6.6767330494666703</v>
       </c>
       <c r="F60">
-        <v>2403.7755380923099</v>
+        <v>2.4037755380923098</v>
       </c>
       <c r="G60">
-        <v>790.08281178871198</v>
+        <v>0.79008281178871198</v>
       </c>
       <c r="H60">
-        <v>9008.2276553106203</v>
+        <v>9.0082276553106198</v>
       </c>
       <c r="I60">
-        <v>2960.86124613326</v>
+        <v>2.96086124613326</v>
       </c>
       <c r="J60">
-        <v>4008.4283767534998</v>
+        <v>4.0084283767534998</v>
       </c>
       <c r="K60">
-        <v>1317.5066941867799</v>
+        <v>1.3175066941867799</v>
       </c>
       <c r="L60">
-        <v>14419.0410420841</v>
+        <v>14.4190410420841</v>
       </c>
       <c r="M60">
-        <v>4739.3096024547303</v>
+        <v>4.7393096024547301</v>
       </c>
       <c r="N60">
-        <v>20294.503983967901</v>
+        <v>20.2945039839679</v>
       </c>
       <c r="O60">
-        <v>6670.4808820193703</v>
+        <v>6.67048088201937</v>
       </c>
       <c r="P60">
-        <v>11933.594655978601</v>
+        <v>11.933594655978601</v>
       </c>
       <c r="Q60">
-        <v>3922.38288106759</v>
+        <v>3.9223828810675898</v>
       </c>
       <c r="R60">
-        <v>957.92148387096802</v>
+        <v>0.95792148387096798</v>
       </c>
       <c r="S60">
-        <v>314.85356575773699</v>
+        <v>0.31485356575773699</v>
       </c>
       <c r="T60">
-        <v>8228.6301563126199</v>
+        <v>8.2286301563126205</v>
       </c>
       <c r="U60">
-        <v>2704.6199397754199</v>
+        <v>2.7046199397754198</v>
       </c>
       <c r="V60">
-        <v>2339.1861290322499</v>
+        <v>2.33918612903225</v>
       </c>
       <c r="W60">
-        <v>768.85329966777601</v>
+        <v>0.76885329966777605</v>
       </c>
       <c r="X60">
-        <v>2667.8508467741899</v>
+        <v>2.6678508467741899</v>
       </c>
       <c r="Y60">
-        <v>876.88016832264805</v>
+        <v>0.87688016832264803</v>
       </c>
       <c r="Z60" s="4"/>
       <c r="AA60" s="4"/>
@@ -7826,76 +7826,76 @@
         <v>0.60416666666666696</v>
       </c>
       <c r="B61">
-        <v>12772.098526149</v>
+        <v>12.772098526149</v>
       </c>
       <c r="C61">
-        <v>4197.9857753235801</v>
+        <v>4.1979857753235796</v>
       </c>
       <c r="D61">
-        <v>19719.935983244999</v>
+        <v>19.719935983245001</v>
       </c>
       <c r="E61">
-        <v>6481.6295128373704</v>
+        <v>6.4816295128373698</v>
       </c>
       <c r="F61">
-        <v>2403.4229891233999</v>
+        <v>2.4034229891234</v>
       </c>
       <c r="G61">
-        <v>789.96693454633498</v>
+        <v>0.78996693454633504</v>
       </c>
       <c r="H61">
-        <v>8725.0348697394802</v>
+        <v>8.7250348697394795</v>
       </c>
       <c r="I61">
-        <v>2867.7802788147001</v>
+        <v>2.8677802788146902</v>
       </c>
       <c r="J61">
-        <v>3882.4149098196399</v>
+        <v>3.8824149098196399</v>
       </c>
       <c r="K61">
-        <v>1276.08807056714</v>
+        <v>1.27608807056714</v>
       </c>
       <c r="L61">
-        <v>13965.7478356713</v>
+        <v>13.9657478356713</v>
       </c>
       <c r="M61">
-        <v>4590.3193305212799</v>
+        <v>4.5903193305212797</v>
       </c>
       <c r="N61">
-        <v>19656.503110220401</v>
+        <v>19.656503110220399</v>
       </c>
       <c r="O61">
-        <v>6460.7801357283397</v>
+        <v>6.4607801357283403</v>
       </c>
       <c r="P61">
-        <v>11558.436740146901</v>
+        <v>11.558436740146901</v>
       </c>
       <c r="Q61">
-        <v>3799.0744372016902</v>
+        <v>3.7990744372016998</v>
       </c>
       <c r="R61">
-        <v>976.18935483870905</v>
+        <v>0.97618935483870894</v>
       </c>
       <c r="S61">
-        <v>320.857924580293</v>
+        <v>0.320857924580293</v>
       </c>
       <c r="T61">
-        <v>7969.9456753507002</v>
+        <v>7.9699456753506999</v>
       </c>
       <c r="U61">
-        <v>2619.5944626267901</v>
+        <v>2.61959446262679</v>
       </c>
       <c r="V61">
-        <v>2383.7951612903198</v>
+        <v>2.3837951612903199</v>
       </c>
       <c r="W61">
-        <v>783.51557951841301</v>
+        <v>0.783515579518413</v>
       </c>
       <c r="X61">
-        <v>2718.7276209677402</v>
+        <v>2.7187276209677398</v>
       </c>
       <c r="Y61">
-        <v>893.602555322841</v>
+        <v>0.89360255532284105</v>
       </c>
       <c r="Z61" s="4"/>
       <c r="AA61" s="4"/>
@@ -7950,76 +7950,76 @@
         <v>0.61458333333333304</v>
       </c>
       <c r="B62">
-        <v>12430.351464412601</v>
+        <v>12.430351464412601</v>
       </c>
       <c r="C62">
-        <v>4085.6589481392498</v>
+        <v>4.0856589481392502</v>
       </c>
       <c r="D62">
-        <v>19240.7778988551</v>
+        <v>19.2407778988551</v>
       </c>
       <c r="E62">
-        <v>6324.1378666304299</v>
+        <v>6.32413786663043</v>
       </c>
       <c r="F62">
-        <v>2395.8435277813601</v>
+        <v>2.3958435277813601</v>
       </c>
       <c r="G62">
-        <v>787.47568607739004</v>
+        <v>0.78747568607739005</v>
       </c>
       <c r="H62">
-        <v>8475.5555110220394</v>
+        <v>8.4755555110220406</v>
       </c>
       <c r="I62">
-        <v>2785.7803790340599</v>
+        <v>2.7857803790340601</v>
       </c>
       <c r="J62">
-        <v>3771.4030460921799</v>
+        <v>3.7714030460921801</v>
       </c>
       <c r="K62">
-        <v>1239.6002354736399</v>
+        <v>1.23960023547364</v>
       </c>
       <c r="L62">
-        <v>13566.418106212401</v>
+        <v>13.566418106212399</v>
       </c>
       <c r="M62">
-        <v>4459.0659957227499</v>
+        <v>4.4590659957227503</v>
       </c>
       <c r="N62">
-        <v>19094.454721442798</v>
+        <v>19.094454721442801</v>
       </c>
       <c r="O62">
-        <v>6276.04376399577</v>
+        <v>6.2760437639957702</v>
       </c>
       <c r="P62">
-        <v>11227.940480961901</v>
+        <v>11.2279404809619</v>
       </c>
       <c r="Q62">
-        <v>3690.4455699864998</v>
+        <v>3.6904455699865002</v>
       </c>
       <c r="R62">
-        <v>987.60677419354795</v>
+        <v>0.98760677419354803</v>
       </c>
       <c r="S62">
-        <v>324.61064884439003</v>
+        <v>0.32461064884439</v>
       </c>
       <c r="T62">
-        <v>7742.0569659318598</v>
+        <v>7.7420569659318597</v>
       </c>
       <c r="U62">
-        <v>2544.6910660910899</v>
+        <v>2.5446910660910902</v>
       </c>
       <c r="V62">
-        <v>2411.6758064516098</v>
+        <v>2.4116758064516102</v>
       </c>
       <c r="W62">
-        <v>792.67950442506105</v>
+        <v>0.79267950442506097</v>
       </c>
       <c r="X62">
-        <v>2750.5256048387</v>
+        <v>2.7505256048387001</v>
       </c>
       <c r="Y62">
-        <v>904.05404719796195</v>
+        <v>0.90405404719796201</v>
       </c>
       <c r="Z62" s="4"/>
       <c r="AA62" s="4"/>
@@ -8074,76 +8074,76 @@
         <v>0.625</v>
       </c>
       <c r="B63">
-        <v>12119.477973430699</v>
+        <v>12.119477973430699</v>
       </c>
       <c r="C63">
-        <v>3983.4797729320198</v>
+        <v>3.9834797729320202</v>
       </c>
       <c r="D63">
-        <v>18877.998240652501</v>
+        <v>18.877998240652499</v>
       </c>
       <c r="E63">
-        <v>6204.89795929704</v>
+        <v>6.2048979592970399</v>
       </c>
       <c r="F63">
-        <v>2373.2527462182402</v>
+        <v>2.37325274621824</v>
       </c>
       <c r="G63">
-        <v>780.05045525402204</v>
+        <v>0.78005045525402195</v>
       </c>
       <c r="H63">
-        <v>8253.0468937875703</v>
+        <v>8.2530468937875696</v>
       </c>
       <c r="I63">
-        <v>2712.64533328376</v>
+        <v>2.7126453332837599</v>
       </c>
       <c r="J63">
-        <v>3672.3924649298601</v>
+        <v>3.6723924649298598</v>
       </c>
       <c r="K63">
-        <v>1207.05703120107</v>
+        <v>1.20705703120107</v>
       </c>
       <c r="L63">
-        <v>13210.259158316599</v>
+        <v>13.2102591583166</v>
       </c>
       <c r="M63">
-        <v>4342.0022106321803</v>
+        <v>4.3420022106321801</v>
       </c>
       <c r="N63">
-        <v>18593.168320641202</v>
+        <v>18.593168320641201</v>
       </c>
       <c r="O63">
-        <v>6111.2788919099603</v>
+        <v>6.1112788919099597</v>
       </c>
       <c r="P63">
-        <v>10933.1735470941</v>
+        <v>10.9331735470941</v>
       </c>
       <c r="Q63">
-        <v>3593.5603640918698</v>
+        <v>3.5935603640918701</v>
       </c>
       <c r="R63">
-        <v>987.60677419354795</v>
+        <v>0.98760677419354803</v>
       </c>
       <c r="S63">
-        <v>324.61064884439003</v>
+        <v>0.32461064884439</v>
       </c>
       <c r="T63">
-        <v>7538.8048737474901</v>
+        <v>7.5388048737474902</v>
       </c>
       <c r="U63">
-        <v>2477.8853340457399</v>
+        <v>2.4778853340457401</v>
       </c>
       <c r="V63">
-        <v>2411.6758064516098</v>
+        <v>2.4116758064516102</v>
       </c>
       <c r="W63">
-        <v>792.67950442506105</v>
+        <v>0.79267950442506097</v>
       </c>
       <c r="X63">
-        <v>2750.5256048387</v>
+        <v>2.7505256048387001</v>
       </c>
       <c r="Y63">
-        <v>904.05404719796195</v>
+        <v>0.90405404719796201</v>
       </c>
       <c r="Z63" s="4"/>
       <c r="AA63" s="4"/>
@@ -8198,76 +8198,76 @@
         <v>0.63541666666666696</v>
       </c>
       <c r="B64">
-        <v>11851.621687827201</v>
+        <v>11.851621687827199</v>
       </c>
       <c r="C64">
-        <v>3895.4396693819099</v>
+        <v>3.89543966938191</v>
       </c>
       <c r="D64">
-        <v>18617.1052827409</v>
+        <v>18.617105282740901</v>
       </c>
       <c r="E64">
-        <v>6119.1465908784003</v>
+        <v>6.1191465908784002</v>
       </c>
       <c r="F64">
-        <v>2343.43505228198</v>
+        <v>2.34343505228198</v>
       </c>
       <c r="G64">
-        <v>770.24985320408598</v>
+        <v>0.77024985320408601</v>
       </c>
       <c r="H64">
-        <v>8064.2517034068096</v>
+        <v>8.0642517034068106</v>
       </c>
       <c r="I64">
-        <v>2650.5913550713899</v>
+        <v>2.65059135507139</v>
       </c>
       <c r="J64">
-        <v>3588.3834869739399</v>
+        <v>3.5883834869739402</v>
       </c>
       <c r="K64">
-        <v>1179.4446154546399</v>
+        <v>1.1794446154546401</v>
       </c>
       <c r="L64">
-        <v>12908.063687374701</v>
+        <v>12.9080636873747</v>
       </c>
       <c r="M64">
-        <v>4242.6753626765403</v>
+        <v>4.2426753626765397</v>
       </c>
       <c r="N64">
-        <v>18167.834404809601</v>
+        <v>18.1678344048096</v>
       </c>
       <c r="O64">
-        <v>5971.4783943826096</v>
+        <v>5.9714783943826104</v>
       </c>
       <c r="P64">
-        <v>10683.068269873</v>
+        <v>10.683068269873001</v>
       </c>
       <c r="Q64">
-        <v>3511.3547348479301</v>
+        <v>3.5113547348479299</v>
       </c>
       <c r="R64">
-        <v>980.75632258064502</v>
+        <v>0.98075632258064505</v>
       </c>
       <c r="S64">
-        <v>322.35901428593098</v>
+        <v>0.322359014285931</v>
       </c>
       <c r="T64">
-        <v>7366.3485531062097</v>
+        <v>7.3663485531062101</v>
       </c>
       <c r="U64">
-        <v>2421.2016826133199</v>
+        <v>2.42120168261332</v>
       </c>
       <c r="V64">
-        <v>2394.9474193548299</v>
+        <v>2.3949474193548301</v>
       </c>
       <c r="W64">
-        <v>787.181149481072</v>
+        <v>0.78718114948107198</v>
       </c>
       <c r="X64">
-        <v>2731.44681451612</v>
+        <v>2.7314468145161199</v>
       </c>
       <c r="Y64">
-        <v>897.78315207288995</v>
+        <v>0.89778315207288995</v>
       </c>
       <c r="Z64" s="4"/>
       <c r="AA64" s="4"/>
@@ -8322,76 +8322,76 @@
         <v>0.64583333333333304</v>
       </c>
       <c r="B65">
-        <v>11638.245435774699</v>
+        <v>11.638245435774699</v>
       </c>
       <c r="C65">
-        <v>3825.3062869096202</v>
+        <v>3.8253062869096199</v>
       </c>
       <c r="D65">
-        <v>18445.383495885198</v>
+        <v>18.445383495885199</v>
       </c>
       <c r="E65">
-        <v>6062.7043690259998</v>
+        <v>6.0627043690260001</v>
       </c>
       <c r="F65">
-        <v>2312.39989414312</v>
+        <v>2.3123998941431201</v>
       </c>
       <c r="G65">
-        <v>760.04909002213003</v>
+        <v>0.76004909002212995</v>
       </c>
       <c r="H65">
-        <v>7915.9126252505002</v>
+        <v>7.9159126252504999</v>
       </c>
       <c r="I65">
-        <v>2601.8346579045201</v>
+        <v>2.60183465790452</v>
       </c>
       <c r="J65">
-        <v>3522.3764328657298</v>
+        <v>3.5223764328657299</v>
       </c>
       <c r="K65">
-        <v>1157.7491459395801</v>
+        <v>1.1577491459395799</v>
       </c>
       <c r="L65">
-        <v>12670.6243887775</v>
+        <v>12.670624388777499</v>
       </c>
       <c r="M65">
-        <v>4164.63283928283</v>
+        <v>4.16463283928283</v>
       </c>
       <c r="N65">
-        <v>17833.643470941799</v>
+        <v>17.833643470941801</v>
       </c>
       <c r="O65">
-        <v>5861.6351463253995</v>
+        <v>5.8616351463254004</v>
       </c>
       <c r="P65">
-        <v>10486.5569806279</v>
+        <v>10.486556980627901</v>
       </c>
       <c r="Q65">
-        <v>3446.76459758484</v>
+        <v>3.4467645975848402</v>
       </c>
       <c r="R65">
-        <v>970.48064516129</v>
+        <v>0.97048064516128996</v>
       </c>
       <c r="S65">
-        <v>318.98156244824401</v>
+        <v>0.31898156244824399</v>
       </c>
       <c r="T65">
-        <v>7230.8471583166302</v>
+        <v>7.2308471583166298</v>
       </c>
       <c r="U65">
-        <v>2376.66452791642</v>
+        <v>2.3766645279164198</v>
       </c>
       <c r="V65">
-        <v>2369.8548387096698</v>
+        <v>2.3698548387096698</v>
       </c>
       <c r="W65">
-        <v>778.93361706508904</v>
+        <v>0.77893361706508901</v>
       </c>
       <c r="X65">
-        <v>2702.8286290322499</v>
+        <v>2.7028286290322501</v>
       </c>
       <c r="Y65">
-        <v>888.37680938528104</v>
+        <v>0.88837680938528096</v>
       </c>
       <c r="Z65" s="4"/>
       <c r="AA65" s="4"/>
@@ -8446,76 +8446,76 @@
         <v>0.65625</v>
       </c>
       <c r="B66">
-        <v>11471.9712278104</v>
+        <v>11.4719712278104</v>
       </c>
       <c r="C66">
-        <v>3770.6545976505399</v>
+        <v>3.7706545976505401</v>
       </c>
       <c r="D66">
-        <v>18318.218990452799</v>
+        <v>18.318218990452799</v>
       </c>
       <c r="E66">
-        <v>6020.9074173474401</v>
+        <v>6.0209074173474404</v>
       </c>
       <c r="F66">
-        <v>2284.7875816956398</v>
+        <v>2.2847875816956398</v>
       </c>
       <c r="G66">
-        <v>750.97336181341302</v>
+        <v>0.75097336181341301</v>
       </c>
       <c r="H66">
-        <v>7801.2869739478901</v>
+        <v>7.8012869739478896</v>
       </c>
       <c r="I66">
-        <v>2564.1590282755801</v>
+        <v>2.5641590282755802</v>
       </c>
       <c r="J66">
-        <v>3471.3709819639198</v>
+        <v>3.4713709819639198</v>
       </c>
       <c r="K66">
-        <v>1140.9844649506799</v>
+        <v>1.14098446495068</v>
       </c>
       <c r="L66">
-        <v>12487.1485671342</v>
+        <v>12.4871485671342</v>
       </c>
       <c r="M66">
-        <v>4104.3272530240502</v>
+        <v>4.1043272530240502</v>
       </c>
       <c r="N66">
-        <v>17575.405022044</v>
+        <v>17.575405022043999</v>
       </c>
       <c r="O66">
-        <v>5776.7562728266503</v>
+        <v>5.7767562728266499</v>
       </c>
       <c r="P66">
-        <v>10334.7073480293</v>
+        <v>10.334707348029299</v>
       </c>
       <c r="Q66">
-        <v>3396.8540369724601</v>
+        <v>3.39685403697246</v>
       </c>
       <c r="R66">
-        <v>960.20496774193498</v>
+        <v>0.96020496774193498</v>
       </c>
       <c r="S66">
-        <v>315.60411061055697</v>
+        <v>0.31560411061055699</v>
       </c>
       <c r="T66">
-        <v>7126.14153507014</v>
+        <v>7.1261415350701398</v>
       </c>
       <c r="U66">
-        <v>2342.2494538324499</v>
+        <v>2.3422494538324501</v>
       </c>
       <c r="V66">
-        <v>2344.7622580645102</v>
+        <v>2.34476225806451</v>
       </c>
       <c r="W66">
-        <v>770.68608464910596</v>
+        <v>0.77068608464910604</v>
       </c>
       <c r="X66">
-        <v>2674.2104435483802</v>
+        <v>2.6742104435483798</v>
       </c>
       <c r="Y66">
-        <v>878.97046669767201</v>
+        <v>0.87897046669767198</v>
       </c>
       <c r="Z66" s="4"/>
       <c r="AA66" s="4"/>
@@ -8570,76 +8570,76 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="B67">
-        <v>11365.62350501</v>
+        <v>11.365623505009999</v>
       </c>
       <c r="C67">
-        <v>3735.6997915440702</v>
+        <v>3.7356997915440702</v>
       </c>
       <c r="D67">
-        <v>18222.896237208701</v>
+        <v>18.222896237208701</v>
       </c>
       <c r="E67">
-        <v>5989.5763434942201</v>
+        <v>5.9895763434942202</v>
       </c>
       <c r="F67">
-        <v>2270.1574824649201</v>
+        <v>2.2701574824649202</v>
       </c>
       <c r="G67">
-        <v>746.16468073908595</v>
+        <v>0.74616468073908604</v>
       </c>
       <c r="H67">
-        <v>7727.1174348697295</v>
+        <v>7.7271174348697302</v>
       </c>
       <c r="I67">
-        <v>2539.78067969215</v>
+        <v>2.53978067969215</v>
       </c>
       <c r="J67">
-        <v>3438.36745490981</v>
+        <v>3.4383674549098102</v>
       </c>
       <c r="K67">
-        <v>1130.13673019315</v>
+        <v>1.13013673019315</v>
       </c>
       <c r="L67">
-        <v>12368.428917835599</v>
+        <v>12.368428917835599</v>
       </c>
       <c r="M67">
-        <v>4065.30599132719</v>
+        <v>4.0653059913271896</v>
       </c>
       <c r="N67">
-        <v>17408.309555110201</v>
+        <v>17.408309555110201</v>
       </c>
       <c r="O67">
-        <v>5721.8346487980498</v>
+        <v>5.7218346487980503</v>
       </c>
       <c r="P67">
-        <v>10236.451703406799</v>
+        <v>10.2364517034068</v>
       </c>
       <c r="Q67">
-        <v>3364.5589683409098</v>
+        <v>3.3645589683409098</v>
       </c>
       <c r="R67">
-        <v>955.63800000000003</v>
+        <v>0.95563799999999999</v>
       </c>
       <c r="S67">
-        <v>314.10302090491803</v>
+        <v>0.31410302090491798</v>
       </c>
       <c r="T67">
-        <v>7058.3908376753498</v>
+        <v>7.0583908376753497</v>
       </c>
       <c r="U67">
-        <v>2319.980876484</v>
+        <v>2.3199808764840002</v>
       </c>
       <c r="V67">
-        <v>2333.61</v>
+        <v>2.3336100000000002</v>
       </c>
       <c r="W67">
-        <v>767.02051468644595</v>
+        <v>0.76702051468644605</v>
       </c>
       <c r="X67">
-        <v>2661.49125</v>
+        <v>2.6614912500000001</v>
       </c>
       <c r="Y67">
-        <v>874.78986994762397</v>
+        <v>0.87478986994762398</v>
       </c>
       <c r="Z67" s="4"/>
       <c r="AA67" s="4"/>
@@ -8694,76 +8694,76 @@
         <v>0.67708333333333304</v>
       </c>
       <c r="B68">
-        <v>11326.5802568362</v>
+        <v>11.3265802568362</v>
       </c>
       <c r="C68">
-        <v>3722.8668964548001</v>
+        <v>3.7228668964548</v>
       </c>
       <c r="D68">
-        <v>18185.608197801401</v>
+        <v>18.1856081978014</v>
       </c>
       <c r="E68">
-        <v>5977.3203576277701</v>
+        <v>5.9773203576277698</v>
       </c>
       <c r="F68">
-        <v>2263.8692865569801</v>
+        <v>2.2638692865569801</v>
       </c>
       <c r="G68">
-        <v>744.09785069389295</v>
+        <v>0.744097850693893</v>
       </c>
       <c r="H68">
-        <v>7700.1466933867696</v>
+        <v>7.7001466933867704</v>
       </c>
       <c r="I68">
-        <v>2530.9158256618098</v>
+        <v>2.5309158256618098</v>
       </c>
       <c r="J68">
-        <v>3426.3661723446799</v>
+        <v>3.4263661723446801</v>
       </c>
       <c r="K68">
-        <v>1126.1920993722399</v>
+        <v>1.1261920993722401</v>
       </c>
       <c r="L68">
-        <v>12325.2581362725</v>
+        <v>12.325258136272501</v>
       </c>
       <c r="M68">
-        <v>4051.11644161924</v>
+        <v>4.0511164416192402</v>
       </c>
       <c r="N68">
-        <v>17347.547567134199</v>
+        <v>17.3475475671342</v>
       </c>
       <c r="O68">
-        <v>5701.8631491512897</v>
+        <v>5.7018631491512899</v>
       </c>
       <c r="P68">
-        <v>10200.7223780895</v>
+        <v>10.2007223780895</v>
       </c>
       <c r="Q68">
-        <v>3352.8153070203498</v>
+        <v>3.3528153070203501</v>
       </c>
       <c r="R68">
-        <v>953.35451612903205</v>
+        <v>0.95335451612903199</v>
       </c>
       <c r="S68">
-        <v>313.35247605209901</v>
+        <v>0.31335247605209898</v>
       </c>
       <c r="T68">
-        <v>7033.7542204408801</v>
+        <v>7.0337542204408798</v>
       </c>
       <c r="U68">
-        <v>2311.8832119936601</v>
+        <v>2.3118832119936599</v>
       </c>
       <c r="V68">
-        <v>2328.0338709677399</v>
+        <v>2.3280338709677402</v>
       </c>
       <c r="W68">
-        <v>765.18772970511702</v>
+        <v>0.76518772970511695</v>
       </c>
       <c r="X68">
-        <v>2655.1316532258002</v>
+        <v>2.6551316532258</v>
       </c>
       <c r="Y68">
-        <v>872.69957157259898</v>
+        <v>0.87269957157259903</v>
       </c>
       <c r="Z68" s="4"/>
       <c r="AA68" s="4"/>
@@ -8818,76 +8818,76 @@
         <v>0.6875</v>
       </c>
       <c r="B69">
-        <v>11362.900279203501</v>
+        <v>11.362900279203499</v>
       </c>
       <c r="C69">
-        <v>3734.8047105066798</v>
+        <v>3.73480471050667</v>
       </c>
       <c r="D69">
-        <v>18241.5404691806</v>
+        <v>18.241540469180599</v>
       </c>
       <c r="E69">
-        <v>5995.7044061966499</v>
+        <v>5.9957044061966496</v>
       </c>
       <c r="F69">
-        <v>2263.05764375525</v>
+        <v>2.2630576437552499</v>
       </c>
       <c r="G69">
-        <v>743.83107660588098</v>
+        <v>0.74383107660588099</v>
       </c>
       <c r="H69">
-        <v>7727.1174348697295</v>
+        <v>7.7271174348697302</v>
       </c>
       <c r="I69">
-        <v>2539.78067969215</v>
+        <v>2.53978067969215</v>
       </c>
       <c r="J69">
-        <v>3438.36745490981</v>
+        <v>3.4383674549098102</v>
       </c>
       <c r="K69">
-        <v>1130.13673019315</v>
+        <v>1.13013673019315</v>
       </c>
       <c r="L69">
-        <v>12368.428917835599</v>
+        <v>12.368428917835599</v>
       </c>
       <c r="M69">
-        <v>4065.30599132719</v>
+        <v>4.0653059913271896</v>
       </c>
       <c r="N69">
-        <v>17408.309555110201</v>
+        <v>17.408309555110201</v>
       </c>
       <c r="O69">
-        <v>5721.8346487980498</v>
+        <v>5.7218346487980503</v>
       </c>
       <c r="P69">
-        <v>10236.451703406799</v>
+        <v>10.2364517034068</v>
       </c>
       <c r="Q69">
-        <v>3364.5589683409098</v>
+        <v>3.3645589683409098</v>
       </c>
       <c r="R69">
-        <v>951.07103225806395</v>
+        <v>0.951071032258064</v>
       </c>
       <c r="S69">
-        <v>312.60193119927902</v>
+        <v>0.31260193119927898</v>
       </c>
       <c r="T69">
-        <v>7058.3908376753498</v>
+        <v>7.0583908376753497</v>
       </c>
       <c r="U69">
-        <v>2319.980876484</v>
+        <v>2.3199808764840002</v>
       </c>
       <c r="V69">
-        <v>2322.45774193548</v>
+        <v>2.3224577419354802</v>
       </c>
       <c r="W69">
-        <v>763.35494472378696</v>
+        <v>0.76335494472378695</v>
       </c>
       <c r="X69">
-        <v>2648.7720564516098</v>
+        <v>2.6487720564516102</v>
       </c>
       <c r="Y69">
-        <v>870.60927319757502</v>
+        <v>0.87060927319757497</v>
       </c>
       <c r="Z69" s="4"/>
       <c r="AA69" s="4"/>
@@ -8942,76 +8942,76 @@
         <v>0.69791666666666696</v>
       </c>
       <c r="B70">
-        <v>11464.4823568427</v>
+        <v>11.4644823568427</v>
       </c>
       <c r="C70">
-        <v>3768.19312479771</v>
+        <v>3.7681931247977101</v>
       </c>
       <c r="D70">
-        <v>18402.8277040719</v>
+        <v>18.4028277040719</v>
       </c>
       <c r="E70">
-        <v>6048.7169566736702</v>
+        <v>6.0487169566736698</v>
       </c>
       <c r="F70">
-        <v>2265.2630252440299</v>
+        <v>2.26526302524403</v>
       </c>
       <c r="G70">
-        <v>744.55595044710003</v>
+        <v>0.74455595044709999</v>
       </c>
       <c r="H70">
-        <v>7801.2869739478901</v>
+        <v>7.8012869739478896</v>
       </c>
       <c r="I70">
-        <v>2564.1590282755801</v>
+        <v>2.5641590282755802</v>
       </c>
       <c r="J70">
-        <v>3471.3709819639198</v>
+        <v>3.4713709819639198</v>
       </c>
       <c r="K70">
-        <v>1140.9844649506799</v>
+        <v>1.14098446495068</v>
       </c>
       <c r="L70">
-        <v>12487.1485671342</v>
+        <v>12.4871485671342</v>
       </c>
       <c r="M70">
-        <v>4104.3272530240502</v>
+        <v>4.1043272530240502</v>
       </c>
       <c r="N70">
-        <v>17575.405022044</v>
+        <v>17.575405022043999</v>
       </c>
       <c r="O70">
-        <v>5776.7562728266503</v>
+        <v>5.7767562728266499</v>
       </c>
       <c r="P70">
-        <v>10334.7073480293</v>
+        <v>10.334707348029299</v>
       </c>
       <c r="Q70">
-        <v>3396.8540369724601</v>
+        <v>3.39685403697246</v>
       </c>
       <c r="R70">
-        <v>947.645806451613</v>
+        <v>0.947645806451613</v>
       </c>
       <c r="S70">
-        <v>311.47611392005001</v>
+        <v>0.31147611392004998</v>
       </c>
       <c r="T70">
-        <v>7126.14153507014</v>
+        <v>7.1261415350701398</v>
       </c>
       <c r="U70">
-        <v>2342.2494538324499</v>
+        <v>2.3422494538324501</v>
       </c>
       <c r="V70">
-        <v>2314.0935483870899</v>
+        <v>2.3140935483870901</v>
       </c>
       <c r="W70">
-        <v>760.60576725179305</v>
+        <v>0.76060576725179296</v>
       </c>
       <c r="X70">
-        <v>2639.2326612903198</v>
+        <v>2.6392326612903201</v>
       </c>
       <c r="Y70">
-        <v>867.47382563503902</v>
+        <v>0.86747382563503905</v>
       </c>
       <c r="Z70" s="4"/>
       <c r="AA70" s="4"/>
@@ -9066,76 +9066,76 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="B71">
-        <v>11642.1085114745</v>
+        <v>11.6421085114745</v>
       </c>
       <c r="C71">
-        <v>3826.5760184892401</v>
+        <v>3.8265760184892401</v>
       </c>
       <c r="D71">
-        <v>18691.2391560371</v>
+        <v>18.691239156037099</v>
       </c>
       <c r="E71">
-        <v>6143.5132166862104</v>
+        <v>6.1435132166862099</v>
       </c>
       <c r="F71">
-        <v>2274.7199195164499</v>
+        <v>2.2747199195164498</v>
       </c>
       <c r="G71">
-        <v>747.66428127879999</v>
+        <v>0.74766428127880002</v>
       </c>
       <c r="H71">
-        <v>7929.3979959919798</v>
+        <v>7.9293979959919803</v>
       </c>
       <c r="I71">
-        <v>2606.2670849196902</v>
+        <v>2.6062670849196898</v>
       </c>
       <c r="J71">
-        <v>3528.3770741482899</v>
+        <v>3.52837707414829</v>
       </c>
       <c r="K71">
-        <v>1159.72146135004</v>
+        <v>1.15972146135004</v>
       </c>
       <c r="L71">
-        <v>12692.2097795591</v>
+        <v>12.6922097795591</v>
       </c>
       <c r="M71">
-        <v>4171.7276141368002</v>
+        <v>4.1717276141367998</v>
       </c>
       <c r="N71">
-        <v>17864.0244649298</v>
+        <v>17.864024464929798</v>
       </c>
       <c r="O71">
-        <v>5871.6208961487901</v>
+        <v>5.8716208961487899</v>
       </c>
       <c r="P71">
-        <v>10504.4216432865</v>
+        <v>10.5044216432865</v>
       </c>
       <c r="Q71">
-        <v>3452.63642824513</v>
+        <v>3.4526364282451301</v>
       </c>
       <c r="R71">
-        <v>945.36232258064501</v>
+        <v>0.94536232258064501</v>
       </c>
       <c r="S71">
-        <v>310.72556906723099</v>
+        <v>0.31072556906723098</v>
       </c>
       <c r="T71">
-        <v>7243.1654669338604</v>
+        <v>7.2431654669338599</v>
       </c>
       <c r="U71">
-        <v>2380.7133601616001</v>
+        <v>2.3807133601616002</v>
       </c>
       <c r="V71">
-        <v>2308.5174193548301</v>
+        <v>2.3085174193548301</v>
       </c>
       <c r="W71">
-        <v>758.77298227046299</v>
+        <v>0.75877298227046297</v>
       </c>
       <c r="X71">
-        <v>2632.8730645161199</v>
+        <v>2.63287306451612</v>
       </c>
       <c r="Y71">
-        <v>865.38352726001494</v>
+        <v>0.865383527260015</v>
       </c>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
@@ -9190,76 +9190,76 @@
         <v>0.71875</v>
       </c>
       <c r="B72">
-        <v>11916.2029366474</v>
+        <v>11.9162029366474</v>
       </c>
       <c r="C72">
-        <v>3916.6664993617201</v>
+        <v>3.9166664993617202</v>
       </c>
       <c r="D72">
-        <v>19077.439846002901</v>
+        <v>19.0774398460029</v>
       </c>
       <c r="E72">
-        <v>6270.4512448870701</v>
+        <v>6.2704512448870702</v>
       </c>
       <c r="F72">
-        <v>2344.67711689508</v>
+        <v>2.3446771168950802</v>
       </c>
       <c r="G72">
-        <v>770.65810010001599</v>
+        <v>0.77065810010001601</v>
       </c>
       <c r="H72">
-        <v>8111.4505010020002</v>
+        <v>8.1114505010020004</v>
       </c>
       <c r="I72">
-        <v>2666.1048496244798</v>
+        <v>2.6661048496244799</v>
       </c>
       <c r="J72">
-        <v>3609.3857314629199</v>
+        <v>3.6093857314629201</v>
       </c>
       <c r="K72">
-        <v>1186.3477193912399</v>
+        <v>1.18634771939124</v>
       </c>
       <c r="L72">
-        <v>12983.6125551102</v>
+        <v>12.9836125551102</v>
       </c>
       <c r="M72">
-        <v>4267.5070746654501</v>
+        <v>4.26750707466545</v>
       </c>
       <c r="N72">
-        <v>18274.167883767499</v>
+        <v>18.2741678837675</v>
       </c>
       <c r="O72">
-        <v>6006.42851876445</v>
+        <v>6.0064285187644497</v>
       </c>
       <c r="P72">
-        <v>10745.594589178299</v>
+        <v>10.7455945891783</v>
       </c>
       <c r="Q72">
-        <v>3531.9061421589199</v>
+        <v>3.53190614215892</v>
       </c>
       <c r="R72">
-        <v>978.47283870967703</v>
+        <v>0.97847283870967705</v>
       </c>
       <c r="S72">
-        <v>321.60846943311202</v>
+        <v>0.321608469433112</v>
       </c>
       <c r="T72">
-        <v>7409.4626332665302</v>
+        <v>7.4094626332665303</v>
       </c>
       <c r="U72">
-        <v>2435.37259547143</v>
+        <v>2.43537259547143</v>
       </c>
       <c r="V72">
-        <v>2389.3712903225801</v>
+        <v>2.3893712903225799</v>
       </c>
       <c r="W72">
-        <v>785.34836449974296</v>
+        <v>0.78534836449974299</v>
       </c>
       <c r="X72">
-        <v>2725.0872177419301</v>
+        <v>2.7250872177419301</v>
       </c>
       <c r="Y72">
-        <v>895.69285369786496</v>
+        <v>0.895692853697865</v>
       </c>
       <c r="Z72" s="4"/>
       <c r="AA72" s="4"/>
@@ -9314,76 +9314,76 @@
         <v>0.72916666666666696</v>
       </c>
       <c r="B73">
-        <v>12319.333460533901</v>
+        <v>12.319333460533899</v>
       </c>
       <c r="C73">
-        <v>4049.16909487563</v>
+        <v>4.04916909487563</v>
       </c>
       <c r="D73">
-        <v>19535.8787778558</v>
+        <v>19.5358787778558</v>
       </c>
       <c r="E73">
-        <v>6421.1328349822697</v>
+        <v>6.4211328349822701</v>
       </c>
       <c r="F73">
-        <v>2536.1678155504501</v>
+        <v>2.5361678155504501</v>
       </c>
       <c r="G73">
-        <v>833.59804903763302</v>
+        <v>0.83359804903763302</v>
       </c>
       <c r="H73">
-        <v>8354.18717434869</v>
+        <v>8.3541871743486897</v>
       </c>
       <c r="I73">
-        <v>2745.8885358975299</v>
+        <v>2.7458885358975298</v>
       </c>
       <c r="J73">
-        <v>3717.3972745490901</v>
+        <v>3.7173972745490902</v>
       </c>
       <c r="K73">
-        <v>1221.84939677951</v>
+        <v>1.2218493967795101</v>
       </c>
       <c r="L73">
-        <v>13372.1495891783</v>
+        <v>13.372149589178299</v>
       </c>
       <c r="M73">
-        <v>4395.21302203699</v>
+        <v>4.39521302203699</v>
       </c>
       <c r="N73">
-        <v>18821.025775551101</v>
+        <v>18.821025775551099</v>
       </c>
       <c r="O73">
-        <v>6186.17201558533</v>
+        <v>6.1861720155853304</v>
       </c>
       <c r="P73">
-        <v>11067.158517034</v>
+        <v>11.067158517034001</v>
       </c>
       <c r="Q73">
-        <v>3637.5990940439701</v>
+        <v>3.6375990940439702</v>
       </c>
       <c r="R73">
-        <v>1085.79658064516</v>
+        <v>1.0857965806451599</v>
       </c>
       <c r="S73">
-        <v>356.88407751562403</v>
+        <v>0.35688407751562401</v>
       </c>
       <c r="T73">
-        <v>7631.19218837675</v>
+        <v>7.6311921883767502</v>
       </c>
       <c r="U73">
-        <v>2508.2515758845402</v>
+        <v>2.5082515758845401</v>
       </c>
       <c r="V73">
-        <v>2651.4493548386999</v>
+        <v>2.6514493548387001</v>
       </c>
       <c r="W73">
-        <v>871.48925862223496</v>
+        <v>0.87148925862223503</v>
       </c>
       <c r="X73">
-        <v>3023.9882661290299</v>
+        <v>3.02398826612903</v>
       </c>
       <c r="Y73">
-        <v>993.93687732400201</v>
+        <v>0.99393687732400204</v>
       </c>
       <c r="Z73" s="4"/>
       <c r="AA73" s="4"/>
@@ -9438,76 +9438,76 @@
         <v>0.73958333333333304</v>
       </c>
       <c r="B74">
-        <v>12856.487491305101</v>
+        <v>12.856487491305099</v>
       </c>
       <c r="C74">
-        <v>4225.7230868228899</v>
+        <v>4.2257230868228897</v>
       </c>
       <c r="D74">
-        <v>20009.7463202117</v>
+        <v>20.009746320211701</v>
       </c>
       <c r="E74">
-        <v>6576.8855641148302</v>
+        <v>6.5768855641148303</v>
       </c>
       <c r="F74">
-        <v>2909.9464659157002</v>
+        <v>2.9099464659156999</v>
       </c>
       <c r="G74">
-        <v>956.45315026789694</v>
+        <v>0.95645315026789701</v>
       </c>
       <c r="H74">
-        <v>8644.1226452905794</v>
+        <v>8.6441226452905795</v>
       </c>
       <c r="I74">
-        <v>2841.1857167236799</v>
+        <v>2.8411857167236798</v>
       </c>
       <c r="J74">
-        <v>3846.4110621242398</v>
+        <v>3.8464110621242402</v>
       </c>
       <c r="K74">
-        <v>1264.2541781043799</v>
+        <v>1.2642541781043799</v>
       </c>
       <c r="L74">
-        <v>13836.235490981901</v>
+        <v>13.836235490981901</v>
       </c>
       <c r="M74">
-        <v>4547.7506813974296</v>
+        <v>4.5477506813974298</v>
       </c>
       <c r="N74">
-        <v>19474.2171462925</v>
+        <v>19.474217146292499</v>
       </c>
       <c r="O74">
-        <v>6400.8656367880503</v>
+        <v>6.4008656367880503</v>
       </c>
       <c r="P74">
-        <v>11451.248764194999</v>
+        <v>11.451248764195</v>
       </c>
       <c r="Q74">
-        <v>3763.8434532400101</v>
+        <v>3.76384345324001</v>
       </c>
       <c r="R74">
-        <v>1307.2945161290299</v>
+        <v>1.3072945161290299</v>
       </c>
       <c r="S74">
-        <v>429.68692823910499</v>
+        <v>0.42968692823910598</v>
       </c>
       <c r="T74">
-        <v>7896.0358236472903</v>
+        <v>7.8960358236472903</v>
       </c>
       <c r="U74">
-        <v>2595.3014691557501</v>
+        <v>2.5953014691557499</v>
       </c>
       <c r="V74">
-        <v>3192.33387096774</v>
+        <v>3.1923338709677398</v>
       </c>
       <c r="W74">
-        <v>1049.2694018111999</v>
+        <v>1.0492694018112001</v>
       </c>
       <c r="X74">
-        <v>3640.8691532257999</v>
+        <v>3.6408691532258</v>
       </c>
       <c r="Y74">
-        <v>1196.69581970134</v>
+        <v>1.19669581970134</v>
       </c>
       <c r="Z74" s="4"/>
       <c r="AA74" s="4"/>
@@ -9562,76 +9562,76 @@
         <v>0.75</v>
       </c>
       <c r="B75">
-        <v>13537.196319283699</v>
+        <v>13.5371963192837</v>
       </c>
       <c r="C75">
-        <v>4449.4612588343698</v>
+        <v>4.4494612588343703</v>
       </c>
       <c r="D75">
-        <v>20472.064567167901</v>
+        <v>20.472064567167902</v>
       </c>
       <c r="E75">
-        <v>6728.8422234234904</v>
+        <v>6.7288422234234897</v>
       </c>
       <c r="F75">
-        <v>3490.8625034746901</v>
+        <v>3.4908625034746898</v>
       </c>
       <c r="G75">
-        <v>1147.3910182570201</v>
+        <v>1.1473910182570199</v>
       </c>
       <c r="H75">
-        <v>8981.2569138276504</v>
+        <v>8.9812569138276501</v>
       </c>
       <c r="I75">
-        <v>2951.9963921029198</v>
+        <v>2.9519963921029202</v>
       </c>
       <c r="J75">
-        <v>3996.4270941883701</v>
+        <v>3.9964270941883702</v>
       </c>
       <c r="K75">
-        <v>1313.56206336587</v>
+        <v>1.31356206336587</v>
       </c>
       <c r="L75">
-        <v>14375.870260521</v>
+        <v>14.375870260520999</v>
       </c>
       <c r="M75">
-        <v>4725.1200527467799</v>
+        <v>4.7251200527467798</v>
       </c>
       <c r="N75">
-        <v>20233.741995991899</v>
+        <v>20.233741995991899</v>
       </c>
       <c r="O75">
-        <v>6650.5093823726002</v>
+        <v>6.6505093823726096</v>
       </c>
       <c r="P75">
-        <v>11897.8653306613</v>
+        <v>11.8978653306613</v>
       </c>
       <c r="Q75">
-        <v>3910.63921974703</v>
+        <v>3.9106392197470301</v>
       </c>
       <c r="R75">
-        <v>1658.95103225806</v>
+        <v>1.6589510322580601</v>
       </c>
       <c r="S75">
-        <v>545.27083557329297</v>
+        <v>0.54527083557329303</v>
       </c>
       <c r="T75">
-        <v>8203.9935390781502</v>
+        <v>8.2039935390781498</v>
       </c>
       <c r="U75">
-        <v>2696.52227528507</v>
+        <v>2.6965222752850702</v>
       </c>
       <c r="V75">
-        <v>4051.05774193548</v>
+        <v>4.0510577419354803</v>
       </c>
       <c r="W75">
-        <v>1331.5182889359701</v>
+        <v>1.33151828893597</v>
       </c>
       <c r="X75">
-        <v>4620.2470564516098</v>
+        <v>4.6202470564516096</v>
       </c>
       <c r="Y75">
-        <v>1518.6017694550701</v>
+        <v>1.51860176945507</v>
       </c>
       <c r="Z75" s="4"/>
       <c r="AA75" s="4"/>
@@ -9686,76 +9686,76 @@
         <v>0.76041666666666696</v>
       </c>
       <c r="B76">
-        <v>14317.888331566301</v>
+        <v>14.3178883315663</v>
       </c>
       <c r="C76">
-        <v>4706.06231431177</v>
+        <v>4.7060623143117697</v>
       </c>
       <c r="D76">
-        <v>20935.814204730101</v>
+        <v>20.9358142047301</v>
       </c>
       <c r="E76">
-        <v>6881.26935807265</v>
+        <v>6.8812693580726503</v>
       </c>
       <c r="F76">
-        <v>4165.3185088725804</v>
+        <v>4.1653185088725797</v>
       </c>
       <c r="G76">
-        <v>1369.0739868737401</v>
+        <v>1.36907398687374</v>
       </c>
       <c r="H76">
-        <v>9365.5899799599192</v>
+        <v>9.3655899799599194</v>
       </c>
       <c r="I76">
-        <v>3078.3205620352501</v>
+        <v>3.0783205620352501</v>
       </c>
       <c r="J76">
-        <v>4167.4453707414796</v>
+        <v>4.16744537074148</v>
       </c>
       <c r="K76">
-        <v>1369.7730525639599</v>
+        <v>1.36977305256396</v>
       </c>
       <c r="L76">
-        <v>14991.0538977955</v>
+        <v>14.991053897795499</v>
       </c>
       <c r="M76">
-        <v>4927.3211360850501</v>
+        <v>4.92732113608505</v>
       </c>
       <c r="N76">
-        <v>21099.600324649298</v>
+        <v>21.099600324649298</v>
       </c>
       <c r="O76">
-        <v>6935.1032523390004</v>
+        <v>6.9351032523390002</v>
       </c>
       <c r="P76">
-        <v>12407.0082164328</v>
+        <v>12.4070082164328</v>
       </c>
       <c r="Q76">
-        <v>4077.9863935650301</v>
+        <v>4.0779863935650296</v>
       </c>
       <c r="R76">
-        <v>2067.6946451612898</v>
+        <v>2.0676946451612901</v>
       </c>
       <c r="S76">
-        <v>679.618364227965</v>
+        <v>0.67961836422796496</v>
       </c>
       <c r="T76">
-        <v>8555.0653346693398</v>
+        <v>8.5550653346693402</v>
       </c>
       <c r="U76">
-        <v>2811.9139942725001</v>
+        <v>2.8119139942725</v>
       </c>
       <c r="V76">
-        <v>5049.1848387096697</v>
+        <v>5.0491848387096701</v>
       </c>
       <c r="W76">
-        <v>1659.5868005939701</v>
+        <v>1.65958680059397</v>
       </c>
       <c r="X76">
-        <v>5758.6148790322504</v>
+        <v>5.7586148790322502</v>
       </c>
       <c r="Y76">
-        <v>1892.7651785844</v>
+        <v>1.8927651785844</v>
       </c>
       <c r="Z76" s="4"/>
       <c r="AA76" s="4"/>
@@ -9810,76 +9810,76 @@
         <v>0.77083333333333304</v>
       </c>
       <c r="B77">
-        <v>15124.577387937101</v>
+        <v>15.1245773879371</v>
       </c>
       <c r="C77">
-        <v>4971.2081849625902</v>
+        <v>4.97120818496259</v>
       </c>
       <c r="D77">
-        <v>21413.479172496201</v>
+        <v>21.413479172496199</v>
       </c>
       <c r="E77">
-        <v>7038.2702405781502</v>
+        <v>7.0382702405781501</v>
       </c>
       <c r="F77">
-        <v>4788.1736099618502</v>
+        <v>4.7881736099618504</v>
       </c>
       <c r="G77">
-        <v>1573.7965584313599</v>
+        <v>1.57379655843136</v>
       </c>
       <c r="H77">
-        <v>9783.6364729458892</v>
+        <v>9.78363647294589</v>
       </c>
       <c r="I77">
-        <v>3215.7257995055002</v>
+        <v>3.2157257995055</v>
       </c>
       <c r="J77">
-        <v>4353.4652505009999</v>
+        <v>4.3534652505010003</v>
       </c>
       <c r="K77">
-        <v>1430.9148302881899</v>
+        <v>1.43091483028819</v>
       </c>
       <c r="L77">
-        <v>15660.201012023999</v>
+        <v>15.660201012024</v>
       </c>
       <c r="M77">
-        <v>5147.2591565582497</v>
+        <v>5.1472591565582499</v>
       </c>
       <c r="N77">
-        <v>22041.4111382765</v>
+        <v>22.041411138276501</v>
       </c>
       <c r="O77">
-        <v>7244.6614968638496</v>
+        <v>7.2446614968638503</v>
       </c>
       <c r="P77">
-        <v>12960.812758851</v>
+        <v>12.960812758851</v>
       </c>
       <c r="Q77">
-        <v>4260.01314403374</v>
+        <v>4.2600131440337403</v>
       </c>
       <c r="R77">
-        <v>2441.0442580645099</v>
+        <v>2.44104425806451</v>
       </c>
       <c r="S77">
-        <v>802.33244766393705</v>
+        <v>0.80233244766393697</v>
       </c>
       <c r="T77">
-        <v>8936.9329018036005</v>
+        <v>8.9369329018035994</v>
       </c>
       <c r="U77">
-        <v>2937.4277938728501</v>
+        <v>2.9374277938728501</v>
       </c>
       <c r="V77">
-        <v>5960.8819354838697</v>
+        <v>5.9608819354838696</v>
       </c>
       <c r="W77">
-        <v>1959.24714504136</v>
+        <v>1.95924714504136</v>
       </c>
       <c r="X77">
-        <v>6798.4089516128997</v>
+        <v>6.7984089516128998</v>
       </c>
       <c r="Y77">
-        <v>2234.5289629008598</v>
+        <v>2.23452896290086</v>
       </c>
       <c r="Z77" s="4"/>
       <c r="AA77" s="4"/>
@@ -9934,76 +9934,76 @@
         <v>0.78125</v>
       </c>
       <c r="B78">
-        <v>15870.4529071045</v>
+        <v>15.8704529071045</v>
       </c>
       <c r="C78">
-        <v>5216.3656125549396</v>
+        <v>5.2163656125549398</v>
       </c>
       <c r="D78">
-        <v>21902.554937759702</v>
+        <v>21.9025549377597</v>
       </c>
       <c r="E78">
-        <v>7199.0216708484604</v>
+        <v>7.1990216708484596</v>
       </c>
       <c r="F78">
-        <v>5204.7275670696199</v>
+        <v>5.2047275670696198</v>
       </c>
       <c r="G78">
-        <v>1710.7112230820401</v>
+        <v>1.71071122308204</v>
       </c>
       <c r="H78">
-        <v>10215.1683366733</v>
+        <v>10.215168336673299</v>
       </c>
       <c r="I78">
-        <v>3357.5634639909299</v>
+        <v>3.35756346399093</v>
       </c>
       <c r="J78">
-        <v>4545.4857715430799</v>
+        <v>4.5454857715430803</v>
       </c>
       <c r="K78">
-        <v>1494.0289234228901</v>
+        <v>1.4940289234228901</v>
       </c>
       <c r="L78">
-        <v>16350.933517034</v>
+        <v>16.350933517034001</v>
       </c>
       <c r="M78">
-        <v>5374.2919518854196</v>
+        <v>5.3742919518854197</v>
       </c>
       <c r="N78">
-        <v>23013.6029458917</v>
+        <v>23.013602945891702</v>
       </c>
       <c r="O78">
-        <v>7564.2054912120902</v>
+        <v>7.56420549121209</v>
       </c>
       <c r="P78">
-        <v>13532.481963927799</v>
+        <v>13.5324819639278</v>
       </c>
       <c r="Q78">
-        <v>4447.9117251627304</v>
+        <v>4.4479117251627303</v>
       </c>
       <c r="R78">
-        <v>2680.8100645161298</v>
+        <v>2.6808100645161299</v>
       </c>
       <c r="S78">
-        <v>881.13965720997396</v>
+        <v>0.881139657209974</v>
       </c>
       <c r="T78">
-        <v>9331.1187775551098</v>
+        <v>9.3311187775551101</v>
       </c>
       <c r="U78">
-        <v>3066.9904257183798</v>
+        <v>3.0669904257183802</v>
       </c>
       <c r="V78">
-        <v>6546.3754838709601</v>
+        <v>6.5463754838709596</v>
       </c>
       <c r="W78">
-        <v>2151.6895680809698</v>
+        <v>2.15168956808097</v>
       </c>
       <c r="X78">
-        <v>7466.1666129032201</v>
+        <v>7.46616661290322</v>
       </c>
       <c r="Y78">
-        <v>2454.0102922783999</v>
+        <v>2.4540102922784</v>
       </c>
       <c r="Z78" s="4"/>
       <c r="AA78" s="4"/>
@@ -10058,76 +10058,76 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="B79">
-        <v>16497.868103691198</v>
+        <v>16.4978681036912</v>
       </c>
       <c r="C79">
-        <v>5422.5870150206601</v>
+        <v>5.4225870150206603</v>
       </c>
       <c r="D79">
-        <v>22402.109096730899</v>
+        <v>22.4021090967309</v>
       </c>
       <c r="E79">
-        <v>7363.2171825782698</v>
+        <v>7.3632171825782704</v>
       </c>
       <c r="F79">
-        <v>5312.4385403064098</v>
+        <v>5.3124385403064096</v>
       </c>
       <c r="G79">
-        <v>1746.1141079383201</v>
+        <v>1.74611410793832</v>
       </c>
       <c r="H79">
-        <v>10646.700200400801</v>
+        <v>10.646700200400799</v>
       </c>
       <c r="I79">
-        <v>3499.4011284763601</v>
+        <v>3.49940112847636</v>
       </c>
       <c r="J79">
-        <v>4737.5062925851698</v>
+        <v>4.7375062925851701</v>
       </c>
       <c r="K79">
-        <v>1557.14301655759</v>
+        <v>1.5571430165575899</v>
       </c>
       <c r="L79">
-        <v>17041.666022043999</v>
+        <v>17.041666022044001</v>
       </c>
       <c r="M79">
-        <v>5601.3247472125904</v>
+        <v>5.6013247472125904</v>
       </c>
       <c r="N79">
-        <v>23985.794753507002</v>
+        <v>23.985794753507001</v>
       </c>
       <c r="O79">
-        <v>7883.74948556032</v>
+        <v>7.8837494855603198</v>
       </c>
       <c r="P79">
-        <v>14104.151169004601</v>
+        <v>14.1041511690046</v>
       </c>
       <c r="Q79">
-        <v>4635.8103062917098</v>
+        <v>4.6358103062917104</v>
       </c>
       <c r="R79">
-        <v>2721.9127741935399</v>
+        <v>2.7219127741935401</v>
       </c>
       <c r="S79">
-        <v>894.649464560723</v>
+        <v>0.89464946456072303</v>
       </c>
       <c r="T79">
-        <v>9725.3046533066099</v>
+        <v>9.7253046533066101</v>
       </c>
       <c r="U79">
-        <v>3196.55305756391</v>
+        <v>3.1965530575639098</v>
       </c>
       <c r="V79">
-        <v>6646.7458064516104</v>
+        <v>6.6467458064516096</v>
       </c>
       <c r="W79">
-        <v>2184.6796977448998</v>
+        <v>2.1846796977449001</v>
       </c>
       <c r="X79">
-        <v>7580.6393548387096</v>
+        <v>7.5806393548387101</v>
       </c>
       <c r="Y79">
-        <v>2491.6356630288301</v>
+        <v>2.4916356630288301</v>
       </c>
       <c r="Z79" s="4"/>
       <c r="AA79" s="4"/>
@@ -10182,76 +10182,76 @@
         <v>0.80208333333333304</v>
       </c>
       <c r="B80">
-        <v>16980.145127157499</v>
+        <v>16.980145127157499</v>
       </c>
       <c r="C80">
-        <v>5581.1038069270098</v>
+        <v>5.5811038069270102</v>
       </c>
       <c r="D80">
-        <v>22877.593537178502</v>
+        <v>22.877593537178502</v>
       </c>
       <c r="E80">
-        <v>7519.50136041327</v>
+        <v>7.5195013604132699</v>
       </c>
       <c r="F80">
-        <v>5161.1324743034402</v>
+        <v>5.1611324743034404</v>
       </c>
       <c r="G80">
-        <v>1696.3822090259901</v>
+        <v>1.6963822090259899</v>
       </c>
       <c r="H80">
-        <v>11044.518637274499</v>
+        <v>11.0445186372745</v>
       </c>
       <c r="I80">
-        <v>3630.15772542386</v>
+        <v>3.6301577254238602</v>
       </c>
       <c r="J80">
-        <v>4914.5252104208403</v>
+        <v>4.9145252104208401</v>
       </c>
       <c r="K80">
-        <v>1615.3263211661299</v>
+        <v>1.61532632116613</v>
       </c>
       <c r="L80">
-        <v>17678.435050100201</v>
+        <v>17.678435050100202</v>
       </c>
       <c r="M80">
-        <v>5810.6206054048298</v>
+        <v>5.8106206054048304</v>
       </c>
       <c r="N80">
-        <v>24882.0340761523</v>
+        <v>24.882034076152301</v>
       </c>
       <c r="O80">
-        <v>8178.3291053500998</v>
+        <v>8.1783291053500999</v>
       </c>
       <c r="P80">
-        <v>14631.158717434801</v>
+        <v>14.631158717434801</v>
       </c>
       <c r="Q80">
-        <v>4809.0293107699999</v>
+        <v>4.8090293107699997</v>
       </c>
       <c r="R80">
-        <v>2598.6046451612901</v>
+        <v>2.5986046451612901</v>
       </c>
       <c r="S80">
-        <v>854.12004250847599</v>
+        <v>0.85412004250847595</v>
       </c>
       <c r="T80">
-        <v>10088.694757515001</v>
+        <v>10.088694757515</v>
       </c>
       <c r="U80">
-        <v>3315.9936087965102</v>
+        <v>3.3159936087965098</v>
       </c>
       <c r="V80">
-        <v>6345.6348387096696</v>
+        <v>6.3456348387096702</v>
       </c>
       <c r="W80">
-        <v>2085.7093087531098</v>
+        <v>2.0857093087531098</v>
       </c>
       <c r="X80">
-        <v>7237.2211290322502</v>
+        <v>7.2372211290322497</v>
       </c>
       <c r="Y80">
-        <v>2378.75955077752</v>
+        <v>2.3787595507775201</v>
       </c>
       <c r="Z80" s="4"/>
       <c r="AA80" s="4"/>
@@ -10306,76 +10306,76 @@
         <v>0.8125</v>
       </c>
       <c r="B81">
-        <v>17271.987072338201</v>
+        <v>17.271987072338199</v>
       </c>
       <c r="C81">
-        <v>5677.02761553238</v>
+        <v>5.6770276155323796</v>
       </c>
       <c r="D81">
-        <v>23239.220403995801</v>
+        <v>23.239220403995802</v>
       </c>
       <c r="E81">
-        <v>7638.3623635417498</v>
+        <v>7.6383623635417504</v>
       </c>
       <c r="F81">
-        <v>4847.5959081065303</v>
+        <v>4.8475959081065296</v>
       </c>
       <c r="G81">
-        <v>1593.32772332471</v>
+        <v>1.5933277233247101</v>
       </c>
       <c r="H81">
-        <v>11347.9394789579</v>
+        <v>11.347939478957899</v>
       </c>
       <c r="I81">
-        <v>3729.8873332651701</v>
+        <v>3.7298873332651699</v>
       </c>
       <c r="J81">
-        <v>5049.5396392785497</v>
+        <v>5.0495396392785503</v>
       </c>
       <c r="K81">
-        <v>1659.7034179014699</v>
+        <v>1.65970341790147</v>
       </c>
       <c r="L81">
-        <v>18164.1063426853</v>
+        <v>18.164106342685301</v>
       </c>
       <c r="M81">
-        <v>5970.2530396192496</v>
+        <v>5.9702530396192497</v>
       </c>
       <c r="N81">
-        <v>25565.6064408817</v>
+        <v>25.565606440881702</v>
       </c>
       <c r="O81">
-        <v>8403.0084763762006</v>
+        <v>8.4030084763762005</v>
       </c>
       <c r="P81">
-        <v>15033.113627254501</v>
+        <v>15.033113627254499</v>
       </c>
       <c r="Q81">
-        <v>4941.1455006263204</v>
+        <v>4.9411455006263196</v>
       </c>
       <c r="R81">
-        <v>2377.10670967741</v>
+        <v>2.3771067096774101</v>
       </c>
       <c r="S81">
-        <v>781.31719178499395</v>
+        <v>0.78131719178499404</v>
       </c>
       <c r="T81">
-        <v>10365.856701402799</v>
+        <v>10.3658567014028</v>
       </c>
       <c r="U81">
-        <v>3407.0923343129002</v>
+        <v>3.4070923343129</v>
       </c>
       <c r="V81">
-        <v>5804.7503225806404</v>
+        <v>5.8047503225806398</v>
       </c>
       <c r="W81">
-        <v>1907.92916556413</v>
+        <v>1.9079291655641299</v>
       </c>
       <c r="X81">
-        <v>6620.3402419354798</v>
+        <v>6.6203402419354802</v>
       </c>
       <c r="Y81">
-        <v>2176.0006084001802</v>
+        <v>2.1760006084001802</v>
       </c>
       <c r="Z81" s="4"/>
       <c r="AA81" s="4"/>
@@ -10430,76 +10430,76 @@
         <v>0.82291666666666696</v>
       </c>
       <c r="B82">
-        <v>17336.155829982501</v>
+        <v>17.336155829982498</v>
       </c>
       <c r="C82">
-        <v>5698.1188662191398</v>
+        <v>5.69811886621914</v>
       </c>
       <c r="D82">
-        <v>23414.547387550901</v>
+        <v>23.4145473875509</v>
       </c>
       <c r="E82">
-        <v>7695.9895562452703</v>
+        <v>7.6959895562452703</v>
       </c>
       <c r="F82">
-        <v>4465.7500305449603</v>
+        <v>4.4657500305449602</v>
       </c>
       <c r="G82">
-        <v>1467.82105274215</v>
+        <v>1.46782105274215</v>
       </c>
       <c r="H82">
-        <v>11503.0212424849</v>
+        <v>11.5030212424849</v>
       </c>
       <c r="I82">
-        <v>3780.86024393962</v>
+        <v>3.7808602439396202</v>
       </c>
       <c r="J82">
-        <v>5118.5470140280504</v>
+        <v>5.1185470140280502</v>
       </c>
       <c r="K82">
-        <v>1682.38504512175</v>
+        <v>1.6823850451217499</v>
       </c>
       <c r="L82">
-        <v>18412.3383366733</v>
+        <v>18.412338336673301</v>
       </c>
       <c r="M82">
-        <v>6051.8429504399501</v>
+        <v>6.0518429504399496</v>
       </c>
       <c r="N82">
-        <v>25914.9878717434</v>
+        <v>25.914987871743399</v>
       </c>
       <c r="O82">
-        <v>8517.8445993450896</v>
+        <v>8.5178445993450893</v>
       </c>
       <c r="P82">
-        <v>15238.5572478289</v>
+        <v>15.238557247828901</v>
       </c>
       <c r="Q82">
-        <v>5008.6715532195503</v>
+        <v>5.0086715532195498</v>
       </c>
       <c r="R82">
-        <v>2121.3565161290298</v>
+        <v>2.1213565161290302</v>
       </c>
       <c r="S82">
-        <v>697.25616826922101</v>
+        <v>0.69725616826922099</v>
       </c>
       <c r="T82">
-        <v>10507.517250501</v>
+        <v>10.507517250500999</v>
       </c>
       <c r="U82">
-        <v>3453.6539051323898</v>
+        <v>3.45365390513239</v>
       </c>
       <c r="V82">
-        <v>5180.2238709677404</v>
+        <v>5.1802238709677404</v>
       </c>
       <c r="W82">
-        <v>1702.6572476552101</v>
+        <v>1.70265724765521</v>
       </c>
       <c r="X82">
-        <v>5908.0654032257999</v>
+        <v>5.9080654032258</v>
       </c>
       <c r="Y82">
-        <v>1941.88719039747</v>
+        <v>1.9418871903974699</v>
       </c>
       <c r="Z82" s="4"/>
       <c r="AA82" s="4"/>
@@ -10554,76 +10554,76 @@
         <v>0.83333333333333304</v>
       </c>
       <c r="B83">
-        <v>17175.026463960101</v>
+        <v>17.175026463960101</v>
       </c>
       <c r="C83">
-        <v>5645.1582047300399</v>
+        <v>5.6451582047300404</v>
       </c>
       <c r="D83">
-        <v>23372.170633446</v>
+        <v>23.372170633446</v>
       </c>
       <c r="E83">
-        <v>7682.0609907419102</v>
+        <v>7.6820609907419097</v>
       </c>
       <c r="F83">
-        <v>4093.4143196877599</v>
+        <v>4.0934143196877599</v>
       </c>
       <c r="G83">
-        <v>1345.4402227929099</v>
+        <v>1.3454402227929101</v>
       </c>
       <c r="H83">
-        <v>11489.535871743399</v>
+        <v>11.489535871743399</v>
       </c>
       <c r="I83">
-        <v>3776.4278169244499</v>
+        <v>3.7764278169244498</v>
       </c>
       <c r="J83">
-        <v>5112.5463727454899</v>
+        <v>5.1125463727454896</v>
       </c>
       <c r="K83">
-        <v>1680.41272971129</v>
+        <v>1.6804127297112901</v>
       </c>
       <c r="L83">
-        <v>18390.752945891702</v>
+        <v>18.390752945891698</v>
       </c>
       <c r="M83">
-        <v>6044.7481755859799</v>
+        <v>6.0447481755859798</v>
       </c>
       <c r="N83">
-        <v>25884.606877755501</v>
+        <v>25.884606877755498</v>
       </c>
       <c r="O83">
-        <v>8507.85884952171</v>
+        <v>8.5078588495217105</v>
       </c>
       <c r="P83">
-        <v>15220.6925851703</v>
+        <v>15.220692585170299</v>
       </c>
       <c r="Q83">
-        <v>5002.7997225592699</v>
+        <v>5.0027997225592697</v>
       </c>
       <c r="R83">
-        <v>1882.7324516128999</v>
+        <v>1.8827324516129</v>
       </c>
       <c r="S83">
-        <v>618.82423114959397</v>
+        <v>0.61882423114959395</v>
       </c>
       <c r="T83">
-        <v>10495.1989418837</v>
+        <v>10.4951989418837</v>
       </c>
       <c r="U83">
-        <v>3449.6050728872101</v>
+        <v>3.4496050728872101</v>
       </c>
       <c r="V83">
-        <v>4597.5183870967703</v>
+        <v>4.5975183870967697</v>
       </c>
       <c r="W83">
-        <v>1511.13121710627</v>
+        <v>1.5111312171062701</v>
       </c>
       <c r="X83">
-        <v>5243.4875403225797</v>
+        <v>5.2434875403225796</v>
       </c>
       <c r="Y83">
-        <v>1723.45101020744</v>
+        <v>1.7234510102074401</v>
       </c>
       <c r="Z83" s="4"/>
       <c r="AA83" s="4"/>
@@ -10678,76 +10678,76 @@
         <v>0.84375</v>
       </c>
       <c r="B84">
-        <v>16851.929491693001</v>
+        <v>16.851929491692999</v>
       </c>
       <c r="C84">
-        <v>5538.9613655144203</v>
+        <v>5.5389613655144201</v>
       </c>
       <c r="D84">
-        <v>23157.057799002301</v>
+        <v>23.157057799002299</v>
       </c>
       <c r="E84">
-        <v>7611.3568212402997</v>
+        <v>7.6113568212403004</v>
       </c>
       <c r="F84">
-        <v>3752.4457871387899</v>
+        <v>3.75244578713879</v>
       </c>
       <c r="G84">
-        <v>1233.3692857778999</v>
+        <v>1.2333692857778999</v>
       </c>
       <c r="H84">
-        <v>11347.9394789579</v>
+        <v>11.347939478957899</v>
       </c>
       <c r="I84">
-        <v>3729.8873332651701</v>
+        <v>3.7298873332651699</v>
       </c>
       <c r="J84">
-        <v>5049.5396392785497</v>
+        <v>5.0495396392785503</v>
       </c>
       <c r="K84">
-        <v>1659.7034179014699</v>
+        <v>1.65970341790147</v>
       </c>
       <c r="L84">
-        <v>18164.1063426853</v>
+        <v>18.164106342685301</v>
       </c>
       <c r="M84">
-        <v>5970.2530396192496</v>
+        <v>5.9702530396192497</v>
       </c>
       <c r="N84">
-        <v>25565.6064408817</v>
+        <v>25.565606440881702</v>
       </c>
       <c r="O84">
-        <v>8403.0084763762006</v>
+        <v>8.4030084763762005</v>
       </c>
       <c r="P84">
-        <v>15033.113627254501</v>
+        <v>15.033113627254499</v>
       </c>
       <c r="Q84">
-        <v>4941.1455006263204</v>
+        <v>4.9411455006263196</v>
       </c>
       <c r="R84">
-        <v>1672.6519354838699</v>
+        <v>1.67265193548387</v>
       </c>
       <c r="S84">
-        <v>549.77410469020901</v>
+        <v>0.54977410469020904</v>
       </c>
       <c r="T84">
-        <v>10365.856701402799</v>
+        <v>10.3658567014028</v>
       </c>
       <c r="U84">
-        <v>3407.0923343129002</v>
+        <v>3.4070923343129</v>
       </c>
       <c r="V84">
-        <v>4084.5145161290302</v>
+        <v>4.0845145161290297</v>
       </c>
       <c r="W84">
-        <v>1342.51499882394</v>
+        <v>1.34251499882394</v>
       </c>
       <c r="X84">
-        <v>4658.4046370967699</v>
+        <v>4.65840463709677</v>
       </c>
       <c r="Y84">
-        <v>1531.14355970522</v>
+        <v>1.5311435597052201</v>
       </c>
       <c r="Z84" s="4"/>
       <c r="AA84" s="4"/>
@@ -10802,76 +10802,76 @@
         <v>0.85416666666666696</v>
       </c>
       <c r="B85">
-        <v>16460.3881949059</v>
+        <v>16.460388194905899</v>
       </c>
       <c r="C85">
-        <v>5410.2679647393797</v>
+        <v>5.4102679647393801</v>
       </c>
       <c r="D85">
-        <v>22854.0785252405</v>
+        <v>22.854078525240499</v>
       </c>
       <c r="E85">
-        <v>7511.7723497561401</v>
+        <v>7.5117723497561402</v>
       </c>
       <c r="F85">
-        <v>3447.9151646034002</v>
+        <v>3.4479151646033999</v>
       </c>
       <c r="G85">
-        <v>1133.2749106102999</v>
+        <v>1.1332749106102999</v>
       </c>
       <c r="H85">
-        <v>11145.658917835601</v>
+        <v>11.1456589178356</v>
       </c>
       <c r="I85">
-        <v>3663.4009280376299</v>
+        <v>3.6634009280376301</v>
       </c>
       <c r="J85">
-        <v>4959.5300200400798</v>
+        <v>4.9595300200400798</v>
       </c>
       <c r="K85">
-        <v>1630.1186867445799</v>
+        <v>1.63011868674458</v>
       </c>
       <c r="L85">
-        <v>17840.325480961899</v>
+        <v>17.840325480961901</v>
       </c>
       <c r="M85">
-        <v>5863.8314168096404</v>
+        <v>5.8638314168096404</v>
       </c>
       <c r="N85">
-        <v>25109.891531062101</v>
+        <v>25.1098915310621</v>
       </c>
       <c r="O85">
-        <v>8253.2222290254595</v>
+        <v>8.2532222290254698</v>
       </c>
       <c r="P85">
-        <v>14765.143687374701</v>
+        <v>14.7651436873747</v>
       </c>
       <c r="Q85">
-        <v>4853.0680407221098</v>
+        <v>4.8530680407221096</v>
       </c>
       <c r="R85">
-        <v>1489.97322580645</v>
+        <v>1.48997322580645</v>
       </c>
       <c r="S85">
-        <v>489.730516464657</v>
+        <v>0.48973051646465698</v>
       </c>
       <c r="T85">
-        <v>10181.0820721442</v>
+        <v>10.1810820721442</v>
       </c>
       <c r="U85">
-        <v>3346.3598506353101</v>
+        <v>3.3463598506353098</v>
       </c>
       <c r="V85">
-        <v>3638.4241935483801</v>
+        <v>3.6384241935483801</v>
       </c>
       <c r="W85">
-        <v>1195.8922003175701</v>
+        <v>1.19589220031757</v>
       </c>
       <c r="X85">
-        <v>4149.6368951612903</v>
+        <v>4.1496368951612901</v>
       </c>
       <c r="Y85">
-        <v>1363.91968970328</v>
+        <v>1.3639196897032799</v>
       </c>
       <c r="Z85" s="4"/>
       <c r="AA85" s="4"/>
@@ -10926,76 +10926,76 @@
         <v>0.86458333333333304</v>
       </c>
       <c r="B86">
-        <v>16084.5054465059</v>
+        <v>16.084505446505901</v>
       </c>
       <c r="C86">
-        <v>5286.7212799293402</v>
+        <v>5.2867212799293402</v>
       </c>
       <c r="D86">
-        <v>22535.325834920201</v>
+        <v>22.535325834920201</v>
       </c>
       <c r="E86">
-        <v>7407.00340696487</v>
+        <v>7.4070034069648703</v>
       </c>
       <c r="F86">
-        <v>3184.2086146486499</v>
+        <v>3.1842086146486501</v>
       </c>
       <c r="G86">
-        <v>1046.5987592086101</v>
+        <v>1.0465987592086099</v>
       </c>
       <c r="H86">
-        <v>10943.3783567134</v>
+        <v>10.943378356713399</v>
       </c>
       <c r="I86">
-        <v>3596.9145228100901</v>
+        <v>3.5969145228100898</v>
       </c>
       <c r="J86">
-        <v>4869.5204008015999</v>
+        <v>4.8695204008016004</v>
       </c>
       <c r="K86">
-        <v>1600.5339555876899</v>
+        <v>1.6005339555876901</v>
       </c>
       <c r="L86">
-        <v>17516.544619238401</v>
+        <v>17.516544619238399</v>
       </c>
       <c r="M86">
-        <v>5757.4097940000202</v>
+        <v>5.7574097940000204</v>
       </c>
       <c r="N86">
-        <v>24654.176621242401</v>
+        <v>24.654176621242399</v>
       </c>
       <c r="O86">
-        <v>8103.4359816747301</v>
+        <v>8.1034359816747301</v>
       </c>
       <c r="P86">
-        <v>14497.1737474949</v>
+        <v>14.4971737474949</v>
       </c>
       <c r="Q86">
-        <v>4764.9905808178901</v>
+        <v>4.7649905808178898</v>
       </c>
       <c r="R86">
-        <v>1333.5545806451601</v>
+        <v>1.3335545806451601</v>
       </c>
       <c r="S86">
-        <v>438.31819404652799</v>
+        <v>0.438318194046529</v>
       </c>
       <c r="T86">
-        <v>9996.3074428857708</v>
+        <v>9.9963074428857706</v>
       </c>
       <c r="U86">
-        <v>3285.6273669577199</v>
+        <v>3.2856273669577098</v>
       </c>
       <c r="V86">
-        <v>3256.4593548387002</v>
+        <v>3.2564593548387002</v>
       </c>
       <c r="W86">
-        <v>1070.3464290964901</v>
+        <v>1.0703464290964899</v>
       </c>
       <c r="X86">
-        <v>3714.00451612903</v>
+        <v>3.7140045161290298</v>
       </c>
       <c r="Y86">
-        <v>1220.73425101412</v>
+        <v>1.2207342510141199</v>
       </c>
       <c r="Z86" s="4"/>
       <c r="AA86" s="4"/>
@@ -11050,76 +11050,76 @@
         <v>0.875</v>
       </c>
       <c r="B87">
-        <v>15799.644517033999</v>
+        <v>15.799644517034</v>
       </c>
       <c r="C87">
-        <v>5193.0920202254702</v>
+        <v>5.1930920202254702</v>
       </c>
       <c r="D87">
-        <v>22264.249402372399</v>
+        <v>22.2642494023724</v>
       </c>
       <c r="E87">
-        <v>7317.90489229782</v>
+        <v>7.31790489229782</v>
       </c>
       <c r="F87">
-        <v>2966.8026903807599</v>
+        <v>2.9668026903807601</v>
       </c>
       <c r="G87">
-        <v>975.14088753004398</v>
+        <v>0.97514088753004402</v>
       </c>
       <c r="H87">
-        <v>10795.0392785571</v>
+        <v>10.7950392785571</v>
       </c>
       <c r="I87">
-        <v>3548.1578256432199</v>
+        <v>3.5481578256432198</v>
       </c>
       <c r="J87">
-        <v>4803.5133466933803</v>
+        <v>4.8035133466933804</v>
       </c>
       <c r="K87">
-        <v>1578.8384860726401</v>
+        <v>1.5788384860726401</v>
       </c>
       <c r="L87">
-        <v>17279.1053206412</v>
+        <v>17.2791053206412</v>
       </c>
       <c r="M87">
-        <v>5679.3672706063098</v>
+        <v>5.6793672706063099</v>
       </c>
       <c r="N87">
-        <v>24319.985687374701</v>
+        <v>24.3199856873747</v>
       </c>
       <c r="O87">
-        <v>7993.59273361752</v>
+        <v>7.9935927336175201</v>
       </c>
       <c r="P87">
-        <v>14300.662458249801</v>
+        <v>14.3006624582498</v>
       </c>
       <c r="Q87">
-        <v>4700.4004435548004</v>
+        <v>4.7004004435548001</v>
       </c>
       <c r="R87">
-        <v>1203.396</v>
+        <v>1.2033959999999999</v>
       </c>
       <c r="S87">
-        <v>395.53713743582301</v>
+        <v>0.39553713743582303</v>
       </c>
       <c r="T87">
-        <v>9860.8060480961904</v>
+        <v>9.8608060480961903</v>
       </c>
       <c r="U87">
-        <v>3241.0902122608099</v>
+        <v>3.2410902122608101</v>
       </c>
       <c r="V87">
-        <v>2938.62</v>
+        <v>2.9386199999999998</v>
       </c>
       <c r="W87">
-        <v>965.87768516071003</v>
+        <v>0.96587768516071004</v>
       </c>
       <c r="X87">
-        <v>3351.5075000000002</v>
+        <v>3.3515074999999999</v>
       </c>
       <c r="Y87">
-        <v>1101.5872436377399</v>
+        <v>1.1015872436377401</v>
       </c>
       <c r="Z87" s="4"/>
       <c r="AA87" s="4"/>
@@ -11174,76 +11174,76 @@
         <v>0.88541666666666696</v>
       </c>
       <c r="B88">
-        <v>15576.182567134199</v>
+        <v>15.5761825671342</v>
       </c>
       <c r="C88">
-        <v>5119.6436291811297</v>
+        <v>5.1196436291811303</v>
       </c>
       <c r="D88">
-        <v>21997.660007345599</v>
+        <v>21.997660007345601</v>
       </c>
       <c r="E88">
-        <v>7230.2811955432599</v>
+        <v>7.2302811955432604</v>
       </c>
       <c r="F88">
-        <v>2790.0937650300598</v>
+        <v>2.7900937650300599</v>
       </c>
       <c r="G88">
-        <v>917.05947252402996</v>
+        <v>0.91705947252402997</v>
       </c>
       <c r="H88">
-        <v>10680.4136272545</v>
+        <v>10.6804136272545</v>
       </c>
       <c r="I88">
-        <v>3510.4821960142799</v>
+        <v>3.51048219601428</v>
       </c>
       <c r="J88">
-        <v>4752.5078957915803</v>
+        <v>4.7525078957915801</v>
       </c>
       <c r="K88">
-        <v>1562.0738050837299</v>
+        <v>1.5620738050837299</v>
       </c>
       <c r="L88">
-        <v>17095.6294989979</v>
+        <v>17.095629498997901</v>
       </c>
       <c r="M88">
-        <v>5619.06168434753</v>
+        <v>5.6190616843475301</v>
       </c>
       <c r="N88">
-        <v>24061.747238476899</v>
+        <v>24.061747238476901</v>
       </c>
       <c r="O88">
-        <v>7908.7138601187798</v>
+        <v>7.9087138601187803</v>
       </c>
       <c r="P88">
-        <v>14148.812825651299</v>
+        <v>14.1488128256513</v>
       </c>
       <c r="Q88">
-        <v>4650.4898829424201</v>
+        <v>4.6504898829424199</v>
       </c>
       <c r="R88">
-        <v>1097.2139999999999</v>
+        <v>1.0972139999999999</v>
       </c>
       <c r="S88">
-        <v>360.636801779721</v>
+        <v>0.36063680177972102</v>
       </c>
       <c r="T88">
-        <v>9756.1004248496993</v>
+        <v>9.7561004248497003</v>
       </c>
       <c r="U88">
-        <v>3206.6751381768499</v>
+        <v>3.2066751381768501</v>
       </c>
       <c r="V88">
-        <v>2679.3299999999899</v>
+        <v>2.67932999999999</v>
       </c>
       <c r="W88">
-        <v>880.65318352888301</v>
+        <v>0.880653183528883</v>
       </c>
       <c r="X88">
-        <v>3055.7862500000001</v>
+        <v>3.0557862500000001</v>
       </c>
       <c r="Y88">
-        <v>1004.38836919912</v>
+        <v>1.00438836919912</v>
       </c>
       <c r="Z88" s="4"/>
       <c r="AA88" s="4"/>
@@ -11298,76 +11298,76 @@
         <v>0.89583333333333304</v>
       </c>
       <c r="B89">
-        <v>15375.0763486327</v>
+        <v>15.3750763486327</v>
       </c>
       <c r="C89">
-        <v>5053.5432117070504</v>
+        <v>5.0535432117070496</v>
       </c>
       <c r="D89">
-        <v>21690.360643289499</v>
+        <v>21.690360643289502</v>
       </c>
       <c r="E89">
-        <v>7129.2767790464504</v>
+        <v>7.1292767790464602</v>
       </c>
       <c r="F89">
-        <v>2647.7936426885999</v>
+        <v>2.6477936426886002</v>
       </c>
       <c r="G89">
-        <v>870.28768414538501</v>
+        <v>0.87028768414538504</v>
       </c>
       <c r="H89">
-        <v>10572.5306613226</v>
+        <v>10.572530661322601</v>
       </c>
       <c r="I89">
-        <v>3475.02277989292</v>
+        <v>3.4750227798929201</v>
       </c>
       <c r="J89">
-        <v>4704.5027655310596</v>
+        <v>4.7045027655310596</v>
       </c>
       <c r="K89">
-        <v>1546.2952818000599</v>
+        <v>1.5462952818000599</v>
       </c>
       <c r="L89">
-        <v>16922.946372745399</v>
+        <v>16.9229463727454</v>
       </c>
       <c r="M89">
-        <v>5562.3034855157402</v>
+        <v>5.5623034855157396</v>
       </c>
       <c r="N89">
-        <v>23818.699286573101</v>
+        <v>23.8186992865731</v>
       </c>
       <c r="O89">
-        <v>7828.8278615317204</v>
+        <v>7.8288278615317202</v>
       </c>
       <c r="P89">
-        <v>14005.8955243821</v>
+        <v>14.005895524382099</v>
       </c>
       <c r="Q89">
-        <v>4603.51523766017</v>
+        <v>4.6035152376601696</v>
       </c>
       <c r="R89">
-        <v>1012.72509677419</v>
+        <v>1.0127250967741901</v>
       </c>
       <c r="S89">
-        <v>332.86664222540298</v>
+        <v>0.33286664222540302</v>
       </c>
       <c r="T89">
-        <v>9657.5539559118206</v>
+        <v>9.6575539559118209</v>
       </c>
       <c r="U89">
-        <v>3174.28448021546</v>
+        <v>3.1742844802154599</v>
       </c>
       <c r="V89">
-        <v>2473.01322580645</v>
+        <v>2.4730132258064499</v>
       </c>
       <c r="W89">
-        <v>812.84013921968699</v>
+        <v>0.81284013921968701</v>
       </c>
       <c r="X89">
-        <v>2820.4811693548299</v>
+        <v>2.8204811693548302</v>
       </c>
       <c r="Y89">
-        <v>927.04732932322804</v>
+        <v>0.92704732932322798</v>
       </c>
       <c r="Z89" s="4"/>
       <c r="AA89" s="4"/>
@@ -11422,76 +11422,76 @@
         <v>0.90625</v>
       </c>
       <c r="B90">
-        <v>15147.8622045381</v>
+        <v>15.1478622045381</v>
       </c>
       <c r="C90">
-        <v>4978.8615340713304</v>
+        <v>4.9788615340713296</v>
       </c>
       <c r="D90">
-        <v>21282.456269604401</v>
+        <v>21.282456269604399</v>
       </c>
       <c r="E90">
-        <v>6995.2050949832301</v>
+        <v>6.9952050949832296</v>
       </c>
       <c r="F90">
-        <v>2532.9295583101598</v>
+        <v>2.5329295583101601</v>
       </c>
       <c r="G90">
-        <v>832.53368535427001</v>
+        <v>0.83253368535426997</v>
       </c>
       <c r="H90">
-        <v>10437.6769539078</v>
+        <v>10.4376769539078</v>
       </c>
       <c r="I90">
-        <v>3430.6985097412298</v>
+        <v>3.4306985097412301</v>
       </c>
       <c r="J90">
-        <v>4644.4963527054097</v>
+        <v>4.6444963527054099</v>
       </c>
       <c r="K90">
-        <v>1526.57212769547</v>
+        <v>1.52657212769547</v>
       </c>
       <c r="L90">
-        <v>16707.092464929799</v>
+        <v>16.707092464929801</v>
       </c>
       <c r="M90">
-        <v>5491.3557369759901</v>
+        <v>5.49135573697599</v>
       </c>
       <c r="N90">
-        <v>23514.8893466933</v>
+        <v>23.514889346693302</v>
       </c>
       <c r="O90">
-        <v>7728.9703632978899</v>
+        <v>7.7289703632978899</v>
       </c>
       <c r="P90">
-        <v>13827.2488977955</v>
+        <v>13.827248897795499</v>
       </c>
       <c r="Q90">
-        <v>4544.7969310573599</v>
+        <v>4.5447969310573599</v>
       </c>
       <c r="R90">
-        <v>947.645806451613</v>
+        <v>0.947645806451613</v>
       </c>
       <c r="S90">
-        <v>311.47611392005001</v>
+        <v>0.31147611392004998</v>
       </c>
       <c r="T90">
-        <v>9534.3708697394795</v>
+        <v>9.5343708697394796</v>
       </c>
       <c r="U90">
-        <v>3133.7961577637402</v>
+        <v>3.1337961577637401</v>
       </c>
       <c r="V90">
-        <v>2314.0935483870899</v>
+        <v>2.3140935483870901</v>
       </c>
       <c r="W90">
-        <v>760.60576725179305</v>
+        <v>0.76060576725179296</v>
       </c>
       <c r="X90">
-        <v>2639.2326612903198</v>
+        <v>2.6392326612903201</v>
       </c>
       <c r="Y90">
-        <v>867.47382563503902</v>
+        <v>0.86747382563503905</v>
       </c>
       <c r="Z90" s="4"/>
       <c r="AA90" s="4"/>
@@ -11546,76 +11546,76 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="B91">
-        <v>14844.7148649557</v>
+        <v>14.8447148649557</v>
       </c>
       <c r="C91">
-        <v>4879.2218220233299</v>
+        <v>4.8792218220233297</v>
       </c>
       <c r="D91">
-        <v>20721.123065202799</v>
+        <v>20.7211230652028</v>
       </c>
       <c r="E91">
-        <v>6810.7037929872804</v>
+        <v>6.8107037929872796</v>
       </c>
       <c r="F91">
-        <v>2434.97882749369</v>
+        <v>2.4349788274936901</v>
       </c>
       <c r="G91">
-        <v>800.33883704424295</v>
+        <v>0.80033883704424302</v>
       </c>
       <c r="H91">
-        <v>10242.1390781563</v>
+        <v>10.242139078156301</v>
       </c>
       <c r="I91">
-        <v>3366.4283180212701</v>
+        <v>3.3664283180212702</v>
       </c>
       <c r="J91">
-        <v>4557.48705410821</v>
+        <v>4.5574870541082104</v>
       </c>
       <c r="K91">
-        <v>1497.97355424381</v>
+        <v>1.49797355424381</v>
       </c>
       <c r="L91">
-        <v>16394.1042985971</v>
+        <v>16.3941042985971</v>
       </c>
       <c r="M91">
-        <v>5388.48150159337</v>
+        <v>5.38848150159337</v>
       </c>
       <c r="N91">
-        <v>23074.364933867699</v>
+        <v>23.074364933867699</v>
       </c>
       <c r="O91">
-        <v>7584.1769908588503</v>
+        <v>7.5841769908588503</v>
       </c>
       <c r="P91">
-        <v>13568.2112892451</v>
+        <v>13.568211289245101</v>
       </c>
       <c r="Q91">
-        <v>4459.6553864832904</v>
+        <v>4.4596553864832904</v>
       </c>
       <c r="R91">
-        <v>897.409161290322</v>
+        <v>0.897409161290322</v>
       </c>
       <c r="S91">
-        <v>294.96412715802302</v>
+        <v>0.294964127158023</v>
       </c>
       <c r="T91">
-        <v>9355.7553947895794</v>
+        <v>9.3557553947895702</v>
       </c>
       <c r="U91">
-        <v>3075.0880902087301</v>
+        <v>3.0750880902087299</v>
       </c>
       <c r="V91">
-        <v>2191.4187096774099</v>
+        <v>2.1914187096774098</v>
       </c>
       <c r="W91">
-        <v>720.28449766254096</v>
+        <v>0.72028449766254099</v>
       </c>
       <c r="X91">
-        <v>2499.32153225806</v>
+        <v>2.49932153225806</v>
       </c>
       <c r="Y91">
-        <v>821.48726138450695</v>
+        <v>0.82148726138450601</v>
       </c>
       <c r="Z91" s="4"/>
       <c r="AA91" s="4"/>
@@ -11670,76 +11670,76 @@
         <v>0.92708333333333304</v>
       </c>
       <c r="B92">
-        <v>14445.431899347001</v>
+        <v>14.445431899347</v>
       </c>
       <c r="C92">
-        <v>4747.9838577590999</v>
+        <v>4.7479838577590998</v>
       </c>
       <c r="D92">
-        <v>20004.37852527</v>
+        <v>20.004378525269999</v>
       </c>
       <c r="E92">
-        <v>6575.1212552376301</v>
+        <v>6.5751212552376304</v>
       </c>
       <c r="F92">
-        <v>2349.0223926077902</v>
+        <v>2.34902239260779</v>
       </c>
       <c r="G92">
-        <v>772.08632315940497</v>
+        <v>0.77208632315940495</v>
       </c>
       <c r="H92">
-        <v>9972.4316633266499</v>
+        <v>9.9724316633266508</v>
       </c>
       <c r="I92">
-        <v>3277.7797777178798</v>
+        <v>3.2777797777178801</v>
       </c>
       <c r="J92">
-        <v>4437.4742284569102</v>
+        <v>4.4374742284569102</v>
       </c>
       <c r="K92">
-        <v>1458.52724603462</v>
+        <v>1.4585272460346199</v>
       </c>
       <c r="L92">
-        <v>15962.3964829659</v>
+        <v>15.9623964829659</v>
       </c>
       <c r="M92">
-        <v>5246.5860045138897</v>
+        <v>5.2465860045138797</v>
       </c>
       <c r="N92">
-        <v>22466.7450541082</v>
+        <v>22.466745054108198</v>
       </c>
       <c r="O92">
-        <v>7384.4619943912003</v>
+        <v>7.3844619943912004</v>
       </c>
       <c r="P92">
-        <v>13210.9180360721</v>
+        <v>13.210918036072099</v>
       </c>
       <c r="Q92">
-        <v>4342.2187732776702</v>
+        <v>4.3422187732776703</v>
       </c>
       <c r="R92">
-        <v>859.73167741935401</v>
+        <v>0.85973167741935497</v>
       </c>
       <c r="S92">
-        <v>282.58013708650299</v>
+        <v>0.28258013708650298</v>
       </c>
       <c r="T92">
-        <v>9109.38922244489</v>
+        <v>9.1093892224448894</v>
       </c>
       <c r="U92">
-        <v>2994.1114453052701</v>
+        <v>2.9941114453052702</v>
       </c>
       <c r="V92">
-        <v>2099.4125806451598</v>
+        <v>2.09941258064516</v>
       </c>
       <c r="W92">
-        <v>690.043545470602</v>
+        <v>0.69004354547060198</v>
       </c>
       <c r="X92">
-        <v>2394.3881854838701</v>
+        <v>2.3943881854838698</v>
       </c>
       <c r="Y92">
-        <v>786.99733819660798</v>
+        <v>0.786997338196608</v>
       </c>
       <c r="Z92" s="4"/>
       <c r="AA92" s="4"/>
@@ -11794,76 +11794,76 @@
         <v>0.9375</v>
       </c>
       <c r="B93">
-        <v>13918.348049001201</v>
+        <v>13.918348049001199</v>
       </c>
       <c r="C93">
-        <v>4574.73977405394</v>
+        <v>4.5747397740539402</v>
       </c>
       <c r="D93">
-        <v>19131.896404009702</v>
+        <v>19.131896404009701</v>
       </c>
       <c r="E93">
-        <v>6288.3502499266397</v>
+        <v>6.2883502499266397</v>
       </c>
       <c r="F93">
-        <v>2264.1317478505398</v>
+        <v>2.2641317478505401</v>
       </c>
       <c r="G93">
-        <v>744.18411754931003</v>
+        <v>0.74418411754931002</v>
       </c>
       <c r="H93">
-        <v>9608.3266533066108</v>
+        <v>9.6083266533066105</v>
       </c>
       <c r="I93">
-        <v>3158.1042483083002</v>
+        <v>3.1581042483082999</v>
       </c>
       <c r="J93">
-        <v>4275.4569138276502</v>
+        <v>4.2754569138276501</v>
       </c>
       <c r="K93">
-        <v>1405.27472995222</v>
+        <v>1.4052747299522199</v>
       </c>
       <c r="L93">
-        <v>15379.5909318637</v>
+        <v>15.379590931863699</v>
       </c>
       <c r="M93">
-        <v>5055.0270834565799</v>
+        <v>5.0550270834565803</v>
       </c>
       <c r="N93">
-        <v>21646.458216432799</v>
+        <v>21.646458216432801</v>
       </c>
       <c r="O93">
-        <v>7114.8467491598803</v>
+        <v>7.1148467491598799</v>
       </c>
       <c r="P93">
-        <v>12728.572144288501</v>
+        <v>12.728572144288499</v>
       </c>
       <c r="Q93">
-        <v>4183.6793454500903</v>
+        <v>4.1836793454500896</v>
       </c>
       <c r="R93">
-        <v>828.90464516128998</v>
+        <v>0.82890464516129003</v>
       </c>
       <c r="S93">
-        <v>272.44778157344098</v>
+        <v>0.27244778157344102</v>
       </c>
       <c r="T93">
-        <v>8776.7948897795595</v>
+        <v>8.7767948897795591</v>
       </c>
       <c r="U93">
-        <v>2884.7929746856098</v>
+        <v>2.88479297468561</v>
       </c>
       <c r="V93">
-        <v>2024.13483870967</v>
+        <v>2.0241348387096698</v>
       </c>
       <c r="W93">
-        <v>665.30094822265198</v>
+        <v>0.66530094822265196</v>
       </c>
       <c r="X93">
-        <v>2308.5336290322498</v>
+        <v>2.30853362903225</v>
       </c>
       <c r="Y93">
-        <v>758.77831013378102</v>
+        <v>0.75877831013378105</v>
       </c>
       <c r="Z93" s="4"/>
       <c r="AA93" s="4"/>
@@ -11918,76 +11918,76 @@
         <v>0.94791666666666696</v>
       </c>
       <c r="B94">
-        <v>13260.740088111699</v>
+        <v>13.260740088111699</v>
       </c>
       <c r="C94">
-        <v>4358.5944898704702</v>
+        <v>4.3585944898704696</v>
       </c>
       <c r="D94">
-        <v>18127.683090511298</v>
+        <v>18.127683090511301</v>
       </c>
       <c r="E94">
-        <v>5958.2812955707204</v>
+        <v>5.9582812955707203</v>
       </c>
       <c r="F94">
-        <v>2173.2070545122401</v>
+        <v>2.1732070545122499</v>
       </c>
       <c r="G94">
-        <v>714.298616080751</v>
+        <v>0.71429861608075096</v>
       </c>
       <c r="H94">
-        <v>9149.8240480961904</v>
+        <v>9.1498240480961908</v>
       </c>
       <c r="I94">
-        <v>3007.4017297925402</v>
+        <v>3.0074017297925399</v>
       </c>
       <c r="J94">
-        <v>4071.43511022044</v>
+        <v>4.07143511022044</v>
       </c>
       <c r="K94">
-        <v>1338.21600599661</v>
+        <v>1.3382160059966099</v>
       </c>
       <c r="L94">
-        <v>14645.6876452905</v>
+        <v>14.645687645290501</v>
       </c>
       <c r="M94">
-        <v>4813.8047384214597</v>
+        <v>4.8138047384214602</v>
       </c>
       <c r="N94">
-        <v>20613.5044208416</v>
+        <v>20.613504420841601</v>
       </c>
       <c r="O94">
-        <v>6775.3312551648796</v>
+        <v>6.7753312551648799</v>
       </c>
       <c r="P94">
-        <v>12121.1736138944</v>
+        <v>12.121173613894401</v>
       </c>
       <c r="Q94">
-        <v>3984.0371030005399</v>
+        <v>3.9840371030005399</v>
       </c>
       <c r="R94">
-        <v>800.36109677419302</v>
+        <v>0.80036109677419298</v>
       </c>
       <c r="S94">
-        <v>263.06597091319901</v>
+        <v>0.263065970913199</v>
       </c>
       <c r="T94">
-        <v>8357.9723967935806</v>
+        <v>8.3579723967935795</v>
       </c>
       <c r="U94">
-        <v>2747.1326783497302</v>
+        <v>2.7471326783497299</v>
       </c>
       <c r="V94">
-        <v>1954.4332258064501</v>
+        <v>1.9544332258064501</v>
       </c>
       <c r="W94">
-        <v>642.39113595603203</v>
+        <v>0.64239113595603203</v>
       </c>
       <c r="X94">
-        <v>2229.0386693548298</v>
+        <v>2.2290386693548299</v>
       </c>
       <c r="Y94">
-        <v>732.64958044597802</v>
+        <v>0.73264958044597805</v>
       </c>
       <c r="Z94" s="4"/>
       <c r="AA94" s="4"/>
@@ -12042,76 +12042,76 @@
         <v>0.95833333333333304</v>
       </c>
       <c r="B95">
-        <v>12441.6235644191</v>
+        <v>12.4416235644191</v>
       </c>
       <c r="C95">
-        <v>4089.3639082433701</v>
+        <v>4.0893639082433699</v>
       </c>
       <c r="D95">
-        <v>16979.481753997399</v>
+        <v>16.979481753997401</v>
       </c>
       <c r="E95">
-        <v>5580.8857667134798</v>
+        <v>5.5808857667134797</v>
       </c>
       <c r="F95">
-        <v>2067.0947664684199</v>
+        <v>2.0670947664684198</v>
       </c>
       <c r="G95">
-        <v>679.42119363658401</v>
+        <v>0.67942119363658304</v>
       </c>
       <c r="H95">
-        <v>8576.6957915831608</v>
+        <v>8.5766957915831608</v>
       </c>
       <c r="I95">
-        <v>2819.0235816478298</v>
+        <v>2.81902358164783</v>
       </c>
       <c r="J95">
-        <v>3816.4078557114199</v>
+        <v>3.8164078557114198</v>
       </c>
       <c r="K95">
-        <v>1254.39260105209</v>
+        <v>1.2543926010520901</v>
       </c>
       <c r="L95">
-        <v>13728.308537074099</v>
+        <v>13.728308537074099</v>
       </c>
       <c r="M95">
-        <v>4512.2768071275596</v>
+        <v>4.5122768071275603</v>
       </c>
       <c r="N95">
-        <v>19322.312176352701</v>
+        <v>19.3223121763527</v>
       </c>
       <c r="O95">
-        <v>6350.9368876711396</v>
+        <v>6.3509368876711401</v>
       </c>
       <c r="P95">
-        <v>11361.925450901799</v>
+        <v>11.361925450901801</v>
       </c>
       <c r="Q95">
-        <v>3734.4842999386101</v>
+        <v>3.7344842999386101</v>
       </c>
       <c r="R95">
-        <v>769.53406451612898</v>
+        <v>0.76953406451612905</v>
       </c>
       <c r="S95">
-        <v>252.933615400137</v>
+        <v>0.25293361540013698</v>
       </c>
       <c r="T95">
-        <v>7834.4442805611197</v>
+        <v>7.8344442805611196</v>
       </c>
       <c r="U95">
-        <v>2575.0573079298902</v>
+        <v>2.5750573079298902</v>
       </c>
       <c r="V95">
-        <v>1879.1554838709601</v>
+        <v>1.8791554838709601</v>
       </c>
       <c r="W95">
-        <v>617.64853870808201</v>
+        <v>0.61764853870808201</v>
       </c>
       <c r="X95">
-        <v>2143.18411290322</v>
+        <v>2.1431841129032199</v>
       </c>
       <c r="Y95">
-        <v>704.43055238315196</v>
+        <v>0.704430552383152</v>
       </c>
       <c r="Z95" s="4"/>
       <c r="AA95" s="4"/>
@@ -12166,76 +12166,76 @@
         <v>0.96875</v>
       </c>
       <c r="B96">
-        <v>11508.781328463299</v>
+        <v>11.5087813284633</v>
       </c>
       <c r="C96">
-        <v>3782.7534926451899</v>
+        <v>3.78275349264519</v>
       </c>
       <c r="D96">
-        <v>15741.892412216999</v>
+        <v>15.741892412217</v>
       </c>
       <c r="E96">
-        <v>5174.1098213314899</v>
+        <v>5.1741098213314896</v>
       </c>
       <c r="F96">
-        <v>1950.9926890878501</v>
+        <v>1.95099268908785</v>
       </c>
       <c r="G96">
-        <v>641.260286223344</v>
+        <v>0.64126028622334397</v>
       </c>
       <c r="H96">
-        <v>7922.6553106212396</v>
+        <v>7.9226553106212396</v>
       </c>
       <c r="I96">
-        <v>2604.0508714121102</v>
+        <v>2.60405087141211</v>
       </c>
       <c r="J96">
-        <v>3525.3767535070101</v>
+        <v>3.5253767535070102</v>
       </c>
       <c r="K96">
-        <v>1158.7353036448101</v>
+        <v>1.15873530364481</v>
       </c>
       <c r="L96">
-        <v>12681.417084168301</v>
+        <v>12.6814170841683</v>
       </c>
       <c r="M96">
-        <v>4168.1802267098101</v>
+        <v>4.1681802267098096</v>
       </c>
       <c r="N96">
-        <v>17848.8339679358</v>
+        <v>17.8488339679358</v>
       </c>
       <c r="O96">
-        <v>5866.6280212370903</v>
+        <v>5.8666280212370898</v>
       </c>
       <c r="P96">
-        <v>10495.489311957201</v>
+        <v>10.495489311957201</v>
       </c>
       <c r="Q96">
-        <v>3449.7005129149902</v>
+        <v>3.44970051291499</v>
       </c>
       <c r="R96">
-        <v>737.56529032258004</v>
+        <v>0.73756529032258</v>
       </c>
       <c r="S96">
-        <v>242.425987460665</v>
+        <v>0.24242598746066499</v>
       </c>
       <c r="T96">
-        <v>7237.0063126252498</v>
+        <v>7.2370063126252502</v>
       </c>
       <c r="U96">
-        <v>2378.68894403901</v>
+        <v>2.37868894403901</v>
       </c>
       <c r="V96">
-        <v>1801.08967741935</v>
+        <v>1.8010896774193501</v>
       </c>
       <c r="W96">
-        <v>591.98954896946702</v>
+        <v>0.59198954896946698</v>
       </c>
       <c r="X96">
-        <v>2054.14975806451</v>
+        <v>2.0541497580645101</v>
       </c>
       <c r="Y96">
-        <v>675.16637513281296</v>
+        <v>0.67516637513281297</v>
       </c>
       <c r="Z96" s="4"/>
       <c r="AA96" s="4"/>
@@ -12290,76 +12290,76 @@
         <v>0.97916666666666696</v>
       </c>
       <c r="B97">
-        <v>10510.6770372357</v>
+        <v>10.5106770372357</v>
       </c>
       <c r="C97">
-        <v>3454.6924768078602</v>
+        <v>3.45469247680786</v>
       </c>
       <c r="D97">
-        <v>14453.015570723899</v>
+        <v>14.453015570723901</v>
       </c>
       <c r="E97">
-        <v>4750.4764899995798</v>
+        <v>4.7504764899995804</v>
       </c>
       <c r="F97">
-        <v>1831.8735874167601</v>
+        <v>1.83187358741676</v>
       </c>
       <c r="G97">
-        <v>602.10773088087399</v>
+        <v>0.60210773088087399</v>
       </c>
       <c r="H97">
-        <v>7221.4160320641204</v>
+        <v>7.2214160320641199</v>
       </c>
       <c r="I97">
-        <v>2373.5646666232901</v>
+        <v>2.3735646666232899</v>
       </c>
       <c r="J97">
-        <v>3213.3434068136198</v>
+        <v>3.2133434068136202</v>
       </c>
       <c r="K97">
-        <v>1056.1749023009299</v>
+        <v>1.0561749023009299</v>
       </c>
       <c r="L97">
-        <v>11558.976763527</v>
+        <v>11.558976763526999</v>
       </c>
       <c r="M97">
-        <v>3799.2519343031599</v>
+        <v>3.7992519343031601</v>
       </c>
       <c r="N97">
-        <v>16269.022280561099</v>
+        <v>16.269022280561099</v>
       </c>
       <c r="O97">
-        <v>5347.3690304212096</v>
+        <v>5.3473690304212198</v>
       </c>
       <c r="P97">
-        <v>9566.5268537074098</v>
+        <v>9.5665268537074102</v>
       </c>
       <c r="Q97">
-        <v>3144.3653185803801</v>
+        <v>3.1443653185803799</v>
       </c>
       <c r="R97">
-        <v>706.738258064516</v>
+        <v>0.70673825806451596</v>
       </c>
       <c r="S97">
-        <v>232.29363194760299</v>
+        <v>0.232293631947604</v>
       </c>
       <c r="T97">
-        <v>6596.4542645290503</v>
+        <v>6.5964542645290498</v>
       </c>
       <c r="U97">
-        <v>2168.1496672900198</v>
+        <v>2.1681496672900198</v>
       </c>
       <c r="V97">
-        <v>1725.81193548387</v>
+        <v>1.7258119354838699</v>
       </c>
       <c r="W97">
-        <v>567.24695172151803</v>
+        <v>0.56724695172151796</v>
       </c>
       <c r="X97">
-        <v>1968.2952016129</v>
+        <v>1.9682952016129001</v>
       </c>
       <c r="Y97">
-        <v>646.94734706998702</v>
+        <v>0.64694734706998702</v>
       </c>
       <c r="Z97" s="4"/>
       <c r="AA97" s="4"/>
@@ -12414,76 +12414,76 @@
         <v>0.98958333333333304</v>
       </c>
       <c r="B98">
-        <v>9496.4551541793207</v>
+        <v>9.4964551541793192</v>
       </c>
       <c r="C98">
-        <v>3121.3338647226301</v>
+        <v>3.1213338647226299</v>
       </c>
       <c r="D98">
-        <v>13158.022954584299</v>
+        <v>13.1580229545843</v>
       </c>
       <c r="E98">
-        <v>4324.8330007504801</v>
+        <v>4.3248330007504796</v>
       </c>
       <c r="F98">
-        <v>1718.4851861787999</v>
+        <v>1.7184851861788</v>
       </c>
       <c r="G98">
-        <v>564.83876568231301</v>
+        <v>0.56483876568231295</v>
       </c>
       <c r="H98">
-        <v>6506.6913827655299</v>
+        <v>6.5066913827655304</v>
       </c>
       <c r="I98">
-        <v>2138.6460348193</v>
+        <v>2.1386460348192999</v>
       </c>
       <c r="J98">
-        <v>2895.3094188376699</v>
+        <v>2.89530941883767</v>
       </c>
       <c r="K98">
-        <v>951.64218554659499</v>
+        <v>0.95164218554659497</v>
       </c>
       <c r="L98">
-        <v>10414.951052104199</v>
+        <v>10.4149510521042</v>
       </c>
       <c r="M98">
-        <v>3423.2288670425301</v>
+        <v>3.4232288670425302</v>
       </c>
       <c r="N98">
-        <v>14658.8295991983</v>
+        <v>14.658829599198301</v>
       </c>
       <c r="O98">
-        <v>4818.1242897819502</v>
+        <v>4.8181242897819496</v>
       </c>
       <c r="P98">
-        <v>8619.6997327989302</v>
+        <v>8.6196997327989298</v>
       </c>
       <c r="Q98">
-        <v>2833.1582935854999</v>
+        <v>2.8331582935855</v>
       </c>
       <c r="R98">
-        <v>680.47819354838703</v>
+        <v>0.68047819354838701</v>
       </c>
       <c r="S98">
-        <v>223.66236614018001</v>
+        <v>0.22366236614018001</v>
       </c>
       <c r="T98">
-        <v>5943.5839078156296</v>
+        <v>5.9435839078156301</v>
       </c>
       <c r="U98">
-        <v>1953.5615582958701</v>
+        <v>1.9535615582958701</v>
       </c>
       <c r="V98">
-        <v>1661.6864516129001</v>
+        <v>1.6616864516129</v>
       </c>
       <c r="W98">
-        <v>546.16992443622701</v>
+        <v>0.54616992443622703</v>
       </c>
       <c r="X98">
-        <v>1895.1598387096701</v>
+        <v>1.89515983870967</v>
       </c>
       <c r="Y98">
-        <v>622.90891575720798</v>
+        <v>0.62290891575720797</v>
       </c>
     </row>
   </sheetData>
@@ -12498,6 +12498,14 @@
     <protectedRange sqref="T3:W97" name="Plage1_13"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12510,14 +12518,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12852,6 +12852,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12864,14 +12872,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\max\github\rhtlab\grodent-magnenat-mini-projet-trey\input-data\load_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFE2FA2-D488-4079-9063-DC9C92B06CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC465387-EF23-46CE-8481-1C190EF93BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
@@ -633,76 +633,76 @@
       <c r="A3" s="1">
         <v>0</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <v>8.5226381321998803E-3</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>2.8012556882453699E-3</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>1.19123606148269E-2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>3.9154035892523097E-3</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>1.6149349002036299E-3</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>5.30803432595547E-4</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>5.8189374749499003E-3</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>1.91259225704566E-3</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="4">
         <v>2.5892767134268499E-3</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="4">
         <v>8.5105409961317303E-4</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="4">
         <v>9.3140961222444897E-3</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="4">
         <v>3.06139534948984E-3</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="4">
         <v>1.3109398905811601E-2</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="4">
         <v>4.3088510487894601E-3</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="4">
         <v>7.7086019372077401E-3</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="4">
         <v>2.5336949299111801E-3</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="4">
         <v>6.5878509677419299E-4</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="4">
         <v>2.1653219003839601E-4</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="4">
         <v>5.3153501683366701E-3</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="4">
         <v>1.74707111379205E-3</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="4">
         <v>1.60871322580645E-3</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="4">
         <v>5.2875846711359601E-4</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="4">
         <v>1.83474366935483E-3</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="4">
         <v>6.0305108119447905E-4</v>
       </c>
       <c r="Z3" s="4"/>
@@ -757,76 +757,76 @@
       <c r="A4" s="1">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <v>7.6269076065679699E-3</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>2.5068433019466599E-3</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>1.0764487513069999E-2</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>3.5381159459424599E-3</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>1.5239610060443401E-3</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>5.00901759599166E-4</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>5.1851250501001997E-3</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="4">
         <v>1.70426818733269E-3</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="4">
         <v>2.3072465731462902E-3</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="4">
         <v>7.5835527532158698E-4</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="4">
         <v>8.2995827555110199E-3</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="4">
         <v>2.7279409313530601E-3</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="4">
         <v>1.16814921883767E-2</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="4">
         <v>3.8395208070904898E-3</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="4">
         <v>6.8689627922511598E-3</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="4">
         <v>2.25771888887798E-3</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="4">
         <v>6.4165896774193501E-4</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="4">
         <v>2.10903103642251E-4</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="4">
         <v>4.7363896633266494E-3</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="4">
         <v>1.55677599826893E-3</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="4">
         <v>1.5668922580645099E-3</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="4">
         <v>5.1501257975362306E-4</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="4">
         <v>1.78704669354838E-3</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="4">
         <v>5.8737384338179699E-4</v>
       </c>
       <c r="Z4" s="4"/>
@@ -881,76 +881,76 @@
       <c r="A5" s="1">
         <v>2.0833333333333301E-2</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4">
         <v>6.8550040084685397E-3</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>2.2531308585209998E-3</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>9.7665013747645392E-3</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>3.2100937650926201E-3</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="4">
         <v>1.44543643003749E-3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="4">
         <v>4.7509197959980402E-4</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="4">
         <v>4.63896753507014E-3</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="4">
         <v>1.52475489321832E-3</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="4">
         <v>2.0642206012023998E-3</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="4">
         <v>6.7847650119798699E-4</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="4">
         <v>7.42537442885771E-3</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="4">
         <v>2.4406025497670999E-3</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="4">
         <v>1.04510619318637E-2</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="4">
         <v>3.43509793924351E-3</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="4">
         <v>6.1454439545758086E-3</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="4">
         <v>2.0199097471365998E-3</v>
       </c>
-      <c r="R5">
+      <c r="R5" s="4">
         <v>6.2681632258064501E-4</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="4">
         <v>2.0602456209892499E-4</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="4">
         <v>4.2374981643286498E-3</v>
       </c>
-      <c r="U5">
+      <c r="U5" s="4">
         <v>1.39279829233944E-3</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="4">
         <v>1.5306474193548299E-3</v>
       </c>
-      <c r="W5">
+      <c r="W5" s="4">
         <v>5.0309947737498092E-4</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="4">
         <v>1.74570931451612E-3</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" s="4">
         <v>5.7378690394413998E-4</v>
       </c>
       <c r="Z5" s="4"/>
@@ -1005,76 +1005,76 @@
       <c r="A6" s="1">
         <v>3.125E-2</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <v>6.2439281667205299E-3</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>2.0522799422796399E-3</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>8.9670063806560497E-3</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>2.9473124683590899E-3</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>1.3803244890587599E-3</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <v>4.5369071954275001E-4</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="4">
         <v>4.2074356713426801E-3</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="4">
         <v>1.3829172287328901E-3</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="4">
         <v>1.8722000801603201E-3</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="4">
         <v>6.1536240806329002E-4</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="4">
         <v>6.7346419238476897E-3</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="4">
         <v>2.2135697544399301E-3</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="4">
         <v>9.4788701242484886E-3</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="4">
         <v>3.1155539448952702E-3</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="4">
         <v>5.5737747494989899E-3</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="4">
         <v>1.8320111660076199E-3</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="4">
         <v>6.1311541935483809E-4</v>
       </c>
-      <c r="S6">
+      <c r="S6" s="4">
         <v>2.0152129298200801E-4</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="4">
         <v>3.8433122885771498E-3</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="4">
         <v>1.2632356604939099E-3</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="4">
         <v>1.4971906451612901E-3</v>
       </c>
-      <c r="W6">
+      <c r="W6" s="4">
         <v>4.92102767487003E-4</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="4">
         <v>1.70755173387096E-3</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" s="4">
         <v>5.6124511369399501E-4</v>
       </c>
       <c r="Z6" s="4"/>
@@ -1129,76 +1129,76 @@
       <c r="A7" s="1">
         <v>4.1666666666666699E-2</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <v>5.8219413077768402E-3</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>1.9135795691504901E-3</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>8.4038967281452708E-3</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>2.762227276106E-3</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>1.3306788905229801E-3</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="4">
         <v>4.37373000411948E-4</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="4">
         <v>3.9107575150300602E-3</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="4">
         <v>1.28540383439917E-3</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="4">
         <v>1.74018597194388E-3</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="4">
         <v>5.7197146903318697E-4</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="4">
         <v>6.2597633266533014E-3</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="4">
         <v>2.0574847076525E-3</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="4">
         <v>8.8104882565130209E-3</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="4">
         <v>2.89586744878086E-3</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="4">
         <v>5.1807521710086797E-3</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="4">
         <v>1.7028308914814399E-3</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="4">
         <v>6.0055625806451597E-4</v>
       </c>
-      <c r="S7">
+      <c r="S7" s="4">
         <v>1.9739329629150099E-4</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="4">
         <v>3.5723094989979901E-3</v>
       </c>
-      <c r="U7">
+      <c r="U7" s="4">
         <v>1.1741613511000999E-3</v>
       </c>
-      <c r="V7">
+      <c r="V7" s="4">
         <v>1.46652193548387E-3</v>
       </c>
-      <c r="W7">
+      <c r="W7" s="4">
         <v>4.8202245008968999E-4</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="4">
         <v>1.6725739516128999E-3</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" s="4">
         <v>5.4974847263136197E-4</v>
       </c>
       <c r="Z7" s="4"/>
@@ -1253,76 +1253,76 @@
       <c r="A8" s="1">
         <v>5.2083333333333301E-2</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <v>5.5607822051845597E-3</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>1.8277407232056299E-3</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>8.0434114896635999E-3</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>2.6437415080654602E-3</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="4">
         <v>1.2944459270153199E-3</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="4">
         <v>4.2546380122345401E-4</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="4">
         <v>3.72870501002004E-3</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="4">
         <v>1.22556606969438E-3</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="4">
         <v>1.6591773146292499E-3</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="4">
         <v>5.4534521099198693E-4</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="4">
         <v>5.9683605511022001E-3</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="4">
         <v>1.9617052471238498E-3</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="4">
         <v>8.4003448376753498E-3</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="4">
         <v>2.7610598261651998E-3</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="4">
         <v>4.9395792251169003E-3</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="4">
         <v>1.62356117756765E-3</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="4">
         <v>5.8913883870967702E-4</v>
       </c>
-      <c r="S8">
+      <c r="S8" s="4">
         <v>1.9364057202740401E-4</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="4">
         <v>3.4060123326653301E-3</v>
       </c>
-      <c r="U8">
+      <c r="U8" s="4">
         <v>1.11950211579027E-3</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="4">
         <v>1.43864129032258E-3</v>
       </c>
-      <c r="W8">
+      <c r="W8" s="4">
         <v>4.7285852518304201E-4</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="4">
         <v>1.6407759677419299E-3</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" s="4">
         <v>5.3929698075624096E-4</v>
       </c>
       <c r="Z8" s="4"/>
@@ -1377,76 +1377,76 @@
       <c r="A9" s="1">
         <v>6.25E-2</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <v>5.3951888036718604E-3</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>1.7733128042059E-3</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>7.8031855568968297E-3</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>2.5647830623132602E-3</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="4">
         <v>1.2686085742452599E-3</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="4">
         <v>4.169714740480381E-4</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="4">
         <v>3.61407935871743E-3</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="4">
         <v>1.1878904400654301E-3</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="4">
         <v>1.6081718637274501E-3</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="4">
         <v>5.2858053000308304E-4</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="4">
         <v>5.7848847294589096E-3</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="4">
         <v>1.9013996608650699E-3</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="4">
         <v>8.1421063887775515E-3</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="4">
         <v>2.6761809526664499E-3</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="4">
         <v>4.7877295925183704E-3</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="4">
         <v>1.5736506169552601E-3</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="4">
         <v>5.8000490322580596E-4</v>
       </c>
-      <c r="S9">
+      <c r="S9" s="4">
         <v>1.90638392616127E-4</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="4">
         <v>3.30130670941883E-3</v>
       </c>
-      <c r="U9">
+      <c r="U9" s="4">
         <v>1.0850870417063001E-3</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="4">
         <v>1.41633677419354E-3</v>
       </c>
-      <c r="W9">
+      <c r="W9" s="4">
         <v>4.6552738525772397E-4</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="4">
         <v>1.6153375806451601E-3</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" s="4">
         <v>5.3093578725614402E-4</v>
       </c>
       <c r="Z9" s="4"/>
@@ -1501,76 +1501,76 @@
       <c r="A10" s="1">
         <v>7.2916666666666699E-2</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="4">
         <v>5.2780590591505498E-3</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
         <v>1.7348141189380899E-3</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="4">
         <v>7.6308307661393897E-3</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="4">
         <v>2.50813278213986E-3</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="4">
         <v>1.2497439865214301E-3</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="4">
         <v>4.1077098391246103E-4</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="4">
         <v>3.5331671342685301E-3</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="4">
         <v>1.1612958779744201E-3</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="4">
         <v>1.5721680160320601E-3</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="4">
         <v>5.1674663754032707E-4</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="4">
         <v>5.6553723847695397E-3</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="4">
         <v>1.85883101174122E-3</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="4">
         <v>7.9598204248497E-3</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="4">
         <v>2.6162664537261598E-3</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="4">
         <v>4.6805416165664601E-3</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="4">
         <v>1.53841963299357E-3</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="4">
         <v>5.7315445161290298E-4</v>
       </c>
-      <c r="S10">
+      <c r="S10" s="4">
         <v>1.8838675805766899E-4</v>
       </c>
-      <c r="T10">
+      <c r="T10" s="4">
         <v>3.2273968577154299E-3</v>
       </c>
-      <c r="U10">
+      <c r="U10" s="4">
         <v>1.06079404823527E-3</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="4">
         <v>1.3996083870967701E-3</v>
       </c>
-      <c r="W10">
+      <c r="W10" s="4">
         <v>4.6002903031373501E-4</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="4">
         <v>1.5962587903225801E-3</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" s="4">
         <v>5.2466489213107105E-4</v>
       </c>
       <c r="Z10" s="4"/>
@@ -1625,76 +1625,76 @@
       <c r="A11" s="1">
         <v>8.3333333333333301E-2</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="4">
         <v>5.1737537557049497E-3</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
         <v>1.70053062360966E-3</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="4">
         <v>7.4798095715617506E-3</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="4">
         <v>2.4584945159370698E-3</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="4">
         <v>1.2404387663229599E-3</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="4">
         <v>4.0771250593803698E-4</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="4">
         <v>3.4589975951903802E-3</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="4">
         <v>1.1369175293909799E-3</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="4">
         <v>1.5391644889779499E-3</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="4">
         <v>5.0589890278280106E-4</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="4">
         <v>5.5366527354709406E-3</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="4">
         <v>1.8198097500443701E-3</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="4">
         <v>7.79272495791583E-3</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="4">
         <v>2.5613448296975499E-3</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="4">
         <v>4.5822859719438797E-3</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="4">
         <v>1.5061245643620299E-3</v>
       </c>
-      <c r="R11">
+      <c r="R11" s="4">
         <v>5.7201270967741904E-4</v>
       </c>
-      <c r="S11">
+      <c r="S11" s="4">
         <v>1.88011485631259E-4</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="4">
         <v>3.1596461603206399E-3</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="4">
         <v>1.03852547088682E-3</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="4">
         <v>1.3968203225806399E-3</v>
       </c>
-      <c r="W11">
+      <c r="W11" s="4">
         <v>4.5911263782306999E-4</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="4">
         <v>1.5930789919354801E-3</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" s="4">
         <v>5.236197429435589E-4</v>
       </c>
       <c r="Z11" s="4"/>
@@ -1749,76 +1749,76 @@
       <c r="A12" s="1">
         <v>9.375E-2</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="4">
         <v>5.0802304739802099E-3</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="4">
         <v>1.6697910074425801E-3</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="4">
         <v>7.3504124114185899E-3</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="4">
         <v>2.4159637261427299E-3</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="4">
         <v>1.2353680346176199E-3</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="4">
         <v>4.0604583702486398E-4</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="4">
         <v>3.3915707414829601E-3</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="4">
         <v>1.11475539431514E-3</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="4">
         <v>1.5091612825651299E-3</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="4">
         <v>4.9603732573050502E-4</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="4">
         <v>5.4287257815631203E-3</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="4">
         <v>1.7843358757745E-3</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="4">
         <v>7.6408199879759503E-3</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="4">
         <v>2.5114160805806401E-3</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="4">
         <v>4.4929626586506302E-3</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="4">
         <v>1.4767654110606199E-3</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="4">
         <v>5.7315445161290298E-4</v>
       </c>
-      <c r="S12">
+      <c r="S12" s="4">
         <v>1.8838675805766899E-4</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="4">
         <v>3.09805461723446E-3</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="4">
         <v>1.0182813096609501E-3</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="4">
         <v>1.3996083870967701E-3</v>
       </c>
-      <c r="W12">
+      <c r="W12" s="4">
         <v>4.6002903031373501E-4</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="4">
         <v>1.5962587903225801E-3</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" s="4">
         <v>5.2466489213107105E-4</v>
       </c>
       <c r="Z12" s="4"/>
@@ -1873,76 +1873,76 @@
       <c r="A13" s="1">
         <v>0.104166666666667</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="4">
         <v>4.9772867834378407E-3</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="4">
         <v>1.6359550526328401E-3</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="4">
         <v>7.2150194142720399E-3</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="4">
         <v>2.3714622000281299E-3</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="4">
         <v>1.2296127337739901E-3</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="4">
         <v>4.0415416111704201E-4</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="4">
         <v>3.3174012024048002E-3</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="4">
         <v>1.0903770457316999E-3</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="4">
         <v>1.4761577555110199E-3</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="4">
         <v>4.8518959097297901E-4</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="4">
         <v>5.3100061322645196E-3</v>
       </c>
-      <c r="M13">
+      <c r="M13" s="4">
         <v>1.7453146140776401E-3</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="4">
         <v>7.4737245210420803E-3</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="4">
         <v>2.4564944565520401E-3</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="4">
         <v>4.3947070140280499E-3</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="4">
         <v>1.4444703424290801E-3</v>
       </c>
-      <c r="R13">
+      <c r="R13" s="4">
         <v>5.7429619354838703E-4</v>
       </c>
-      <c r="S13">
+      <c r="S13" s="4">
         <v>1.88762030484078E-4</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="4">
         <v>3.03030391983967E-3</v>
       </c>
-      <c r="U13">
+      <c r="U13" s="4">
         <v>9.9601273231250589E-4</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="4">
         <v>1.4023964516129001E-3</v>
       </c>
-      <c r="W13">
+      <c r="W13" s="4">
         <v>4.6094542280439901E-4</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="4">
         <v>1.5994385887096701E-3</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" s="4">
         <v>5.2571004131858406E-4</v>
       </c>
       <c r="Z13" s="4"/>
@@ -1997,76 +1997,76 @@
       <c r="A14" s="1">
         <v>0.114583333333333</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="4">
         <v>4.89182229762751E-3</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="4">
         <v>1.6078642345897E-3</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="4">
         <v>7.1096033617341001E-3</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="4">
         <v>2.3368136191282102E-3</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="4">
         <v>1.22167665185209E-3</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="4">
         <v>4.01545697131914E-4</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="4">
         <v>3.2567170340681299E-3</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="4">
         <v>1.0704311241634401E-3</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="4">
         <v>1.4491548697394699E-3</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="4">
         <v>4.7631417162591198E-4</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="4">
         <v>5.2128718737474902E-3</v>
       </c>
-      <c r="M14">
+      <c r="M14" s="4">
         <v>1.71338812723475E-3</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="4">
         <v>7.3370100480961908E-3</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="4">
         <v>2.4115585823468199E-3</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="4">
         <v>4.3143160320641199E-3</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="4">
         <v>1.41804710445782E-3</v>
       </c>
-      <c r="R14">
+      <c r="R14" s="4">
         <v>5.7315445161290298E-4</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="4">
         <v>1.8838675805766899E-4</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="4">
         <v>2.9748715310621201E-3</v>
       </c>
-      <c r="U14">
+      <c r="U14" s="4">
         <v>9.7779298720922811E-4</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="4">
         <v>1.3996083870967701E-3</v>
       </c>
-      <c r="W14">
+      <c r="W14" s="4">
         <v>4.6002903031373501E-4</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="4">
         <v>1.5962587903225801E-3</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="4">
         <v>5.2466489213107105E-4</v>
       </c>
       <c r="Z14" s="4"/>
@@ -2121,76 +2121,76 @@
       <c r="A15" s="1">
         <v>0.125</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="4">
         <v>4.8144166077315901E-3</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="4">
         <v>1.5824222146705101E-3</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="4">
         <v>7.0194662197551397E-3</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="4">
         <v>2.3071869732734702E-3</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="4">
         <v>1.2108752197136201E-3</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="4">
         <v>3.9799543807482999E-4</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="4">
         <v>3.2027755511022001E-3</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="4">
         <v>1.05270141610276E-3</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="4">
         <v>1.4251523046092101E-3</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="4">
         <v>4.6842490998407502E-4</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="4">
         <v>5.1265303106212386E-3</v>
       </c>
-      <c r="M15">
+      <c r="M15" s="4">
         <v>1.68500902781886E-3</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="4">
         <v>7.2154860721442803E-3</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="4">
         <v>2.3716155830532902E-3</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="4">
         <v>4.24285738142952E-3</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="4">
         <v>1.39455978181669E-3</v>
       </c>
-      <c r="R15">
+      <c r="R15" s="4">
         <v>5.6972922580645106E-4</v>
       </c>
-      <c r="S15">
+      <c r="S15" s="4">
         <v>1.8726094077844001E-4</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="4">
         <v>2.9255982965931799E-3</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="4">
         <v>9.6159765822853701E-4</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="4">
         <v>1.39124419354838E-3</v>
       </c>
-      <c r="W15">
+      <c r="W15" s="4">
         <v>4.5727985284173999E-4</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="4">
         <v>1.5867193951612901E-3</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" s="4">
         <v>5.2152944456853505E-4</v>
       </c>
       <c r="Z15" s="4"/>
@@ -2245,76 +2245,76 @@
       <c r="A16" s="1">
         <v>0.13541666666666699</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="4">
         <v>4.7531285096644796E-3</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="4">
         <v>1.5622777909992101E-3</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="4">
         <v>6.9615178764281804E-3</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="4">
         <v>2.2881402739004502E-3</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="4">
         <v>1.19434308714202E-3</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="4">
         <v>3.9256158887383699E-4</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="4">
         <v>3.1623194388777499E-3</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="4">
         <v>1.03940413505725E-3</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="4">
         <v>1.40715038076152E-3</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="4">
         <v>4.6250796375269697E-4</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="4">
         <v>5.0617741382765497E-3</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="4">
         <v>1.66372470325693E-3</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="4">
         <v>7.1243430901803597E-3</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="4">
         <v>2.3416583335831402E-3</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="4">
         <v>4.1892633934535704E-3</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="4">
         <v>1.3769442898358499E-3</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="4">
         <v>5.6173703225806404E-4</v>
       </c>
-      <c r="S16">
+      <c r="S16" s="4">
         <v>1.8463403379357201E-4</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="4">
         <v>2.8886433707414798E-3</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="4">
         <v>9.4945116149301896E-4</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="4">
         <v>1.37172774193548E-3</v>
       </c>
-      <c r="W16">
+      <c r="W16" s="4">
         <v>4.5086510540708698E-4</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="4">
         <v>1.5644608064516101E-3</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="4">
         <v>5.1421340025595101E-4</v>
       </c>
       <c r="Z16" s="4"/>
@@ -2369,76 +2369,76 @@
       <c r="A17" s="1">
         <v>0.14583333333333301</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="4">
         <v>4.7106812292326593E-3</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="4">
         <v>1.5483260446131999E-3</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="4">
         <v>6.9421034556287203E-3</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>2.2817590623724201E-3</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="4">
         <v>1.17918009284698E-3</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="4">
         <v>3.87577753662139E-4</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="4">
         <v>3.13534869739479E-3</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="4">
         <v>1.0305392810269201E-3</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="4">
         <v>1.3951490981963901E-3</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="4">
         <v>4.5856333293177898E-4</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="4">
         <v>5.01860335671342E-3</v>
       </c>
-      <c r="M17">
+      <c r="M17" s="4">
         <v>1.6495351535489901E-3</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="4">
         <v>7.0635811022043997E-3</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="4">
         <v>2.3216868339363799E-3</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="4">
         <v>4.1535340681362696E-3</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="4">
         <v>1.36520062851529E-3</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="4">
         <v>5.5374483870967691E-4</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="4">
         <v>1.8200712680870401E-4</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="4">
         <v>2.8640067535070099E-3</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="4">
         <v>9.4135349700267298E-4</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="4">
         <v>1.3522112903225801E-3</v>
       </c>
-      <c r="W17">
+      <c r="W17" s="4">
         <v>4.4445035797243299E-4</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="4">
         <v>1.5422022177419301E-3</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" s="4">
         <v>5.06897355943366E-4</v>
       </c>
       <c r="Z17" s="4"/>
@@ -2493,76 +2493,76 @@
       <c r="A18" s="1">
         <v>0.15625</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="4">
         <v>4.7160167993406102E-3</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="4">
         <v>1.5500797616997499E-3</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="4">
         <v>6.9944030084160202E-3</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="4">
         <v>2.29894909408156E-3</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="4">
         <v>1.1692149039207399E-3</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="4">
         <v>3.8430235445697998E-4</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="4">
         <v>3.1420913827655298E-3</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="4">
         <v>1.0327554945344999E-3</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="4">
         <v>1.3981494188376701E-3</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="4">
         <v>4.5954949063700798E-4</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="4">
         <v>5.0293960521042014E-3</v>
       </c>
-      <c r="M18">
+      <c r="M18" s="4">
         <v>1.6530825409759699E-3</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="4">
         <v>7.0787715991983899E-3</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="4">
         <v>2.32667970884807E-3</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="4">
         <v>4.16246639946559E-3</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="4">
         <v>1.3681365438454299E-3</v>
       </c>
-      <c r="R18">
+      <c r="R18" s="4">
         <v>5.4689438709677393E-4</v>
       </c>
-      <c r="S18">
+      <c r="S18" s="4">
         <v>1.7975549225024599E-4</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="4">
         <v>2.87016590781563E-3</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="4">
         <v>9.4337791312525999E-4</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="4">
         <v>1.3354829032258E-3</v>
       </c>
-      <c r="W18">
+      <c r="W18" s="4">
         <v>4.3895200302844403E-4</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="4">
         <v>1.5231234274193501E-3</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" s="4">
         <v>5.0062646081829303E-4</v>
       </c>
       <c r="Z18" s="4"/>
@@ -2617,76 +2617,76 @@
       <c r="A19" s="1">
         <v>0.16666666666666699</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="4">
         <v>4.75971481117072E-3</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="4">
         <v>1.56444260361623E-3</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="4">
         <v>7.1100636246159499E-3</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="4">
         <v>2.3369649002216702E-3</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="4">
         <v>1.16376295122503E-3</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="4">
         <v>3.8251038426371202E-4</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="4">
         <v>3.1758048096192301E-3</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="4">
         <v>1.0438365620724201E-3</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="4">
         <v>1.41315102204408E-3</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="4">
         <v>4.6448027916315703E-4</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="4">
         <v>5.0833595290581098E-3</v>
       </c>
-      <c r="M19">
+      <c r="M19" s="4">
         <v>1.6708194781109101E-3</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="4">
         <v>7.1547240841683298E-3</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="4">
         <v>2.3516440834065299E-3</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="4">
         <v>4.20712805611222E-3</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="4">
         <v>1.38281612049613E-3</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="4">
         <v>5.4118567741935392E-4</v>
       </c>
-      <c r="S19">
+      <c r="S19" s="4">
         <v>1.7787913011819699E-4</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="4">
         <v>2.90096167935871E-3</v>
       </c>
-      <c r="U19">
+      <c r="U19" s="4">
         <v>9.5349999373819201E-4</v>
       </c>
-      <c r="V19">
+      <c r="V19" s="4">
         <v>1.32154258064516E-3</v>
       </c>
-      <c r="W19">
+      <c r="W19" s="4">
         <v>4.3437004057511998E-4</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="4">
         <v>1.50722443548387E-3</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" s="4">
         <v>4.9540071488073296E-4</v>
       </c>
       <c r="Z19" s="4"/>
@@ -2741,76 +2741,76 @@
       <c r="A20" s="1">
         <v>0.17708333333333301</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="4">
         <v>4.8431368776262196E-3</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="4">
         <v>1.5918621108813201E-3</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="4">
         <v>7.27831647226622E-3</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="4">
         <v>2.3922669368953999E-3</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="4">
         <v>1.16637415411468E-3</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="4">
         <v>3.8336864514893702E-4</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="4">
         <v>3.2364889779559099E-3</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="4">
         <v>1.0637824836406901E-3</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="4">
         <v>1.44015390781563E-3</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="4">
         <v>4.7335569851022298E-4</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="4">
         <v>5.1804937875751496E-3</v>
       </c>
-      <c r="M20">
+      <c r="M20" s="4">
         <v>1.7027459649537899E-3</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="4">
         <v>7.2914385571142297E-3</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="4">
         <v>2.3965799576117501E-3</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="4">
         <v>4.2875190380761499E-3</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="4">
         <v>1.4092393584673999E-3</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="4">
         <v>5.3890219354838702E-4</v>
       </c>
-      <c r="S20">
+      <c r="S20" s="4">
         <v>1.7712858526537799E-4</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="4">
         <v>2.9563940681362698E-3</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="4">
         <v>9.7171973884146903E-4</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="4">
         <v>1.3159664516129001E-3</v>
       </c>
-      <c r="W20">
+      <c r="W20" s="4">
         <v>4.3253725559378998E-4</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="4">
         <v>1.50086483870967E-3</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" s="4">
         <v>4.93310416505709E-4</v>
       </c>
       <c r="Z20" s="4"/>
@@ -2865,76 +2865,76 @@
       <c r="A21" s="1">
         <v>0.1875</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="4">
         <v>4.9669638051587006E-3</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="4">
         <v>1.63256205375439E-3</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="4">
         <v>7.4929616466186798E-3</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="4">
         <v>2.4628173939584001E-3</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="4">
         <v>1.17882347226711E-3</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="4">
         <v>3.87460538145957E-4</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="4">
         <v>3.32414388777555E-3</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="4">
         <v>1.09259325923929E-3</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="4">
         <v>1.4791580761522999E-3</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="4">
         <v>4.8617574867820801E-4</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="4">
         <v>5.3207988276553096E-3</v>
       </c>
-      <c r="M21">
+      <c r="M21" s="4">
         <v>1.7488620015046301E-3</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="4">
         <v>7.4889150180360697E-3</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="4">
         <v>2.4614873314637302E-3</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="4">
         <v>4.4036393453573798E-3</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="4">
         <v>1.44740625775922E-3</v>
       </c>
-      <c r="R21">
+      <c r="R21" s="4">
         <v>5.4118567741935392E-4</v>
       </c>
-      <c r="S21">
+      <c r="S21" s="4">
         <v>1.7787913011819699E-4</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="4">
         <v>3.03646307414829E-3</v>
       </c>
-      <c r="U21">
+      <c r="U21" s="4">
         <v>9.9803714843509301E-4</v>
       </c>
-      <c r="V21">
+      <c r="V21" s="4">
         <v>1.32154258064516E-3</v>
       </c>
-      <c r="W21">
+      <c r="W21" s="4">
         <v>4.3437004057511998E-4</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="4">
         <v>1.50722443548387E-3</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" s="4">
         <v>4.9540071488073296E-4</v>
       </c>
       <c r="Z21" s="4"/>
@@ -2989,76 +2989,76 @@
       <c r="A22" s="1">
         <v>0.19791666666666699</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="4">
         <v>5.1116739696812899E-3</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="4">
         <v>1.6801259846907801E-3</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="4">
         <v>7.7157556634004998E-3</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="4">
         <v>2.5360462460035302E-3</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="4">
         <v>1.1979668077283501E-3</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="4">
         <v>3.93752648232175E-4</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="4">
         <v>3.4252841683366699E-3</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="4">
         <v>1.12583646185306E-3</v>
       </c>
-      <c r="J22">
+      <c r="J22" s="4">
         <v>1.52416288577154E-3</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="4">
         <v>5.0096811425665304E-4</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="4">
         <v>5.4826892585170296E-3</v>
       </c>
-      <c r="M22">
+      <c r="M22" s="4">
         <v>1.8020728129094299E-3</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="4">
         <v>7.7167724729458901E-3</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="4">
         <v>2.5363804551391E-3</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="4">
         <v>4.5376243152972602E-3</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="4">
         <v>1.49144498771133E-3</v>
       </c>
-      <c r="R22">
+      <c r="R22" s="4">
         <v>5.4689438709677393E-4</v>
       </c>
-      <c r="S22">
+      <c r="S22" s="4">
         <v>1.7975549225024599E-4</v>
       </c>
-      <c r="T22">
+      <c r="T22" s="4">
         <v>3.1288503887775499E-3</v>
       </c>
-      <c r="U22">
+      <c r="U22" s="4">
         <v>1.0284033902738801E-3</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="4">
         <v>1.3354829032258E-3</v>
       </c>
-      <c r="W22">
+      <c r="W22" s="4">
         <v>4.3895200302844403E-4</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="4">
         <v>1.5231234274193501E-3</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" s="4">
         <v>5.0062646081829303E-4</v>
       </c>
       <c r="Z22" s="4"/>
@@ -3113,76 +3113,76 @@
       <c r="A23" s="1">
         <v>0.20833333333333301</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="4">
         <v>5.2974698017324894E-3</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="4">
         <v>1.74119412149449E-3</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="4">
         <v>7.9566235617024202E-3</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="4">
         <v>2.6152156956232098E-3</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="4">
         <v>1.2287232181298E-3</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="4">
         <v>4.03861791463488E-4</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="4">
         <v>3.5533951903807602E-3</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="4">
         <v>1.1679445184971701E-3</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="4">
         <v>1.58116897795591E-3</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="4">
         <v>5.1970511065601601E-4</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="4">
         <v>5.6877504709418793E-3</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="4">
         <v>1.8694731740221901E-3</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="4">
         <v>8.0053919158316611E-3</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="4">
         <v>2.6312450784612301E-3</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="4">
         <v>4.7073386105544396E-3</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="4">
         <v>1.54722737898399E-3</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="4">
         <v>5.5831180645161309E-4</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="4">
         <v>1.83508216514343E-4</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="4">
         <v>3.2458743206412802E-3</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="4">
         <v>1.0668672966030301E-3</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="4">
         <v>1.3633635483870899E-3</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="4">
         <v>4.4811592793509201E-4</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="4">
         <v>1.5549214112903201E-3</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="4">
         <v>5.1107795269341404E-4</v>
       </c>
       <c r="Z23" s="4"/>
@@ -3237,76 +3237,76 @@
       <c r="A24" s="1">
         <v>0.21875</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="4">
         <v>5.5829161735729497E-3</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="4">
         <v>1.83501580679942E-3</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="4">
         <v>8.2867848091117517E-3</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="4">
         <v>2.7237344497926899E-3</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="4">
         <v>1.2805249973333701E-3</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="4">
         <v>4.2088821290768601E-4</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="4">
         <v>3.7489330661322601E-3</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="4">
         <v>1.23221471021713E-3</v>
       </c>
-      <c r="J24">
+      <c r="J24" s="4">
         <v>1.6681782765531001E-3</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="4">
         <v>5.4830368410767501E-4</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="4">
         <v>6.0007386372745494E-3</v>
       </c>
-      <c r="M24">
+      <c r="M24" s="4">
         <v>1.9723474094048101E-3</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="4">
         <v>8.4459163286573092E-3</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="4">
         <v>2.77603845090027E-3</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="4">
         <v>4.9663762191048686E-3</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="4">
         <v>1.63236892355807E-3</v>
       </c>
-      <c r="R24">
+      <c r="R24" s="4">
         <v>5.7886316129032202E-4</v>
       </c>
-      <c r="S24">
+      <c r="S24" s="4">
         <v>1.9026312018971699E-4</v>
       </c>
-      <c r="T24">
+      <c r="T24" s="4">
         <v>3.4244897955911799E-3</v>
       </c>
-      <c r="U24">
+      <c r="U24" s="4">
         <v>1.1255753641580301E-3</v>
       </c>
-      <c r="V24">
+      <c r="V24" s="4">
         <v>1.4135487096774101E-3</v>
       </c>
-      <c r="W24">
+      <c r="W24" s="4">
         <v>4.6461099276705889E-4</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="4">
         <v>1.6121577822580601E-3</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" s="4">
         <v>5.2989063806863199E-4</v>
       </c>
       <c r="Z24" s="4"/>
@@ -3361,76 +3361,76 @@
       <c r="A25" s="1">
         <v>0.22916666666666699</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="4">
         <v>6.0628979798306197E-3</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="4">
         <v>1.9927781972913601E-3</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="4">
         <v>8.8120658340643289E-3</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="4">
         <v>2.8963859734466601E-3</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="4">
         <v>1.36199279639925E-3</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="4">
         <v>4.4766538354454501E-4</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="4">
         <v>4.0793246492985893E-3</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="4">
         <v>1.34080917208878E-3</v>
       </c>
-      <c r="J25">
+      <c r="J25" s="4">
         <v>1.8151939879759501E-3</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="4">
         <v>5.9662541166392706E-4</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="4">
         <v>6.52958071142284E-3</v>
       </c>
-      <c r="M25">
+      <c r="M25" s="4">
         <v>2.1461693933271801E-3</v>
       </c>
-      <c r="N25">
+      <c r="N25" s="4">
         <v>9.1902506813627202E-3</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="4">
         <v>3.0206893215731401E-3</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="4">
         <v>5.4040604542418104E-3</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="4">
         <v>1.7762287747349499E-3</v>
       </c>
-      <c r="R25">
+      <c r="R25" s="4">
         <v>6.0969019354838703E-4</v>
       </c>
-      <c r="S25">
+      <c r="S25" s="4">
         <v>2.00395475702779E-4</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="4">
         <v>3.72628835671342E-3</v>
       </c>
-      <c r="U25">
+      <c r="U25" s="4">
         <v>1.2247717541647601E-3</v>
       </c>
-      <c r="V25">
+      <c r="V25" s="4">
         <v>1.4888264516129E-3</v>
       </c>
-      <c r="W25">
+      <c r="W25" s="4">
         <v>4.8935359001500895E-4</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="4">
         <v>1.6980123387096699E-3</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" s="4">
         <v>5.5810966613145901E-4</v>
       </c>
       <c r="Z25" s="4"/>
@@ -3485,76 +3485,76 @@
       <c r="A26" s="1">
         <v>0.23958333333333301</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="4">
         <v>6.8141401039498303E-3</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="4">
         <v>2.23969954263015E-3</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="4">
         <v>9.6288036832872896E-3</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="4">
         <v>3.1648347225842199E-3</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="4">
         <v>1.48215308778848E-3</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="4">
         <v>4.87160161397845E-4</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="4">
         <v>4.5985114228456903E-3</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="4">
         <v>1.51145761217281E-3</v>
       </c>
-      <c r="J26">
+      <c r="J26" s="4">
         <v>2.0462186773546999E-3</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="4">
         <v>6.72559554966609E-4</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="4">
         <v>7.3606182565130202E-3</v>
       </c>
-      <c r="M26">
+      <c r="M26" s="4">
         <v>2.4193182252051802E-3</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="4">
         <v>1.03599189498998E-2</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="4">
         <v>3.40514068977336E-3</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="4">
         <v>6.0918499665998599E-3</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="4">
         <v>2.0022942551557602E-3</v>
       </c>
-      <c r="R26">
+      <c r="R26" s="4">
         <v>6.5307638709677395E-4</v>
       </c>
-      <c r="S26">
+      <c r="S26" s="4">
         <v>2.1465582790634801E-4</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="4">
         <v>4.2005432384769502E-3</v>
       </c>
-      <c r="U26">
+      <c r="U26" s="4">
         <v>1.3806517956039201E-3</v>
       </c>
-      <c r="V26">
+      <c r="V26" s="4">
         <v>1.5947729032258001E-3</v>
       </c>
-      <c r="W26">
+      <c r="W26" s="4">
         <v>5.2417650466027104E-4</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="4">
         <v>1.81884467741935E-3</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" s="4">
         <v>5.9782533525691789E-4</v>
       </c>
       <c r="Z26" s="4"/>
@@ -3609,76 +3609,76 @@
       <c r="A27" s="1">
         <v>0.25</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="4">
         <v>7.8885102351800296E-3</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="4">
         <v>2.5928279278444499E-3</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
         <v>1.0795441206107001E-2</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="4">
         <v>3.5482899328403098E-3</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="4">
         <v>1.65685343493438E-3</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="4">
         <v>5.44581388673934E-4</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="4">
         <v>5.3402068136272499E-3</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="4">
         <v>1.75524109800714E-3</v>
       </c>
-      <c r="J27">
+      <c r="J27" s="4">
         <v>2.3762539478957901E-3</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="4">
         <v>7.8103690254186897E-4</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="4">
         <v>8.5478147494989897E-3</v>
       </c>
-      <c r="M27">
+      <c r="M27" s="4">
         <v>2.8095308421737602E-3</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="4">
         <v>1.2030873619238399E-2</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="4">
         <v>3.9543569300593802E-3</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="4">
         <v>7.0744064128256496E-3</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="4">
         <v>2.3252449414712102E-3</v>
       </c>
-      <c r="R27">
+      <c r="R27" s="4">
         <v>7.1701393548387099E-4</v>
       </c>
-      <c r="S27">
+      <c r="S27" s="4">
         <v>2.35671083785291E-4</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="4">
         <v>4.8780502124248504E-3</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="4">
         <v>1.6033375690884201E-3</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="4">
         <v>1.7509045161290301E-3</v>
       </c>
-      <c r="W27">
+      <c r="W27" s="4">
         <v>5.7549448413750099E-4</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="4">
         <v>1.9969133870967699E-3</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" s="4">
         <v>6.5635368975759504E-4</v>
       </c>
       <c r="Z27" s="4"/>
@@ -3733,76 +3733,76 @@
       <c r="A28" s="1">
         <v>0.26041666666666702</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="4">
         <v>9.1515103057728288E-3</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="4">
         <v>3.0079559758880801E-3</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="4">
         <v>1.2169246788685801E-2</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="4">
         <v>3.9998379914399614E-3</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="4">
         <v>1.8935748975370001E-3</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="4">
         <v>6.2238797078610901E-4</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="4">
         <v>6.2032705410821603E-3</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="4">
         <v>2.0389164269779898E-3</v>
       </c>
-      <c r="J28">
+      <c r="J28" s="4">
         <v>2.7602949899799599E-3</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="4">
         <v>9.0726508881126204E-4</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="4">
         <v>9.9292797595190302E-3</v>
       </c>
-      <c r="M28">
+      <c r="M28" s="4">
         <v>3.2635964328281098E-3</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="4">
         <v>1.3975257234468901E-2</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="4">
         <v>4.5934449187558504E-3</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="4">
         <v>8.2177448229792897E-3</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="4">
         <v>2.70104210372918E-3</v>
       </c>
-      <c r="R28">
+      <c r="R28" s="4">
         <v>8.1292025806451601E-4</v>
       </c>
-      <c r="S28">
+      <c r="S28" s="4">
         <v>2.6719396760370602E-4</v>
       </c>
-      <c r="T28">
+      <c r="T28" s="4">
         <v>5.6664219639278503E-3</v>
       </c>
-      <c r="U28">
+      <c r="U28" s="4">
         <v>1.86246283277948E-3</v>
       </c>
-      <c r="V28">
+      <c r="V28" s="4">
         <v>1.98510193548387E-3</v>
       </c>
-      <c r="W28">
+      <c r="W28" s="4">
         <v>6.5247145335334505E-4</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="4">
         <v>2.2640164516129001E-3</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" s="4">
         <v>7.4414622150861202E-4</v>
       </c>
       <c r="Z28" s="4"/>
@@ -3857,76 +3857,76 @@
       <c r="A29" s="1">
         <v>0.27083333333333298</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="4">
         <v>1.0435045451418899E-2</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="4">
         <v>3.4298335767003999E-3</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="4">
         <v>1.35662462942074E-2</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="4">
         <v>4.4590095238476301E-3</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="4">
         <v>2.2077100168077998E-3</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="4">
         <v>7.2563919136888703E-4</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="4">
         <v>7.0595915831663299E-3</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="4">
         <v>2.3203755424412598E-3</v>
       </c>
-      <c r="J29">
+      <c r="J29" s="4">
         <v>3.1413357114228398E-3</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="4">
         <v>1.0325071173754199E-3</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="4">
         <v>1.12999520741482E-2</v>
       </c>
-      <c r="M29">
+      <c r="M29" s="4">
         <v>3.7141146360554701E-3</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="4">
         <v>1.59044503527054E-2</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="4">
         <v>5.2275400325406301E-3</v>
       </c>
-      <c r="P29">
+      <c r="P29" s="4">
         <v>9.3521509018036093E-3</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" s="4">
         <v>3.0739033506570102E-3</v>
       </c>
-      <c r="R29">
+      <c r="R29" s="4">
         <v>9.5906322580645103E-4</v>
       </c>
-      <c r="S29">
+      <c r="S29" s="4">
         <v>3.1522883818414701E-4</v>
       </c>
-      <c r="T29">
+      <c r="T29" s="4">
         <v>6.4486345611222406E-3</v>
       </c>
-      <c r="U29">
+      <c r="U29" s="4">
         <v>2.1195636803479499E-3</v>
       </c>
-      <c r="V29">
+      <c r="V29" s="4">
         <v>2.3419741935483802E-3</v>
       </c>
-      <c r="W29">
+      <c r="W29" s="4">
         <v>7.6976969215844103E-4</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="4">
         <v>2.6710306451612899E-3</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" s="4">
         <v>8.7792531751015998E-4</v>
       </c>
       <c r="Z29" s="4"/>
@@ -3981,76 +3981,76 @@
       <c r="A30" s="1">
         <v>0.28125</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="4">
         <v>1.1599282034262E-2</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="4">
         <v>3.8124996361486902E-3</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="4">
         <v>1.4840214564128601E-2</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="4">
         <v>4.8777426446729704E-3</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="4">
         <v>2.6167050413730599E-3</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="4">
         <v>8.6006935504072705E-4</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="4">
         <v>7.8012869739478904E-3</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="4">
         <v>2.5641590282755801E-3</v>
       </c>
-      <c r="J30">
+      <c r="J30" s="4">
         <v>3.47137098196392E-3</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="4">
         <v>1.14098446495068E-3</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="4">
         <v>1.2487148567134201E-2</v>
       </c>
-      <c r="M30">
+      <c r="M30" s="4">
         <v>4.1043272530240501E-3</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="4">
         <v>1.7575405022044001E-2</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="4">
         <v>5.7767562728266502E-3</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="4">
         <v>1.03347073480293E-2</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="4">
         <v>3.3968540369724602E-3</v>
       </c>
-      <c r="R30">
+      <c r="R30" s="4">
         <v>1.1737107096774101E-3</v>
       </c>
-      <c r="S30">
+      <c r="S30" s="4">
         <v>3.8578005434917101E-4</v>
       </c>
-      <c r="T30">
+      <c r="T30" s="4">
         <v>7.12614153507014E-3</v>
       </c>
-      <c r="U30">
+      <c r="U30" s="4">
         <v>2.3422494538324502E-3</v>
       </c>
-      <c r="V30">
+      <c r="V30" s="4">
         <v>2.8661303225806399E-3</v>
       </c>
-      <c r="W30">
+      <c r="W30" s="4">
         <v>9.42051480403425E-4</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="4">
         <v>3.2688327419354798E-3</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" s="4">
         <v>1.0744133647624301E-3</v>
       </c>
       <c r="Z30" s="4"/>
@@ -4105,76 +4105,76 @@
       <c r="A31" s="1">
         <v>0.29166666666666702</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="4">
         <v>1.25063179542956E-2</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="4">
         <v>4.1106279258900204E-3</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="4">
         <v>1.5844286714779901E-2</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="4">
         <v>5.2077652010447803E-3</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="4">
         <v>3.1191662325457301E-3</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="4">
         <v>1.02522036204842E-3</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="4">
         <v>8.3272164328657312E-3</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="4">
         <v>2.7370236818671902E-3</v>
       </c>
-      <c r="J31">
+      <c r="J31" s="4">
         <v>3.70539599198396E-3</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="4">
         <v>1.2179047659585901E-3</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="4">
         <v>1.33289788076152E-2</v>
       </c>
-      <c r="M31">
+      <c r="M31" s="4">
         <v>4.38102347232904E-3</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="4">
         <v>1.8760263787575102E-2</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="4">
         <v>6.1662005159385603E-3</v>
       </c>
-      <c r="P31">
+      <c r="P31" s="4">
         <v>1.10314291917167E-2</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="4">
         <v>3.6258554327234099E-3</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="4">
         <v>1.4625714193548299E-3</v>
       </c>
-      <c r="S31">
+      <c r="S31" s="4">
         <v>4.8072397823082502E-4</v>
       </c>
-      <c r="T31">
+      <c r="T31" s="4">
         <v>7.6065555711422803E-3</v>
       </c>
-      <c r="U31">
+      <c r="U31" s="4">
         <v>2.5001539113941899E-3</v>
       </c>
-      <c r="V31">
+      <c r="V31" s="4">
         <v>3.5715106451612898E-3</v>
       </c>
-      <c r="W31">
+      <c r="W31" s="4">
         <v>1.1738987805416201E-3</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="4">
         <v>4.0733217338709601E-3</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="4">
         <v>1.3388361092029899E-3</v>
       </c>
       <c r="Z31" s="4"/>
@@ -4229,76 +4229,76 @@
       <c r="A32" s="1">
         <v>0.30208333333333298</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="4">
         <v>1.31828310620596E-2</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="4">
         <v>4.3329870313571798E-3</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="4">
         <v>1.6641474522701601E-2</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="4">
         <v>5.4697881623510299E-3</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="4">
         <v>3.66526764569461E-3</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="4">
         <v>1.2047152163661701E-3</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="4">
         <v>8.6710933867735398E-3</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="4">
         <v>2.8500505707540198E-3</v>
       </c>
-      <c r="J32">
+      <c r="J32" s="4">
         <v>3.8584123446893698E-3</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="4">
         <v>1.2681988089252999E-3</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="4">
         <v>1.3879406272545001E-2</v>
       </c>
-      <c r="M32">
+      <c r="M32" s="4">
         <v>4.5619402311053801E-3</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="4">
         <v>1.95349791342685E-2</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="4">
         <v>6.42083713643481E-3</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="4">
         <v>1.14869780895123E-2</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="4">
         <v>3.7755871145605702E-3</v>
       </c>
-      <c r="R32">
+      <c r="R32" s="4">
         <v>1.7913930967741901E-3</v>
       </c>
-      <c r="S32">
+      <c r="S32" s="4">
         <v>5.8880243703681801E-4</v>
       </c>
-      <c r="T32">
+      <c r="T32" s="4">
         <v>7.92067244088176E-3</v>
       </c>
-      <c r="U32">
+      <c r="U32" s="4">
         <v>2.6033991336461E-3</v>
       </c>
-      <c r="V32">
+      <c r="V32" s="4">
         <v>4.3744732258064502E-3</v>
       </c>
-      <c r="W32">
+      <c r="W32" s="4">
         <v>1.4378198178530801E-3</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="4">
         <v>4.9891036693548302E-3</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" s="4">
         <v>1.6398390752064701E-3</v>
       </c>
       <c r="Z32" s="4"/>
@@ -4353,76 +4353,76 @@
       <c r="A33" s="1">
         <v>0.3125</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="4">
         <v>1.36957931876656E-2</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="4">
         <v>4.5015895286026498E-3</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="4">
         <v>1.7344820854969099E-2</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="4">
         <v>5.7009669222032296E-3</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="4">
         <v>4.1908565851056902E-3</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="4">
         <v>1.37746794660841E-3</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="4">
         <v>8.9003446893787495E-3</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="4">
         <v>2.9254018300119001E-3</v>
       </c>
-      <c r="J33">
+      <c r="J33" s="4">
         <v>3.9604232464929799E-3</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="4">
         <v>1.3017281709031101E-3</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="4">
         <v>1.4246357915831599E-2</v>
       </c>
-      <c r="M33">
+      <c r="M33" s="4">
         <v>4.6825514036229398E-3</v>
       </c>
-      <c r="N33">
+      <c r="N33" s="4">
         <v>2.00514560320641E-2</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="4">
         <v>6.5905948834323099E-3</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="4">
         <v>1.17906773547094E-2</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="4">
         <v>3.8754082357853499E-3</v>
       </c>
-      <c r="R33">
+      <c r="R33" s="4">
         <v>2.1145060645161198E-3</v>
       </c>
-      <c r="S33">
+      <c r="S33" s="4">
         <v>6.9500453371076302E-4</v>
       </c>
-      <c r="T33">
+      <c r="T33" s="4">
         <v>8.1300836873747506E-3</v>
       </c>
-      <c r="U33">
+      <c r="U33" s="4">
         <v>2.6722292818140399E-3</v>
       </c>
-      <c r="V33">
+      <c r="V33" s="4">
         <v>5.1634954838709604E-3</v>
       </c>
-      <c r="W33">
+      <c r="W33" s="4">
         <v>1.6971588927112301E-3</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="4">
         <v>5.8889866129032201E-3</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" s="4">
         <v>1.9356162952724001E-3</v>
       </c>
       <c r="Z33" s="4"/>
@@ -4477,76 +4477,76 @@
       <c r="A34" s="1">
         <v>0.32291666666666702</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="4">
         <v>1.41222773764949E-2</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="4">
         <v>4.64176810258093E-3</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="4">
         <v>1.8070862123363202E-2</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="4">
         <v>5.9396051468282697E-3</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="4">
         <v>4.6342398838806606E-3</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="4">
         <v>1.5232009894175101E-3</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="4">
         <v>9.08913987975952E-3</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="4">
         <v>2.98745580822427E-3</v>
       </c>
-      <c r="J34">
+      <c r="J34" s="4">
         <v>4.0444322244488897E-3</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="4">
         <v>1.32934058664954E-3</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="4">
         <v>1.4548553386773499E-2</v>
       </c>
-      <c r="M34">
+      <c r="M34" s="4">
         <v>4.7818782515785798E-3</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="4">
         <v>2.0476789947895702E-2</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="4">
         <v>6.7303953809596598E-3</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="4">
         <v>1.2040782631930501E-2</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="4">
         <v>3.9576138650292804E-3</v>
       </c>
-      <c r="R34">
+      <c r="R34" s="4">
         <v>2.38738238709677E-3</v>
       </c>
-      <c r="S34">
+      <c r="S34" s="4">
         <v>7.8469464362268104E-4</v>
       </c>
-      <c r="T34">
+      <c r="T34" s="4">
         <v>8.3025400080160294E-3</v>
       </c>
-      <c r="U34">
+      <c r="U34" s="4">
         <v>2.7289129332464601E-3</v>
       </c>
-      <c r="V34">
+      <c r="V34" s="4">
         <v>5.8298429032257997E-3</v>
       </c>
-      <c r="W34">
+      <c r="W34" s="4">
         <v>1.91617669798011E-3</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="4">
         <v>6.6489584274193499E-3</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" s="4">
         <v>2.1854069510877901E-3</v>
       </c>
       <c r="Z34" s="4"/>
@@ -4601,76 +4601,76 @@
       <c r="A35" s="1">
         <v>0.33333333333333298</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="4">
         <v>1.45151802861852E-2</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="4">
         <v>4.7709090438746802E-3</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="4">
         <v>1.8905166542648701E-2</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="4">
         <v>6.21382774832789E-3</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="4">
         <v>4.9423204257708899E-3</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="4">
         <v>1.6244621666517199E-3</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="4">
         <v>9.2914204408817598E-3</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="4">
         <v>3.05394221345182E-3</v>
       </c>
-      <c r="J35">
+      <c r="J35" s="4">
         <v>4.1344418436873708E-3</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="4">
         <v>1.35892531780643E-3</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="4">
         <v>1.4872334248496899E-2</v>
       </c>
-      <c r="M35">
+      <c r="M35" s="4">
         <v>4.8882998743881899E-3</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="4">
         <v>2.09325048577154E-2</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="4">
         <v>6.8801816283103993E-3</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="4">
         <v>1.2308752571810201E-2</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="4">
         <v>4.0456913249334904E-3</v>
       </c>
-      <c r="R35">
+      <c r="R35" s="4">
         <v>2.5723445806451598E-3</v>
       </c>
-      <c r="S35">
+      <c r="S35" s="4">
         <v>8.4548877670105301E-4</v>
       </c>
-      <c r="T35">
+      <c r="T35" s="4">
         <v>8.4873146372745484E-3</v>
       </c>
-      <c r="U35">
+      <c r="U35" s="4">
         <v>2.7896454169240499E-3</v>
       </c>
-      <c r="V35">
+      <c r="V35" s="4">
         <v>6.2815093548387003E-3</v>
       </c>
-      <c r="W35">
+      <c r="W35" s="4">
         <v>2.0646322814678098E-3</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="4">
         <v>7.1640857661290297E-3</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" s="4">
         <v>2.3547211194647499E-3</v>
       </c>
       <c r="Z35" s="4"/>
@@ -4725,76 +4725,76 @@
       <c r="A36" s="1">
         <v>0.34375</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="4">
         <v>1.48380710128644E-2</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="4">
         <v>4.8770380934437694E-3</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="4">
         <v>1.97579507385355E-2</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="4">
         <v>6.4941243586636001E-3</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="4">
         <v>5.0917449872325202E-3</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="4">
         <v>1.67357564492748E-3</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="4">
         <v>9.4869583166332597E-3</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="4">
         <v>3.1182124051717798E-3</v>
       </c>
-      <c r="J36">
+      <c r="J36" s="4">
         <v>4.2214511422845602E-3</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="4">
         <v>1.38752389125809E-3</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="4">
         <v>1.5185322414829601E-2</v>
       </c>
-      <c r="M36">
+      <c r="M36" s="4">
         <v>4.9911741097708106E-3</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="4">
         <v>2.1373029270541001E-2</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="4">
         <v>7.0249750007494397E-3</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="4">
         <v>1.2567790180360699E-2</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="4">
         <v>4.1308328695075598E-3</v>
       </c>
-      <c r="R36">
+      <c r="R36" s="4">
         <v>2.65569174193548E-3</v>
       </c>
-      <c r="S36">
+      <c r="S36" s="4">
         <v>8.7288366382896096E-4</v>
       </c>
-      <c r="T36">
+      <c r="T36" s="4">
         <v>8.665930112224449E-3</v>
       </c>
-      <c r="U36">
+      <c r="U36" s="4">
         <v>2.8483534844790498E-3</v>
       </c>
-      <c r="V36">
+      <c r="V36" s="4">
         <v>6.4850380645161201E-3</v>
       </c>
-      <c r="W36">
+      <c r="W36" s="4">
         <v>2.1315289332863498E-3</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="4">
         <v>7.3962110483870901E-3</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" s="4">
         <v>2.4310170101531298E-3</v>
       </c>
       <c r="Z36" s="4"/>
@@ -4849,76 +4849,76 @@
       <c r="A37" s="1">
         <v>0.35416666666666702</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="4">
         <v>1.50620075236279E-2</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="4">
         <v>4.9506424651009403E-3</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="4">
         <v>2.05286625047711E-2</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="4">
         <v>6.74744506589957E-3</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="4">
         <v>5.0786849011733104E-3</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="4">
         <v>1.6692830022275501E-3</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="4">
         <v>9.6555254509018001E-3</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="4">
         <v>3.1736177428613901E-3</v>
       </c>
-      <c r="J37">
+      <c r="J37" s="4">
         <v>4.2964591583166296E-3</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="4">
         <v>1.4121778338888301E-3</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="4">
         <v>1.54551397995991E-2</v>
       </c>
-      <c r="M37">
+      <c r="M37" s="4">
         <v>5.0798587954454886E-3</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="4">
         <v>2.17527916953907E-2</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="4">
         <v>7.1497968735417198E-3</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="4">
         <v>1.27910984635938E-2</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="4">
         <v>4.2042307527610703E-3</v>
       </c>
-      <c r="R37">
+      <c r="R37" s="4">
         <v>2.6362821290322499E-3</v>
       </c>
-      <c r="S37">
+      <c r="S37" s="4">
         <v>8.6650403257999592E-4</v>
       </c>
-      <c r="T37">
+      <c r="T37" s="4">
         <v>8.8199089699398797E-3</v>
       </c>
-      <c r="U37">
+      <c r="U37" s="4">
         <v>2.89896388754371E-3</v>
       </c>
-      <c r="V37">
+      <c r="V37" s="4">
         <v>6.4376409677419314E-3</v>
       </c>
-      <c r="W37">
+      <c r="W37" s="4">
         <v>2.11595026094504E-3</v>
       </c>
-      <c r="X37">
+      <c r="X37" s="4">
         <v>7.3421544758064498E-3</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" s="4">
         <v>2.41324947396542E-3</v>
       </c>
       <c r="Z37" s="4"/>
@@ -4973,76 +4973,76 @@
       <c r="A38" s="1">
         <v>0.36458333333333298</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="4">
         <v>1.5135802935677799E-2</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="4">
         <v>4.9748978440768699E-3</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="4">
         <v>2.1100043814754901E-2</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="4">
         <v>6.9352490204875198E-3</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="4">
         <v>4.8890675638373496E-3</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="4">
         <v>1.6069587973788801E-3</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="4">
         <v>9.7634084168336591E-3</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="4">
         <v>3.20907715898275E-3</v>
       </c>
-      <c r="J38">
+      <c r="J38" s="4">
         <v>4.3444642885771502E-3</v>
       </c>
-      <c r="K38">
+      <c r="K38" s="4">
         <v>1.4279563571725001E-3</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="4">
         <v>1.56278229258517E-2</v>
       </c>
-      <c r="M38">
+      <c r="M38" s="4">
         <v>5.1366169942772899E-3</v>
       </c>
-      <c r="N38">
+      <c r="N38" s="4">
         <v>2.1995839647294499E-2</v>
       </c>
-      <c r="O38">
+      <c r="O38" s="4">
         <v>7.2296828721287801E-3</v>
       </c>
-      <c r="P38">
+      <c r="P38" s="4">
         <v>1.2934015764862999E-2</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="4">
         <v>4.2512053980433197E-3</v>
       </c>
-      <c r="R38">
+      <c r="R38" s="4">
         <v>2.5072652903225801E-3</v>
       </c>
-      <c r="S38">
+      <c r="S38" s="4">
         <v>8.2409824839570006E-4</v>
       </c>
-      <c r="T38">
+      <c r="T38" s="4">
         <v>8.9184554388777506E-3</v>
       </c>
-      <c r="U38">
+      <c r="U38" s="4">
         <v>2.9313545455051E-3</v>
       </c>
-      <c r="V38">
+      <c r="V38" s="4">
         <v>6.1225896774193492E-3</v>
       </c>
-      <c r="W38">
+      <c r="W38" s="4">
         <v>2.0123979094999198E-3</v>
       </c>
-      <c r="X38">
+      <c r="X38" s="4">
         <v>6.9828372580645103E-3</v>
       </c>
-      <c r="Y38">
+      <c r="Y38" s="4">
         <v>2.2951476157765599E-3</v>
       </c>
       <c r="Z38" s="4"/>
@@ -5097,76 +5097,76 @@
       <c r="A39" s="1">
         <v>0.375</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="4">
         <v>1.50453820765401E-2</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="4">
         <v>4.9451779449017101E-3</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="4">
         <v>2.1404370986013301E-2</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="4">
         <v>7.0352765244541997E-3</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="4">
         <v>4.5339485546900199E-3</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="4">
         <v>1.49023682362529E-3</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="4">
         <v>9.7971218436873689E-3</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="4">
         <v>3.2201582265206702E-3</v>
       </c>
-      <c r="J39">
+      <c r="J39" s="4">
         <v>4.3594658917835601E-3</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="4">
         <v>1.4328871456986501E-3</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="4">
         <v>1.5681786402805601E-2</v>
       </c>
-      <c r="M39">
+      <c r="M39" s="4">
         <v>5.1543539314122186E-3</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="4">
         <v>2.2071792132264501E-2</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="4">
         <v>7.25464724668723E-3</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="4">
         <v>1.2978677421509601E-2</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="4">
         <v>4.2658849746940201E-3</v>
       </c>
-      <c r="R39">
+      <c r="R39" s="4">
         <v>2.2766334193548301E-3</v>
       </c>
-      <c r="S39">
+      <c r="S39" s="4">
         <v>7.4829321826093995E-4</v>
       </c>
-      <c r="T39">
+      <c r="T39" s="4">
         <v>8.9492512104208406E-3</v>
       </c>
-      <c r="U39">
+      <c r="U39" s="4">
         <v>2.94147662611803E-3</v>
       </c>
-      <c r="V39">
+      <c r="V39" s="4">
         <v>5.5594006451612898E-3</v>
       </c>
-      <c r="W39">
+      <c r="W39" s="4">
         <v>1.82728662638563E-3</v>
       </c>
-      <c r="X39">
+      <c r="X39" s="4">
         <v>6.3405179838709599E-3</v>
       </c>
-      <c r="Y39">
+      <c r="Y39" s="4">
         <v>2.08402747989911E-3</v>
       </c>
       <c r="Z39" s="4"/>
@@ -5221,76 +5221,76 @@
       <c r="A40" s="1">
         <v>0.38541666666666702</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="4">
         <v>1.48354564090115E-2</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="4">
         <v>4.876178714716E-3</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="4">
         <v>2.1501101161355601E-2</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="4">
         <v>7.0670701955803999E-3</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="4">
         <v>4.0821454797498203E-3</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="4">
         <v>1.3417363342215099E-3</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="4">
         <v>9.7701511022044111E-3</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="4">
         <v>3.2112933724903398E-3</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="4">
         <v>4.3474646092184297E-3</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="4">
         <v>1.42894251487773E-3</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="4">
         <v>1.5638615621242399E-2</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="4">
         <v>5.1401643817042706E-3</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="4">
         <v>2.2011030144288499E-2</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="4">
         <v>7.2346757470404697E-3</v>
       </c>
-      <c r="P40">
+      <c r="P40" s="4">
         <v>1.29429480961923E-2</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="4">
         <v>4.2541413133734603E-3</v>
       </c>
-      <c r="R40">
+      <c r="R40" s="4">
         <v>1.9877727096774202E-3</v>
       </c>
-      <c r="S40">
+      <c r="S40" s="4">
         <v>6.5334929437928604E-4</v>
       </c>
-      <c r="T40">
+      <c r="T40" s="4">
         <v>8.9246145931863689E-3</v>
       </c>
-      <c r="U40">
+      <c r="U40" s="4">
         <v>2.9333789616276802E-3</v>
       </c>
-      <c r="V40">
+      <c r="V40" s="4">
         <v>4.8540203225806398E-3</v>
       </c>
-      <c r="W40">
+      <c r="W40" s="4">
         <v>1.59543932624743E-3</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="4">
         <v>5.5360289919354801E-3</v>
       </c>
-      <c r="Y40">
+      <c r="Y40" s="4">
         <v>1.81960473545855E-3</v>
       </c>
       <c r="Z40" s="4"/>
@@ -5345,76 +5345,76 @@
       <c r="A41" s="1">
         <v>0.39583333333333298</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="4">
         <v>1.45575454604046E-2</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="4">
         <v>4.7848338032537314E-3</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="4">
         <v>2.1469743389109199E-2</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="4">
         <v>7.0567633942692004E-3</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="4">
         <v>3.6202255418094202E-3</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="4">
         <v>1.1899105927552899E-3</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="4">
         <v>9.6959815631262498E-3</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="4">
         <v>3.1869150239069001E-3</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="4">
         <v>4.31446108216432E-3</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="4">
         <v>1.4180947801202099E-3</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="4">
         <v>1.55198959719438E-2</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="4">
         <v>5.1011431200074196E-3</v>
       </c>
-      <c r="N41">
+      <c r="N41" s="4">
         <v>2.1843934677354699E-2</v>
       </c>
-      <c r="O41">
+      <c r="O41" s="4">
         <v>7.1797541230118698E-3</v>
       </c>
-      <c r="P41">
+      <c r="P41" s="4">
         <v>1.28446924515698E-2</v>
       </c>
-      <c r="Q41">
+      <c r="Q41" s="4">
         <v>4.2218462447419199E-3</v>
       </c>
-      <c r="R41">
+      <c r="R41" s="4">
         <v>1.69548677419354E-3</v>
       </c>
-      <c r="S41">
+      <c r="S41" s="4">
         <v>5.5727955321840299E-4</v>
       </c>
-      <c r="T41">
+      <c r="T41" s="4">
         <v>8.8568638957915793E-3</v>
       </c>
-      <c r="U41">
+      <c r="U41" s="4">
         <v>2.9111103842792301E-3</v>
       </c>
-      <c r="V41">
+      <c r="V41" s="4">
         <v>4.14027580645161E-3</v>
       </c>
-      <c r="W41">
+      <c r="W41" s="4">
         <v>1.36084284863724E-3</v>
       </c>
-      <c r="X41">
+      <c r="X41" s="4">
         <v>4.7220006048386996E-3</v>
       </c>
-      <c r="Y41">
+      <c r="Y41" s="4">
         <v>1.55204654345546E-3</v>
       </c>
       <c r="Z41" s="4"/>
@@ -5469,76 +5469,76 @@
       <c r="A42" s="1">
         <v>0.40625</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="4">
         <v>1.4271908360398201E-2</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="4">
         <v>4.6909494286322198E-3</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="4">
         <v>2.1400371481818899E-2</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="4">
         <v>7.0339619509969297E-3</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="4">
         <v>3.2336655531223701E-3</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="4">
         <v>1.06285446877574E-3</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="4">
         <v>9.5948412825651291E-3</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="4">
         <v>3.1536718212931301E-3</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="4">
         <v>4.2694562725450903E-3</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="4">
         <v>1.40330241454176E-3</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="4">
         <v>1.53580055410821E-2</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="4">
         <v>5.0479323086026102E-3</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="4">
         <v>2.16160772224448E-2</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="4">
         <v>7.1048609993365E-3</v>
       </c>
-      <c r="P42">
+      <c r="P42" s="4">
         <v>1.2710707481629901E-2</v>
       </c>
-      <c r="Q42">
+      <c r="Q42" s="4">
         <v>4.1778075147898101E-3</v>
       </c>
-      <c r="R42">
+      <c r="R42" s="4">
         <v>1.4534374838709599E-3</v>
       </c>
-      <c r="S42">
+      <c r="S42" s="4">
         <v>4.7772179881954698E-4</v>
       </c>
-      <c r="T42">
+      <c r="T42" s="4">
         <v>8.7644765811623199E-3</v>
       </c>
-      <c r="U42">
+      <c r="U42" s="4">
         <v>2.8807441424404398E-3</v>
       </c>
-      <c r="V42">
+      <c r="V42" s="4">
         <v>3.5492061290322498E-3</v>
       </c>
-      <c r="W42">
+      <c r="W42" s="4">
         <v>1.1665676406163001E-3</v>
       </c>
-      <c r="X42">
+      <c r="X42" s="4">
         <v>4.0478833467741896E-3</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" s="4">
         <v>1.3304749157028899E-3</v>
       </c>
       <c r="Z42" s="4"/>
@@ -5593,76 +5593,76 @@
       <c r="A43" s="1">
         <v>0.41666666666666702</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="4">
         <v>1.4042778195875599E-2</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="4">
         <v>4.6156379855366199E-3</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="4">
         <v>2.1382274307775399E-2</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="4">
         <v>7.0280136975401494E-3</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="4">
         <v>2.9944272176611201E-3</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="4">
         <v>9.8422063056018009E-4</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="4">
         <v>9.4937010020040083E-3</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="4">
         <v>3.1204286186793601E-3</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="4">
         <v>4.2244514629258502E-3</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="4">
         <v>1.3885100489633201E-3</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="4">
         <v>1.51961151102204E-2</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="4">
         <v>4.9947214971977991E-3</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="4">
         <v>2.1388219767535001E-2</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="4">
         <v>7.0299678756611302E-3</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="4">
         <v>1.257672251169E-2</v>
       </c>
-      <c r="Q43">
+      <c r="Q43" s="4">
         <v>4.1337687848377004E-3</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="4">
         <v>1.3061527741935401E-3</v>
       </c>
-      <c r="S43">
+      <c r="S43" s="4">
         <v>4.2931165581269602E-4</v>
       </c>
-      <c r="T43">
+      <c r="T43" s="4">
         <v>8.6720892665330604E-3</v>
       </c>
-      <c r="U43">
+      <c r="U43" s="4">
         <v>2.85037790060164E-3</v>
       </c>
-      <c r="V43">
+      <c r="V43" s="4">
         <v>3.1895458064516101E-3</v>
       </c>
-      <c r="W43">
+      <c r="W43" s="4">
         <v>1.0483530093205399E-3</v>
       </c>
-      <c r="X43">
+      <c r="X43" s="4">
         <v>3.63768935483871E-3</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" s="4">
         <v>1.1956506705138299E-3</v>
       </c>
       <c r="Z43" s="4"/>
@@ -5717,76 +5717,76 @@
       <c r="A44" s="1">
         <v>0.42708333333333298</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="4">
         <v>1.3881506913504401E-2</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="4">
         <v>4.5626306783993998E-3</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="4">
         <v>2.1440569446118302E-2</v>
       </c>
-      <c r="E44">
+      <c r="E44" s="4">
         <v>7.0471743829226899E-3</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="4">
         <v>2.8843551172506301E-3</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="4">
         <v>9.4804168073159799E-4</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="4">
         <v>9.4060460921843708E-3</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="4">
         <v>3.0916178430807602E-3</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="4">
         <v>4.18544729458917E-3</v>
       </c>
-      <c r="K44">
+      <c r="K44" s="4">
         <v>1.3756899987953299E-3</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="4">
         <v>1.50558100701402E-2</v>
       </c>
-      <c r="M44">
+      <c r="M44" s="4">
         <v>4.9486054606469702E-3</v>
       </c>
-      <c r="N44">
+      <c r="N44" s="4">
         <v>2.1190743306613202E-2</v>
       </c>
-      <c r="O44">
+      <c r="O44" s="4">
         <v>6.9650605018091501E-3</v>
       </c>
-      <c r="P44">
+      <c r="P44" s="4">
         <v>1.24606022044088E-2</v>
       </c>
-      <c r="Q44">
+      <c r="Q44" s="4">
         <v>4.0956018855458796E-3</v>
       </c>
-      <c r="R44">
+      <c r="R44" s="4">
         <v>1.2410734838709601E-3</v>
       </c>
-      <c r="S44">
+      <c r="S44" s="4">
         <v>4.0792112750734301E-4</v>
       </c>
-      <c r="T44">
+      <c r="T44" s="4">
         <v>8.5920202605210393E-3</v>
       </c>
-      <c r="U44">
+      <c r="U44" s="4">
         <v>2.82406049100802E-3</v>
       </c>
-      <c r="V44">
+      <c r="V44" s="4">
         <v>3.03062612903225E-3</v>
       </c>
-      <c r="W44">
+      <c r="W44" s="4">
         <v>9.96118637352649E-4</v>
       </c>
-      <c r="X44">
+      <c r="X44" s="4">
         <v>3.4564408467741901E-3</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" s="4">
         <v>1.13607716682564E-3</v>
       </c>
       <c r="Z44" s="4"/>
@@ -5841,76 +5841,76 @@
       <c r="A45" s="1">
         <v>0.4375</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="4">
         <v>1.3784579599521601E-2</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="4">
         <v>4.53077221093557E-3</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="4">
         <v>2.1569612587124899E-2</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="4">
         <v>7.0895888122539099E-3</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="4">
         <v>2.8704095871581801E-3</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="4">
         <v>9.4345800665191805E-4</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="4">
         <v>9.3386192384769494E-3</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="4">
         <v>3.0694557080049099E-3</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="4">
         <v>4.1554440881763502E-3</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="4">
         <v>1.3658284217430399E-3</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="4">
         <v>1.4947883116232401E-2</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="4">
         <v>4.9131315863770999E-3</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="4">
         <v>2.1038838336673301E-2</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="4">
         <v>6.9151317526922398E-3</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="4">
         <v>1.23712788911155E-2</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="4">
         <v>4.0662427322444702E-3</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="4">
         <v>1.23650651612903E-3</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="4">
         <v>4.0642003780170399E-4</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="4">
         <v>8.5304287174348698E-3</v>
       </c>
-      <c r="U45">
+      <c r="U45" s="4">
         <v>2.8038163297821501E-3</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="4">
         <v>3.0194738709677402E-3</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="4">
         <v>9.9245306738998998E-4</v>
       </c>
-      <c r="X45">
+      <c r="X45" s="4">
         <v>3.4437216532258001E-3</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="4">
         <v>1.1318965700755901E-3</v>
       </c>
       <c r="Z45" s="4"/>
@@ -5965,76 +5965,76 @@
       <c r="A46" s="1">
         <v>0.44791666666666702</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="4">
         <v>1.37747001472622E-2</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="4">
         <v>4.5275249920100494E-3</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="4">
         <v>2.18065129839418E-2</v>
       </c>
-      <c r="E46">
+      <c r="E46" s="4">
         <v>7.1674542071981703E-3</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="4">
         <v>2.9162797910336699E-3</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="4">
         <v>9.5853481356710706E-4</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="4">
         <v>9.3183911823647297E-3</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="4">
         <v>3.0628070674821499E-3</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="4">
         <v>4.1464431262524994E-3</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="4">
         <v>1.3628699486273499E-3</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="4">
         <v>1.4915505030060099E-2</v>
       </c>
-      <c r="M46">
+      <c r="M46" s="4">
         <v>4.9024894240961396E-3</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="4">
         <v>2.0993266845691302E-2</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="4">
         <v>6.9001531279571596E-3</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="4">
         <v>1.23444818971275E-2</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="4">
         <v>4.0574349862540502E-3</v>
       </c>
-      <c r="R46">
+      <c r="R46" s="4">
         <v>1.2673335483870899E-3</v>
       </c>
-      <c r="S46">
+      <c r="S46" s="4">
         <v>4.16552393314766E-4</v>
       </c>
-      <c r="T46">
+      <c r="T46" s="4">
         <v>8.5119512545090096E-3</v>
       </c>
-      <c r="U46">
+      <c r="U46" s="4">
         <v>2.7977430814143901E-3</v>
       </c>
-      <c r="V46">
+      <c r="V46" s="4">
         <v>3.0947516129032201E-3</v>
       </c>
-      <c r="W46">
+      <c r="W46" s="4">
         <v>1.01719566463794E-3</v>
       </c>
-      <c r="X46">
+      <c r="X46" s="4">
         <v>3.52957620967741E-3</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" s="4">
         <v>1.1601155981384201E-3</v>
       </c>
       <c r="Z46" s="4"/>
@@ -6089,76 +6089,76 @@
       <c r="A47" s="1">
         <v>0.45833333333333298</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="4">
         <v>1.38396140405973E-2</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="4">
         <v>4.54886115695456E-3</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="4">
         <v>2.2130492635414199E-2</v>
       </c>
-      <c r="E47">
+      <c r="E47" s="4">
         <v>7.27394116903856E-3</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="4">
         <v>2.9900164546835602E-3</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="4">
         <v>9.8277088287774205E-4</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="4">
         <v>9.345361923847691E-3</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="4">
         <v>3.0716719215124898E-3</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="4">
         <v>4.1584444088176298E-3</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="4">
         <v>1.36681457944827E-3</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="4">
         <v>1.49586758116232E-2</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="4">
         <v>4.9166789738040902E-3</v>
       </c>
-      <c r="N47">
+      <c r="N47" s="4">
         <v>2.1054028833667301E-2</v>
       </c>
-      <c r="O47">
+      <c r="O47" s="4">
         <v>6.9201246276039304E-3</v>
       </c>
-      <c r="P47">
+      <c r="P47" s="4">
         <v>1.2380211222444801E-2</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="4">
         <v>4.0691786475746099E-3</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="4">
         <v>1.31300322580645E-3</v>
       </c>
-      <c r="S47">
+      <c r="S47" s="4">
         <v>4.3156329037115398E-4</v>
       </c>
-      <c r="T47">
+      <c r="T47" s="4">
         <v>8.5365878717434795E-3</v>
       </c>
-      <c r="U47">
+      <c r="U47" s="4">
         <v>2.8058407459047399E-3</v>
       </c>
-      <c r="V47">
+      <c r="V47" s="4">
         <v>3.2062741935483799E-3</v>
       </c>
-      <c r="W47">
+      <c r="W47" s="4">
         <v>1.05385136426453E-3</v>
       </c>
-      <c r="X47">
+      <c r="X47" s="4">
         <v>3.65676814516128E-3</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" s="4">
         <v>1.2019215656389E-3</v>
       </c>
       <c r="Z47" s="4"/>
@@ -6213,76 +6213,76 @@
       <c r="A48" s="1">
         <v>0.46875</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="4">
         <v>1.4006110011571499E-2</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="4">
         <v>4.6035857361900996E-3</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="4">
         <v>2.2550956793149501E-2</v>
       </c>
-      <c r="E48">
+      <c r="E48" s="4">
         <v>7.4121410544835701E-3</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="4">
         <v>3.0659584998222202E-3</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="4">
         <v>1.00773182602959E-3</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="4">
         <v>9.44650220440881E-3</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="4">
         <v>3.1049151241262698E-3</v>
       </c>
-      <c r="J48">
+      <c r="J48" s="4">
         <v>4.2034492184368707E-3</v>
       </c>
-      <c r="K48">
+      <c r="K48" s="4">
         <v>1.3816069450267099E-3</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="4">
         <v>1.51205662424849E-2</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="4">
         <v>4.96988978520889E-3</v>
       </c>
-      <c r="N48">
+      <c r="N48" s="4">
         <v>2.12818862885771E-2</v>
       </c>
-      <c r="O48">
+      <c r="O48" s="4">
         <v>6.9950177512792897E-3</v>
       </c>
-      <c r="P48">
+      <c r="P48" s="4">
         <v>1.25141961923847E-2</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="4">
         <v>4.1132173775267197E-3</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="4">
         <v>1.35524767741935E-3</v>
       </c>
-      <c r="S48">
+      <c r="S48" s="4">
         <v>4.4544837014831302E-4</v>
       </c>
-      <c r="T48">
+      <c r="T48" s="4">
         <v>8.6289751863727407E-3</v>
       </c>
-      <c r="U48">
+      <c r="U48" s="4">
         <v>2.8362069877435302E-3</v>
       </c>
-      <c r="V48">
+      <c r="V48" s="4">
         <v>3.3094325806451602E-3</v>
       </c>
-      <c r="W48">
+      <c r="W48" s="4">
         <v>1.0877578864191299E-3</v>
       </c>
-      <c r="X48">
+      <c r="X48" s="4">
         <v>3.7744206854838699E-3</v>
       </c>
-      <c r="Y48">
+      <c r="Y48" s="4">
         <v>1.2405920855768501E-3</v>
       </c>
       <c r="Z48" s="4"/>
@@ -6337,76 +6337,76 @@
       <c r="A49" s="1">
         <v>0.47916666666666702</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="4">
         <v>1.42572787803995E-2</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="4">
         <v>4.6861409182212014E-3</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="4">
         <v>2.30252129833039E-2</v>
       </c>
-      <c r="E49">
+      <c r="E49" s="4">
         <v>7.56802152597001E-3</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="4">
         <v>3.1238968008597801E-3</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="4">
         <v>1.02677522466171E-3</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="4">
         <v>9.6150693386773487E-3</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="4">
         <v>3.1603204618158901E-3</v>
       </c>
-      <c r="J49">
+      <c r="J49" s="4">
         <v>4.2784572344689298E-3</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="4">
         <v>1.40626088765745E-3</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="4">
         <v>1.5390383627254501E-2</v>
       </c>
-      <c r="M49">
+      <c r="M49" s="4">
         <v>5.0585744708835697E-3</v>
       </c>
-      <c r="N49">
+      <c r="N49" s="4">
         <v>2.1661648713426799E-2</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="4">
         <v>7.1198396240715698E-3</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="4">
         <v>1.2737504475617899E-2</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="4">
         <v>4.1866152607802302E-3</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="4">
         <v>1.38150774193548E-3</v>
       </c>
-      <c r="S49">
+      <c r="S49" s="4">
         <v>4.5407963595573602E-4</v>
       </c>
-      <c r="T49">
+      <c r="T49" s="4">
         <v>8.7829540440881697E-3</v>
       </c>
-      <c r="U49">
+      <c r="U49" s="4">
         <v>2.8868173908081899E-3</v>
       </c>
-      <c r="V49">
+      <c r="V49" s="4">
         <v>3.3735580645161199E-3</v>
       </c>
-      <c r="W49">
+      <c r="W49" s="4">
         <v>1.10883491370442E-3</v>
       </c>
-      <c r="X49">
+      <c r="X49" s="4">
         <v>3.8475560483870901E-3</v>
       </c>
-      <c r="Y49">
+      <c r="Y49" s="4">
         <v>1.2646305168896299E-3</v>
       </c>
       <c r="Z49" s="4"/>
@@ -6461,76 +6461,76 @@
       <c r="A50" s="1">
         <v>0.48958333333333298</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="4">
         <v>1.4619909079125901E-2</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="4">
         <v>4.8053317334688598E-3</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="4">
         <v>2.35488144567149E-2</v>
       </c>
-      <c r="E50">
+      <c r="E50" s="4">
         <v>7.7401210077284203E-3</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="4">
         <v>3.1381702795106299E-3</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="4">
         <v>1.03146669021985E-3</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="4">
         <v>9.87803406813627E-3</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="4">
         <v>3.2467527886116902E-3</v>
       </c>
-      <c r="J50">
+      <c r="J50" s="4">
         <v>4.3954697394789502E-3</v>
       </c>
-      <c r="K50">
+      <c r="K50" s="4">
         <v>1.44472103816141E-3</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="4">
         <v>1.5811298747494901E-2</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="4">
         <v>5.1969225805360694E-3</v>
       </c>
-      <c r="N50">
+      <c r="N50" s="4">
         <v>2.2254078096192301E-2</v>
       </c>
-      <c r="O50">
+      <c r="O50" s="4">
         <v>7.31456174562753E-3</v>
       </c>
-      <c r="P50">
+      <c r="P50" s="4">
         <v>1.30858653974615E-2</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="4">
         <v>4.3011159586557098E-3</v>
       </c>
-      <c r="R50">
+      <c r="R50" s="4">
         <v>1.3735155483870899E-3</v>
       </c>
-      <c r="S50">
+      <c r="S50" s="4">
         <v>4.5145272897086802E-4</v>
       </c>
-      <c r="T50">
+      <c r="T50" s="4">
         <v>9.0231610621242398E-3</v>
       </c>
-      <c r="U50">
+      <c r="U50" s="4">
         <v>2.9657696195890598E-3</v>
       </c>
-      <c r="V50">
+      <c r="V50" s="4">
         <v>3.3540416129032198E-3</v>
       </c>
-      <c r="W50">
+      <c r="W50" s="4">
         <v>1.1024201662697599E-3</v>
       </c>
-      <c r="X50">
+      <c r="X50" s="4">
         <v>3.8252974596774099E-3</v>
       </c>
-      <c r="Y50">
+      <c r="Y50" s="4">
         <v>1.25731447257705E-3</v>
       </c>
       <c r="Z50" s="4"/>
@@ -6585,76 +6585,76 @@
       <c r="A51" s="1">
         <v>0.5</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="4">
         <v>1.5061654842588401E-2</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="4">
         <v>4.9505265444490599E-3</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="4">
         <v>2.4067512722913902E-2</v>
       </c>
-      <c r="E51">
+      <c r="E51" s="4">
         <v>7.9106088832118695E-3</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="4">
         <v>3.09607547029542E-3</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="4">
         <v>1.0176307955202799E-3</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="4">
         <v>1.0215168336673301E-2</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="4">
         <v>3.3575634639909299E-3</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="4">
         <v>4.5454857715430796E-3</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="4">
         <v>1.4940289234228899E-3</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="4">
         <v>1.6350933517034E-2</v>
       </c>
-      <c r="M51">
+      <c r="M51" s="4">
         <v>5.3742919518854201E-3</v>
       </c>
-      <c r="N51">
+      <c r="N51" s="4">
         <v>2.3013602945891699E-2</v>
       </c>
-      <c r="O51">
+      <c r="O51" s="4">
         <v>7.5642054912120902E-3</v>
       </c>
-      <c r="P51">
+      <c r="P51" s="4">
         <v>1.3532481963927799E-2</v>
       </c>
-      <c r="Q51">
+      <c r="Q51" s="4">
         <v>4.4479117251627299E-3</v>
       </c>
-      <c r="R51">
+      <c r="R51" s="4">
         <v>1.32442064516129E-3</v>
       </c>
-      <c r="S51">
+      <c r="S51" s="4">
         <v>4.3531601463525101E-4</v>
       </c>
-      <c r="T51">
+      <c r="T51" s="4">
         <v>9.3311187775551099E-3</v>
       </c>
-      <c r="U51">
+      <c r="U51" s="4">
         <v>3.0669904257183802E-3</v>
       </c>
-      <c r="V51">
+      <c r="V51" s="4">
         <v>3.2341548387096698E-3</v>
       </c>
-      <c r="W51">
+      <c r="W51" s="4">
         <v>1.0630152891711799E-3</v>
       </c>
-      <c r="X51">
+      <c r="X51" s="4">
         <v>3.6885661290322501E-3</v>
       </c>
-      <c r="Y51">
+      <c r="Y51" s="4">
         <v>1.2123730575140301E-3</v>
       </c>
       <c r="Z51" s="4"/>
@@ -6709,76 +6709,76 @@
       <c r="A52" s="1">
         <v>0.51041666666666696</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="4">
         <v>1.55038596494925E-2</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="4">
         <v>5.0958722357121299E-3</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="4">
         <v>2.4503595730902501E-2</v>
       </c>
-      <c r="E52">
+      <c r="E52" s="4">
         <v>8.0539424364762992E-3</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="4">
         <v>3.00742588806645E-3</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="4">
         <v>9.8849308691087E-4</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="4">
         <v>1.0565787975951899E-2</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="4">
         <v>3.4728065663853398E-3</v>
       </c>
-      <c r="J52">
+      <c r="J52" s="4">
         <v>4.7015024448897698E-3</v>
       </c>
-      <c r="K52">
+      <c r="K52" s="4">
         <v>1.54530912409483E-3</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="4">
         <v>1.6912153677354699E-2</v>
       </c>
-      <c r="M52">
+      <c r="M52" s="4">
         <v>5.5587560980887504E-3</v>
       </c>
-      <c r="N52">
+      <c r="N52" s="4">
         <v>2.3803508789579101E-2</v>
       </c>
-      <c r="O52">
+      <c r="O52" s="4">
         <v>7.8238349866200305E-3</v>
       </c>
-      <c r="P52">
+      <c r="P52" s="4">
         <v>1.39969631930527E-2</v>
       </c>
-      <c r="Q52">
+      <c r="Q52" s="4">
         <v>4.6005793223300303E-3</v>
       </c>
-      <c r="R52">
+      <c r="R52" s="4">
         <v>1.2444987096774101E-3</v>
       </c>
-      <c r="S52">
+      <c r="S52" s="4">
         <v>4.0904694478657199E-4</v>
       </c>
-      <c r="T52">
+      <c r="T52" s="4">
         <v>9.6513948016031994E-3</v>
       </c>
-      <c r="U52">
+      <c r="U52" s="4">
         <v>3.17226006409288E-3</v>
       </c>
-      <c r="V52">
+      <c r="V52" s="4">
         <v>3.0389903225806398E-3</v>
       </c>
-      <c r="W52">
+      <c r="W52" s="4">
         <v>9.9886781482464403E-4</v>
       </c>
-      <c r="X52">
+      <c r="X52" s="4">
         <v>3.4659802419354799E-3</v>
       </c>
-      <c r="Y52">
+      <c r="Y52" s="4">
         <v>1.13921261438818E-3</v>
       </c>
       <c r="Z52" s="4"/>
@@ -6833,76 +6833,76 @@
       <c r="A53" s="1">
         <v>0.52083333333333304</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="4">
         <v>1.58255306796172E-2</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="4">
         <v>5.2016003904106498E-3</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="4">
         <v>2.4743172339916901E-2</v>
       </c>
-      <c r="E53">
+      <c r="E53" s="4">
         <v>8.1326874598320002E-3</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="4">
         <v>2.8910369197265402E-3</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="4">
         <v>9.50237882999377E-4</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="4">
         <v>1.08354953907815E-2</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="4">
         <v>3.5614551066887302E-3</v>
       </c>
-      <c r="J53">
+      <c r="J53" s="4">
         <v>4.8215152705410802E-3</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="4">
         <v>1.5847554323040101E-3</v>
       </c>
-      <c r="L53">
+      <c r="L53" s="4">
         <v>1.7343861492985901E-2</v>
       </c>
-      <c r="M53">
+      <c r="M53" s="4">
         <v>5.70065159516823E-3</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="4">
         <v>2.4411128669338599E-2</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="4">
         <v>8.0235499830876716E-3</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="4">
         <v>1.43542564462257E-2</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="4">
         <v>4.7180159355356402E-3</v>
       </c>
-      <c r="R53">
+      <c r="R53" s="4">
         <v>1.1520176129032199E-3</v>
       </c>
-      <c r="S53">
+      <c r="S53" s="4">
         <v>3.78649878247386E-4</v>
       </c>
-      <c r="T53">
+      <c r="T53" s="4">
         <v>9.8977609739478896E-3</v>
       </c>
-      <c r="U53">
+      <c r="U53" s="4">
         <v>3.25323670899633E-3</v>
       </c>
-      <c r="V53">
+      <c r="V53" s="4">
         <v>2.8131570967741899E-3</v>
       </c>
-      <c r="W53">
+      <c r="W53" s="4">
         <v>9.2464002308079401E-4</v>
       </c>
-      <c r="X53">
+      <c r="X53" s="4">
         <v>3.20841657258064E-3</v>
       </c>
-      <c r="Y53">
+      <c r="Y53" s="4">
         <v>1.0545555301997001E-3</v>
       </c>
       <c r="Z53" s="4"/>
@@ -6957,76 +6957,76 @@
       <c r="A54" s="1">
         <v>0.53125</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="4">
         <v>1.5925877543280099E-2</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="4">
         <v>5.2345828095011699E-3</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="4">
         <v>2.46912690835852E-2</v>
       </c>
-      <c r="E54">
+      <c r="E54" s="4">
         <v>8.1156276844687493E-3</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="4">
         <v>2.7706430098099399E-3</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="4">
         <v>9.1066631844945298E-4</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="4">
         <v>1.09433783567134E-2</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="4">
         <v>3.59691452281009E-3</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="4">
         <v>4.8695204008016007E-3</v>
       </c>
-      <c r="K54">
+      <c r="K54" s="4">
         <v>1.60053395558769E-3</v>
       </c>
-      <c r="L54">
+      <c r="L54" s="4">
         <v>1.7516544619238399E-2</v>
       </c>
-      <c r="M54">
+      <c r="M54" s="4">
         <v>5.75740979400002E-3</v>
       </c>
-      <c r="N54">
+      <c r="N54" s="4">
         <v>2.4654176621242401E-2</v>
       </c>
-      <c r="O54">
+      <c r="O54" s="4">
         <v>8.1034359816747302E-3</v>
       </c>
-      <c r="P54">
+      <c r="P54" s="4">
         <v>1.44971737474949E-2</v>
       </c>
-      <c r="Q54">
+      <c r="Q54" s="4">
         <v>4.7649905808178896E-3</v>
       </c>
-      <c r="R54">
+      <c r="R54" s="4">
         <v>1.06752870967741E-3</v>
       </c>
-      <c r="S54">
+      <c r="S54" s="4">
         <v>3.5087971869306899E-4</v>
       </c>
-      <c r="T54">
+      <c r="T54" s="4">
         <v>9.9963074428857709E-3</v>
       </c>
-      <c r="U54">
+      <c r="U54" s="4">
         <v>3.28562736695771E-3</v>
       </c>
-      <c r="V54">
+      <c r="V54" s="4">
         <v>2.6068403225806402E-3</v>
       </c>
-      <c r="W54">
+      <c r="W54" s="4">
         <v>8.5682697877159794E-4</v>
       </c>
-      <c r="X54">
+      <c r="X54" s="4">
         <v>2.9731114919354798E-3</v>
       </c>
-      <c r="Y54">
+      <c r="Y54" s="4">
         <v>9.7721449032380902E-4</v>
       </c>
       <c r="Z54" s="4"/>
@@ -7081,76 +7081,76 @@
       <c r="A55" s="1">
         <v>0.54166666666666696</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="4">
         <v>1.57181850232723E-2</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="4">
         <v>5.1663175794100799E-3</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="4">
         <v>2.4268747001119601E-2</v>
       </c>
-      <c r="E55">
+      <c r="E55" s="4">
         <v>7.9767513918752309E-3</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="4">
         <v>2.6589230233854799E-3</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="4">
         <v>8.7394573468093392E-4</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="4">
         <v>1.0822010020039999E-2</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="4">
         <v>3.55702267967356E-3</v>
       </c>
-      <c r="J55">
+      <c r="J55" s="4">
         <v>4.8155146292585098E-3</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="4">
         <v>1.5827831168935601E-3</v>
       </c>
-      <c r="L55">
+      <c r="L55" s="4">
         <v>1.7322276102204399E-2</v>
       </c>
-      <c r="M55">
+      <c r="M55" s="4">
         <v>5.6935568203142599E-3</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="4">
         <v>2.43807476753507E-2</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="4">
         <v>8.0135642332642906E-3</v>
       </c>
-      <c r="P55">
+      <c r="P55" s="4">
         <v>1.4336391783567101E-2</v>
       </c>
-      <c r="Q55">
+      <c r="Q55" s="4">
         <v>4.7121441048753702E-3</v>
       </c>
-      <c r="R55">
+      <c r="R55" s="4">
         <v>1.0035911612903199E-3</v>
       </c>
-      <c r="S55">
+      <c r="S55" s="4">
         <v>3.2986446281412499E-4</v>
       </c>
-      <c r="T55">
+      <c r="T55" s="4">
         <v>9.8854426653306599E-3</v>
       </c>
-      <c r="U55">
+      <c r="U55" s="4">
         <v>3.2491878767511601E-3</v>
       </c>
-      <c r="V55">
+      <c r="V55" s="4">
         <v>2.4507087096774099E-3</v>
       </c>
-      <c r="W55">
+      <c r="W55" s="4">
         <v>8.0550899929436907E-4</v>
       </c>
-      <c r="X55">
+      <c r="X55" s="4">
         <v>2.7950427822580602E-3</v>
       </c>
-      <c r="Y55">
+      <c r="Y55" s="4">
         <v>9.1868613582313198E-4</v>
       </c>
       <c r="Z55" s="4"/>
@@ -7205,76 +7205,76 @@
       <c r="A56" s="1">
         <v>0.55208333333333304</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="4">
         <v>1.52784971965867E-2</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="4">
         <v>5.0217991795378693E-3</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="4">
         <v>2.3569876504331198E-2</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="4">
         <v>7.7470437680024094E-3</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="4">
         <v>2.5631284732367901E-3</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="4">
         <v>8.4245958868430101E-4</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="4">
         <v>1.0525331863727399E-2</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="4">
         <v>3.4595092853398298E-3</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="4">
         <v>4.6835005210420803E-3</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="4">
         <v>1.53939217786345E-3</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="4">
         <v>1.6847397505009999E-2</v>
       </c>
-      <c r="M56">
+      <c r="M56" s="4">
         <v>5.5374717735268203E-3</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="4">
         <v>2.37123658076152E-2</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="4">
         <v>7.7938777371498796E-3</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="4">
         <v>1.39433692050768E-2</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="4">
         <v>4.5829638303491894E-3</v>
       </c>
-      <c r="R56">
+      <c r="R56" s="4">
         <v>9.6134670967741901E-4</v>
       </c>
-      <c r="S56">
+      <c r="S56" s="4">
         <v>3.1597938303696698E-4</v>
       </c>
-      <c r="T56">
+      <c r="T56" s="4">
         <v>9.6144398757514998E-3</v>
       </c>
-      <c r="U56">
+      <c r="U56" s="4">
         <v>3.1601135673573599E-3</v>
       </c>
-      <c r="V56">
+      <c r="V56" s="4">
         <v>2.34755032258064E-3</v>
       </c>
-      <c r="W56">
+      <c r="W56" s="4">
         <v>7.7160247713977E-4</v>
       </c>
-      <c r="X56">
+      <c r="X56" s="4">
         <v>2.6773902419354799E-3</v>
       </c>
-      <c r="Y56">
+      <c r="Y56" s="4">
         <v>8.8001561588518394E-4</v>
       </c>
       <c r="Z56" s="4"/>
@@ -7329,76 +7329,76 @@
       <c r="A57" s="1">
         <v>0.5625</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="4">
         <v>1.4709076947313901E-2</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="4">
         <v>4.8346397944349414E-3</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="4">
         <v>2.2712970201661999E-2</v>
       </c>
-      <c r="E57">
+      <c r="E57" s="4">
         <v>7.4653922866874502E-3</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="4">
         <v>2.4872397005300901E-3</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="4">
         <v>8.1751615533407591E-4</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="4">
         <v>1.0127513426853699E-2</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="4">
         <v>3.32875268839233E-3</v>
       </c>
-      <c r="J57">
+      <c r="J57" s="4">
         <v>4.5064816032064098E-3</v>
       </c>
-      <c r="K57">
+      <c r="K57" s="4">
         <v>1.4812088732548999E-3</v>
       </c>
-      <c r="L57">
+      <c r="L57" s="4">
         <v>1.6210628476953901E-2</v>
       </c>
-      <c r="M57">
+      <c r="M57" s="4">
         <v>5.3281759153345903E-3</v>
       </c>
-      <c r="N57">
+      <c r="N57" s="4">
         <v>2.28161264849699E-2</v>
       </c>
-      <c r="O57">
+      <c r="O57" s="4">
         <v>7.4992981173600997E-3</v>
       </c>
-      <c r="P57">
+      <c r="P57" s="4">
         <v>1.34163616566466E-2</v>
       </c>
-      <c r="Q57">
+      <c r="Q57" s="4">
         <v>4.4097448258708996E-3</v>
       </c>
-      <c r="R57">
+      <c r="R57" s="4">
         <v>9.3851187096774199E-4</v>
       </c>
-      <c r="S57">
+      <c r="S57" s="4">
         <v>3.0847393450877302E-4</v>
       </c>
-      <c r="T57">
+      <c r="T57" s="4">
         <v>9.2510497715430802E-3</v>
       </c>
-      <c r="U57">
+      <c r="U57" s="4">
         <v>3.0406730161247602E-3</v>
       </c>
-      <c r="V57">
+      <c r="V57" s="4">
         <v>2.2917890322580602E-3</v>
       </c>
-      <c r="W57">
+      <c r="W57" s="4">
         <v>7.5327462732647404E-4</v>
       </c>
-      <c r="X57">
+      <c r="X57" s="4">
         <v>2.6137942741935398E-3</v>
       </c>
-      <c r="Y57">
+      <c r="Y57" s="4">
         <v>8.5911263213494203E-4</v>
       </c>
       <c r="Z57" s="4"/>
@@ -7453,76 +7453,76 @@
       <c r="A58" s="1">
         <v>0.57291666666666696</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="4">
         <v>1.41222883748141E-2</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="4">
         <v>4.64177171755364E-3</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="4">
         <v>2.1824838830855502E-2</v>
       </c>
-      <c r="E58">
+      <c r="E58" s="4">
         <v>7.1734776217926514E-3</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="4">
         <v>2.43769657524726E-3</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="4">
         <v>8.0123211753272707E-4</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="4">
         <v>9.7094669338677313E-3</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="4">
         <v>3.1913474509220698E-3</v>
       </c>
-      <c r="J58">
+      <c r="J58" s="4">
         <v>4.3204617234468886E-3</v>
       </c>
-      <c r="K58">
+      <c r="K58" s="4">
         <v>1.4200670955306701E-3</v>
       </c>
-      <c r="L58">
+      <c r="L58" s="4">
         <v>1.5541481362725399E-2</v>
       </c>
-      <c r="M58">
+      <c r="M58" s="4">
         <v>5.1082378948613914E-3</v>
       </c>
-      <c r="N58">
+      <c r="N58" s="4">
         <v>2.1874315671342601E-2</v>
       </c>
-      <c r="O58">
+      <c r="O58" s="4">
         <v>7.1897398728352499E-3</v>
       </c>
-      <c r="P58">
+      <c r="P58" s="4">
         <v>1.2862557114228399E-2</v>
       </c>
-      <c r="Q58">
+      <c r="Q58" s="4">
         <v>4.2277180754022002E-3</v>
       </c>
-      <c r="R58">
+      <c r="R58" s="4">
         <v>9.3394490322580603E-4</v>
       </c>
-      <c r="S58">
+      <c r="S58" s="4">
         <v>3.0697284480313411E-4</v>
       </c>
-      <c r="T58">
+      <c r="T58" s="4">
         <v>8.8691822044088108E-3</v>
       </c>
-      <c r="U58">
+      <c r="U58" s="4">
         <v>2.9151592165244E-3</v>
       </c>
-      <c r="V58">
+      <c r="V58" s="4">
         <v>2.28063677419354E-3</v>
       </c>
-      <c r="W58">
+      <c r="W58" s="4">
         <v>7.4960905736381502E-4</v>
       </c>
-      <c r="X58">
+      <c r="X58" s="4">
         <v>2.6010750806451598E-3</v>
       </c>
-      <c r="Y58">
+      <c r="Y58" s="4">
         <v>8.54932035384894E-4</v>
       </c>
       <c r="Z58" s="4"/>
@@ -7577,76 +7577,76 @@
       <c r="A59" s="1">
         <v>0.58333333333333304</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="4">
         <v>1.35995111261878E-2</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="4">
         <v>4.4699431453810497E-3</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="4">
         <v>2.10123842028564E-2</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="4">
         <v>6.90643669939036E-3</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="4">
         <v>2.4117854212457098E-3</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="4">
         <v>7.9271553306557599E-4</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="4">
         <v>9.3318765531062095E-3</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="4">
         <v>3.0672394944973201E-3</v>
       </c>
-      <c r="J59">
+      <c r="J59" s="4">
         <v>4.1524437675350698E-3</v>
       </c>
-      <c r="K59">
+      <c r="K59" s="4">
         <v>1.3648422640378101E-3</v>
       </c>
-      <c r="L59">
+      <c r="L59" s="4">
         <v>1.49370904208416E-2</v>
       </c>
-      <c r="M59">
+      <c r="M59" s="4">
         <v>4.9095841989501114E-3</v>
       </c>
-      <c r="N59">
+      <c r="N59" s="4">
         <v>2.1023647839679301E-2</v>
       </c>
-      <c r="O59">
+      <c r="O59" s="4">
         <v>6.9101388777805502E-3</v>
       </c>
-      <c r="P59">
+      <c r="P59" s="4">
         <v>1.23623465597862E-2</v>
       </c>
-      <c r="Q59">
+      <c r="Q59" s="4">
         <v>4.0633068169143296E-3</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="4">
         <v>9.4193709677419305E-4</v>
       </c>
-      <c r="S59">
+      <c r="S59" s="4">
         <v>3.09599751788002E-4</v>
       </c>
-      <c r="T59">
+      <c r="T59" s="4">
         <v>8.5242695631262497E-3</v>
       </c>
-      <c r="U59">
+      <c r="U59" s="4">
         <v>2.80179191365957E-3</v>
       </c>
-      <c r="V59">
+      <c r="V59" s="4">
         <v>2.30015322580645E-3</v>
       </c>
-      <c r="W59">
+      <c r="W59" s="4">
         <v>7.5602380479846895E-4</v>
       </c>
-      <c r="X59">
+      <c r="X59" s="4">
         <v>2.6233336693548301E-3</v>
       </c>
-      <c r="Y59">
+      <c r="Y59" s="4">
         <v>8.6224807969747792E-4</v>
       </c>
       <c r="Z59" s="4"/>
@@ -7701,76 +7701,76 @@
       <c r="A60" s="1">
         <v>0.59375</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="4">
         <v>1.3156862793263901E-2</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="4">
         <v>4.3244516741650302E-3</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="4">
         <v>2.03135257965496E-2</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="4">
         <v>6.6767330494666701E-3</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="4">
         <v>2.4037755380923102E-3</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="4">
         <v>7.9008281178871199E-4</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="4">
         <v>9.0082276553106206E-3</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="4">
         <v>2.96086124613326E-3</v>
       </c>
-      <c r="J60">
+      <c r="J60" s="4">
         <v>4.0084283767534996E-3</v>
       </c>
-      <c r="K60">
+      <c r="K60" s="4">
         <v>1.3175066941867801E-3</v>
       </c>
-      <c r="L60">
+      <c r="L60" s="4">
         <v>1.4419041042084101E-2</v>
       </c>
-      <c r="M60">
+      <c r="M60" s="4">
         <v>4.7393096024547299E-3</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="4">
         <v>2.0294503983967899E-2</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="4">
         <v>6.6704808820193702E-3</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="4">
         <v>1.19335946559786E-2</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="4">
         <v>3.9223828810675898E-3</v>
       </c>
-      <c r="R60">
+      <c r="R60" s="4">
         <v>9.5792148387096796E-4</v>
       </c>
-      <c r="S60">
+      <c r="S60" s="4">
         <v>3.1485356575773702E-4</v>
       </c>
-      <c r="T60">
+      <c r="T60" s="4">
         <v>8.2286301563126198E-3</v>
       </c>
-      <c r="U60">
+      <c r="U60" s="4">
         <v>2.7046199397754199E-3</v>
       </c>
-      <c r="V60">
+      <c r="V60" s="4">
         <v>2.3391861290322502E-3</v>
       </c>
-      <c r="W60">
+      <c r="W60" s="4">
         <v>7.6885329966777606E-4</v>
       </c>
-      <c r="X60">
+      <c r="X60" s="4">
         <v>2.6678508467741901E-3</v>
       </c>
-      <c r="Y60">
+      <c r="Y60" s="4">
         <v>8.7688016832264805E-4</v>
       </c>
       <c r="Z60" s="4"/>
@@ -7825,76 +7825,76 @@
       <c r="A61" s="1">
         <v>0.60416666666666696</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="4">
         <v>1.2772098526149E-2</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="4">
         <v>4.1979857753235792E-3</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="4">
         <v>1.9719935983245E-2</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="4">
         <v>6.4816295128373698E-3</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="4">
         <v>2.4034229891234E-3</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="4">
         <v>7.8996693454633509E-4</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="4">
         <v>8.7250348697394797E-3</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="4">
         <v>2.86778027881469E-3</v>
       </c>
-      <c r="J61">
+      <c r="J61" s="4">
         <v>3.88241490981964E-3</v>
       </c>
-      <c r="K61">
+      <c r="K61" s="4">
         <v>1.2760880705671399E-3</v>
       </c>
-      <c r="L61">
+      <c r="L61" s="4">
         <v>1.39657478356713E-2</v>
       </c>
-      <c r="M61">
+      <c r="M61" s="4">
         <v>4.5903193305212786E-3</v>
       </c>
-      <c r="N61">
+      <c r="N61" s="4">
         <v>1.9656503110220401E-2</v>
       </c>
-      <c r="O61">
+      <c r="O61" s="4">
         <v>6.4607801357283402E-3</v>
       </c>
-      <c r="P61">
+      <c r="P61" s="4">
         <v>1.15584367401469E-2</v>
       </c>
-      <c r="Q61">
+      <c r="Q61" s="4">
         <v>3.7990744372017001E-3</v>
       </c>
-      <c r="R61">
+      <c r="R61" s="4">
         <v>9.761893548387089E-4</v>
       </c>
-      <c r="S61">
+      <c r="S61" s="4">
         <v>3.2085792458029299E-4</v>
       </c>
-      <c r="T61">
+      <c r="T61" s="4">
         <v>7.9699456753506998E-3</v>
       </c>
-      <c r="U61">
+      <c r="U61" s="4">
         <v>2.61959446262679E-3</v>
       </c>
-      <c r="V61">
+      <c r="V61" s="4">
         <v>2.3837951612903198E-3</v>
       </c>
-      <c r="W61">
+      <c r="W61" s="4">
         <v>7.83515579518413E-4</v>
       </c>
-      <c r="X61">
+      <c r="X61" s="4">
         <v>2.7187276209677401E-3</v>
       </c>
-      <c r="Y61">
+      <c r="Y61" s="4">
         <v>8.9360255532284106E-4</v>
       </c>
       <c r="Z61" s="4"/>
@@ -7949,76 +7949,76 @@
       <c r="A62" s="1">
         <v>0.61458333333333304</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="4">
         <v>1.24303514644126E-2</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="4">
         <v>4.0856589481392501E-3</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="4">
         <v>1.9240777898855099E-2</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="4">
         <v>6.3241378666304303E-3</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="4">
         <v>2.3958435277813602E-3</v>
       </c>
-      <c r="G62">
+      <c r="G62" s="4">
         <v>7.8747568607739004E-4</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="4">
         <v>8.4755555110220399E-3</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="4">
         <v>2.7857803790340601E-3</v>
       </c>
-      <c r="J62">
+      <c r="J62" s="4">
         <v>3.77140304609218E-3</v>
       </c>
-      <c r="K62">
+      <c r="K62" s="4">
         <v>1.2396002354736399E-3</v>
       </c>
-      <c r="L62">
+      <c r="L62" s="4">
         <v>1.35664181062124E-2</v>
       </c>
-      <c r="M62">
+      <c r="M62" s="4">
         <v>4.4590659957227507E-3</v>
       </c>
-      <c r="N62">
+      <c r="N62" s="4">
         <v>1.9094454721442802E-2</v>
       </c>
-      <c r="O62">
+      <c r="O62" s="4">
         <v>6.2760437639957714E-3</v>
       </c>
-      <c r="P62">
+      <c r="P62" s="4">
         <v>1.1227940480961899E-2</v>
       </c>
-      <c r="Q62">
+      <c r="Q62" s="4">
         <v>3.6904455699864999E-3</v>
       </c>
-      <c r="R62">
+      <c r="R62" s="4">
         <v>9.8760677419354806E-4</v>
       </c>
-      <c r="S62">
+      <c r="S62" s="4">
         <v>3.2461064884439002E-4</v>
       </c>
-      <c r="T62">
+      <c r="T62" s="4">
         <v>7.7420569659318586E-3</v>
       </c>
-      <c r="U62">
+      <c r="U62" s="4">
         <v>2.54469106609109E-3</v>
       </c>
-      <c r="V62">
+      <c r="V62" s="4">
         <v>2.4116758064516102E-3</v>
       </c>
-      <c r="W62">
+      <c r="W62" s="4">
         <v>7.9267950442506098E-4</v>
       </c>
-      <c r="X62">
+      <c r="X62" s="4">
         <v>2.7505256048387001E-3</v>
       </c>
-      <c r="Y62">
+      <c r="Y62" s="4">
         <v>9.0405404719796196E-4</v>
       </c>
       <c r="Z62" s="4"/>
@@ -8073,76 +8073,76 @@
       <c r="A63" s="1">
         <v>0.625</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="4">
         <v>1.2119477973430701E-2</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="4">
         <v>3.9834797729320203E-3</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="4">
         <v>1.8877998240652501E-2</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="4">
         <v>6.2048979592970403E-3</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="4">
         <v>2.3732527462182402E-3</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="4">
         <v>7.8005045525402199E-4</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="4">
         <v>8.25304689378757E-3</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="4">
         <v>2.71264533328376E-3</v>
       </c>
-      <c r="J63">
+      <c r="J63" s="4">
         <v>3.6723924649298598E-3</v>
       </c>
-      <c r="K63">
+      <c r="K63" s="4">
         <v>1.20705703120107E-3</v>
       </c>
-      <c r="L63">
+      <c r="L63" s="4">
         <v>1.32102591583166E-2</v>
       </c>
-      <c r="M63">
+      <c r="M63" s="4">
         <v>4.3420022106321803E-3</v>
       </c>
-      <c r="N63">
+      <c r="N63" s="4">
         <v>1.8593168320641201E-2</v>
       </c>
-      <c r="O63">
+      <c r="O63" s="4">
         <v>6.1112788919099586E-3</v>
       </c>
-      <c r="P63">
+      <c r="P63" s="4">
         <v>1.09331735470941E-2</v>
       </c>
-      <c r="Q63">
+      <c r="Q63" s="4">
         <v>3.5935603640918699E-3</v>
       </c>
-      <c r="R63">
+      <c r="R63" s="4">
         <v>9.8760677419354806E-4</v>
       </c>
-      <c r="S63">
+      <c r="S63" s="4">
         <v>3.2461064884439002E-4</v>
       </c>
-      <c r="T63">
+      <c r="T63" s="4">
         <v>7.5388048737474898E-3</v>
       </c>
-      <c r="U63">
+      <c r="U63" s="4">
         <v>2.4778853340457398E-3</v>
       </c>
-      <c r="V63">
+      <c r="V63" s="4">
         <v>2.4116758064516102E-3</v>
       </c>
-      <c r="W63">
+      <c r="W63" s="4">
         <v>7.9267950442506098E-4</v>
       </c>
-      <c r="X63">
+      <c r="X63" s="4">
         <v>2.7505256048387001E-3</v>
       </c>
-      <c r="Y63">
+      <c r="Y63" s="4">
         <v>9.0405404719796196E-4</v>
       </c>
       <c r="Z63" s="4"/>
@@ -8197,76 +8197,76 @@
       <c r="A64" s="1">
         <v>0.63541666666666696</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="4">
         <v>1.1851621687827199E-2</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="4">
         <v>3.8954396693819098E-3</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="4">
         <v>1.8617105282740899E-2</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="4">
         <v>6.1191465908783998E-3</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="4">
         <v>2.34343505228198E-3</v>
       </c>
-      <c r="G64">
+      <c r="G64" s="4">
         <v>7.7024985320408603E-4</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="4">
         <v>8.0642517034068099E-3</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="4">
         <v>2.6505913550713901E-3</v>
       </c>
-      <c r="J64">
+      <c r="J64" s="4">
         <v>3.58838348697394E-3</v>
       </c>
-      <c r="K64">
+      <c r="K64" s="4">
         <v>1.1794446154546399E-3</v>
       </c>
-      <c r="L64">
+      <c r="L64" s="4">
         <v>1.29080636873747E-2</v>
       </c>
-      <c r="M64">
+      <c r="M64" s="4">
         <v>4.2426753626765394E-3</v>
       </c>
-      <c r="N64">
+      <c r="N64" s="4">
         <v>1.81678344048096E-2</v>
       </c>
-      <c r="O64">
+      <c r="O64" s="4">
         <v>5.9714783943826096E-3</v>
       </c>
-      <c r="P64">
+      <c r="P64" s="4">
         <v>1.0683068269872999E-2</v>
       </c>
-      <c r="Q64">
+      <c r="Q64" s="4">
         <v>3.5113547348479299E-3</v>
       </c>
-      <c r="R64">
+      <c r="R64" s="4">
         <v>9.8075632258064508E-4</v>
       </c>
-      <c r="S64">
+      <c r="S64" s="4">
         <v>3.2235901428593098E-4</v>
       </c>
-      <c r="T64">
+      <c r="T64" s="4">
         <v>7.3663485531062101E-3</v>
       </c>
-      <c r="U64">
+      <c r="U64" s="4">
         <v>2.42120168261332E-3</v>
       </c>
-      <c r="V64">
+      <c r="V64" s="4">
         <v>2.3949474193548301E-3</v>
       </c>
-      <c r="W64">
+      <c r="W64" s="4">
         <v>7.8718114948107202E-4</v>
       </c>
-      <c r="X64">
+      <c r="X64" s="4">
         <v>2.7314468145161201E-3</v>
       </c>
-      <c r="Y64">
+      <c r="Y64" s="4">
         <v>8.9778315207288996E-4</v>
       </c>
       <c r="Z64" s="4"/>
@@ -8321,76 +8321,76 @@
       <c r="A65" s="1">
         <v>0.64583333333333304</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="4">
         <v>1.1638245435774699E-2</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="4">
         <v>3.8253062869096199E-3</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="4">
         <v>1.84453834958852E-2</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="4">
         <v>6.0627043690260002E-3</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="4">
         <v>2.3123998941431199E-3</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="4">
         <v>7.6004909002213E-4</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="4">
         <v>7.9159126252504996E-3</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="4">
         <v>2.6018346579045198E-3</v>
       </c>
-      <c r="J65">
+      <c r="J65" s="4">
         <v>3.52237643286573E-3</v>
       </c>
-      <c r="K65">
+      <c r="K65" s="4">
         <v>1.1577491459395801E-3</v>
       </c>
-      <c r="L65">
+      <c r="L65" s="4">
         <v>1.26706243887775E-2</v>
       </c>
-      <c r="M65">
+      <c r="M65" s="4">
         <v>4.1646328392828296E-3</v>
       </c>
-      <c r="N65">
+      <c r="N65" s="4">
         <v>1.7833643470941799E-2</v>
       </c>
-      <c r="O65">
+      <c r="O65" s="4">
         <v>5.8616351463254002E-3</v>
       </c>
-      <c r="P65">
+      <c r="P65" s="4">
         <v>1.0486556980627899E-2</v>
       </c>
-      <c r="Q65">
+      <c r="Q65" s="4">
         <v>3.4467645975848398E-3</v>
       </c>
-      <c r="R65">
+      <c r="R65" s="4">
         <v>9.7048064516128997E-4</v>
       </c>
-      <c r="S65">
+      <c r="S65" s="4">
         <v>3.1898156244824399E-4</v>
       </c>
-      <c r="T65">
+      <c r="T65" s="4">
         <v>7.2308471583166301E-3</v>
       </c>
-      <c r="U65">
+      <c r="U65" s="4">
         <v>2.3766645279164199E-3</v>
       </c>
-      <c r="V65">
+      <c r="V65" s="4">
         <v>2.3698548387096701E-3</v>
       </c>
-      <c r="W65">
+      <c r="W65" s="4">
         <v>7.7893361706508901E-4</v>
       </c>
-      <c r="X65">
+      <c r="X65" s="4">
         <v>2.7028286290322499E-3</v>
       </c>
-      <c r="Y65">
+      <c r="Y65" s="4">
         <v>8.8837680938528099E-4</v>
       </c>
       <c r="Z65" s="4"/>
@@ -8445,76 +8445,76 @@
       <c r="A66" s="1">
         <v>0.65625</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="4">
         <v>1.14719712278104E-2</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="4">
         <v>3.7706545976505402E-3</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="4">
         <v>1.83182189904528E-2</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="4">
         <v>6.0209074173474403E-3</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="4">
         <v>2.2847875816956399E-3</v>
       </c>
-      <c r="G66">
+      <c r="G66" s="4">
         <v>7.5097336181341305E-4</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="4">
         <v>7.8012869739478904E-3</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="4">
         <v>2.5641590282755801E-3</v>
       </c>
-      <c r="J66">
+      <c r="J66" s="4">
         <v>3.47137098196392E-3</v>
       </c>
-      <c r="K66">
+      <c r="K66" s="4">
         <v>1.14098446495068E-3</v>
       </c>
-      <c r="L66">
+      <c r="L66" s="4">
         <v>1.2487148567134201E-2</v>
       </c>
-      <c r="M66">
+      <c r="M66" s="4">
         <v>4.1043272530240501E-3</v>
       </c>
-      <c r="N66">
+      <c r="N66" s="4">
         <v>1.7575405022044001E-2</v>
       </c>
-      <c r="O66">
+      <c r="O66" s="4">
         <v>5.7767562728266502E-3</v>
       </c>
-      <c r="P66">
+      <c r="P66" s="4">
         <v>1.03347073480293E-2</v>
       </c>
-      <c r="Q66">
+      <c r="Q66" s="4">
         <v>3.3968540369724602E-3</v>
       </c>
-      <c r="R66">
+      <c r="R66" s="4">
         <v>9.6020496774193497E-4</v>
       </c>
-      <c r="S66">
+      <c r="S66" s="4">
         <v>3.1560411061055699E-4</v>
       </c>
-      <c r="T66">
+      <c r="T66" s="4">
         <v>7.12614153507014E-3</v>
       </c>
-      <c r="U66">
+      <c r="U66" s="4">
         <v>2.3422494538324502E-3</v>
       </c>
-      <c r="V66">
+      <c r="V66" s="4">
         <v>2.3447622580645101E-3</v>
       </c>
-      <c r="W66">
+      <c r="W66" s="4">
         <v>7.70686084649106E-4</v>
       </c>
-      <c r="X66">
+      <c r="X66" s="4">
         <v>2.6742104435483801E-3</v>
       </c>
-      <c r="Y66">
+      <c r="Y66" s="4">
         <v>8.7897046669767201E-4</v>
       </c>
       <c r="Z66" s="4"/>
@@ -8569,76 +8569,76 @@
       <c r="A67" s="1">
         <v>0.66666666666666696</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="4">
         <v>1.1365623505009999E-2</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="4">
         <v>3.7356997915440702E-3</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="4">
         <v>1.8222896237208699E-2</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="4">
         <v>5.98957634349422E-3</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="4">
         <v>2.2701574824649201E-3</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="4">
         <v>7.4616468073908609E-4</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="4">
         <v>7.72711743486973E-3</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="4">
         <v>2.5397806796921499E-3</v>
       </c>
-      <c r="J67">
+      <c r="J67" s="4">
         <v>3.4383674549098098E-3</v>
       </c>
-      <c r="K67">
+      <c r="K67" s="4">
         <v>1.13013673019315E-3</v>
       </c>
-      <c r="L67">
+      <c r="L67" s="4">
         <v>1.23684289178356E-2</v>
       </c>
-      <c r="M67">
+      <c r="M67" s="4">
         <v>4.0653059913271896E-3</v>
       </c>
-      <c r="N67">
+      <c r="N67" s="4">
         <v>1.7408309555110201E-2</v>
       </c>
-      <c r="O67">
+      <c r="O67" s="4">
         <v>5.7218346487980503E-3</v>
       </c>
-      <c r="P67">
+      <c r="P67" s="4">
         <v>1.02364517034068E-2</v>
       </c>
-      <c r="Q67">
+      <c r="Q67" s="4">
         <v>3.3645589683409102E-3</v>
       </c>
-      <c r="R67">
+      <c r="R67" s="4">
         <v>9.5563799999999997E-4</v>
       </c>
-      <c r="S67">
+      <c r="S67" s="4">
         <v>3.1410302090491803E-4</v>
       </c>
-      <c r="T67">
+      <c r="T67" s="4">
         <v>7.0583908376753504E-3</v>
       </c>
-      <c r="U67">
+      <c r="U67" s="4">
         <v>2.3199808764840001E-3</v>
       </c>
-      <c r="V67">
+      <c r="V67" s="4">
         <v>2.3336099999999999E-3</v>
       </c>
-      <c r="W67">
+      <c r="W67" s="4">
         <v>7.6702051468644601E-4</v>
       </c>
-      <c r="X67">
+      <c r="X67" s="4">
         <v>2.6614912500000001E-3</v>
       </c>
-      <c r="Y67">
+      <c r="Y67" s="4">
         <v>8.7478986994762398E-4</v>
       </c>
       <c r="Z67" s="4"/>
@@ -8693,76 +8693,76 @@
       <c r="A68" s="1">
         <v>0.67708333333333304</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="4">
         <v>1.1326580256836199E-2</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="4">
         <v>3.7228668964548002E-3</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="4">
         <v>1.8185608197801399E-2</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="4">
         <v>5.9773203576277698E-3</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="4">
         <v>2.2638692865569799E-3</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="4">
         <v>7.4409785069389303E-4</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="4">
         <v>7.7001466933867696E-3</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="4">
         <v>2.5309158256618101E-3</v>
       </c>
-      <c r="J68">
+      <c r="J68" s="4">
         <v>3.4263661723446799E-3</v>
       </c>
-      <c r="K68">
+      <c r="K68" s="4">
         <v>1.1261920993722401E-3</v>
       </c>
-      <c r="L68">
+      <c r="L68" s="4">
         <v>1.2325258136272501E-2</v>
       </c>
-      <c r="M68">
+      <c r="M68" s="4">
         <v>4.0511164416192399E-3</v>
       </c>
-      <c r="N68">
+      <c r="N68" s="4">
         <v>1.7347547567134199E-2</v>
       </c>
-      <c r="O68">
+      <c r="O68" s="4">
         <v>5.70186314915129E-3</v>
       </c>
-      <c r="P68">
+      <c r="P68" s="4">
         <v>1.02007223780895E-2</v>
       </c>
-      <c r="Q68">
+      <c r="Q68" s="4">
         <v>3.35281530702035E-3</v>
       </c>
-      <c r="R68">
+      <c r="R68" s="4">
         <v>9.5335451612903199E-4</v>
       </c>
-      <c r="S68">
+      <c r="S68" s="4">
         <v>3.1335247605209898E-4</v>
       </c>
-      <c r="T68">
+      <c r="T68" s="4">
         <v>7.0337542204408797E-3</v>
       </c>
-      <c r="U68">
+      <c r="U68" s="4">
         <v>2.3118832119936599E-3</v>
       </c>
-      <c r="V68">
+      <c r="V68" s="4">
         <v>2.32803387096774E-3</v>
       </c>
-      <c r="W68">
+      <c r="W68" s="4">
         <v>7.6518772970511693E-4</v>
       </c>
-      <c r="X68">
+      <c r="X68" s="4">
         <v>2.6551316532258001E-3</v>
       </c>
-      <c r="Y68">
+      <c r="Y68" s="4">
         <v>8.7269957157259904E-4</v>
       </c>
       <c r="Z68" s="4"/>
@@ -8817,76 +8817,76 @@
       <c r="A69" s="1">
         <v>0.6875</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="4">
         <v>1.1362900279203499E-2</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="4">
         <v>3.73480471050667E-3</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="4">
         <v>1.8241540469180601E-2</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="4">
         <v>5.9957044061966494E-3</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="4">
         <v>2.2630576437552498E-3</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="4">
         <v>7.4383107660588095E-4</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="4">
         <v>7.72711743486973E-3</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="4">
         <v>2.5397806796921499E-3</v>
       </c>
-      <c r="J69">
+      <c r="J69" s="4">
         <v>3.4383674549098098E-3</v>
       </c>
-      <c r="K69">
+      <c r="K69" s="4">
         <v>1.13013673019315E-3</v>
       </c>
-      <c r="L69">
+      <c r="L69" s="4">
         <v>1.23684289178356E-2</v>
       </c>
-      <c r="M69">
+      <c r="M69" s="4">
         <v>4.0653059913271896E-3</v>
       </c>
-      <c r="N69">
+      <c r="N69" s="4">
         <v>1.7408309555110201E-2</v>
       </c>
-      <c r="O69">
+      <c r="O69" s="4">
         <v>5.7218346487980503E-3</v>
       </c>
-      <c r="P69">
+      <c r="P69" s="4">
         <v>1.02364517034068E-2</v>
       </c>
-      <c r="Q69">
+      <c r="Q69" s="4">
         <v>3.3645589683409102E-3</v>
       </c>
-      <c r="R69">
+      <c r="R69" s="4">
         <v>9.5107103225806401E-4</v>
       </c>
-      <c r="S69">
+      <c r="S69" s="4">
         <v>3.1260193119927901E-4</v>
       </c>
-      <c r="T69">
+      <c r="T69" s="4">
         <v>7.0583908376753504E-3</v>
       </c>
-      <c r="U69">
+      <c r="U69" s="4">
         <v>2.3199808764840001E-3</v>
       </c>
-      <c r="V69">
+      <c r="V69" s="4">
         <v>2.3224577419354801E-3</v>
       </c>
-      <c r="W69">
+      <c r="W69" s="4">
         <v>7.6335494472378699E-4</v>
       </c>
-      <c r="X69">
+      <c r="X69" s="4">
         <v>2.6487720564516101E-3</v>
       </c>
-      <c r="Y69">
+      <c r="Y69" s="4">
         <v>8.7060927319757497E-4</v>
       </c>
       <c r="Z69" s="4"/>
@@ -8941,76 +8941,76 @@
       <c r="A70" s="1">
         <v>0.69791666666666696</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="4">
         <v>1.1464482356842699E-2</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="4">
         <v>3.7681931247977099E-3</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="4">
         <v>1.8402827704071902E-2</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="4">
         <v>6.04871695667367E-3</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="4">
         <v>2.26526302524403E-3</v>
       </c>
-      <c r="G70">
+      <c r="G70" s="4">
         <v>7.4455595044709997E-4</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="4">
         <v>7.8012869739478904E-3</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="4">
         <v>2.5641590282755801E-3</v>
       </c>
-      <c r="J70">
+      <c r="J70" s="4">
         <v>3.47137098196392E-3</v>
       </c>
-      <c r="K70">
+      <c r="K70" s="4">
         <v>1.14098446495068E-3</v>
       </c>
-      <c r="L70">
+      <c r="L70" s="4">
         <v>1.2487148567134201E-2</v>
       </c>
-      <c r="M70">
+      <c r="M70" s="4">
         <v>4.1043272530240501E-3</v>
       </c>
-      <c r="N70">
+      <c r="N70" s="4">
         <v>1.7575405022044001E-2</v>
       </c>
-      <c r="O70">
+      <c r="O70" s="4">
         <v>5.7767562728266502E-3</v>
       </c>
-      <c r="P70">
+      <c r="P70" s="4">
         <v>1.03347073480293E-2</v>
       </c>
-      <c r="Q70">
+      <c r="Q70" s="4">
         <v>3.3968540369724602E-3</v>
       </c>
-      <c r="R70">
+      <c r="R70" s="4">
         <v>9.4764580645161295E-4</v>
       </c>
-      <c r="S70">
+      <c r="S70" s="4">
         <v>3.1147611392005003E-4</v>
       </c>
-      <c r="T70">
+      <c r="T70" s="4">
         <v>7.12614153507014E-3</v>
       </c>
-      <c r="U70">
+      <c r="U70" s="4">
         <v>2.3422494538324502E-3</v>
       </c>
-      <c r="V70">
+      <c r="V70" s="4">
         <v>2.3140935483870898E-3</v>
       </c>
-      <c r="W70">
+      <c r="W70" s="4">
         <v>7.6060576725179294E-4</v>
       </c>
-      <c r="X70">
+      <c r="X70" s="4">
         <v>2.6392326612903198E-3</v>
       </c>
-      <c r="Y70">
+      <c r="Y70" s="4">
         <v>8.6747382563503908E-4</v>
       </c>
       <c r="Z70" s="4"/>
@@ -9065,76 +9065,76 @@
       <c r="A71" s="1">
         <v>0.70833333333333304</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="4">
         <v>1.16421085114745E-2</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="4">
         <v>3.82657601848924E-3</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="4">
         <v>1.8691239156037098E-2</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="4">
         <v>6.1435132166862104E-3</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="4">
         <v>2.2747199195164501E-3</v>
       </c>
-      <c r="G71">
+      <c r="G71" s="4">
         <v>7.4766428127880005E-4</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="4">
         <v>7.9293979959919811E-3</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="4">
         <v>2.60626708491969E-3</v>
       </c>
-      <c r="J71">
+      <c r="J71" s="4">
         <v>3.52837707414829E-3</v>
       </c>
-      <c r="K71">
+      <c r="K71" s="4">
         <v>1.15972146135004E-3</v>
       </c>
-      <c r="L71">
+      <c r="L71" s="4">
         <v>1.2692209779559101E-2</v>
       </c>
-      <c r="M71">
+      <c r="M71" s="4">
         <v>4.1717276141367996E-3</v>
       </c>
-      <c r="N71">
+      <c r="N71" s="4">
         <v>1.7864024464929799E-2</v>
       </c>
-      <c r="O71">
+      <c r="O71" s="4">
         <v>5.8716208961487899E-3</v>
       </c>
-      <c r="P71">
+      <c r="P71" s="4">
         <v>1.05044216432865E-2</v>
       </c>
-      <c r="Q71">
+      <c r="Q71" s="4">
         <v>3.4526364282451301E-3</v>
       </c>
-      <c r="R71">
+      <c r="R71" s="4">
         <v>9.4536232258064497E-4</v>
       </c>
-      <c r="S71">
+      <c r="S71" s="4">
         <v>3.1072556906723098E-4</v>
       </c>
-      <c r="T71">
+      <c r="T71" s="4">
         <v>7.2431654669338598E-3</v>
       </c>
-      <c r="U71">
+      <c r="U71" s="4">
         <v>2.3807133601616002E-3</v>
       </c>
-      <c r="V71">
+      <c r="V71" s="4">
         <v>2.3085174193548299E-3</v>
       </c>
-      <c r="W71">
+      <c r="W71" s="4">
         <v>7.58772982270463E-4</v>
       </c>
-      <c r="X71">
+      <c r="X71" s="4">
         <v>2.6328730645161199E-3</v>
       </c>
-      <c r="Y71">
+      <c r="Y71" s="4">
         <v>8.65383527260015E-4</v>
       </c>
       <c r="Z71" s="4"/>
@@ -9189,76 +9189,76 @@
       <c r="A72" s="1">
         <v>0.71875</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="4">
         <v>1.1916202936647399E-2</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="4">
         <v>3.9166664993617196E-3</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="4">
         <v>1.9077439846002901E-2</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="4">
         <v>6.2704512448870696E-3</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="4">
         <v>2.3446771168950799E-3</v>
       </c>
-      <c r="G72">
+      <c r="G72" s="4">
         <v>7.7065810010001597E-4</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="4">
         <v>8.1114505010019995E-3</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="4">
         <v>2.66610484962448E-3</v>
       </c>
-      <c r="J72">
+      <c r="J72" s="4">
         <v>3.6093857314629199E-3</v>
       </c>
-      <c r="K72">
+      <c r="K72" s="4">
         <v>1.1863477193912401E-3</v>
       </c>
-      <c r="L72">
+      <c r="L72" s="4">
         <v>1.2983612555110199E-2</v>
       </c>
-      <c r="M72">
+      <c r="M72" s="4">
         <v>4.2675070746654503E-3</v>
       </c>
-      <c r="N72">
+      <c r="N72" s="4">
         <v>1.8274167883767501E-2</v>
       </c>
-      <c r="O72">
+      <c r="O72" s="4">
         <v>6.0064285187644501E-3</v>
       </c>
-      <c r="P72">
+      <c r="P72" s="4">
         <v>1.0745594589178301E-2</v>
       </c>
-      <c r="Q72">
+      <c r="Q72" s="4">
         <v>3.5319061421589201E-3</v>
       </c>
-      <c r="R72">
+      <c r="R72" s="4">
         <v>9.7847283870967699E-4</v>
       </c>
-      <c r="S72">
+      <c r="S72" s="4">
         <v>3.2160846943311199E-4</v>
       </c>
-      <c r="T72">
+      <c r="T72" s="4">
         <v>7.4094626332665307E-3</v>
       </c>
-      <c r="U72">
+      <c r="U72" s="4">
         <v>2.4353725954714299E-3</v>
       </c>
-      <c r="V72">
+      <c r="V72" s="4">
         <v>2.3893712903225802E-3</v>
       </c>
-      <c r="W72">
+      <c r="W72" s="4">
         <v>7.8534836449974295E-4</v>
       </c>
-      <c r="X72">
+      <c r="X72" s="4">
         <v>2.7250872177419301E-3</v>
       </c>
-      <c r="Y72">
+      <c r="Y72" s="4">
         <v>8.9569285369786502E-4</v>
       </c>
       <c r="Z72" s="4"/>
@@ -9313,76 +9313,76 @@
       <c r="A73" s="1">
         <v>0.72916666666666696</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="4">
         <v>1.2319333460533899E-2</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="4">
         <v>4.04916909487563E-3</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="4">
         <v>1.95358787778558E-2</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="4">
         <v>6.4211328349822704E-3</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="4">
         <v>2.5361678155504499E-3</v>
       </c>
-      <c r="G73">
+      <c r="G73" s="4">
         <v>8.3359804903763307E-4</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="4">
         <v>8.354187174348689E-3</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="4">
         <v>2.7458885358975301E-3</v>
       </c>
-      <c r="J73">
+      <c r="J73" s="4">
         <v>3.7173972745490899E-3</v>
       </c>
-      <c r="K73">
+      <c r="K73" s="4">
         <v>1.22184939677951E-3</v>
       </c>
-      <c r="L73">
+      <c r="L73" s="4">
         <v>1.33721495891783E-2</v>
       </c>
-      <c r="M73">
+      <c r="M73" s="4">
         <v>4.3952130220369897E-3</v>
       </c>
-      <c r="N73">
+      <c r="N73" s="4">
         <v>1.8821025775551101E-2</v>
       </c>
-      <c r="O73">
+      <c r="O73" s="4">
         <v>6.1861720155853301E-3</v>
       </c>
-      <c r="P73">
+      <c r="P73" s="4">
         <v>1.1067158517033999E-2</v>
       </c>
-      <c r="Q73">
+      <c r="Q73" s="4">
         <v>3.6375990940439701E-3</v>
       </c>
-      <c r="R73">
+      <c r="R73" s="4">
         <v>1.08579658064516E-3</v>
       </c>
-      <c r="S73">
+      <c r="S73" s="4">
         <v>3.5688407751562399E-4</v>
       </c>
-      <c r="T73">
+      <c r="T73" s="4">
         <v>7.6311921883767501E-3</v>
       </c>
-      <c r="U73">
+      <c r="U73" s="4">
         <v>2.5082515758845401E-3</v>
       </c>
-      <c r="V73">
+      <c r="V73" s="4">
         <v>2.6514493548386998E-3</v>
       </c>
-      <c r="W73">
+      <c r="W73" s="4">
         <v>8.7148925862223499E-4</v>
       </c>
-      <c r="X73">
+      <c r="X73" s="4">
         <v>3.0239882661290299E-3</v>
       </c>
-      <c r="Y73">
+      <c r="Y73" s="4">
         <v>9.9393687732400203E-4</v>
       </c>
       <c r="Z73" s="4"/>
@@ -9437,76 +9437,76 @@
       <c r="A74" s="1">
         <v>0.73958333333333304</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="4">
         <v>1.2856487491305101E-2</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="4">
         <v>4.2257230868228898E-3</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="4">
         <v>2.0009746320211699E-2</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="4">
         <v>6.5768855641148314E-3</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="4">
         <v>2.9099464659157002E-3</v>
       </c>
-      <c r="G74">
+      <c r="G74" s="4">
         <v>9.5645315026789699E-4</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="4">
         <v>8.6441226452905803E-3</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="4">
         <v>2.8411857167236799E-3</v>
       </c>
-      <c r="J74">
+      <c r="J74" s="4">
         <v>3.8464110621242399E-3</v>
       </c>
-      <c r="K74">
+      <c r="K74" s="4">
         <v>1.26425417810438E-3</v>
       </c>
-      <c r="L74">
+      <c r="L74" s="4">
         <v>1.38362354909819E-2</v>
       </c>
-      <c r="M74">
+      <c r="M74" s="4">
         <v>4.5477506813974304E-3</v>
       </c>
-      <c r="N74">
+      <c r="N74" s="4">
         <v>1.9474217146292501E-2</v>
       </c>
-      <c r="O74">
+      <c r="O74" s="4">
         <v>6.4008656367880506E-3</v>
       </c>
-      <c r="P74">
+      <c r="P74" s="4">
         <v>1.1451248764195E-2</v>
       </c>
-      <c r="Q74">
+      <c r="Q74" s="4">
         <v>3.76384345324001E-3</v>
       </c>
-      <c r="R74">
+      <c r="R74" s="4">
         <v>1.30729451612903E-3</v>
       </c>
-      <c r="S74">
+      <c r="S74" s="4">
         <v>4.29686928239106E-4</v>
       </c>
-      <c r="T74">
+      <c r="T74" s="4">
         <v>7.8960358236472902E-3</v>
       </c>
-      <c r="U74">
+      <c r="U74" s="4">
         <v>2.5953014691557498E-3</v>
       </c>
-      <c r="V74">
+      <c r="V74" s="4">
         <v>3.1923338709677401E-3</v>
       </c>
-      <c r="W74">
+      <c r="W74" s="4">
         <v>1.0492694018112E-3</v>
       </c>
-      <c r="X74">
+      <c r="X74" s="4">
         <v>3.6408691532257998E-3</v>
       </c>
-      <c r="Y74">
+      <c r="Y74" s="4">
         <v>1.19669581970134E-3</v>
       </c>
       <c r="Z74" s="4"/>
@@ -9561,76 +9561,76 @@
       <c r="A75" s="1">
         <v>0.75</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="4">
         <v>1.35371963192837E-2</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="4">
         <v>4.4494612588343706E-3</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="4">
         <v>2.0472064567167901E-2</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="4">
         <v>6.7288422234234894E-3</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="4">
         <v>3.4908625034746898E-3</v>
       </c>
-      <c r="G75">
+      <c r="G75" s="4">
         <v>1.14739101825702E-3</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="4">
         <v>8.9812569138276507E-3</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="4">
         <v>2.9519963921029201E-3</v>
       </c>
-      <c r="J75">
+      <c r="J75" s="4">
         <v>3.9964270941883701E-3</v>
       </c>
-      <c r="K75">
+      <c r="K75" s="4">
         <v>1.3135620633658699E-3</v>
       </c>
-      <c r="L75">
+      <c r="L75" s="4">
         <v>1.4375870260521E-2</v>
       </c>
-      <c r="M75">
+      <c r="M75" s="4">
         <v>4.7251200527467802E-3</v>
       </c>
-      <c r="N75">
+      <c r="N75" s="4">
         <v>2.02337419959919E-2</v>
       </c>
-      <c r="O75">
+      <c r="O75" s="4">
         <v>6.6505093823726099E-3</v>
       </c>
-      <c r="P75">
+      <c r="P75" s="4">
         <v>1.1897865330661299E-2</v>
       </c>
-      <c r="Q75">
+      <c r="Q75" s="4">
         <v>3.9106392197470301E-3</v>
       </c>
-      <c r="R75">
+      <c r="R75" s="4">
         <v>1.65895103225806E-3</v>
       </c>
-      <c r="S75">
+      <c r="S75" s="4">
         <v>5.45270835573293E-4</v>
       </c>
-      <c r="T75">
+      <c r="T75" s="4">
         <v>8.2039935390781499E-3</v>
       </c>
-      <c r="U75">
+      <c r="U75" s="4">
         <v>2.6965222752850702E-3</v>
       </c>
-      <c r="V75">
+      <c r="V75" s="4">
         <v>4.0510577419354803E-3</v>
       </c>
-      <c r="W75">
+      <c r="W75" s="4">
         <v>1.3315182889359701E-3</v>
       </c>
-      <c r="X75">
+      <c r="X75" s="4">
         <v>4.6202470564516099E-3</v>
       </c>
-      <c r="Y75">
+      <c r="Y75" s="4">
         <v>1.51860176945507E-3</v>
       </c>
       <c r="Z75" s="4"/>
@@ -9685,76 +9685,76 @@
       <c r="A76" s="1">
         <v>0.76041666666666696</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="4">
         <v>1.43178883315663E-2</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="4">
         <v>4.7060623143117698E-3</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="4">
         <v>2.0935814204730101E-2</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="4">
         <v>6.8812693580726503E-3</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="4">
         <v>4.1653185088725798E-3</v>
       </c>
-      <c r="G76">
+      <c r="G76" s="4">
         <v>1.36907398687374E-3</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="4">
         <v>9.3655899799599193E-3</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="4">
         <v>3.0783205620352502E-3</v>
       </c>
-      <c r="J76">
+      <c r="J76" s="4">
         <v>4.1674453707414797E-3</v>
       </c>
-      <c r="K76">
+      <c r="K76" s="4">
         <v>1.36977305256396E-3</v>
       </c>
-      <c r="L76">
+      <c r="L76" s="4">
         <v>1.49910538977955E-2</v>
       </c>
-      <c r="M76">
+      <c r="M76" s="4">
         <v>4.9273211360850496E-3</v>
       </c>
-      <c r="N76">
+      <c r="N76" s="4">
         <v>2.10996003246493E-2</v>
       </c>
-      <c r="O76">
+      <c r="O76" s="4">
         <v>6.9351032523390001E-3</v>
       </c>
-      <c r="P76">
+      <c r="P76" s="4">
         <v>1.2407008216432799E-2</v>
       </c>
-      <c r="Q76">
+      <c r="Q76" s="4">
         <v>4.07798639356503E-3</v>
       </c>
-      <c r="R76">
+      <c r="R76" s="4">
         <v>2.06769464516129E-3</v>
       </c>
-      <c r="S76">
+      <c r="S76" s="4">
         <v>6.7961836422796495E-4</v>
       </c>
-      <c r="T76">
+      <c r="T76" s="4">
         <v>8.5550653346693397E-3</v>
       </c>
-      <c r="U76">
+      <c r="U76" s="4">
         <v>2.8119139942724999E-3</v>
       </c>
-      <c r="V76">
+      <c r="V76" s="4">
         <v>5.0491848387096703E-3</v>
       </c>
-      <c r="W76">
+      <c r="W76" s="4">
         <v>1.65958680059397E-3</v>
       </c>
-      <c r="X76">
+      <c r="X76" s="4">
         <v>5.7586148790322502E-3</v>
       </c>
-      <c r="Y76">
+      <c r="Y76" s="4">
         <v>1.8927651785843999E-3</v>
       </c>
       <c r="Z76" s="4"/>
@@ -9809,76 +9809,76 @@
       <c r="A77" s="1">
         <v>0.77083333333333304</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="4">
         <v>1.5124577387937099E-2</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="4">
         <v>4.9712081849625899E-3</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="4">
         <v>2.1413479172496201E-2</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="4">
         <v>7.0382702405781504E-3</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="4">
         <v>4.7881736099618507E-3</v>
       </c>
-      <c r="G77">
+      <c r="G77" s="4">
         <v>1.5737965584313601E-3</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="4">
         <v>9.7836364729458909E-3</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="4">
         <v>3.2157257995055E-3</v>
       </c>
-      <c r="J77">
+      <c r="J77" s="4">
         <v>4.3534652505010001E-3</v>
       </c>
-      <c r="K77">
+      <c r="K77" s="4">
         <v>1.4309148302881899E-3</v>
       </c>
-      <c r="L77">
+      <c r="L77" s="4">
         <v>1.5660201012023998E-2</v>
       </c>
-      <c r="M77">
+      <c r="M77" s="4">
         <v>5.1472591565582503E-3</v>
       </c>
-      <c r="N77">
+      <c r="N77" s="4">
         <v>2.2041411138276502E-2</v>
       </c>
-      <c r="O77">
+      <c r="O77" s="4">
         <v>7.2446614968638499E-3</v>
       </c>
-      <c r="P77">
+      <c r="P77" s="4">
         <v>1.2960812758851E-2</v>
       </c>
-      <c r="Q77">
+      <c r="Q77" s="4">
         <v>4.2600131440337407E-3</v>
       </c>
-      <c r="R77">
+      <c r="R77" s="4">
         <v>2.4410442580645102E-3</v>
       </c>
-      <c r="S77">
+      <c r="S77" s="4">
         <v>8.0233244766393695E-4</v>
       </c>
-      <c r="T77">
+      <c r="T77" s="4">
         <v>8.9369329018035987E-3</v>
       </c>
-      <c r="U77">
+      <c r="U77" s="4">
         <v>2.9374277938728501E-3</v>
       </c>
-      <c r="V77">
+      <c r="V77" s="4">
         <v>5.9608819354838704E-3</v>
       </c>
-      <c r="W77">
+      <c r="W77" s="4">
         <v>1.9592471450413599E-3</v>
       </c>
-      <c r="X77">
+      <c r="X77" s="4">
         <v>6.7984089516129002E-3</v>
       </c>
-      <c r="Y77">
+      <c r="Y77" s="4">
         <v>2.2345289629008601E-3</v>
       </c>
       <c r="Z77" s="4"/>
@@ -9933,76 +9933,76 @@
       <c r="A78" s="1">
         <v>0.78125</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="4">
         <v>1.5870452907104499E-2</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="4">
         <v>5.2163656125549396E-3</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="4">
         <v>2.1902554937759701E-2</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="4">
         <v>7.1990216708484591E-3</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="4">
         <v>5.2047275670696197E-3</v>
       </c>
-      <c r="G78">
+      <c r="G78" s="4">
         <v>1.71071122308204E-3</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="4">
         <v>1.0215168336673301E-2</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="4">
         <v>3.3575634639909299E-3</v>
       </c>
-      <c r="J78">
+      <c r="J78" s="4">
         <v>4.5454857715430796E-3</v>
       </c>
-      <c r="K78">
+      <c r="K78" s="4">
         <v>1.4940289234228899E-3</v>
       </c>
-      <c r="L78">
+      <c r="L78" s="4">
         <v>1.6350933517034E-2</v>
       </c>
-      <c r="M78">
+      <c r="M78" s="4">
         <v>5.3742919518854201E-3</v>
       </c>
-      <c r="N78">
+      <c r="N78" s="4">
         <v>2.3013602945891699E-2</v>
       </c>
-      <c r="O78">
+      <c r="O78" s="4">
         <v>7.5642054912120902E-3</v>
       </c>
-      <c r="P78">
+      <c r="P78" s="4">
         <v>1.3532481963927799E-2</v>
       </c>
-      <c r="Q78">
+      <c r="Q78" s="4">
         <v>4.4479117251627299E-3</v>
       </c>
-      <c r="R78">
+      <c r="R78" s="4">
         <v>2.6808100645161299E-3</v>
       </c>
-      <c r="S78">
+      <c r="S78" s="4">
         <v>8.8113965720997402E-4</v>
       </c>
-      <c r="T78">
+      <c r="T78" s="4">
         <v>9.3311187775551099E-3</v>
       </c>
-      <c r="U78">
+      <c r="U78" s="4">
         <v>3.0669904257183802E-3</v>
       </c>
-      <c r="V78">
+      <c r="V78" s="4">
         <v>6.5463754838709599E-3</v>
       </c>
-      <c r="W78">
+      <c r="W78" s="4">
         <v>2.1516895680809699E-3</v>
       </c>
-      <c r="X78">
+      <c r="X78" s="4">
         <v>7.4661666129032201E-3</v>
       </c>
-      <c r="Y78">
+      <c r="Y78" s="4">
         <v>2.4540102922783998E-3</v>
       </c>
       <c r="Z78" s="4"/>
@@ -10057,76 +10057,76 @@
       <c r="A79" s="1">
         <v>0.79166666666666696</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="4">
         <v>1.64978681036912E-2</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="4">
         <v>5.4225870150206596E-3</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="4">
         <v>2.2402109096730901E-2</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="4">
         <v>7.3632171825782702E-3</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="4">
         <v>5.3124385403064099E-3</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="4">
         <v>1.74611410793832E-3</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="4">
         <v>1.06467002004008E-2</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="4">
         <v>3.4994011284763598E-3</v>
       </c>
-      <c r="J79">
+      <c r="J79" s="4">
         <v>4.7375062925851703E-3</v>
       </c>
-      <c r="K79">
+      <c r="K79" s="4">
         <v>1.5571430165575899E-3</v>
       </c>
-      <c r="L79">
+      <c r="L79" s="4">
         <v>1.7041666022043999E-2</v>
       </c>
-      <c r="M79">
+      <c r="M79" s="4">
         <v>5.6013247472125908E-3</v>
       </c>
-      <c r="N79">
+      <c r="N79" s="4">
         <v>2.3985794753507001E-2</v>
       </c>
-      <c r="O79">
+      <c r="O79" s="4">
         <v>7.88374948556032E-3</v>
       </c>
-      <c r="P79">
+      <c r="P79" s="4">
         <v>1.4104151169004601E-2</v>
       </c>
-      <c r="Q79">
+      <c r="Q79" s="4">
         <v>4.6358103062917114E-3</v>
       </c>
-      <c r="R79">
+      <c r="R79" s="4">
         <v>2.7219127741935399E-3</v>
       </c>
-      <c r="S79">
+      <c r="S79" s="4">
         <v>8.9464946456072308E-4</v>
       </c>
-      <c r="T79">
+      <c r="T79" s="4">
         <v>9.7253046533066108E-3</v>
       </c>
-      <c r="U79">
+      <c r="U79" s="4">
         <v>3.1965530575639098E-3</v>
       </c>
-      <c r="V79">
+      <c r="V79" s="4">
         <v>6.6467458064516094E-3</v>
       </c>
-      <c r="W79">
+      <c r="W79" s="4">
         <v>2.1846796977449002E-3</v>
       </c>
-      <c r="X79">
+      <c r="X79" s="4">
         <v>7.5806393548387098E-3</v>
       </c>
-      <c r="Y79">
+      <c r="Y79" s="4">
         <v>2.49163566302883E-3</v>
       </c>
       <c r="Z79" s="4"/>
@@ -10181,76 +10181,76 @@
       <c r="A80" s="1">
         <v>0.80208333333333304</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="4">
         <v>1.6980145127157498E-2</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="4">
         <v>5.58110380692701E-3</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="4">
         <v>2.2877593537178501E-2</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="4">
         <v>7.51950136041327E-3</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="4">
         <v>5.16113247430344E-3</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="4">
         <v>1.6963822090259901E-3</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="4">
         <v>1.10445186372745E-2</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="4">
         <v>3.63015772542386E-3</v>
       </c>
-      <c r="J80">
+      <c r="J80" s="4">
         <v>4.9145252104208399E-3</v>
       </c>
-      <c r="K80">
+      <c r="K80" s="4">
         <v>1.61532632116613E-3</v>
       </c>
-      <c r="L80">
+      <c r="L80" s="4">
         <v>1.7678435050100201E-2</v>
       </c>
-      <c r="M80">
+      <c r="M80" s="4">
         <v>5.8106206054048303E-3</v>
       </c>
-      <c r="N80">
+      <c r="N80" s="4">
         <v>2.4882034076152301E-2</v>
       </c>
-      <c r="O80">
+      <c r="O80" s="4">
         <v>8.1783291053501E-3</v>
       </c>
-      <c r="P80">
+      <c r="P80" s="4">
         <v>1.4631158717434801E-2</v>
       </c>
-      <c r="Q80">
+      <c r="Q80" s="4">
         <v>4.8090293107699994E-3</v>
       </c>
-      <c r="R80">
+      <c r="R80" s="4">
         <v>2.5986046451612899E-3</v>
       </c>
-      <c r="S80">
+      <c r="S80" s="4">
         <v>8.54120042508476E-4</v>
       </c>
-      <c r="T80">
+      <c r="T80" s="4">
         <v>1.0088694757515001E-2</v>
       </c>
-      <c r="U80">
+      <c r="U80" s="4">
         <v>3.3159936087965099E-3</v>
       </c>
-      <c r="V80">
+      <c r="V80" s="4">
         <v>6.3456348387096696E-3</v>
       </c>
-      <c r="W80">
+      <c r="W80" s="4">
         <v>2.0857093087531101E-3</v>
       </c>
-      <c r="X80">
+      <c r="X80" s="4">
         <v>7.2372211290322496E-3</v>
       </c>
-      <c r="Y80">
+      <c r="Y80" s="4">
         <v>2.3787595507775202E-3</v>
       </c>
       <c r="Z80" s="4"/>
@@ -10305,76 +10305,76 @@
       <c r="A81" s="1">
         <v>0.8125</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="4">
         <v>1.72719870723382E-2</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="4">
         <v>5.6770276155323797E-3</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="4">
         <v>2.32392204039958E-2</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="4">
         <v>7.6383623635417506E-3</v>
       </c>
-      <c r="F81">
+      <c r="F81" s="4">
         <v>4.8475959081065298E-3</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="4">
         <v>1.5933277233247101E-3</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="4">
         <v>1.1347939478957901E-2</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="4">
         <v>3.7298873332651701E-3</v>
       </c>
-      <c r="J81">
+      <c r="J81" s="4">
         <v>5.0495396392785507E-3</v>
       </c>
-      <c r="K81">
+      <c r="K81" s="4">
         <v>1.6597034179014699E-3</v>
       </c>
-      <c r="L81">
+      <c r="L81" s="4">
         <v>1.81641063426853E-2</v>
       </c>
-      <c r="M81">
+      <c r="M81" s="4">
         <v>5.9702530396192497E-3</v>
       </c>
-      <c r="N81">
+      <c r="N81" s="4">
         <v>2.55656064408817E-2</v>
       </c>
-      <c r="O81">
+      <c r="O81" s="4">
         <v>8.4030084763762006E-3</v>
       </c>
-      <c r="P81">
+      <c r="P81" s="4">
         <v>1.5033113627254501E-2</v>
       </c>
-      <c r="Q81">
+      <c r="Q81" s="4">
         <v>4.94114550062632E-3</v>
       </c>
-      <c r="R81">
+      <c r="R81" s="4">
         <v>2.3771067096774101E-3</v>
       </c>
-      <c r="S81">
+      <c r="S81" s="4">
         <v>7.8131719178499404E-4</v>
       </c>
-      <c r="T81">
+      <c r="T81" s="4">
         <v>1.03658567014028E-2</v>
       </c>
-      <c r="U81">
+      <c r="U81" s="4">
         <v>3.4070923343128999E-3</v>
       </c>
-      <c r="V81">
+      <c r="V81" s="4">
         <v>5.8047503225806402E-3</v>
       </c>
-      <c r="W81">
+      <c r="W81" s="4">
         <v>1.9079291655641299E-3</v>
       </c>
-      <c r="X81">
+      <c r="X81" s="4">
         <v>6.6203402419354801E-3</v>
       </c>
-      <c r="Y81">
+      <c r="Y81" s="4">
         <v>2.17600060840018E-3</v>
       </c>
       <c r="Z81" s="4"/>
@@ -10429,76 +10429,76 @@
       <c r="A82" s="1">
         <v>0.82291666666666696</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="4">
         <v>1.7336155829982498E-2</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="4">
         <v>5.6981188662191401E-3</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="4">
         <v>2.3414547387550898E-2</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="4">
         <v>7.6959895562452706E-3</v>
       </c>
-      <c r="F82">
+      <c r="F82" s="4">
         <v>4.4657500305449599E-3</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="4">
         <v>1.4678210527421501E-3</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="4">
         <v>1.1503021242484901E-2</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="4">
         <v>3.7808602439396198E-3</v>
       </c>
-      <c r="J82">
+      <c r="J82" s="4">
         <v>5.1185470140280506E-3</v>
       </c>
-      <c r="K82">
+      <c r="K82" s="4">
         <v>1.6823850451217501E-3</v>
       </c>
-      <c r="L82">
+      <c r="L82" s="4">
         <v>1.8412338336673301E-2</v>
       </c>
-      <c r="M82">
+      <c r="M82" s="4">
         <v>6.0518429504399498E-3</v>
       </c>
-      <c r="N82">
+      <c r="N82" s="4">
         <v>2.59149878717434E-2</v>
       </c>
-      <c r="O82">
+      <c r="O82" s="4">
         <v>8.5178445993450893E-3</v>
       </c>
-      <c r="P82">
+      <c r="P82" s="4">
         <v>1.52385572478289E-2</v>
       </c>
-      <c r="Q82">
+      <c r="Q82" s="4">
         <v>5.0086715532195502E-3</v>
       </c>
-      <c r="R82">
+      <c r="R82" s="4">
         <v>2.1213565161290302E-3</v>
       </c>
-      <c r="S82">
+      <c r="S82" s="4">
         <v>6.9725616826922098E-4</v>
       </c>
-      <c r="T82">
+      <c r="T82" s="4">
         <v>1.0507517250500999E-2</v>
       </c>
-      <c r="U82">
+      <c r="U82" s="4">
         <v>3.4536539051323902E-3</v>
       </c>
-      <c r="V82">
+      <c r="V82" s="4">
         <v>5.1802238709677401E-3</v>
       </c>
-      <c r="W82">
+      <c r="W82" s="4">
         <v>1.7026572476552099E-3</v>
       </c>
-      <c r="X82">
+      <c r="X82" s="4">
         <v>5.9080654032257996E-3</v>
       </c>
-      <c r="Y82">
+      <c r="Y82" s="4">
         <v>1.9418871903974699E-3</v>
       </c>
       <c r="Z82" s="4"/>
@@ -10553,76 +10553,76 @@
       <c r="A83" s="1">
         <v>0.83333333333333304</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="4">
         <v>1.7175026463960099E-2</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="4">
         <v>5.6451582047300402E-3</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="4">
         <v>2.3372170633446002E-2</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="4">
         <v>7.6820609907419096E-3</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="4">
         <v>4.0934143196877599E-3</v>
       </c>
-      <c r="G83">
+      <c r="G83" s="4">
         <v>1.34544022279291E-3</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="4">
         <v>1.14895358717434E-2</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="4">
         <v>3.7764278169244501E-3</v>
       </c>
-      <c r="J83">
+      <c r="J83" s="4">
         <v>5.1125463727454898E-3</v>
       </c>
-      <c r="K83">
+      <c r="K83" s="4">
         <v>1.6804127297112899E-3</v>
       </c>
-      <c r="L83">
+      <c r="L83" s="4">
         <v>1.8390752945891702E-2</v>
       </c>
-      <c r="M83">
+      <c r="M83" s="4">
         <v>6.0447481755859797E-3</v>
       </c>
-      <c r="N83">
+      <c r="N83" s="4">
         <v>2.5884606877755501E-2</v>
       </c>
-      <c r="O83">
+      <c r="O83" s="4">
         <v>8.50785884952171E-3</v>
       </c>
-      <c r="P83">
+      <c r="P83" s="4">
         <v>1.52206925851703E-2</v>
       </c>
-      <c r="Q83">
+      <c r="Q83" s="4">
         <v>5.0027997225592698E-3</v>
       </c>
-      <c r="R83">
+      <c r="R83" s="4">
         <v>1.8827324516129001E-3</v>
       </c>
-      <c r="S83">
+      <c r="S83" s="4">
         <v>6.1882423114959396E-4</v>
       </c>
-      <c r="T83">
+      <c r="T83" s="4">
         <v>1.04951989418837E-2</v>
       </c>
-      <c r="U83">
+      <c r="U83" s="4">
         <v>3.4496050728872098E-3</v>
       </c>
-      <c r="V83">
+      <c r="V83" s="4">
         <v>4.5975183870967697E-3</v>
       </c>
-      <c r="W83">
+      <c r="W83" s="4">
         <v>1.51113121710627E-3</v>
       </c>
-      <c r="X83">
+      <c r="X83" s="4">
         <v>5.2434875403225799E-3</v>
       </c>
-      <c r="Y83">
+      <c r="Y83" s="4">
         <v>1.7234510102074399E-3</v>
       </c>
       <c r="Z83" s="4"/>
@@ -10677,76 +10677,76 @@
       <c r="A84" s="1">
         <v>0.84375</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="4">
         <v>1.6851929491693E-2</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="4">
         <v>5.5389613655144202E-3</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="4">
         <v>2.31570577990023E-2</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="4">
         <v>7.6113568212403003E-3</v>
       </c>
-      <c r="F84">
+      <c r="F84" s="4">
         <v>3.75244578713879E-3</v>
       </c>
-      <c r="G84">
+      <c r="G84" s="4">
         <v>1.2333692857779E-3</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="4">
         <v>1.1347939478957901E-2</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="4">
         <v>3.7298873332651701E-3</v>
       </c>
-      <c r="J84">
+      <c r="J84" s="4">
         <v>5.0495396392785507E-3</v>
       </c>
-      <c r="K84">
+      <c r="K84" s="4">
         <v>1.6597034179014699E-3</v>
       </c>
-      <c r="L84">
+      <c r="L84" s="4">
         <v>1.81641063426853E-2</v>
       </c>
-      <c r="M84">
+      <c r="M84" s="4">
         <v>5.9702530396192497E-3</v>
       </c>
-      <c r="N84">
+      <c r="N84" s="4">
         <v>2.55656064408817E-2</v>
       </c>
-      <c r="O84">
+      <c r="O84" s="4">
         <v>8.4030084763762006E-3</v>
       </c>
-      <c r="P84">
+      <c r="P84" s="4">
         <v>1.5033113627254501E-2</v>
       </c>
-      <c r="Q84">
+      <c r="Q84" s="4">
         <v>4.94114550062632E-3</v>
       </c>
-      <c r="R84">
+      <c r="R84" s="4">
         <v>1.6726519354838701E-3</v>
       </c>
-      <c r="S84">
+      <c r="S84" s="4">
         <v>5.4977410469020903E-4</v>
       </c>
-      <c r="T84">
+      <c r="T84" s="4">
         <v>1.03658567014028E-2</v>
       </c>
-      <c r="U84">
+      <c r="U84" s="4">
         <v>3.4070923343128999E-3</v>
       </c>
-      <c r="V84">
+      <c r="V84" s="4">
         <v>4.0845145161290293E-3</v>
       </c>
-      <c r="W84">
+      <c r="W84" s="4">
         <v>1.34251499882394E-3</v>
       </c>
-      <c r="X84">
+      <c r="X84" s="4">
         <v>4.65840463709677E-3</v>
       </c>
-      <c r="Y84">
+      <c r="Y84" s="4">
         <v>1.5311435597052201E-3</v>
       </c>
       <c r="Z84" s="4"/>
@@ -10801,76 +10801,76 @@
       <c r="A85" s="1">
         <v>0.85416666666666696</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="4">
         <v>1.64603881949059E-2</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="4">
         <v>5.4102679647393803E-3</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="4">
         <v>2.28540785252405E-2</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="4">
         <v>7.5117723497561397E-3</v>
       </c>
-      <c r="F85">
+      <c r="F85" s="4">
         <v>3.4479151646034001E-3</v>
       </c>
-      <c r="G85">
+      <c r="G85" s="4">
         <v>1.1332749106102999E-3</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="4">
         <v>1.11456589178356E-2</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="4">
         <v>3.6634009280376301E-3</v>
       </c>
-      <c r="J85">
+      <c r="J85" s="4">
         <v>4.95953002004008E-3</v>
       </c>
-      <c r="K85">
+      <c r="K85" s="4">
         <v>1.6301186867445801E-3</v>
       </c>
-      <c r="L85">
+      <c r="L85" s="4">
         <v>1.7840325480961899E-2</v>
       </c>
-      <c r="M85">
+      <c r="M85" s="4">
         <v>5.8638314168096414E-3</v>
       </c>
-      <c r="N85">
+      <c r="N85" s="4">
         <v>2.5109891531062099E-2</v>
       </c>
-      <c r="O85">
+      <c r="O85" s="4">
         <v>8.2532222290254698E-3</v>
       </c>
-      <c r="P85">
+      <c r="P85" s="4">
         <v>1.47651436873747E-2</v>
       </c>
-      <c r="Q85">
+      <c r="Q85" s="4">
         <v>4.85306804072211E-3</v>
       </c>
-      <c r="R85">
+      <c r="R85" s="4">
         <v>1.48997322580645E-3</v>
       </c>
-      <c r="S85">
+      <c r="S85" s="4">
         <v>4.8973051646465703E-4</v>
       </c>
-      <c r="T85">
+      <c r="T85" s="4">
         <v>1.01810820721442E-2</v>
       </c>
-      <c r="U85">
+      <c r="U85" s="4">
         <v>3.3463598506353102E-3</v>
       </c>
-      <c r="V85">
+      <c r="V85" s="4">
         <v>3.6384241935483799E-3</v>
       </c>
-      <c r="W85">
+      <c r="W85" s="4">
         <v>1.1958922003175701E-3</v>
       </c>
-      <c r="X85">
+      <c r="X85" s="4">
         <v>4.1496368951612897E-3</v>
       </c>
-      <c r="Y85">
+      <c r="Y85" s="4">
         <v>1.3639196897032801E-3</v>
       </c>
       <c r="Z85" s="4"/>
@@ -10925,76 +10925,76 @@
       <c r="A86" s="1">
         <v>0.86458333333333304</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="4">
         <v>1.6084505446505901E-2</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="4">
         <v>5.2867212799293404E-3</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="4">
         <v>2.2535325834920201E-2</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="4">
         <v>7.4070034069648703E-3</v>
       </c>
-      <c r="F86">
+      <c r="F86" s="4">
         <v>3.1842086146486501E-3</v>
       </c>
-      <c r="G86">
+      <c r="G86" s="4">
         <v>1.04659875920861E-3</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="4">
         <v>1.09433783567134E-2</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="4">
         <v>3.59691452281009E-3</v>
       </c>
-      <c r="J86">
+      <c r="J86" s="4">
         <v>4.8695204008016007E-3</v>
       </c>
-      <c r="K86">
+      <c r="K86" s="4">
         <v>1.60053395558769E-3</v>
       </c>
-      <c r="L86">
+      <c r="L86" s="4">
         <v>1.7516544619238399E-2</v>
       </c>
-      <c r="M86">
+      <c r="M86" s="4">
         <v>5.75740979400002E-3</v>
       </c>
-      <c r="N86">
+      <c r="N86" s="4">
         <v>2.4654176621242401E-2</v>
       </c>
-      <c r="O86">
+      <c r="O86" s="4">
         <v>8.1034359816747302E-3</v>
       </c>
-      <c r="P86">
+      <c r="P86" s="4">
         <v>1.44971737474949E-2</v>
       </c>
-      <c r="Q86">
+      <c r="Q86" s="4">
         <v>4.7649905808178896E-3</v>
       </c>
-      <c r="R86">
+      <c r="R86" s="4">
         <v>1.33355458064516E-3</v>
       </c>
-      <c r="S86">
+      <c r="S86" s="4">
         <v>4.3831819404652899E-4</v>
       </c>
-      <c r="T86">
+      <c r="T86" s="4">
         <v>9.9963074428857709E-3</v>
       </c>
-      <c r="U86">
+      <c r="U86" s="4">
         <v>3.28562736695771E-3</v>
       </c>
-      <c r="V86">
+      <c r="V86" s="4">
         <v>3.2564593548386998E-3</v>
       </c>
-      <c r="W86">
+      <c r="W86" s="4">
         <v>1.0703464290964899E-3</v>
       </c>
-      <c r="X86">
+      <c r="X86" s="4">
         <v>3.7140045161290301E-3</v>
       </c>
-      <c r="Y86">
+      <c r="Y86" s="4">
         <v>1.2207342510141201E-3</v>
       </c>
       <c r="Z86" s="4"/>
@@ -11049,76 +11049,76 @@
       <c r="A87" s="1">
         <v>0.875</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="4">
         <v>1.5799644517034001E-2</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="4">
         <v>5.1930920202254696E-3</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="4">
         <v>2.2264249402372399E-2</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="4">
         <v>7.3179048922978199E-3</v>
       </c>
-      <c r="F87">
+      <c r="F87" s="4">
         <v>2.9668026903807601E-3</v>
       </c>
-      <c r="G87">
+      <c r="G87" s="4">
         <v>9.7514088753004402E-4</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="4">
         <v>1.07950392785571E-2</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="4">
         <v>3.5481578256432202E-3</v>
       </c>
-      <c r="J87">
+      <c r="J87" s="4">
         <v>4.8035133466933803E-3</v>
       </c>
-      <c r="K87">
+      <c r="K87" s="4">
         <v>1.57883848607264E-3</v>
       </c>
-      <c r="L87">
+      <c r="L87" s="4">
         <v>1.7279105320641201E-2</v>
       </c>
-      <c r="M87">
+      <c r="M87" s="4">
         <v>5.6793672706063102E-3</v>
       </c>
-      <c r="N87">
+      <c r="N87" s="4">
         <v>2.4319985687374701E-2</v>
       </c>
-      <c r="O87">
+      <c r="O87" s="4">
         <v>7.9935927336175199E-3</v>
       </c>
-      <c r="P87">
+      <c r="P87" s="4">
         <v>1.43006624582498E-2</v>
       </c>
-      <c r="Q87">
+      <c r="Q87" s="4">
         <v>4.7004004435548001E-3</v>
       </c>
-      <c r="R87">
+      <c r="R87" s="4">
         <v>1.203396E-3</v>
       </c>
-      <c r="S87">
+      <c r="S87" s="4">
         <v>3.9553713743582298E-4</v>
       </c>
-      <c r="T87">
+      <c r="T87" s="4">
         <v>9.86080604809619E-3</v>
       </c>
-      <c r="U87">
+      <c r="U87" s="4">
         <v>3.2410902122608099E-3</v>
       </c>
-      <c r="V87">
+      <c r="V87" s="4">
         <v>2.9386199999999999E-3</v>
       </c>
-      <c r="W87">
+      <c r="W87" s="4">
         <v>9.6587768516071004E-4</v>
       </c>
-      <c r="X87">
+      <c r="X87" s="4">
         <v>3.3515074999999998E-3</v>
       </c>
-      <c r="Y87">
+      <c r="Y87" s="4">
         <v>1.10158724363774E-3</v>
       </c>
       <c r="Z87" s="4"/>
@@ -11173,76 +11173,76 @@
       <c r="A88" s="1">
         <v>0.88541666666666696</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="4">
         <v>1.55761825671342E-2</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="4">
         <v>5.11964362918113E-3</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="4">
         <v>2.1997660007345599E-2</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="4">
         <v>7.2302811955432603E-3</v>
       </c>
-      <c r="F88">
+      <c r="F88" s="4">
         <v>2.7900937650300601E-3</v>
       </c>
-      <c r="G88">
+      <c r="G88" s="4">
         <v>9.1705947252403001E-4</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="4">
         <v>1.06804136272545E-2</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="4">
         <v>3.51048219601428E-3</v>
       </c>
-      <c r="J88">
+      <c r="J88" s="4">
         <v>4.7525078957915802E-3</v>
       </c>
-      <c r="K88">
+      <c r="K88" s="4">
         <v>1.5620738050837299E-3</v>
       </c>
-      <c r="L88">
+      <c r="L88" s="4">
         <v>1.70956294989979E-2</v>
       </c>
-      <c r="M88">
+      <c r="M88" s="4">
         <v>5.6190616843475299E-3</v>
       </c>
-      <c r="N88">
+      <c r="N88" s="4">
         <v>2.4061747238476899E-2</v>
       </c>
-      <c r="O88">
+      <c r="O88" s="4">
         <v>7.9087138601187795E-3</v>
       </c>
-      <c r="P88">
+      <c r="P88" s="4">
         <v>1.4148812825651299E-2</v>
       </c>
-      <c r="Q88">
+      <c r="Q88" s="4">
         <v>4.6504898829424204E-3</v>
       </c>
-      <c r="R88">
+      <c r="R88" s="4">
         <v>1.097214E-3</v>
       </c>
-      <c r="S88">
+      <c r="S88" s="4">
         <v>3.6063680177972102E-4</v>
       </c>
-      <c r="T88">
+      <c r="T88" s="4">
         <v>9.7561004248497007E-3</v>
       </c>
-      <c r="U88">
+      <c r="U88" s="4">
         <v>3.2066751381768501E-3</v>
       </c>
-      <c r="V88">
+      <c r="V88" s="4">
         <v>2.6793299999999902E-3</v>
       </c>
-      <c r="W88">
+      <c r="W88" s="4">
         <v>8.8065318352888297E-4</v>
       </c>
-      <c r="X88">
+      <c r="X88" s="4">
         <v>3.0557862499999999E-3</v>
       </c>
-      <c r="Y88">
+      <c r="Y88" s="4">
         <v>1.00438836919912E-3</v>
       </c>
       <c r="Z88" s="4"/>
@@ -11297,76 +11297,76 @@
       <c r="A89" s="1">
         <v>0.89583333333333304</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="4">
         <v>1.5375076348632701E-2</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="4">
         <v>5.0535432117070492E-3</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="4">
         <v>2.16903606432895E-2</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="4">
         <v>7.1292767790464614E-3</v>
       </c>
-      <c r="F89">
+      <c r="F89" s="4">
         <v>2.6477936426886001E-3</v>
       </c>
-      <c r="G89">
+      <c r="G89" s="4">
         <v>8.7028768414538506E-4</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="4">
         <v>1.0572530661322599E-2</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="4">
         <v>3.4750227798929201E-3</v>
       </c>
-      <c r="J89">
+      <c r="J89" s="4">
         <v>4.7045027655310597E-3</v>
       </c>
-      <c r="K89">
+      <c r="K89" s="4">
         <v>1.5462952818000599E-3</v>
       </c>
-      <c r="L89">
+      <c r="L89" s="4">
         <v>1.6922946372745402E-2</v>
       </c>
-      <c r="M89">
+      <c r="M89" s="4">
         <v>5.5623034855157398E-3</v>
       </c>
-      <c r="N89">
+      <c r="N89" s="4">
         <v>2.3818699286573101E-2</v>
       </c>
-      <c r="O89">
+      <c r="O89" s="4">
         <v>7.828827861531721E-3</v>
       </c>
-      <c r="P89">
+      <c r="P89" s="4">
         <v>1.4005895524382099E-2</v>
       </c>
-      <c r="Q89">
+      <c r="Q89" s="4">
         <v>4.6035152376601692E-3</v>
       </c>
-      <c r="R89">
+      <c r="R89" s="4">
         <v>1.0127250967741899E-3</v>
       </c>
-      <c r="S89">
+      <c r="S89" s="4">
         <v>3.3286664222540298E-4</v>
       </c>
-      <c r="T89">
+      <c r="T89" s="4">
         <v>9.6575539559118212E-3</v>
       </c>
-      <c r="U89">
+      <c r="U89" s="4">
         <v>3.1742844802154602E-3</v>
       </c>
-      <c r="V89">
+      <c r="V89" s="4">
         <v>2.47301322580645E-3</v>
       </c>
-      <c r="W89">
+      <c r="W89" s="4">
         <v>8.12840139219687E-4</v>
       </c>
-      <c r="X89">
+      <c r="X89" s="4">
         <v>2.8204811693548302E-3</v>
       </c>
-      <c r="Y89">
+      <c r="Y89" s="4">
         <v>9.2704732932322794E-4</v>
       </c>
       <c r="Z89" s="4"/>
@@ -11421,76 +11421,76 @@
       <c r="A90" s="1">
         <v>0.90625</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="4">
         <v>1.51478622045381E-2</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="4">
         <v>4.9788615340713299E-3</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="4">
         <v>2.12824562696044E-2</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="4">
         <v>6.9952050949832296E-3</v>
       </c>
-      <c r="F90">
+      <c r="F90" s="4">
         <v>2.53292955831016E-3</v>
       </c>
-      <c r="G90">
+      <c r="G90" s="4">
         <v>8.3253368535426996E-4</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="4">
         <v>1.04376769539078E-2</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="4">
         <v>3.4306985097412299E-3</v>
       </c>
-      <c r="J90">
+      <c r="J90" s="4">
         <v>4.6444963527054097E-3</v>
       </c>
-      <c r="K90">
+      <c r="K90" s="4">
         <v>1.52657212769547E-3</v>
       </c>
-      <c r="L90">
+      <c r="L90" s="4">
         <v>1.6707092464929799E-2</v>
       </c>
-      <c r="M90">
+      <c r="M90" s="4">
         <v>5.4913557369759896E-3</v>
       </c>
-      <c r="N90">
+      <c r="N90" s="4">
         <v>2.35148893466933E-2</v>
       </c>
-      <c r="O90">
+      <c r="O90" s="4">
         <v>7.72897036329789E-3</v>
       </c>
-      <c r="P90">
+      <c r="P90" s="4">
         <v>1.38272488977955E-2</v>
       </c>
-      <c r="Q90">
+      <c r="Q90" s="4">
         <v>4.5447969310573599E-3</v>
       </c>
-      <c r="R90">
+      <c r="R90" s="4">
         <v>9.4764580645161295E-4</v>
       </c>
-      <c r="S90">
+      <c r="S90" s="4">
         <v>3.1147611392005003E-4</v>
       </c>
-      <c r="T90">
+      <c r="T90" s="4">
         <v>9.5343708697394787E-3</v>
       </c>
-      <c r="U90">
+      <c r="U90" s="4">
         <v>3.1337961577637399E-3</v>
       </c>
-      <c r="V90">
+      <c r="V90" s="4">
         <v>2.3140935483870898E-3</v>
       </c>
-      <c r="W90">
+      <c r="W90" s="4">
         <v>7.6060576725179294E-4</v>
       </c>
-      <c r="X90">
+      <c r="X90" s="4">
         <v>2.6392326612903198E-3</v>
       </c>
-      <c r="Y90">
+      <c r="Y90" s="4">
         <v>8.6747382563503908E-4</v>
       </c>
       <c r="Z90" s="4"/>
@@ -11545,76 +11545,76 @@
       <c r="A91" s="1">
         <v>0.91666666666666696</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="4">
         <v>1.4844714864955699E-2</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="4">
         <v>4.87922182202333E-3</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="4">
         <v>2.0721123065202799E-2</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="4">
         <v>6.8107037929872804E-3</v>
       </c>
-      <c r="F91">
+      <c r="F91" s="4">
         <v>2.4349788274936899E-3</v>
       </c>
-      <c r="G91">
+      <c r="G91" s="4">
         <v>8.0033883704424299E-4</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="4">
         <v>1.02421390781563E-2</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="4">
         <v>3.3664283180212702E-3</v>
       </c>
-      <c r="J91">
+      <c r="J91" s="4">
         <v>4.5574870541082108E-3</v>
       </c>
-      <c r="K91">
+      <c r="K91" s="4">
         <v>1.49797355424381E-3</v>
       </c>
-      <c r="L91">
+      <c r="L91" s="4">
         <v>1.6394104298597102E-2</v>
       </c>
-      <c r="M91">
+      <c r="M91" s="4">
         <v>5.3884815015933698E-3</v>
       </c>
-      <c r="N91">
+      <c r="N91" s="4">
         <v>2.3074364933867698E-2</v>
       </c>
-      <c r="O91">
+      <c r="O91" s="4">
         <v>7.5841769908588496E-3</v>
       </c>
-      <c r="P91">
+      <c r="P91" s="4">
         <v>1.35682112892451E-2</v>
       </c>
-      <c r="Q91">
+      <c r="Q91" s="4">
         <v>4.4596553864832914E-3</v>
       </c>
-      <c r="R91">
+      <c r="R91" s="4">
         <v>8.9740916129032197E-4</v>
       </c>
-      <c r="S91">
+      <c r="S91" s="4">
         <v>2.9496412715802298E-4</v>
       </c>
-      <c r="T91">
+      <c r="T91" s="4">
         <v>9.3557553947895694E-3</v>
       </c>
-      <c r="U91">
+      <c r="U91" s="4">
         <v>3.0750880902087299E-3</v>
       </c>
-      <c r="V91">
+      <c r="V91" s="4">
         <v>2.1914187096774098E-3</v>
       </c>
-      <c r="W91">
+      <c r="W91" s="4">
         <v>7.2028449766254102E-4</v>
       </c>
-      <c r="X91">
+      <c r="X91" s="4">
         <v>2.4993215322580602E-3</v>
       </c>
-      <c r="Y91">
+      <c r="Y91" s="4">
         <v>8.2148726138450603E-4</v>
       </c>
       <c r="Z91" s="4"/>
@@ -11669,76 +11669,76 @@
       <c r="A92" s="1">
         <v>0.92708333333333304</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="4">
         <v>1.4445431899347E-2</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="4">
         <v>4.7479838577590998E-3</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="4">
         <v>2.0004378525270001E-2</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="4">
         <v>6.5751212552376303E-3</v>
       </c>
-      <c r="F92">
+      <c r="F92" s="4">
         <v>2.3490223926077901E-3</v>
       </c>
-      <c r="G92">
+      <c r="G92" s="4">
         <v>7.72086323159405E-4</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="4">
         <v>9.9724316633266509E-3</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="4">
         <v>3.2777797777178799E-3</v>
       </c>
-      <c r="J92">
+      <c r="J92" s="4">
         <v>4.4374742284569099E-3</v>
       </c>
-      <c r="K92">
+      <c r="K92" s="4">
         <v>1.45852724603462E-3</v>
       </c>
-      <c r="L92">
+      <c r="L92" s="4">
         <v>1.59623964829659E-2</v>
       </c>
-      <c r="M92">
+      <c r="M92" s="4">
         <v>5.2465860045138799E-3</v>
       </c>
-      <c r="N92">
+      <c r="N92" s="4">
         <v>2.24667450541082E-2</v>
       </c>
-      <c r="O92">
+      <c r="O92" s="4">
         <v>7.3844619943912006E-3</v>
       </c>
-      <c r="P92">
+      <c r="P92" s="4">
         <v>1.32109180360721E-2</v>
       </c>
-      <c r="Q92">
+      <c r="Q92" s="4">
         <v>4.3422187732776703E-3</v>
       </c>
-      <c r="R92">
+      <c r="R92" s="4">
         <v>8.5973167741935496E-4</v>
       </c>
-      <c r="S92">
+      <c r="S92" s="4">
         <v>2.8258013708650301E-4</v>
       </c>
-      <c r="T92">
+      <c r="T92" s="4">
         <v>9.1093892224448896E-3</v>
       </c>
-      <c r="U92">
+      <c r="U92" s="4">
         <v>2.9941114453052699E-3</v>
       </c>
-      <c r="V92">
+      <c r="V92" s="4">
         <v>2.0994125806451601E-3</v>
       </c>
-      <c r="W92">
+      <c r="W92" s="4">
         <v>6.9004354547060195E-4</v>
       </c>
-      <c r="X92">
+      <c r="X92" s="4">
         <v>2.3943881854838699E-3</v>
       </c>
-      <c r="Y92">
+      <c r="Y92" s="4">
         <v>7.8699733819660798E-4</v>
       </c>
       <c r="Z92" s="4"/>
@@ -11793,76 +11793,76 @@
       <c r="A93" s="1">
         <v>0.9375</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="4">
         <v>1.3918348049001199E-2</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="4">
         <v>4.5747397740539403E-3</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="4">
         <v>1.91318964040097E-2</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="4">
         <v>6.28835024992664E-3</v>
       </c>
-      <c r="F93">
+      <c r="F93" s="4">
         <v>2.2641317478505401E-3</v>
       </c>
-      <c r="G93">
+      <c r="G93" s="4">
         <v>7.4418411754930997E-4</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="4">
         <v>9.6083266533066106E-3</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="4">
         <v>3.1581042483082998E-3</v>
       </c>
-      <c r="J93">
+      <c r="J93" s="4">
         <v>4.2754569138276502E-3</v>
       </c>
-      <c r="K93">
+      <c r="K93" s="4">
         <v>1.40527472995222E-3</v>
       </c>
-      <c r="L93">
+      <c r="L93" s="4">
         <v>1.5379590931863699E-2</v>
       </c>
-      <c r="M93">
+      <c r="M93" s="4">
         <v>5.0550270834565803E-3</v>
       </c>
-      <c r="N93">
+      <c r="N93" s="4">
         <v>2.1646458216432799E-2</v>
       </c>
-      <c r="O93">
+      <c r="O93" s="4">
         <v>7.1148467491598802E-3</v>
       </c>
-      <c r="P93">
+      <c r="P93" s="4">
         <v>1.27285721442885E-2</v>
       </c>
-      <c r="Q93">
+      <c r="Q93" s="4">
         <v>4.1836793454500896E-3</v>
       </c>
-      <c r="R93">
+      <c r="R93" s="4">
         <v>8.2890464516129005E-4</v>
       </c>
-      <c r="S93">
+      <c r="S93" s="4">
         <v>2.7244778157344099E-4</v>
       </c>
-      <c r="T93">
+      <c r="T93" s="4">
         <v>8.7767948897795583E-3</v>
       </c>
-      <c r="U93">
+      <c r="U93" s="4">
         <v>2.8847929746856102E-3</v>
       </c>
-      <c r="V93">
+      <c r="V93" s="4">
         <v>2.0241348387096702E-3</v>
       </c>
-      <c r="W93">
+      <c r="W93" s="4">
         <v>6.6530094822265194E-4</v>
       </c>
-      <c r="X93">
+      <c r="X93" s="4">
         <v>2.3085336290322501E-3</v>
       </c>
-      <c r="Y93">
+      <c r="Y93" s="4">
         <v>7.5877831013378106E-4</v>
       </c>
       <c r="Z93" s="4"/>
@@ -11917,76 +11917,76 @@
       <c r="A94" s="1">
         <v>0.94791666666666696</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="4">
         <v>1.32607400881117E-2</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="4">
         <v>4.3585944898704692E-3</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="4">
         <v>1.8127683090511298E-2</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="4">
         <v>5.95828129557072E-3</v>
       </c>
-      <c r="F94">
+      <c r="F94" s="4">
         <v>2.1732070545122501E-3</v>
       </c>
-      <c r="G94">
+      <c r="G94" s="4">
         <v>7.1429861608075091E-4</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="4">
         <v>9.1498240480961911E-3</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="4">
         <v>3.00740172979254E-3</v>
       </c>
-      <c r="J94">
+      <c r="J94" s="4">
         <v>4.0714351102204404E-3</v>
       </c>
-      <c r="K94">
+      <c r="K94" s="4">
         <v>1.33821600599661E-3</v>
       </c>
-      <c r="L94">
+      <c r="L94" s="4">
         <v>1.4645687645290501E-2</v>
       </c>
-      <c r="M94">
+      <c r="M94" s="4">
         <v>4.8138047384214599E-3</v>
       </c>
-      <c r="N94">
+      <c r="N94" s="4">
         <v>2.0613504420841599E-2</v>
       </c>
-      <c r="O94">
+      <c r="O94" s="4">
         <v>6.7753312551648804E-3</v>
       </c>
-      <c r="P94">
+      <c r="P94" s="4">
         <v>1.21211736138944E-2</v>
       </c>
-      <c r="Q94">
+      <c r="Q94" s="4">
         <v>3.9840371030005397E-3</v>
       </c>
-      <c r="R94">
+      <c r="R94" s="4">
         <v>8.0036109677419302E-4</v>
       </c>
-      <c r="S94">
+      <c r="S94" s="4">
         <v>2.63065970913199E-4</v>
       </c>
-      <c r="T94">
+      <c r="T94" s="4">
         <v>8.3579723967935789E-3</v>
       </c>
-      <c r="U94">
+      <c r="U94" s="4">
         <v>2.7471326783497299E-3</v>
       </c>
-      <c r="V94">
+      <c r="V94" s="4">
         <v>1.9544332258064501E-3</v>
       </c>
-      <c r="W94">
+      <c r="W94" s="4">
         <v>6.4239113595603199E-4</v>
       </c>
-      <c r="X94">
+      <c r="X94" s="4">
         <v>2.2290386693548298E-3</v>
       </c>
-      <c r="Y94">
+      <c r="Y94" s="4">
         <v>7.3264958044597811E-4</v>
       </c>
       <c r="Z94" s="4"/>
@@ -12041,76 +12041,76 @@
       <c r="A95" s="1">
         <v>0.95833333333333304</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="4">
         <v>1.2441623564419101E-2</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="4">
         <v>4.0893639082433698E-3</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="4">
         <v>1.69794817539974E-2</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="4">
         <v>5.5808857667134799E-3</v>
       </c>
-      <c r="F95">
+      <c r="F95" s="4">
         <v>2.0670947664684202E-3</v>
       </c>
-      <c r="G95">
+      <c r="G95" s="4">
         <v>6.7942119363658304E-4</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="4">
         <v>8.5766957915831606E-3</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="4">
         <v>2.8190235816478301E-3</v>
       </c>
-      <c r="J95">
+      <c r="J95" s="4">
         <v>3.8164078557114201E-3</v>
       </c>
-      <c r="K95">
+      <c r="K95" s="4">
         <v>1.2543926010520901E-3</v>
       </c>
-      <c r="L95">
+      <c r="L95" s="4">
         <v>1.37283085370741E-2</v>
       </c>
-      <c r="M95">
+      <c r="M95" s="4">
         <v>4.5122768071275601E-3</v>
       </c>
-      <c r="N95">
+      <c r="N95" s="4">
         <v>1.9322312176352701E-2</v>
       </c>
-      <c r="O95">
+      <c r="O95" s="4">
         <v>6.3509368876711403E-3</v>
       </c>
-      <c r="P95">
+      <c r="P95" s="4">
         <v>1.13619254509018E-2</v>
       </c>
-      <c r="Q95">
+      <c r="Q95" s="4">
         <v>3.7344842999386101E-3</v>
       </c>
-      <c r="R95">
+      <c r="R95" s="4">
         <v>7.6953406451612909E-4</v>
       </c>
-      <c r="S95">
+      <c r="S95" s="4">
         <v>2.5293361540013699E-4</v>
       </c>
-      <c r="T95">
+      <c r="T95" s="4">
         <v>7.8344442805611189E-3</v>
       </c>
-      <c r="U95">
+      <c r="U95" s="4">
         <v>2.5750573079298899E-3</v>
       </c>
-      <c r="V95">
+      <c r="V95" s="4">
         <v>1.87915548387096E-3</v>
       </c>
-      <c r="W95">
+      <c r="W95" s="4">
         <v>6.1764853870808199E-4</v>
       </c>
-      <c r="X95">
+      <c r="X95" s="4">
         <v>2.14318411290322E-3</v>
       </c>
-      <c r="Y95">
+      <c r="Y95" s="4">
         <v>7.0443055238315194E-4</v>
       </c>
       <c r="Z95" s="4"/>
@@ -12165,76 +12165,76 @@
       <c r="A96" s="1">
         <v>0.96875</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="4">
         <v>1.1508781328463299E-2</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="4">
         <v>3.7827534926451901E-3</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="4">
         <v>1.5741892412217001E-2</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="4">
         <v>5.1741098213314886E-3</v>
       </c>
-      <c r="F96">
+      <c r="F96" s="4">
         <v>1.9509926890878501E-3</v>
       </c>
-      <c r="G96">
+      <c r="G96" s="4">
         <v>6.4126028622334401E-4</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="4">
         <v>7.9226553106212395E-3</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="4">
         <v>2.6040508714121101E-3</v>
       </c>
-      <c r="J96">
+      <c r="J96" s="4">
         <v>3.52537675350701E-3</v>
       </c>
-      <c r="K96">
+      <c r="K96" s="4">
         <v>1.15873530364481E-3</v>
       </c>
-      <c r="L96">
+      <c r="L96" s="4">
         <v>1.2681417084168299E-2</v>
       </c>
-      <c r="M96">
+      <c r="M96" s="4">
         <v>4.1681802267098094E-3</v>
       </c>
-      <c r="N96">
+      <c r="N96" s="4">
         <v>1.7848833967935799E-2</v>
       </c>
-      <c r="O96">
+      <c r="O96" s="4">
         <v>5.8666280212370898E-3</v>
       </c>
-      <c r="P96">
+      <c r="P96" s="4">
         <v>1.04954893119572E-2</v>
       </c>
-      <c r="Q96">
+      <c r="Q96" s="4">
         <v>3.44970051291499E-3</v>
       </c>
-      <c r="R96">
+      <c r="R96" s="4">
         <v>7.3756529032258003E-4</v>
       </c>
-      <c r="S96">
+      <c r="S96" s="4">
         <v>2.4242598746066499E-4</v>
       </c>
-      <c r="T96">
+      <c r="T96" s="4">
         <v>7.2370063126252502E-3</v>
       </c>
-      <c r="U96">
+      <c r="U96" s="4">
         <v>2.3786889440390101E-3</v>
       </c>
-      <c r="V96">
+      <c r="V96" s="4">
         <v>1.8010896774193501E-3</v>
       </c>
-      <c r="W96">
+      <c r="W96" s="4">
         <v>5.9198954896946701E-4</v>
       </c>
-      <c r="X96">
+      <c r="X96" s="4">
         <v>2.0541497580645099E-3</v>
       </c>
-      <c r="Y96">
+      <c r="Y96" s="4">
         <v>6.7516637513281299E-4</v>
       </c>
       <c r="Z96" s="4"/>
@@ -12289,76 +12289,76 @@
       <c r="A97" s="1">
         <v>0.97916666666666696</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="4">
         <v>1.05106770372357E-2</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="4">
         <v>3.4546924768078602E-3</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="4">
         <v>1.44530155707239E-2</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="4">
         <v>4.75047648999958E-3</v>
       </c>
-      <c r="F97">
+      <c r="F97" s="4">
         <v>1.8318735874167599E-3</v>
       </c>
-      <c r="G97">
+      <c r="G97" s="4">
         <v>6.02107730880874E-4</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="4">
         <v>7.2214160320641201E-3</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="4">
         <v>2.3735646666232899E-3</v>
       </c>
-      <c r="J97">
+      <c r="J97" s="4">
         <v>3.2133434068136201E-3</v>
       </c>
-      <c r="K97">
+      <c r="K97" s="4">
         <v>1.0561749023009299E-3</v>
       </c>
-      <c r="L97">
+      <c r="L97" s="4">
         <v>1.1558976763527001E-2</v>
       </c>
-      <c r="M97">
+      <c r="M97" s="4">
         <v>3.79925193430316E-3</v>
       </c>
-      <c r="N97">
+      <c r="N97" s="4">
         <v>1.62690222805611E-2</v>
       </c>
-      <c r="O97">
+      <c r="O97" s="4">
         <v>5.3473690304212196E-3</v>
       </c>
-      <c r="P97">
+      <c r="P97" s="4">
         <v>9.5665268537074109E-3</v>
       </c>
-      <c r="Q97">
+      <c r="Q97" s="4">
         <v>3.1443653185803801E-3</v>
       </c>
-      <c r="R97">
+      <c r="R97" s="4">
         <v>7.0673825806451599E-4</v>
       </c>
-      <c r="S97">
+      <c r="S97" s="4">
         <v>2.3229363194760401E-4</v>
       </c>
-      <c r="T97">
+      <c r="T97" s="4">
         <v>6.5964542645290504E-3</v>
       </c>
-      <c r="U97">
+      <c r="U97" s="4">
         <v>2.16814966729002E-3</v>
       </c>
-      <c r="V97">
+      <c r="V97" s="4">
         <v>1.7258119354838699E-3</v>
       </c>
-      <c r="W97">
+      <c r="W97" s="4">
         <v>5.6724695172151798E-4</v>
       </c>
-      <c r="X97">
+      <c r="X97" s="4">
         <v>1.9682952016129001E-3</v>
       </c>
-      <c r="Y97">
+      <c r="Y97" s="4">
         <v>6.4694734706998705E-4</v>
       </c>
       <c r="Z97" s="4"/>
@@ -12413,76 +12413,76 @@
       <c r="A98" s="1">
         <v>0.98958333333333304</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="4">
         <v>9.4964551541793195E-3</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="4">
         <v>3.1213338647226299E-3</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="4">
         <v>1.3158022954584301E-2</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="4">
         <v>4.3248330007504797E-3</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="4">
         <v>1.7184851861788001E-3</v>
       </c>
-      <c r="G98">
+      <c r="G98" s="4">
         <v>5.6483876568231292E-4</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="4">
         <v>6.5066913827655304E-3</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="4">
         <v>2.1386460348192999E-3</v>
       </c>
-      <c r="J98">
+      <c r="J98" s="4">
         <v>2.8953094188376698E-3</v>
       </c>
-      <c r="K98">
+      <c r="K98" s="4">
         <v>9.5164218554659495E-4</v>
       </c>
-      <c r="L98">
+      <c r="L98" s="4">
         <v>1.04149510521042E-2</v>
       </c>
-      <c r="M98">
+      <c r="M98" s="4">
         <v>3.4232288670425302E-3</v>
       </c>
-      <c r="N98">
+      <c r="N98" s="4">
         <v>1.46588295991983E-2</v>
       </c>
-      <c r="O98">
+      <c r="O98" s="4">
         <v>4.8181242897819493E-3</v>
       </c>
-      <c r="P98">
+      <c r="P98" s="4">
         <v>8.6196997327989289E-3</v>
       </c>
-      <c r="Q98">
+      <c r="Q98" s="4">
         <v>2.8331582935855002E-3</v>
       </c>
-      <c r="R98">
+      <c r="R98" s="4">
         <v>6.8047819354838705E-4</v>
       </c>
-      <c r="S98">
+      <c r="S98" s="4">
         <v>2.2366236614018001E-4</v>
       </c>
-      <c r="T98">
+      <c r="T98" s="4">
         <v>5.9435839078156296E-3</v>
       </c>
-      <c r="U98">
+      <c r="U98" s="4">
         <v>1.95356155829587E-3</v>
       </c>
-      <c r="V98">
+      <c r="V98" s="4">
         <v>1.6616864516129E-3</v>
       </c>
-      <c r="W98">
+      <c r="W98" s="4">
         <v>5.46169924436227E-4</v>
       </c>
-      <c r="X98">
+      <c r="X98" s="4">
         <v>1.8951598387096701E-3</v>
       </c>
-      <c r="Y98">
+      <c r="Y98" s="4">
         <v>6.2290891575720795E-4</v>
       </c>
     </row>

--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\max\github\rhtlab\grodent-magnenat-mini-projet-trey\input-data\load_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC465387-EF23-46CE-8481-1C190EF93BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156464E3-1D3B-4709-90A0-ECAD2CC9D71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
+    <workbookView xWindow="720" yWindow="720" windowWidth="20983" windowHeight="14794" activeTab="1" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
   <sheets>
     <sheet name="load" sheetId="5" r:id="rId1"/>
@@ -12734,120 +12734,408 @@
       <c r="A3" s="1">
         <v>0</v>
       </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>4.1666666666666664E-2</v>
       </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>8.3333333333333301E-2</v>
       </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>0.125</v>
       </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>0.16666666666666699</v>
       </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>0.20833333333333301</v>
       </c>
+      <c r="V8">
+        <v>9.4083203000000001E-3</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>1.6259327100000002E-2</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>0.25</v>
       </c>
+      <c r="V9">
+        <v>4.39345742E-2</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>4.9704414100000004E-2</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>0.29166666666666702</v>
       </c>
+      <c r="V10">
+        <v>9.1964718799999998E-2</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>9.6043515600000004E-2</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>0.33333333333333298</v>
       </c>
+      <c r="V11">
+        <v>0.1349729844</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0.141470125</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>0.375</v>
       </c>
+      <c r="V12">
+        <v>0.16872196880000001</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0.18009662500000001</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>0.41666666666666702</v>
       </c>
+      <c r="V13">
+        <v>0.19263135939999998</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0.20747953129999999</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>0.45833333333333298</v>
       </c>
+      <c r="V14">
+        <v>0.20567318749999999</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0.22436475</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>0.5</v>
       </c>
+      <c r="V15">
+        <v>0.20856379689999999</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0.23317234380000001</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>0.54166666666666696</v>
       </c>
+      <c r="V16">
+        <v>0.20429056249999999</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0.23407293749999999</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>0.58333333333333304</v>
       </c>
+      <c r="V17">
+        <v>0.19125948439999998</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0.22401164060000001</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>0.625</v>
       </c>
+      <c r="V18">
+        <v>0.16881509380000001</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0.20421040630000001</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>0.66666666666666696</v>
       </c>
+      <c r="V19">
+        <v>0.13611562499999999</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0.17339570310000002</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>0.70833333333333304</v>
       </c>
+      <c r="V20">
+        <v>9.41819297E-2</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0.13052409379999999</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>0.75</v>
       </c>
+      <c r="V21">
+        <v>4.85839219E-2</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>8.4502382800000012E-2</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>0.79166666666666696</v>
       </c>
+      <c r="V22">
+        <v>2.0931398399999999E-2</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>4.8002406300000001E-2</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>0.83333333333333304</v>
       </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>0.875</v>
       </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>0.91666666666666696</v>
       </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>0.95833333333333304</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
+++ b/grodent-magnenat-mini-projet-trey/input-data/load_curve/power_profile_cabinet_summer_week.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\max\github\rhtlab\grodent-magnenat-mini-projet-trey\input-data\load_curve\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156464E3-1D3B-4709-90A0-ECAD2CC9D71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7916C68-4244-4707-BFE1-6389FB3FEE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="20983" windowHeight="14794" activeTab="1" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
+    <workbookView xWindow="3531" yWindow="3531" windowWidth="19749" windowHeight="11512" activeTab="1" xr2:uid="{5FC146A3-AC37-46DC-AD92-E888F69598AC}"/>
   </bookViews>
   <sheets>
     <sheet name="load" sheetId="5" r:id="rId1"/>
@@ -12498,6 +12498,14 @@
     <protectedRange sqref="T3:W97" name="Plage1_13"/>
   </protectedRanges>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -12510,14 +12518,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12820,13 +12820,13 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="V8">
-        <v>9.4083203000000001E-3</v>
+        <v>7.9806076944750007E-3</v>
       </c>
       <c r="W8">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>1.6259327100000002E-2</v>
+        <v>8.1296635500000009E-3</v>
       </c>
       <c r="Y8">
         <v>0</v>
@@ -12837,13 +12837,13 @@
         <v>0.25</v>
       </c>
       <c r="V9">
-        <v>4.39345742E-2</v>
+        <v>3.7267502565150004E-2</v>
       </c>
       <c r="W9">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>4.9704414100000004E-2</v>
+        <v>2.4852207050000002E-2</v>
       </c>
       <c r="Y9">
         <v>0</v>
@@ -12854,13 +12854,13 @@
         <v>0.29166666666666702</v>
       </c>
       <c r="V10">
-        <v>9.1964718799999998E-2</v>
+        <v>7.8009072722100004E-2</v>
       </c>
       <c r="W10">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>9.6043515600000004E-2</v>
+        <v>4.8021757800000002E-2</v>
       </c>
       <c r="Y10">
         <v>0</v>
@@ -12871,13 +12871,13 @@
         <v>0.33333333333333298</v>
       </c>
       <c r="V11">
-        <v>0.1349729844</v>
+        <v>0.11449083401729999</v>
       </c>
       <c r="W11">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>0.141470125</v>
+        <v>7.0735062500000001E-2</v>
       </c>
       <c r="Y11">
         <v>0</v>
@@ -12888,13 +12888,13 @@
         <v>0.375</v>
       </c>
       <c r="V12">
-        <v>0.16872196880000001</v>
+        <v>0.14311841003460002</v>
       </c>
       <c r="W12">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>0.18009662500000001</v>
+        <v>9.0048312500000005E-2</v>
       </c>
       <c r="Y12">
         <v>0</v>
@@ -12905,13 +12905,13 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="V13">
-        <v>0.19263135939999998</v>
+        <v>0.16339955061104999</v>
       </c>
       <c r="W13">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>0.20747953129999999</v>
+        <v>0.10373976565</v>
       </c>
       <c r="Y13">
         <v>0</v>
@@ -12922,13 +12922,13 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="V14">
-        <v>0.20567318749999999</v>
+        <v>0.17446228129687499</v>
       </c>
       <c r="W14">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>0.22436475</v>
+        <v>0.112182375</v>
       </c>
       <c r="Y14">
         <v>0</v>
@@ -12939,13 +12939,13 @@
         <v>0.5</v>
       </c>
       <c r="V15">
-        <v>0.20856379689999999</v>
+        <v>0.176914240720425</v>
       </c>
       <c r="W15">
         <v>0</v>
       </c>
       <c r="X15">
-        <v>0.23317234380000001</v>
+        <v>0.11658617190000001</v>
       </c>
       <c r="Y15">
         <v>0</v>
@@ -12956,13 +12956,13 @@
         <v>0.54166666666666696</v>
       </c>
       <c r="V16">
-        <v>0.20429056249999999</v>
+        <v>0.173289469640625</v>
       </c>
       <c r="W16">
         <v>0</v>
       </c>
       <c r="X16">
-        <v>0.23407293749999999</v>
+        <v>0.11703646875</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -12973,13 +12973,13 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="V17">
-        <v>0.19125948439999998</v>
+        <v>0.1622358576423</v>
       </c>
       <c r="W17">
         <v>0</v>
       </c>
       <c r="X17">
-        <v>0.22401164060000001</v>
+        <v>0.1120058203</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -12990,13 +12990,13 @@
         <v>0.625</v>
       </c>
       <c r="V18">
-        <v>0.16881509380000001</v>
+        <v>0.14319740331585001</v>
       </c>
       <c r="W18">
         <v>0</v>
       </c>
       <c r="X18">
-        <v>0.20421040630000001</v>
+        <v>0.10210520315</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -13007,13 +13007,13 @@
         <v>0.66666666666666696</v>
       </c>
       <c r="V19">
-        <v>0.13611562499999999</v>
+        <v>0.11546007890625</v>
       </c>
       <c r="W19">
         <v>0</v>
       </c>
       <c r="X19">
-        <v>0.17339570310000002</v>
+        <v>8.669785155000001E-2</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -13024,13 +13024,13 @@
         <v>0.70833333333333304</v>
       </c>
       <c r="V20">
-        <v>9.41819297E-2</v>
+        <v>7.9889821868024999E-2</v>
       </c>
       <c r="W20">
         <v>0</v>
       </c>
       <c r="X20">
-        <v>0.13052409379999999</v>
+        <v>6.5262046899999995E-2</v>
       </c>
       <c r="Y20">
         <v>0</v>
@@ -13041,13 +13041,13 @@
         <v>0.75</v>
       </c>
       <c r="V21">
-        <v>4.85839219E-2</v>
+        <v>4.1211311751675007E-2</v>
       </c>
       <c r="W21">
         <v>0</v>
       </c>
       <c r="X21">
-        <v>8.4502382800000012E-2</v>
+        <v>4.2251191400000006E-2</v>
       </c>
       <c r="Y21">
         <v>0</v>
@@ -13058,13 +13058,13 @@
         <v>0.79166666666666696</v>
       </c>
       <c r="V22">
-        <v>2.0931398399999999E-2</v>
+        <v>1.7755058692799999E-2</v>
       </c>
       <c r="W22">
         <v>0</v>
       </c>
       <c r="X22">
-        <v>4.8002406300000001E-2</v>
+        <v>2.4001203150000001E-2</v>
       </c>
       <c r="Y22">
         <v>0</v>
@@ -13140,6 +13140,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AL1:AM1"/>
+    <mergeCell ref="X1:Y1"/>
+    <mergeCell ref="Z1:AA1"/>
+    <mergeCell ref="AB1:AC1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -13152,14 +13160,6 @@
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="T1:U1"/>
-    <mergeCell ref="AJ1:AK1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="X1:Y1"/>
-    <mergeCell ref="Z1:AA1"/>
-    <mergeCell ref="AB1:AC1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AH1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
